--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519256591797</v>
+        <v>174.5519409179688</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672267555024</v>
+        <v>176.4672421817212</v>
       </c>
       <c r="D5" t="n">
-        <v>173.384789767114</v>
+        <v>173.3848049238756</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222540410346</v>
+        <v>174.4222692884882</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394545758820588</v>
+        <v>-0.002394458551239653</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -588,7 +588,7 @@
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207335414736</v>
+        <v>0.0172019844334983</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701171875</v>
+        <v>179.3701324462891</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4649859155824</v>
+        <v>181.4650013525793</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380531425805</v>
+        <v>176.1380681264219</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9136974002478</v>
+        <v>177.913712535141</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022523041638013</v>
+        <v>0.01022531635496304</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253326416016</v>
+        <v>181.3253479003906</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438110385745</v>
+        <v>181.9438263494094</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725671170498</v>
+        <v>178.3725821273594</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195091893087</v>
+        <v>179.6195243045502</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090045256567307</v>
+        <v>0.01090045163838549</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.15576171875</v>
+        <v>181.1557312011719</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435839210746</v>
+        <v>182.0435532539336</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618774176739</v>
+        <v>178.6618473202167</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348217819195</v>
+        <v>181.5347912004848</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009351750270146786</v>
+        <v>-0.00093542740263719</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -684,7 +684,7 @@
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874514497031027</v>
+        <v>-0.007874347363113654</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538757324219</v>
+        <v>173.75390625</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141646735497</v>
+        <v>177.7141958867003</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7263967599338</v>
+        <v>172.7264270970488</v>
       </c>
       <c r="E11" t="n">
-        <v>177.674269227683</v>
+        <v>177.6743004338266</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324652152828622</v>
+        <v>-0.03324635173077994</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3621978759766</v>
+        <v>170.3622131347656</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9582896803931</v>
+        <v>171.9583050821389</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109095936823</v>
+        <v>166.810924534394</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841073072249</v>
+        <v>169.5841224963229</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952001267395287</v>
+        <v>-0.01952009706391489</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026214599609</v>
+        <v>170.2026062011719</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882512542426</v>
+        <v>171.9882358353705</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668876205481</v>
+        <v>168.4668725173688</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415475595936</v>
+        <v>170.6415322614545</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009366891129908295</v>
+        <v>-0.0009368681625865349</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -780,7 +780,7 @@
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095353053086949</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114349365234</v>
+        <v>166.6114196777344</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6165125346066</v>
+        <v>168.6164970921864</v>
       </c>
       <c r="D15" t="n">
-        <v>163.668654359155</v>
+        <v>163.6686393698748</v>
       </c>
       <c r="E15" t="n">
-        <v>167.618958764552</v>
+        <v>167.6189434134908</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703007354316445</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982543945312</v>
+        <v>167.8982391357422</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417807313731</v>
+        <v>170.5417652323373</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406114031506</v>
+        <v>166.9405962313932</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401190912332</v>
+        <v>167.1401039013443</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723476233777449</v>
+        <v>0.007723476941117413</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643629502945</v>
+        <v>0.01455652849910916</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465667724609</v>
+        <v>176.7465515136719</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491345673521</v>
+        <v>179.8491190407138</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0582134178096</v>
+        <v>176.058198218447</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505624618324</v>
+        <v>179.2505469868697</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008458502230944687</v>
+        <v>-0.0008459364815304182</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3949890136719</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731234709029</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.0282531820179</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.34510547722</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668655369389429</v>
+        <v>0.003668828349043585</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251800537109</v>
+        <v>177.3251647949219</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225571584428</v>
+        <v>178.4225418052247</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929181271268</v>
+        <v>174.0929031464731</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501493971494</v>
+        <v>175.2501343169162</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003935227277223063</v>
+        <v>-0.0003936947256518719</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620208740234</v>
+        <v>174.4620361328125</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757538913052</v>
+        <v>177.0757693786965</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632159334845</v>
+        <v>173.9632311486472</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769489507663</v>
+        <v>176.5769643945311</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614637683616205</v>
+        <v>-0.01614620612602058</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -981,22 +981,22 @@
         <v>45917</v>
       </c>
       <c r="B23" t="n">
-        <v>169.8829956054688</v>
+        <v>169.8829803466797</v>
       </c>
       <c r="C23" t="n">
-        <v>172.7860442802747</v>
+        <v>172.7860287607356</v>
       </c>
       <c r="D23" t="n">
-        <v>168.0074992073941</v>
+        <v>168.007484117061</v>
       </c>
       <c r="E23" t="n">
-        <v>172.2273851309623</v>
+        <v>172.2273696616015</v>
       </c>
       <c r="F23" t="n">
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624654492487588</v>
+        <v>-0.02624671755319263</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187866210938</v>
+        <v>175.8187713623047</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767318043244</v>
+        <v>176.6767164710769</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466271367534</v>
+        <v>172.5466121619453</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641783462465</v>
+        <v>173.5641632831282</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.034940465904016</v>
+        <v>0.03494046904234804</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477264404297</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543599509016</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612823170602</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E25" t="n">
-        <v>175.3498836843894</v>
+        <v>175.349898865447</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439670001024075</v>
+        <v>0.00243984378681672</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1068,7 +1068,7 @@
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928238699195052</v>
+        <v>0.03928229701524732</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035247802734</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9839937083107</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888448362941</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350723037516</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204559530932</v>
+        <v>-0.02821196229186118</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470123291016</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3502935078314</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807575937583</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403228895943</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182492189240609</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653198242188</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291695578261</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162207499007</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.062985089831</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068647130534231</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1164,7 +1164,7 @@
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830455718369</v>
+        <v>0.002813916776754244</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153747558594</v>
+        <v>181.4153900146484</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602300506758</v>
+        <v>183.560245489868</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890327563757</v>
+        <v>179.8890478867847</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987552370008</v>
+        <v>179.9987703766385</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053991824341894</v>
+        <v>0.02054000408070467</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041378766245</v>
+        <v>0.02601032749026233</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385375976562</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="C34" t="n">
-        <v>190.59337868299</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105195355423</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E34" t="n">
-        <v>189.146847340247</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812305418101074</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723587148282584</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965270996094</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7824902019781</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918178290645</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566294029491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0110862321012164</v>
+        <v>-0.01108631362422263</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694780736732239</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626288358566</v>
+        <v>0.01829618052309101</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886536282782095</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1428,7 +1428,7 @@
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817213093671711</v>
+        <v>0.02817204507600701</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1437,22 +1437,22 @@
         <v>45944</v>
       </c>
       <c r="B42" t="n">
-        <v>179.5997009277344</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="C42" t="n">
-        <v>184.3583041970053</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D42" t="n">
-        <v>179.2704878489981</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E42" t="n">
-        <v>184.3283771191491</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="F42" t="n">
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402090212326881</v>
+        <v>-0.04402082090329285</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001922607422</v>
+        <v>179.4002075195312</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281395182556</v>
+        <v>184.428155204694</v>
       </c>
       <c r="D43" t="n">
-        <v>176.866254560341</v>
+        <v>176.8662696036074</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3583147400375</v>
+        <v>184.358330420537</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110851888737052</v>
+        <v>-0.001110851794359102</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754577636719</v>
+        <v>181.3754730224609</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419455690647</v>
+        <v>182.8419609512268</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3403553050442</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944521048813</v>
+        <v>181.7944673989196</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038676736099</v>
+        <v>0.01101038583087832</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755441369297289</v>
+        <v>0.007755356588662776</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1533,22 +1533,22 @@
         <v>45950</v>
       </c>
       <c r="B46" t="n">
-        <v>182.2034759521484</v>
+        <v>182.2034912109375</v>
       </c>
       <c r="C46" t="n">
-        <v>184.7573549226016</v>
+        <v>184.7573703952674</v>
       </c>
       <c r="D46" t="n">
-        <v>181.2956472677441</v>
+        <v>181.2956624505063</v>
       </c>
       <c r="E46" t="n">
-        <v>182.6923102950553</v>
+        <v>182.6923255947822</v>
       </c>
       <c r="F46" t="n">
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165673913464562</v>
+        <v>-0.003165590432704146</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1557,22 +1557,22 @@
         <v>45951</v>
       </c>
       <c r="B47" t="n">
-        <v>180.7270050048828</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="C47" t="n">
-        <v>182.3530987175338</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D47" t="n">
-        <v>179.370254993042</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E47" t="n">
-        <v>182.3530987175338</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="F47" t="n">
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103418112909044</v>
+        <v>-0.008103417434281224</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1596,7 +1596,7 @@
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485751374626664</v>
+        <v>-0.004857597766183885</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.724609375</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988762799469</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042820520129983</v>
+        <v>0.01042812035913343</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1644,7 +1644,7 @@
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250756853454439</v>
+        <v>0.02250765439098057</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323333740234</v>
+        <v>191.0323028564453</v>
       </c>
       <c r="C51" t="n">
-        <v>191.5411089646758</v>
+        <v>191.5410783658203</v>
       </c>
       <c r="D51" t="n">
-        <v>187.9796341631504</v>
+        <v>187.9796041332436</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359184602369</v>
+        <v>189.5358881817124</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807902634674164</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495300292969</v>
+        <v>200.5495452880859</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644582837766</v>
+        <v>202.6644737034797</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513320204045</v>
+        <v>191.4513465869582</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886067715161</v>
+        <v>192.5886214245991</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04982006859223453</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.545166015625</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828666070652</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905729140704</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482921843539</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989603608371594</v>
+        <v>0.02989588163930978</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448238730316</v>
+        <v>-0.02004440999182711</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003173828125</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699244802363</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4824106282661</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580848487537</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003722181935406077</v>
+        <v>0.0003721368699238781</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793249204463202</v>
+        <v>0.05793257804752372</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983337402344</v>
+        <v>192.6983184814453</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529266552934</v>
+        <v>194.9529112179747</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427786999811</v>
+        <v>190.8427635881239</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935535589016</v>
+        <v>194.6935381421213</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959067258255743</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368225097656</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218237722109</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6732056162565</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522318976041</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00331341095243709</v>
+        <v>0.003313332029950544</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133758544922</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824307616844</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105757073767</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933635318434</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581028469071756</v>
+        <v>-0.03581005357317613</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2004,7 +2004,7 @@
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771382279154077</v>
+        <v>0.0177137394870075</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540069580078</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482645458532</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794576828592</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E66" t="n">
-        <v>185.525507871713</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877265156263563</v>
+        <v>-0.01877257113277342</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2052,7 +2052,7 @@
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146927787025</v>
+        <v>-0.02808154894469495</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.020516696793347</v>
+        <v>0.02051661128715887</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3949890136719</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341727058355</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447513765687</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919407266003</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0259108417558972</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372168593222045</v>
+        <v>0.01372159873604817</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492846544285</v>
+        <v>-0.01808484361385299</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649711013028865</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030543487972591</v>
+        <v>-0.01030535058927451</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.951904296875</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="C78" t="n">
-        <v>184.0892423581687</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398901129937</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1960032737075</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116062209880032</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841613769531</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2289086763207</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876631773748</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4607020047171</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00528960288028224</v>
+        <v>-0.005289603321452563</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721400043751253</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125830460996126</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114044189453</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3931976659576</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123291208211</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871831157045</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266452212921567</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256277519845034</v>
+        <v>0.007256189498619836</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3051147460938</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733214473424</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916907151964</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485164107673</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111747940743541</v>
+        <v>0.008111661183153096</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814991702143256</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2589,22 +2589,22 @@
         <v>46013</v>
       </c>
       <c r="B90" t="n">
-        <v>183.2611541748047</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="C90" t="n">
-        <v>183.730058116363</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D90" t="n">
-        <v>181.9242862331203</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E90" t="n">
-        <v>183.4906129473229</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="F90" t="n">
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.014917857266596</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2628,7 +2628,7 @@
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005078265538064</v>
+        <v>0.03005069689074391</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2661,22 +2661,22 @@
         <v>46017</v>
       </c>
       <c r="B93" t="n">
-        <v>190.0851898193359</v>
+        <v>190.085205078125</v>
       </c>
       <c r="C93" t="n">
-        <v>192.2401507638228</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5610975436497</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E93" t="n">
-        <v>189.4766133088049</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="F93" t="n">
         <v>139740300</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01017970646506039</v>
+        <v>0.01017978755564442</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>120006100</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.01212401633949489</v>
+        <v>-0.01212409563967642</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646209716797</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151405796458</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546497967401</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E96" t="n">
-        <v>189.127461449755</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545375898472038</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2757,22 +2757,22 @@
         <v>46024</v>
       </c>
       <c r="B97" t="n">
-        <v>188.4091186523438</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="C97" t="n">
-        <v>192.479580126264</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D97" t="n">
-        <v>187.8204844911982</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E97" t="n">
-        <v>189.3967976648124</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="F97" t="n">
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01260044853460296</v>
+        <v>0.0126006135839718</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808319091797</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779786425506</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154296257417</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123337767646</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.003865453797424312</v>
+        <v>-0.00386561545941666</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677861544826856</v>
+        <v>-0.004677780623340899</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2829,22 +2829,22 @@
         <v>46029</v>
       </c>
       <c r="B100" t="n">
-        <v>188.6685028076172</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="C100" t="n">
-        <v>190.9232211122124</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1244530144955</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E100" t="n">
-        <v>188.1297701943655</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="F100" t="n">
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.00998708250744107</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2868,7 +2868,7 @@
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152180029744644</v>
+        <v>-0.02152187943302564</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.376220703125</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708543554723</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718432388734</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5681140987238</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.004704210650191332</v>
+        <v>0.00470412795042785</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124481201172</v>
+        <v>182.7124633789062</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293738083791</v>
+        <v>184.029389177148</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779146434709</v>
+        <v>180.3779297072971</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8897012556695</v>
+        <v>183.889716612774</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436954843994676</v>
+        <v>-0.01436938499763141</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134974032598635</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952270507812</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="C107" t="n">
-        <v>189.99540517049</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455833269296</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385795892923</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383931140514608</v>
+        <v>-0.004383849373637116</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.6543121337891</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542482267672</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953792817215</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753578011745</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381676302343995</v>
+        <v>-0.0438166772979951</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920440673828</v>
+        <v>182.8920288085938</v>
       </c>
       <c r="C109" t="n">
-        <v>184.9472325313386</v>
+        <v>184.947217101084</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835164834521</v>
+        <v>177.9835016341843</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6320081827799</v>
+        <v>178.6319932794081</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948263181397048</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291414334357983</v>
+        <v>0.008291498456701074</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728912353516</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009553855833</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3968053634026</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E114" t="n">
-        <v>190.8234748728661</v>
+        <v>190.823459633995</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591342985123156</v>
+        <v>0.01591334872193784</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3189,22 +3189,22 @@
         <v>46051</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0605621337891</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="C115" t="n">
-        <v>193.0282987969995</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D115" t="n">
-        <v>185.625623299501</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E115" t="n">
-        <v>190.8932954336949</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="F115" t="n">
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169079151165157</v>
+        <v>0.005169239280915949</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3213,22 +3213,22 @@
         <v>46052</v>
       </c>
       <c r="B116" t="n">
-        <v>190.6837921142578</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="C116" t="n">
-        <v>194.0359484555967</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D116" t="n">
-        <v>189.0276639024229</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E116" t="n">
-        <v>190.7636071727618</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="F116" t="n">
         <v>179489500</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.00716841606749119</v>
+        <v>-0.007168415497976421</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766967773438</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557504766133</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4484052141589</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629812920276</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.0288807731158095</v>
+        <v>-0.02888093084756926</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839299457635047</v>
+        <v>-0.02839291451472381</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833404541016</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="C119" t="n">
-        <v>179.160756412826</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086645338761</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410414348666</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221377522338</v>
+        <v>-0.0341021289659974</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787292480469</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4071986282528</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307075914073</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5215964583249</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.01326140468949821</v>
+        <v>-0.0132614035251003</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771423339844</v>
+        <v>184.9771728515625</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634266395524</v>
+        <v>186.5634574188361</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923819783884</v>
+        <v>174.1924107166939</v>
       </c>
       <c r="E121" t="n">
-        <v>176.277498975506</v>
+        <v>176.2775280578147</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0787177112002726</v>
+        <v>0.07871779317924998</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3372,7 +3372,7 @@
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497166051482758</v>
+        <v>0.0249714914147583</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.0998382568359</v>
+        <v>188.099853515625</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306425866914</v>
+        <v>192.0306581643501</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808205923615</v>
+        <v>187.6808358171596</v>
       </c>
       <c r="E123" t="n">
-        <v>190.933219719687</v>
+        <v>190.9332352083219</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893035105149604</v>
+        <v>-0.00789295462474604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063385009766</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088363522974</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D124" t="n">
-        <v>188.3293278304631</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007297023972</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800904593061702</v>
+        <v>0.00800888303954661</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636418228460701</v>
+        <v>-0.01636410312537218</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560567193918</v>
+        <v>0.0118155220086027</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028289794922</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972200828311</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374267327081</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531700210539</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113929721387581</v>
+        <v>0.009113849147715847</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786747007672789</v>
+        <v>0.006786827395534711</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126861572266</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2688145383873</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396472340209</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187649948852</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660639760928495</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119873046875</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6303076754259</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647422536165</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470550179114</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.00163899427668035</v>
+        <v>0.001638994413631911</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048614501953</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333155363547</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4071960911633</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420134514761</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010806418782519</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716230855539603</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H270"/>
+  <dimension ref="A1:H271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103271484375</v>
+        <v>175.2103118896484</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535459787435</v>
+        <v>182.0535301239894</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607001855326</v>
+        <v>175.0606849397743</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837099150805</v>
+        <v>181.9836940664082</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -540,7 +540,7 @@
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366504264196933</v>
+        <v>-0.001366417294784594</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253479003906</v>
+        <v>181.3253326416016</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438263494094</v>
+        <v>181.9438110385745</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725821273594</v>
+        <v>178.3725671170498</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195243045502</v>
+        <v>179.6195091893087</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090045163838549</v>
+        <v>0.0109003665696572</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.00093542740263719</v>
+        <v>-0.0009353433299080782</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874347363113654</v>
+        <v>-0.007874431593344555</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141958867003</v>
+        <v>177.714180280125</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264270970488</v>
+        <v>172.7264119284913</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6743004338266</v>
+        <v>177.6742848307548</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635173077994</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -732,7 +732,7 @@
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952009706391489</v>
+        <v>-0.01952001095973654</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400817871094</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.4395894944585</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955858311417</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527518438138</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095443250276666</v>
+        <v>0.006095532901013501</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016265075109</v>
+        <v>-0.02703024934973741</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422546386719</v>
+        <v>170.3422393798828</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617176578999</v>
+        <v>170.561702379452</v>
       </c>
       <c r="D17" t="n">
-        <v>166.3320999523285</v>
+        <v>166.332085052758</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763418810487</v>
+        <v>168.6763267714875</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455652849910916</v>
+        <v>0.01455643761793546</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512663982333</v>
+        <v>0.03847530924081588</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465515136719</v>
+        <v>176.7465362548828</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491190407138</v>
+        <v>179.8491035140756</v>
       </c>
       <c r="D19" t="n">
-        <v>176.058198218447</v>
+        <v>176.0581830190845</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505469868697</v>
+        <v>179.2505315119071</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008459364815304182</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668828349043585</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947256518719</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620361328125</v>
+        <v>174.4620208740234</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757693786965</v>
+        <v>177.0757538913052</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632311486472</v>
+        <v>173.9632159334845</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769643945311</v>
+        <v>176.5769489507663</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614620612602058</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624671755319263</v>
+        <v>-0.02624663238682878</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813916776754244</v>
+        <v>0.002813830697929731</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153900146484</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="C31" t="n">
-        <v>183.560245489868</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890478867847</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987703766385</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02054000408070467</v>
+        <v>0.02053992000650995</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601032749026233</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385528564453</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="C34" t="n">
-        <v>190.593394116267</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105347272827</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E34" t="n">
-        <v>189.1468626563914</v>
+        <v>189.146847340247</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812305418101074</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587148282584</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965270996094</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7824902019781</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918178290645</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566294029491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108631362422263</v>
+        <v>-0.0110862321012164</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694780736732239</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097412109375</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="C39" t="n">
-        <v>194.8332119113436</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033405552435</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705422839889</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829618052309101</v>
+        <v>0.01829626140377161</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886543837402468</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699035644531</v>
+        <v>187.8699340820312</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556185865847</v>
+        <v>189.6556493942343</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155435929421</v>
+        <v>185.5155737280782</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207340107304</v>
+        <v>187.5207644715895</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817204507600701</v>
+        <v>0.02817229795294884</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402082090329285</v>
+        <v>-0.04402097619247958</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4002075195312</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="C43" t="n">
-        <v>184.428155204694</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D43" t="n">
-        <v>176.8662696036074</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E43" t="n">
-        <v>184.358330420537</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110851794359102</v>
+        <v>-0.001110936754343372</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754730224609</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419609512268</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403553050442</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944673989196</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038583087832</v>
+        <v>0.01101038676736099</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755356588662776</v>
+        <v>0.007755441369297289</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1533,22 +1533,22 @@
         <v>45950</v>
       </c>
       <c r="B46" t="n">
-        <v>182.2034912109375</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="C46" t="n">
-        <v>184.7573703952674</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D46" t="n">
-        <v>181.2956624505063</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E46" t="n">
-        <v>182.6923255947822</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="F46" t="n">
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590432704146</v>
+        <v>-0.003165673913464562</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1572,7 +1572,7 @@
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103417434281224</v>
+        <v>-0.008103334367036585</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250765439098057</v>
+        <v>0.02250773835753361</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323028564453</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="C51" t="n">
-        <v>191.5410783658203</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D51" t="n">
-        <v>187.9796041332436</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5358881817124</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807902634674164</v>
+        <v>0.02807910615919784</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495452880859</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644737034797</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513465869582</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886214245991</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04982006859223453</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989588163930978</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004440999182711</v>
+        <v>-0.02004433759634028</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855438232422</v>
+        <v>206.3855590820312</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348755139714</v>
+        <v>210.8348911017148</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0686914304077</v>
+        <v>205.0687065918373</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826726752522</v>
+        <v>207.5826880225491</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168012836941968</v>
+        <v>0.02168020390572556</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958816719273994</v>
+        <v>-0.03958823819926593</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.0365248560924305</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003021240234</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699092076593</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823961188316</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580698535366</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721368699238781</v>
+        <v>0.0003721369001874475</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793257804752372</v>
+        <v>0.05793266405042918</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983184814453</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529112179747</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427635881239</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935381421213</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959067258255743</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3367919921875</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4217929255223</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6731755191215</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522010776849</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313332029950544</v>
+        <v>0.003313331767584859</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005357317613</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808154894469495</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174000170858</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524536132812</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188702156436</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166628687019</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E70" t="n">
-        <v>180.806813452001</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743162817541062</v>
+        <v>-0.009743078144453632</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051661128715887</v>
+        <v>0.02051660953286172</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341879937998</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447659257062</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E72" t="n">
-        <v>174.491955735681</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067635257405</v>
+        <v>-0.02591067418159221</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159873604817</v>
+        <v>0.01372151153989076</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899749755859</v>
+        <v>179.4899597167969</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690716163194</v>
+        <v>179.8690563253026</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648835948944</v>
+        <v>173.2648688653124</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3423041351479</v>
+        <v>174.3422893139723</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649711013028865</v>
+        <v>0.01649702371590833</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263061523438</v>
+        <v>181.0263214111328</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162648499111</v>
+        <v>185.2162804618737</v>
       </c>
       <c r="D76" t="n">
-        <v>179.569788944198</v>
+        <v>179.5698040802165</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255769560617</v>
+        <v>181.3255922400764</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559426101467649</v>
+        <v>0.008559596852994122</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030535058927451</v>
+        <v>-0.0103055183015206</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116053693065423</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -6921,12 +6921,36 @@
         <v>221.2400054931641</v>
       </c>
       <c r="F270" t="n">
-        <v>88804100</v>
+        <v>89060100</v>
       </c>
       <c r="G270" t="n">
         <v>-0.0003206050742950994</v>
       </c>
       <c r="H270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B271" t="n">
+        <v>210.9600067138672</v>
+      </c>
+      <c r="C271" t="n">
+        <v>212.7700042724609</v>
+      </c>
+      <c r="D271" t="n">
+        <v>208.9299926757812</v>
+      </c>
+      <c r="E271" t="n">
+        <v>211.2400054931641</v>
+      </c>
+      <c r="F271" t="n">
+        <v>131942300</v>
+      </c>
+      <c r="G271" t="n">
+        <v>-0.03357912317427003</v>
+      </c>
+      <c r="H271" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103118896484</v>
+        <v>175.2103271484375</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535301239894</v>
+        <v>182.0535459787435</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0606849397743</v>
+        <v>175.0607001855326</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9836940664082</v>
+        <v>181.9837099150805</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709014892578</v>
+        <v>174.9709167480469</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694397588381</v>
+        <v>175.5694550698242</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870566311777</v>
+        <v>168.3870713158056</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414684152183</v>
+        <v>174.741483653999</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417294784594</v>
+        <v>-0.001366417175785561</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519409179688</v>
+        <v>174.5519256591797</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672421817212</v>
+        <v>176.4672267555024</v>
       </c>
       <c r="D5" t="n">
-        <v>173.3848049238756</v>
+        <v>173.384789767114</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222692884882</v>
+        <v>174.4222540410346</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394458551239653</v>
+        <v>-0.002394632757571458</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545806884766</v>
+        <v>177.5545654296875</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531037491236</v>
+        <v>178.1530884388983</v>
       </c>
       <c r="D6" t="n">
-        <v>170.781182841084</v>
+        <v>170.7811681643912</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877371490149</v>
+        <v>172.1877223514448</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0172019844334983</v>
+        <v>0.01720198593724254</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701324462891</v>
+        <v>179.3701171875</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650013525793</v>
+        <v>181.4649859155824</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380681264219</v>
+        <v>176.1380531425805</v>
       </c>
       <c r="E7" t="n">
-        <v>177.913712535141</v>
+        <v>177.9136974002478</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531635496304</v>
+        <v>0.01022531723371234</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -636,7 +636,7 @@
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0109003665696572</v>
+        <v>0.01090045256567307</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557312011719</v>
+        <v>181.15576171875</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435532539336</v>
+        <v>182.0435839210746</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618473202167</v>
+        <v>178.6618774176739</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5347912004848</v>
+        <v>181.5348217819195</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009353433299080782</v>
+        <v>-0.0009351750270146786</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874431593344555</v>
+        <v>-0.007874514497031027</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538909912109</v>
+        <v>173.7538757324219</v>
       </c>
       <c r="C11" t="n">
-        <v>177.714180280125</v>
+        <v>177.7141646735497</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264119284913</v>
+        <v>172.7263967599338</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6742848307548</v>
+        <v>177.674269227683</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635455335401</v>
+        <v>-0.03324652152828622</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -732,7 +732,7 @@
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952001095973654</v>
+        <v>-0.0195199248555431</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400817871094</v>
+        <v>171.2400512695312</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395894944585</v>
+        <v>171.439558941325</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955858311417</v>
+        <v>168.9955557135668</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527518438138</v>
+        <v>170.1527215200144</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095532901013501</v>
+        <v>0.006095353599539832</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703024934973741</v>
+        <v>-0.02703007595174933</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982391357422</v>
+        <v>167.8982696533203</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417652323373</v>
+        <v>170.5417962304089</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9405962313932</v>
+        <v>166.9406265749079</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401039013443</v>
+        <v>167.140134281122</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723476941117413</v>
+        <v>0.007723660107302521</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422393798828</v>
+        <v>170.3422698974609</v>
       </c>
       <c r="C17" t="n">
-        <v>170.561702379452</v>
+        <v>170.5617329363479</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332085052758</v>
+        <v>166.332114851899</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763267714875</v>
+        <v>168.6763569906099</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643761793546</v>
+        <v>0.01455643497212367</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847530924081588</v>
+        <v>0.03847503361609572</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008460227399664788</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731541223449</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028283464474</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451359862166</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003669001328727717</v>
+        <v>0.003668914997253303</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807076698219</v>
+        <v>-0.0003936947256518719</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187713623047</v>
+        <v>175.8187866210938</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767164710769</v>
+        <v>176.6767318043244</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466121619453</v>
+        <v>172.5466271367534</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641632831282</v>
+        <v>173.5641783462465</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494046904234804</v>
+        <v>0.03494055886175818</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00243984378681672</v>
+        <v>0.002439756788046976</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653045654297</v>
+        <v>177.2652893066406</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291540783439</v>
+        <v>179.8291385988617</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162058826927</v>
+        <v>172.7161910154847</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629701066951</v>
+        <v>174.0629551235593</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068473920816773</v>
+        <v>0.004068387491782843</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7640991210938</v>
+        <v>177.7641296386719</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403244887289</v>
+        <v>179.3403552769049</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118813132914</v>
+        <v>174.5119112725463</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441426621237</v>
+        <v>177.7441731762758</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830697929731</v>
+        <v>0.002814089176637058</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053992000650995</v>
+        <v>0.02053974480577181</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.79248046875</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="C33" t="n">
-        <v>187.6903232769056</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604518817237</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972606974542</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537325381961498</v>
+        <v>0.0035374073593748</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385375976562</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="C34" t="n">
-        <v>190.59337868299</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105195355423</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E34" t="n">
-        <v>189.146847340247</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812223009789566</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715698242188</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050265070322</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369333277354</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378247179256</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.00672366812316183</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0110862321012164</v>
+        <v>-0.01108615148198644</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097564697266</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="C39" t="n">
-        <v>194.833227386451</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033556943829</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705575158363</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626140377161</v>
+        <v>0.01829618052309101</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886543837402468</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699340820312</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556493942343</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155737280782</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207644715895</v>
+        <v>187.52074924116</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817229795294884</v>
+        <v>0.02817212858411589</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402097619247958</v>
+        <v>-0.04402089854789248</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754577636719</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419455690647</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944521048813</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038676736099</v>
+        <v>0.01101030171288664</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7821044921875</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6600061588844</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493615830456</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755441369297289</v>
+        <v>0.007755442021748715</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165673913464562</v>
+        <v>-0.003165590696970089</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.84912109375</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015721983185</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375297972393</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070662621498</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004857597766183885</v>
+        <v>-0.00485768219622118</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.724609375</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925250516066</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602637385785</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988762799469</v>
+        <v>179.988793025541</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042812035913343</v>
+        <v>0.01042837577039868</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250773835753361</v>
+        <v>0.02250748267812286</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910615919784</v>
+        <v>0.02807919058326869</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989595999882533</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004433759634028</v>
+        <v>-0.02004440999182711</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729250244422</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870329046891</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565537660584</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971530859184778</v>
+        <v>-0.001971455471800998</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855590820312</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348911017148</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0687065918373</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826880225491</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168020390572556</v>
+        <v>0.02168005119548289</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958823819926593</v>
+        <v>-0.03958816719273994</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304626464844</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476539294223</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345289438528</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505251524069</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.0365248560924305</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721369001874475</v>
+        <v>0.0003720555463071484</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742645263672</v>
+        <v>198.5742797851562</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621367771523</v>
+        <v>199.462152104167</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268264223904</v>
+        <v>193.3268412779572</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6436938260565</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793266405042918</v>
+        <v>0.05793274534380033</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959067030875928</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.926513671875</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.358293814419</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2205942185541</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.9416897271721</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808163091331894</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0742034912109</v>
+        <v>186.0741882324219</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109971087465</v>
+        <v>187.4109817403353</v>
       </c>
       <c r="D68" t="n">
-        <v>182.3930205111681</v>
+        <v>182.39300555425</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483273978252</v>
+        <v>184.3483122805645</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845174240124138</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152479724769053</v>
+        <v>-0.03152471782905131</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524688720703</v>
+        <v>178.4524536132812</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188859589464</v>
+        <v>184.1188702156436</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166776199441</v>
+        <v>172.5166628687019</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068289121023</v>
+        <v>180.806813452001</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743078144453632</v>
+        <v>-0.009743162817541062</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051660953286172</v>
+        <v>0.02051661128715887</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.734203281764</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447804748437</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919707447618</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067418159221</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372151153989076</v>
+        <v>0.01372159873604817</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899597167969</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690563253026</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648688653124</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3422893139723</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649702371590833</v>
+        <v>0.01649711013028865</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263214111328</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162804618737</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D76" t="n">
-        <v>179.5698040802165</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255922400764</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559596852994122</v>
+        <v>0.008559426101467649</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.0103055183015206</v>
+        <v>-0.01030535058927451</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053693065423</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841461181641</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2288932293168</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876480440623</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4606866221248</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289603321452563</v>
+        <v>-0.005289519918164731</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721400043751253</v>
+        <v>0.01721391514737669</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864265695677</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920356049676</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E81" t="n">
-        <v>185.12679644575</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125830460996126</v>
+        <v>-0.003125748033105724</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509674072266</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469957406681</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150239281505</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5381918075859</v>
+        <v>184.538176449994</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433411769608655</v>
+        <v>-0.006433576610347602</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770933102352</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814983424509077</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021728515625</v>
+        <v>187.1021881103516</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5487999407664</v>
+        <v>188.5488153175326</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4935963146986</v>
+        <v>186.4936115238563</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005508490403</v>
+        <v>187.8005661647843</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612838827051545</v>
+        <v>-0.003612757568446812</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545538552702456</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808166503906</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779629368336</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154145267434</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123182227279</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386561545941666</v>
+        <v>-0.00386553447189375</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8028869628906</v>
+        <v>186.8029022216797</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213703933745</v>
+        <v>191.7213860539245</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838692947835</v>
+        <v>186.3838845193456</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752284670132</v>
+        <v>190.0752439930999</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780623340899</v>
+        <v>-0.004677780243029006</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987164191344933</v>
+        <v>0.009987081691657185</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080169677734</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074981045344</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685228499072</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152187943302564</v>
+        <v>-0.02152196030920583</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009727675505442068</v>
+        <v>-0.0009726849758688871</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.3762054443359</v>
+        <v>185.376220703125</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708389078061</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718281779948</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5680989064521</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.00470412795042785</v>
+        <v>0.004704210650191332</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124633789062</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="C105" t="n">
-        <v>184.029389177148</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779297072971</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E105" t="n">
-        <v>183.889716612774</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436938499763141</v>
+        <v>-0.01436954843994676</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974032598635</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6543121337891</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542482267672</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953792817215</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753578011745</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438166772979951</v>
+        <v>-0.0438168415518142</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920288085938</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="C109" t="n">
-        <v>184.947217101084</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835016341843</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6319932794081</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948263181397048</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291498456701074</v>
+        <v>0.008291414334357983</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.0346832275391</v>
+        <v>186.03466796875</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784906596197</v>
+        <v>188.6784751839824</v>
       </c>
       <c r="D112" t="n">
-        <v>185.555808059744</v>
+        <v>185.5557928402329</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230748442759</v>
+        <v>186.7230595290241</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.00639415348837058</v>
+        <v>-0.006394234985120373</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099371233637481</v>
+        <v>0.01099379525930511</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771728515625</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634574188361</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1924107166939</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775280578147</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871779317924998</v>
+        <v>0.07871770419569057</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963287353516</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2078878887748</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205500126207</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298238555102</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0249714914147583</v>
+        <v>0.024971658454912</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.099853515625</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306581643501</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808358171596</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E123" t="n">
-        <v>190.9332352083219</v>
+        <v>190.933219719687</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.00789295462474604</v>
+        <v>-0.007893114950312197</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063232421875</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088208357837</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D124" t="n">
-        <v>188.329312674443</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007142509167</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800888303954661</v>
+        <v>0.00800904593061702</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5035858154297</v>
+        <v>186.5036010742188</v>
       </c>
       <c r="C125" t="n">
-        <v>193.1580126884611</v>
+        <v>193.158028491682</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745817463215</v>
+        <v>186.0745969700116</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793648877844</v>
+        <v>192.5793806436633</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410312537218</v>
+        <v>-0.01636410180845216</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832244873047</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622780376601</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660713803529</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E126" t="n">
-        <v>187.042320465516</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209266545793198</v>
+        <v>-0.02209282728038808</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130808403767</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7616860728079</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3256935584433</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0118155220086027</v>
+        <v>0.01181569032381558</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627283983140582</v>
+        <v>0.01627275579951704</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613342285156</v>
+        <v>187.4613189697266</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900957055448</v>
+        <v>187.9900804037161</v>
       </c>
       <c r="D129" t="n">
-        <v>185.2265733363672</v>
+        <v>185.226558259481</v>
       </c>
       <c r="E129" t="n">
-        <v>186.62329889396</v>
+        <v>186.6232837033845</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004255251289267958</v>
+        <v>-0.0004256064912840918</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3564,7 +3564,7 @@
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021825301539225</v>
+        <v>0.01021833524412785</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637395256691</v>
+        <v>182.1637238018573</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682453114839</v>
+        <v>175.9682301224481</v>
       </c>
       <c r="E135" t="n">
-        <v>180.8268714126474</v>
+        <v>180.82685580423</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164637217148226</v>
+        <v>-0.04164645489360941</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539855957031</v>
+        <v>182.0539703369141</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317086895539</v>
+        <v>183.0316933488174</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322921838959</v>
+        <v>174.2322775806792</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014235260267</v>
+        <v>174.6014088918714</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486242594537</v>
+        <v>0.02985486500292533</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3732,7 +3732,7 @@
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331646982798718</v>
+        <v>-0.01331638712945649</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126708984375</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2687991412151</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396322236537</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187499528396</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660639760928495</v>
+        <v>0.01660648255510222</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638994413631911</v>
+        <v>0.001638910718471109</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010789985650675</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -6945,12 +6945,36 @@
         <v>211.2400054931641</v>
       </c>
       <c r="F271" t="n">
-        <v>131942300</v>
+        <v>132267200</v>
       </c>
       <c r="G271" t="n">
         <v>-0.03357912317427003</v>
       </c>
       <c r="H271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B272" t="n">
+        <v>212.1699981689453</v>
+      </c>
+      <c r="C272" t="n">
+        <v>213.9400024414062</v>
+      </c>
+      <c r="D272" t="n">
+        <v>211.1600036621094</v>
+      </c>
+      <c r="E272" t="n">
+        <v>213.3800048828125</v>
+      </c>
+      <c r="F272" t="n">
+        <v>87726200</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0.005735643802473378</v>
+      </c>
+      <c r="H272" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H272"/>
+  <dimension ref="A1:H273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701171875</v>
+        <v>179.3701324462891</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4649859155824</v>
+        <v>181.4650013525793</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380531425805</v>
+        <v>176.1380681264219</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9136974002478</v>
+        <v>177.913712535141</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531723371234</v>
+        <v>0.0102254031723028</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -636,7 +636,7 @@
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090045256567307</v>
+        <v>0.0109003665696572</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.15576171875</v>
+        <v>181.1557464599609</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435839210746</v>
+        <v>182.0435685875041</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618774176739</v>
+        <v>178.6618623689453</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348217819195</v>
+        <v>181.5348064912021</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009351750270146786</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874514497031027</v>
+        <v>-0.00787451516030313</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324652152828622</v>
+        <v>-0.03324643945211436</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026062011719</v>
+        <v>170.2026214599609</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882358353705</v>
+        <v>171.9882512542426</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668725173688</v>
+        <v>168.4668876205481</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415322614545</v>
+        <v>170.6415475595936</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368681625865349</v>
+        <v>-0.0009367785958406261</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400512695312</v>
+        <v>171.2400817871094</v>
       </c>
       <c r="C14" t="n">
-        <v>171.439558941325</v>
+        <v>171.4395894944585</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955557135668</v>
+        <v>168.9955858311417</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527215200144</v>
+        <v>170.1527518438138</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095353599539832</v>
+        <v>0.00609544270381579</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114196777344</v>
+        <v>166.6114044189453</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164970921864</v>
+        <v>168.6164816497661</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686393698748</v>
+        <v>163.6686243805947</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189434134908</v>
+        <v>167.6189280624296</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703007595174933</v>
+        <v>-0.02703033845731617</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -828,7 +828,7 @@
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723660107302521</v>
+        <v>0.00772375239776002</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422698974609</v>
+        <v>170.3422546386719</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617329363479</v>
+        <v>170.5617176578999</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332114851899</v>
+        <v>166.3320999523285</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763569906099</v>
+        <v>168.6763418810487</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643497212367</v>
+        <v>0.01455634409096618</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847503361609572</v>
+        <v>0.03847521621706362</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460227399664788</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251647949219</v>
+        <v>177.3251495361328</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225418052247</v>
+        <v>178.4225264520066</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929031464731</v>
+        <v>174.0928881658194</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501343169162</v>
+        <v>175.250119236683</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947256518719</v>
+        <v>-0.0003937807415412831</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -972,7 +972,7 @@
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614620751539797</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477416992188</v>
+        <v>176.2477264404297</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543753314711</v>
+        <v>177.6543599509016</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612974471592</v>
+        <v>174.7612823170602</v>
       </c>
       <c r="E25" t="n">
-        <v>175.349898865447</v>
+        <v>175.3498836843894</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439756788046976</v>
+        <v>0.002439670001024075</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711578369141</v>
+        <v>183.1711730957031</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089135963474</v>
+        <v>184.1089289332547</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924356467209</v>
+        <v>174.2924501658818</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810218455756</v>
+        <v>174.8810364137678</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928229701524732</v>
+        <v>0.03928247356775705</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821196229186118</v>
+        <v>-0.02821204324514892</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470275878906</v>
+        <v>176.5470123291016</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3502935078314</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807727171775</v>
+        <v>174.9807575937583</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403383898065</v>
+        <v>179.3403228895943</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.008182577209651543</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2652893066406</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291385988617</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7161910154847</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629551235593</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387491782843</v>
+        <v>0.004068560701492752</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641296386719</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403552769049</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5119112725463</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441731762758</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002814089176637058</v>
+        <v>0.002813916776754244</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053974480577181</v>
+        <v>0.02053983240613322</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340637207031</v>
+        <v>186.1340484619141</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022276338177</v>
+        <v>186.9022123120565</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462469572146</v>
+        <v>181.0462321155116</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448190078555</v>
+        <v>181.6448041170831</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041597539022</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1236,7 +1236,7 @@
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0035374073593748</v>
+        <v>0.003537489626782131</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385528564453</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="C34" t="n">
-        <v>190.593394116267</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105347272827</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E34" t="n">
-        <v>189.1468626563914</v>
+        <v>189.146847340247</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223009789566</v>
+        <v>0.008812141321341782</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.00672366812316183</v>
+        <v>-0.006723587692724298</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965576171875</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7825209975275</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918479831437</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566599139491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108615148198644</v>
+        <v>-0.01108606995897354</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694945166262119</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199532691778505</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829618052309101</v>
+        <v>0.01829626288358566</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246398925781</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925557149365</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602938591047</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988793025541</v>
+        <v>179.988777912505</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042837577039868</v>
+        <v>0.01042829092822517</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250748267812286</v>
+        <v>0.02250765250109055</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807910615919784</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495300292969</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644582837766</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513320204045</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886067715161</v>
+        <v>192.588592118433</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981974113173093</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.545166015625</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482921843539</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989595999882533</v>
+        <v>0.02989611444324924</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004440999182711</v>
+        <v>-0.02004448238730316</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151184082031</v>
+        <v>198.2151031494141</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824975937368</v>
+        <v>203.4824819294599</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569251230167</v>
+        <v>197.4569099225941</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5148147488263</v>
+        <v>202.5147991590425</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958816719273994</v>
+        <v>-0.03958824112615977</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751463119384</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304931640625</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476859949454</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.934559185592</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505570232203</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.03652469938585123</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003720555463071484</v>
+        <v>0.0003719741924403941</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742797851562</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="C61" t="n">
-        <v>199.462152104167</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268412779572</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436938260565</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793274534380033</v>
+        <v>0.05793266405042918</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959067030875928</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368072509766</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218083488666</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D63" t="n">
-        <v>190.673190567689</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522164876445</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331767584859</v>
+        <v>0.003313252582732629</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581012967027952</v>
+        <v>-0.03581005357317613</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.926513671875</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.358293814419</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2205942185541</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9416897271721</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808163091331894</v>
+        <v>-0.02808154894469495</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0741882324219</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109817403353</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D68" t="n">
-        <v>182.39300555425</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483122805645</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174240124138</v>
+        <v>0.02845174000170858</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152471782905131</v>
+        <v>-0.03152479724769053</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524536132812</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188702156436</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166628687019</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E70" t="n">
-        <v>180.806813452001</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743162817541062</v>
+        <v>-0.009743078144453632</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2148,7 +2148,7 @@
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051661128715887</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808484361385299</v>
+        <v>-0.01808492846544285</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649711013028865</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607818603516</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.0139471586436</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819333075974</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6472262869623</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030535058927451</v>
+        <v>-0.01030526629882311</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116036298998392</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168212890625</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5610985176648</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741660895743</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E80" t="n">
-        <v>182.2136112701494</v>
+        <v>182.213626289633</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721399899417375</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125912631224192</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114196777344</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3932136047752</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123443447362</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871989054384</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266452212921567</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.8784332275391</v>
+        <v>175.87841796875</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0034500370577</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213802569945</v>
+        <v>174.6213651072644</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245903328353</v>
+        <v>177.5245749312296</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256189498619836</v>
+        <v>0.007256190132717499</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2508,7 +2508,7 @@
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111661183153096</v>
+        <v>0.008111748644499261</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814983424509077</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491794177123418</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021881103516</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5488153175326</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4936115238563</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005661647843</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612757568446812</v>
+        <v>-0.003612838827051545</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545538552702456</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8029022216797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213860539245</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838845193456</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752439930999</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780243029006</v>
+        <v>-0.004677861544826856</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987081691657185</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133270263672</v>
+        <v>186.6133117675781</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571344016907</v>
+        <v>189.2571189267257</v>
       </c>
       <c r="D106" t="n">
-        <v>185.895006678512</v>
+        <v>185.8949914784577</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0646079796491</v>
+        <v>186.0645927657271</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134974210895835</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952423095703</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="C107" t="n">
-        <v>189.9954207742267</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455985734289</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385950815971</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849373637116</v>
+        <v>-0.004383849732090828</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.654296875</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438168415518142</v>
+        <v>-0.04381668089652369</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948280612693632</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.03466796875</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784751839824</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D112" t="n">
-        <v>185.5557928402329</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230595290241</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.006394234985120373</v>
+        <v>-0.00639415348837058</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099379525930511</v>
+        <v>0.01099371233637481</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5036010742188</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="C125" t="n">
-        <v>193.158028491682</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745969700116</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793806436633</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410180845216</v>
+        <v>-0.01636418228460701</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209282728038808</v>
+        <v>-0.02209274727292232</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181569032381558</v>
+        <v>0.01181560666047221</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613189697266</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900804037161</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D129" t="n">
-        <v>185.226558259481</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E129" t="n">
-        <v>186.6232837033845</v>
+        <v>186.62329889396</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004256064912840918</v>
+        <v>-0.0004255251289267958</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768615722656</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856654675195</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059147845697</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344488846578</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833524412785</v>
+        <v>0.01021833441238607</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113849147715847</v>
+        <v>0.009113767839714404</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583740234375</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364236513225</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8897126034445</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164813019665</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456121004512637</v>
+        <v>-0.05456128825383422</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637238018573</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682301224481</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E135" t="n">
-        <v>180.82685580423</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164645489360941</v>
+        <v>-0.04164629289442512</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539703369141</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0316933488174</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322775806792</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014088918714</v>
+        <v>174.601438160182</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486500292533</v>
+        <v>0.02985494874285899</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296691894531</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776756968921</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069714269912</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0733135069376</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331638712945649</v>
+        <v>-0.01331663634113589</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660656891157819</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010789985650675</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -6969,12 +6969,36 @@
         <v>213.3800048828125</v>
       </c>
       <c r="F272" t="n">
-        <v>87726200</v>
+        <v>88059700</v>
       </c>
       <c r="G272" t="n">
         <v>0.005735643802473378</v>
       </c>
       <c r="H272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B273" t="n">
+        <v>213.8999938964844</v>
+      </c>
+      <c r="C273" t="n">
+        <v>216.7599945068359</v>
+      </c>
+      <c r="D273" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="E273" t="n">
+        <v>214.1399993896484</v>
+      </c>
+      <c r="F273" t="n">
+        <v>96079300</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0.008153818836165172</v>
+      </c>
+      <c r="H273" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H273"/>
+  <dimension ref="A1:H274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545654296875</v>
+        <v>177.5545806884766</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1530884388983</v>
+        <v>178.1531037491236</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811681643912</v>
+        <v>170.781182841084</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877223514448</v>
+        <v>172.1877371490149</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720198593724254</v>
+        <v>0.01720207335414736</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0102254031723028</v>
+        <v>0.01022531635496304</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538757324219</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141646735497</v>
+        <v>177.714180280125</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7263967599338</v>
+        <v>172.7264119284913</v>
       </c>
       <c r="E11" t="n">
-        <v>177.674269227683</v>
+        <v>177.6742848307548</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643945211436</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622131347656</v>
+        <v>170.3622283935547</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583050821389</v>
+        <v>171.9583204838847</v>
       </c>
       <c r="D12" t="n">
-        <v>166.810924534394</v>
+        <v>166.8109394751057</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841224963229</v>
+        <v>169.5841376854209</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0195199248555431</v>
+        <v>-0.01951992314133455</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026214599609</v>
+        <v>170.2025909423828</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882512542426</v>
+        <v>171.9882204164984</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668876205481</v>
+        <v>168.4668574141896</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415475595936</v>
+        <v>170.6415169633154</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009367785958406261</v>
+        <v>-0.000937047212150155</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400817871094</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395894944585</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955858311417</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527518438138</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00609544270381579</v>
+        <v>0.006095533447482593</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114044189453</v>
+        <v>166.6114349365234</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164816497661</v>
+        <v>168.6165125346066</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686243805947</v>
+        <v>163.668654359155</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189280624296</v>
+        <v>167.618958764552</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703033845731617</v>
+        <v>-0.02703007354316445</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982696533203</v>
+        <v>167.8982391357422</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417962304089</v>
+        <v>170.5417652323373</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406265749079</v>
+        <v>166.9405962313932</v>
       </c>
       <c r="E16" t="n">
-        <v>167.140134281122</v>
+        <v>167.1401039013443</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00772375239776002</v>
+        <v>0.007723384650693443</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634409096618</v>
+        <v>0.01455652849910916</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847521621706362</v>
+        <v>0.03847512663982333</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008460227399664788</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668914997253303</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251495361328</v>
+        <v>177.3251647949219</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225264520066</v>
+        <v>178.4225418052247</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0928881658194</v>
+        <v>174.0929031464731</v>
       </c>
       <c r="E21" t="n">
-        <v>175.250119236683</v>
+        <v>175.2501343169162</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807415412831</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -972,7 +972,7 @@
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614620751539797</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187866210938</v>
+        <v>175.8187713623047</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767318043244</v>
+        <v>176.6767164710769</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466271367534</v>
+        <v>172.5466121619453</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641783462465</v>
+        <v>173.5641632831282</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494055886175818</v>
+        <v>0.03494046904234804</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477264404297</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543599509016</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612823170602</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E25" t="n">
-        <v>175.3498836843894</v>
+        <v>175.349898865447</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439670001024075</v>
+        <v>0.00243984378681672</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711730957031</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089289332547</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924501658818</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810364137678</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928247356775705</v>
+        <v>0.03928229701524732</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204324514892</v>
+        <v>-0.02821196229186118</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470123291016</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3502935078314</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807575937583</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403228895943</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182577209651543</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1140,7 +1140,7 @@
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068560701492752</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813916776754244</v>
+        <v>0.002813830697929731</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053983240613322</v>
+        <v>0.02053992000650995</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340484619141</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022123120565</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462321155116</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448041170831</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041597539022</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.7924957275391</v>
+        <v>186.79248046875</v>
       </c>
       <c r="C33" t="n">
-        <v>187.690338609038</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604668683245</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972757932568</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537489626782131</v>
+        <v>0.003537325381961498</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812141321341782</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715545654297</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050110254035</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369182511207</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378093314507</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587692724298</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965576171875</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825209975275</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918479831437</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566599139491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108606995897354</v>
+        <v>-0.0110862321012164</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694945166262119</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097412109375</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="C39" t="n">
-        <v>194.8332119113436</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033405552435</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705422839889</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626288358566</v>
+        <v>0.01829626140377161</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886543837402468</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699188232422</v>
+        <v>187.8699340820312</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556339904095</v>
+        <v>189.6556493942343</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155586605101</v>
+        <v>185.5155737280782</v>
       </c>
       <c r="E41" t="n">
-        <v>187.52074924116</v>
+        <v>187.5207644715895</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817212858411589</v>
+        <v>0.02817229795294884</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402089854789248</v>
+        <v>-0.04402097619247958</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754425048828</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419301869027</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944368108431</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101030171288664</v>
+        <v>0.01101038676736099</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820892333984</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599908268075</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493465774322</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755442021748715</v>
+        <v>0.007755441369297289</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590696970089</v>
+        <v>-0.003165673913464562</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491058349609</v>
+        <v>179.84912109375</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015566720687</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375148363812</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070509305708</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485768219622118</v>
+        <v>-0.004857597766183885</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.724609375</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988762799469</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829092822517</v>
+        <v>0.01042812035913343</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1644,7 +1644,7 @@
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250765250109055</v>
+        <v>0.02250773835753361</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495147705078</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644428640734</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513174538508</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E52" t="n">
-        <v>192.588592118433</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981974113173093</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.545166015625</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828666070652</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905729140704</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482921843539</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989611444324924</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448238730316</v>
+        <v>-0.02004433759634028</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729406961805</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870481318289</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565693232556</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971455471800998</v>
+        <v>-0.001971530859184778</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855438232422</v>
+        <v>206.3855590820312</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348755139714</v>
+        <v>210.8348911017148</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0686914304077</v>
+        <v>205.0687065918373</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826726752522</v>
+        <v>207.5826880225491</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168005119548289</v>
+        <v>0.02168020390572556</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151031494141</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824819294599</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569099225941</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5147991590425</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958824112615977</v>
+        <v>-0.03958823819926593</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751463119384</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304931640625</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476859949454</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D59" t="n">
-        <v>185.934559185592</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505570232203</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652469938585123</v>
+        <v>-0.0365248560924305</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003719741924403941</v>
+        <v>0.0003721369001874475</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3367919921875</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4217929255223</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6731755191215</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522010776849</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313252582732629</v>
+        <v>0.003313331767584859</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005357317613</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808154894469495</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174000170858</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.02051660953286172</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341879937998</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447659257062</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E72" t="n">
-        <v>174.491955735681</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067635257405</v>
+        <v>-0.02591067418159221</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159873604817</v>
+        <v>0.01372151153989076</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492846544285</v>
+        <v>-0.01808484361385299</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899749755859</v>
+        <v>179.4899597167969</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690716163194</v>
+        <v>179.8690563253026</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648835948944</v>
+        <v>173.2648688653124</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3423041351479</v>
+        <v>174.3422893139723</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649702371590833</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263061523438</v>
+        <v>181.0263214111328</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162648499111</v>
+        <v>185.2162804618737</v>
       </c>
       <c r="D76" t="n">
-        <v>179.569788944198</v>
+        <v>179.5698040802165</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255769560617</v>
+        <v>181.3255922400764</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559426101467649</v>
+        <v>0.008559596852994122</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607818603516</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139471586436</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819333075974</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472262869623</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526629882311</v>
+        <v>-0.0103055183015206</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116036298998392</v>
+        <v>0.02116053693065423</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841613769531</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2289086763207</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876631773748</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4607020047171</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289519918164731</v>
+        <v>-0.005289603321452563</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168365478516</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5611139779305</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741810893209</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E80" t="n">
-        <v>182.213626289633</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721399899417375</v>
+        <v>0.01721400043751253</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2388,7 +2388,7 @@
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125912631224192</v>
+        <v>-0.003125830460996126</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114044189453</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3931976659576</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123291208211</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871831157045</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266452212921567</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.87841796875</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034500370577</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213651072644</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245749312296</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256190132717499</v>
+        <v>0.007256189498619836</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2508,7 +2508,7 @@
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111748644499261</v>
+        <v>0.008111661183153096</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808319091797</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779786425506</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154296257417</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123337767646</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386553447189375</v>
+        <v>-0.00386561545941666</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677861544826856</v>
+        <v>-0.004677780623340899</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080017089844</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074824738404</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685072554968</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152196030920583</v>
+        <v>-0.02152187943302564</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009726849758688871</v>
+        <v>-0.0009727675505442068</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.376220703125</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708543554723</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718432388734</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5681140987238</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.004704210650191332</v>
+        <v>0.00470412795042785</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124481201172</v>
+        <v>182.7124633789062</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293738083791</v>
+        <v>184.029389177148</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779146434709</v>
+        <v>180.3779297072971</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8897012556695</v>
+        <v>183.889716612774</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436954843994676</v>
+        <v>-0.01436938499763141</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133117675781</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571189267257</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D106" t="n">
-        <v>185.8949914784577</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0645927657271</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974210895835</v>
+        <v>0.02134974032598635</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952270507812</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="C107" t="n">
-        <v>189.99540517049</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455833269296</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385795892923</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849732090828</v>
+        <v>-0.004383849373637116</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.654296875</v>
+        <v>177.6543121337891</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542325986551</v>
+        <v>181.9542482267672</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953640623503</v>
+        <v>177.1953792817215</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753422141945</v>
+        <v>181.4753578011745</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381668089652369</v>
+        <v>-0.0438166772979951</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920440673828</v>
+        <v>182.8920288085938</v>
       </c>
       <c r="C109" t="n">
-        <v>184.9472325313386</v>
+        <v>184.947217101084</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835164834521</v>
+        <v>177.9835016341843</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6320081827799</v>
+        <v>178.6319932794081</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948280612693632</v>
+        <v>0.02948263181397048</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291414334357983</v>
+        <v>0.008291498456701074</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771575927734</v>
+        <v>184.9771728515625</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634420291942</v>
+        <v>186.5634574188361</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923963475411</v>
+        <v>174.1924107166939</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775135166603</v>
+        <v>176.2775280578147</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871770419569057</v>
+        <v>0.07871779317924998</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963439941406</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2079034382237</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205647824287</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298386502086</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.024971658454912</v>
+        <v>0.0249714914147583</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.0998382568359</v>
+        <v>188.099853515625</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306425866914</v>
+        <v>192.0306581643501</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808205923615</v>
+        <v>187.6808358171596</v>
       </c>
       <c r="E123" t="n">
-        <v>190.933219719687</v>
+        <v>190.9332352083219</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893114950312197</v>
+        <v>-0.00789295462474604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063385009766</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088363522974</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D124" t="n">
-        <v>188.3293278304631</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007297023972</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800904593061702</v>
+        <v>0.00800888303954661</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636418228460701</v>
+        <v>-0.01636410312537218</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832092285156</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622623874058</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660562233949</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E126" t="n">
-        <v>187.0423048169314</v>
+        <v>187.042320465516</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209274727292232</v>
+        <v>-0.02209266545793198</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3492,7 +3492,7 @@
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560666047221</v>
+        <v>0.0118155220086027</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768768310547</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856807673048</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059297314624</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344638821937</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833441238607</v>
+        <v>0.01021825301539225</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113767839714404</v>
+        <v>0.009113849147715847</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583587646484</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364076167612</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8896973916963</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164652690549</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456128825383422</v>
+        <v>-0.05456121004512637</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164629289442512</v>
+        <v>-0.04164637217148226</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0540008544922</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317240302905</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2323067871125</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E136" t="n">
-        <v>174.601438160182</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985494874285899</v>
+        <v>0.02985486242594537</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296539306641</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776603660684</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069564334623</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0732983803544</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331663634113589</v>
+        <v>-0.01331646982798718</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126861572266</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2688145383873</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396472340209</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187649948852</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660656891157819</v>
+        <v>0.01660639760928495</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638910718471109</v>
+        <v>0.001638994413631911</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -6993,12 +6993,36 @@
         <v>214.1399993896484</v>
       </c>
       <c r="F273" t="n">
-        <v>96079300</v>
+        <v>96563600</v>
       </c>
       <c r="G273" t="n">
         <v>0.008153818836165172</v>
       </c>
       <c r="H273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B274" t="n">
+        <v>219.3399963378906</v>
+      </c>
+      <c r="C274" t="n">
+        <v>219.9100036621094</v>
+      </c>
+      <c r="D274" t="n">
+        <v>217.1499938964844</v>
+      </c>
+      <c r="E274" t="n">
+        <v>218.3800048828125</v>
+      </c>
+      <c r="F274" t="n">
+        <v>93960500</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0.0254324572072635</v>
+      </c>
+      <c r="H274" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H274"/>
+  <dimension ref="A1:H275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103271484375</v>
+        <v>175.2103424072266</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535459787435</v>
+        <v>182.0535618334976</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607001855326</v>
+        <v>175.0607154312909</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837099150805</v>
+        <v>181.9837257637527</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -540,7 +540,7 @@
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417175785561</v>
+        <v>-0.00136650414519035</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187713623047</v>
+        <v>175.8187561035156</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767164710769</v>
+        <v>176.6767011378293</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466121619453</v>
+        <v>172.5465971871373</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641632831282</v>
+        <v>173.5641482200099</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494046904234804</v>
+        <v>0.03494037922293813</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00243984378681672</v>
+        <v>0.002439930785601563</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035400390625</v>
+        <v>178.0035247802734</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9840093083128</v>
+        <v>181.9839937083107</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888599052367</v>
+        <v>175.7888448362941</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350878652714</v>
+        <v>181.5350723037516</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821196229186118</v>
+        <v>-0.02821204559530932</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1116,7 +1116,7 @@
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.00818240646740398</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153594970703</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602146114836</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890176259668</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987400973632</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053992000650995</v>
+        <v>0.020540005843803</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041378766245</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699340820312</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556493942343</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155737280782</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207644715895</v>
+        <v>187.52074924116</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817229795294884</v>
+        <v>0.02817221444483309</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402097619247958</v>
+        <v>-0.04402089854789248</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051660953286172</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2172,7 +2172,7 @@
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067418159221</v>
+        <v>-0.0259105925654145</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263214111328</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162804618737</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D76" t="n">
-        <v>179.5698040802165</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255922400764</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559596852994122</v>
+        <v>0.008559511841057521</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.0103055183015206</v>
+        <v>-0.01030535058927451</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053693065423</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -7017,12 +7017,36 @@
         <v>218.3800048828125</v>
       </c>
       <c r="F274" t="n">
-        <v>93960500</v>
+        <v>94191300</v>
       </c>
       <c r="G274" t="n">
         <v>0.0254324572072635</v>
       </c>
       <c r="H274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B275" t="n">
+        <v>222.2700042724609</v>
+      </c>
+      <c r="C275" t="n">
+        <v>222.7299957275391</v>
+      </c>
+      <c r="D275" t="n">
+        <v>218.0299987792969</v>
+      </c>
+      <c r="E275" t="n">
+        <v>219.3500061035156</v>
+      </c>
+      <c r="F275" t="n">
+        <v>189683500</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0.01335829298572921</v>
+      </c>
+      <c r="H275" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103424072266</v>
+        <v>175.2103271484375</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535618334976</v>
+        <v>182.0535459787435</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607154312909</v>
+        <v>175.0607001855326</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837257637527</v>
+        <v>181.9837099150805</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -540,7 +540,7 @@
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.00136650414519035</v>
+        <v>-0.001366417175785561</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253326416016</v>
+        <v>181.3253173828125</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438110385745</v>
+        <v>181.9437957277396</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725671170498</v>
+        <v>178.3725521067403</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195091893087</v>
+        <v>179.6194940740671</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0109003665696572</v>
+        <v>0.01090028150092892</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009352591784613784</v>
+        <v>-0.0009351751057110613</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622283935547</v>
+        <v>170.3622131347656</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583204838847</v>
+        <v>171.9583050821389</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109394751057</v>
+        <v>166.810924534394</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841376854209</v>
+        <v>169.5841224963229</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01951992314133455</v>
+        <v>-0.01952001095973654</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2025909423828</v>
+        <v>170.2026062011719</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882204164984</v>
+        <v>171.9882358353705</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668574141896</v>
+        <v>168.4668725173688</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415169633154</v>
+        <v>170.6415322614545</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.000937047212150155</v>
+        <v>-0.0009368681625865349</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -780,7 +780,7 @@
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095533447482593</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114349365234</v>
+        <v>166.6114196777344</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6165125346066</v>
+        <v>168.6164970921864</v>
       </c>
       <c r="D15" t="n">
-        <v>163.668654359155</v>
+        <v>163.6686393698748</v>
       </c>
       <c r="E15" t="n">
-        <v>167.618958764552</v>
+        <v>167.6189434134908</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703007354316445</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982391357422</v>
+        <v>167.8982543945312</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417652323373</v>
+        <v>170.5417807313731</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9405962313932</v>
+        <v>166.9406114031506</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401039013443</v>
+        <v>167.1401190912332</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723384650693443</v>
+        <v>0.007723568524209856</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422546386719</v>
+        <v>170.3422393798828</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617176578999</v>
+        <v>170.561702379452</v>
       </c>
       <c r="D17" t="n">
-        <v>166.3320999523285</v>
+        <v>166.332085052758</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763418810487</v>
+        <v>168.6763267714875</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455652849910916</v>
+        <v>0.01455634541386375</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512663982333</v>
+        <v>0.03847530924081588</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465362548828</v>
+        <v>176.7465515136719</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491035140756</v>
+        <v>179.8491190407138</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0581830190845</v>
+        <v>176.058198218447</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505315119071</v>
+        <v>179.2505469868697</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460227399664788</v>
+        <v>-0.0008460226669898541</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.39501953125</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731541223449</v>
+        <v>178.1731234709029</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028283464474</v>
+        <v>176.0282531820179</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451359862166</v>
+        <v>177.34510547722</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003669001328727717</v>
+        <v>0.00366874201757672</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251647949219</v>
+        <v>177.3251800537109</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225418052247</v>
+        <v>178.4225571584428</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929031464731</v>
+        <v>174.0929181271268</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501343169162</v>
+        <v>175.2501493971494</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807076698219</v>
+        <v>-0.0003935227277223063</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620208740234</v>
+        <v>174.4620361328125</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757538913052</v>
+        <v>177.0757693786965</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632159334845</v>
+        <v>173.9632311486472</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769489507663</v>
+        <v>176.5769643945311</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614629078640273</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624663238682878</v>
+        <v>-0.02624671755319263</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187561035156</v>
+        <v>175.8187866210938</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767011378293</v>
+        <v>176.6767318043244</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5465971871373</v>
+        <v>172.5466271367534</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641482200099</v>
+        <v>173.5641783462465</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494037922293813</v>
+        <v>0.03494055886175818</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439930785601563</v>
+        <v>0.002439756788046976</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035247802734</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9839937083107</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888448362941</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350723037516</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204559530932</v>
+        <v>-0.02821196229186118</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1116,7 +1116,7 @@
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.00818240646740398</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153747558594</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602300506758</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890327563757</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987552370008</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.020540005843803</v>
+        <v>0.02053992000650995</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041378766245</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715698242188</v>
+        <v>187.1715850830078</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050265070322</v>
+        <v>189.9050419886609</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369333277354</v>
+        <v>184.9369484043502</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378247179256</v>
+        <v>188.7378401044004</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723425742952704</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0110862321012164</v>
+        <v>-0.01108631272043314</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199532691778505</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097564697266</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="C39" t="n">
-        <v>194.833227386451</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033556943829</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705575158363</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626140377161</v>
+        <v>0.01829626288358566</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1404,7 +1404,7 @@
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886543837402468</v>
+        <v>-0.04886536282782095</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699188232422</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556339904095</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155586605101</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E41" t="n">
-        <v>187.52074924116</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817221444483309</v>
+        <v>0.02817213093671711</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402089854789248</v>
+        <v>-0.04402082090329285</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001922607422</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281395182556</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D43" t="n">
-        <v>176.866254560341</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3583147400375</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110936754343372</v>
+        <v>-0.001111021714327642</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754577636719</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419455690647</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944521048813</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038676736099</v>
+        <v>0.01101038770384366</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7821044921875</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6600061588844</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493615830456</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755441369297289</v>
+        <v>0.007755442021748715</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1533,22 +1533,22 @@
         <v>45950</v>
       </c>
       <c r="B46" t="n">
-        <v>182.2034759521484</v>
+        <v>182.2034606933594</v>
       </c>
       <c r="C46" t="n">
-        <v>184.7573549226016</v>
+        <v>184.7573394499357</v>
       </c>
       <c r="D46" t="n">
-        <v>181.2956472677441</v>
+        <v>181.2956320849819</v>
       </c>
       <c r="E46" t="n">
-        <v>182.6923102950553</v>
+        <v>182.6922949953283</v>
       </c>
       <c r="F46" t="n">
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165673913464562</v>
+        <v>-0.003165674177737388</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1572,7 +1572,7 @@
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103334367036585</v>
+        <v>-0.008103251299777958</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.724609375</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925250516066</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602637385785</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988762799469</v>
+        <v>179.988793025541</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042812035913343</v>
+        <v>0.01042829004346624</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250773835753361</v>
+        <v>0.02250748267812286</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910615919784</v>
+        <v>0.02807919058326869</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495300292969</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644582837766</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513320204045</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886067715161</v>
+        <v>192.588592118433</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981974113173093</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989603835835264</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050750732422</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672637579894</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286166610889</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596680014167</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004433759634028</v>
+        <v>-0.02004448386811519</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729250244422</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870329046891</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565537660584</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971530859184778</v>
+        <v>-0.001971380233034448</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855590820312</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348911017148</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0687065918373</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826880225491</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168020390572556</v>
+        <v>0.02168005119548289</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958823819926593</v>
+        <v>-0.03958816719273994</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304626464844</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476539294223</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345289438528</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505251524069</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.0365248560924305</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7002868652344</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8698939350823</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823816093971</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580548583195</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721369001874475</v>
+        <v>0.0003721368699238781</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742645263672</v>
+        <v>198.5742492675781</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621367771523</v>
+        <v>199.4621214501376</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268264223904</v>
+        <v>193.3268115668235</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6436639125443</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793266405042918</v>
+        <v>0.05793249675415924</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983337402344</v>
+        <v>192.6983489990234</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529266552934</v>
+        <v>194.9529420926121</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427786999811</v>
+        <v>190.8427938118383</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935535589016</v>
+        <v>194.6935689756818</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959044433116265</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368072509766</v>
+        <v>193.3368225097656</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218083488666</v>
+        <v>195.4218237722109</v>
       </c>
       <c r="D63" t="n">
-        <v>190.673190567689</v>
+        <v>190.6732056162565</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522164876445</v>
+        <v>195.2522318976041</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331767584859</v>
+        <v>0.003313331505219175</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581012967027952</v>
+        <v>-0.03581020576737093</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540222167969</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482800008962</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794727552066</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255230789849</v>
+        <v>185.525507871713</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877257113277342</v>
+        <v>-0.01877265156263563</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2052,7 +2052,7 @@
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808138730923948</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524688720703</v>
+        <v>178.4524841308594</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188859589464</v>
+        <v>184.1189017022491</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166776199441</v>
+        <v>172.5166923711864</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068289121023</v>
+        <v>180.8068443722038</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743078144453632</v>
+        <v>-0.009742993471366312</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.02051652227239154</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.39501953125</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C72" t="n">
-        <v>177.734203281764</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447804748437</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919707447618</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0259105925654145</v>
+        <v>-0.0259108417558972</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291778564453</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728535594688</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140165634392</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1959139436215</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372151153989076</v>
+        <v>0.01372185796401415</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808484361385299</v>
+        <v>-0.0180850950995245</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899597167969</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690563253026</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648688653124</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3422893139723</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649702371590833</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2268,7 +2268,7 @@
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559511841057521</v>
+        <v>0.008559426101467649</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.9518890380859</v>
+        <v>182.951904296875</v>
       </c>
       <c r="C78" t="n">
-        <v>184.089227004522</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398751387779</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1959881613664</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116053512845051</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841461181641</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2288932293168</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876480440623</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4606866221248</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289603321452563</v>
+        <v>-0.00528960288028224</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721400043751253</v>
+        <v>0.01721391514737669</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864265695677</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920356049676</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E81" t="n">
-        <v>185.12679644575</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125830460996126</v>
+        <v>-0.003125748033105724</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509674072266</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469957406681</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150239281505</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5381918075859</v>
+        <v>184.538176449994</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433411769608655</v>
+        <v>-0.006433576610347602</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770933102352</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114196777344</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3932136047752</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123443447362</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871989054384</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266452212921567</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256189498619836</v>
+        <v>0.007256277519845034</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3050994873047</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733061224419</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916756985292</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485012773324</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111661183153096</v>
+        <v>0.008111747940743541</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814991702143256</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2589,22 +2589,22 @@
         <v>46013</v>
       </c>
       <c r="B90" t="n">
-        <v>183.2611694335938</v>
+        <v>183.2611541748047</v>
       </c>
       <c r="C90" t="n">
-        <v>183.7300734141942</v>
+        <v>183.730058116363</v>
       </c>
       <c r="D90" t="n">
-        <v>181.9243013805983</v>
+        <v>181.9242862331203</v>
       </c>
       <c r="E90" t="n">
-        <v>183.4906282252173</v>
+        <v>183.4906129473229</v>
       </c>
       <c r="F90" t="n">
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.014917857266596</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2628,7 +2628,7 @@
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005069689074391</v>
+        <v>0.03005078265538064</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2661,22 +2661,22 @@
         <v>46017</v>
       </c>
       <c r="B93" t="n">
-        <v>190.085205078125</v>
+        <v>190.0851898193359</v>
       </c>
       <c r="C93" t="n">
-        <v>192.240166195598</v>
+        <v>192.2401507638228</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5611125998212</v>
+        <v>187.5610975436497</v>
       </c>
       <c r="E93" t="n">
-        <v>189.4766285187414</v>
+        <v>189.4766133088049</v>
       </c>
       <c r="F93" t="n">
         <v>139740300</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01017978755564442</v>
+        <v>0.01017970646506039</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>120006100</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.01212409563967642</v>
+        <v>-0.01212401633949489</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646057128906</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151249886817</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546345387688</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E96" t="n">
-        <v>189.1274459397885</v>
+        <v>189.127461449755</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545375898472038</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2757,22 +2757,22 @@
         <v>46024</v>
       </c>
       <c r="B97" t="n">
-        <v>188.4091339111328</v>
+        <v>188.4091186523438</v>
       </c>
       <c r="C97" t="n">
-        <v>192.4795957147097</v>
+        <v>192.479580126264</v>
       </c>
       <c r="D97" t="n">
-        <v>187.8204997023152</v>
+        <v>187.8204844911982</v>
       </c>
       <c r="E97" t="n">
-        <v>189.3968130035911</v>
+        <v>189.3967976648124</v>
       </c>
       <c r="F97" t="n">
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0126006135839718</v>
+        <v>0.01260044853460296</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808166503906</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779629368336</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154145267434</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123182227279</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386561545941666</v>
+        <v>-0.003865453797424312</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780623340899</v>
+        <v>-0.004677861544826856</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2829,22 +2829,22 @@
         <v>46029</v>
       </c>
       <c r="B100" t="n">
-        <v>188.6685180664062</v>
+        <v>188.6685028076172</v>
       </c>
       <c r="C100" t="n">
-        <v>190.9232365533545</v>
+        <v>190.9232211122124</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1244680675316</v>
+        <v>186.1244530144955</v>
       </c>
       <c r="E100" t="n">
-        <v>188.1297854095839</v>
+        <v>188.1297701943655</v>
       </c>
       <c r="F100" t="n">
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987164191344933</v>
+        <v>0.00998708250744107</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2868,7 +2868,7 @@
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152187943302564</v>
+        <v>-0.02152180029744644</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.3762054443359</v>
+        <v>185.376220703125</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708389078061</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718281779948</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5680989064521</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.00470412795042785</v>
+        <v>0.004704210650191332</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124633789062</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="C105" t="n">
-        <v>184.029389177148</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779297072971</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E105" t="n">
-        <v>183.889716612774</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436938499763141</v>
+        <v>-0.01436954843994676</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974032598635</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952423095703</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="C107" t="n">
-        <v>189.9954207742267</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455985734289</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385950815971</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849373637116</v>
+        <v>-0.004383931140514608</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6543121337891</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542482267672</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953792817215</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753578011745</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438166772979951</v>
+        <v>-0.04381676302343995</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920288085938</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="C109" t="n">
-        <v>184.947217101084</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835016341843</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6319932794081</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948263181397048</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291498456701074</v>
+        <v>0.008291414334357983</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728759765625</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009400606663</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3967902384632</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E114" t="n">
-        <v>190.823459633995</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591334872193784</v>
+        <v>0.01591342985123156</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3189,22 +3189,22 @@
         <v>46051</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0605773925781</v>
+        <v>192.0605621337891</v>
       </c>
       <c r="C115" t="n">
-        <v>193.0283141326731</v>
+        <v>193.0282987969995</v>
       </c>
       <c r="D115" t="n">
-        <v>185.6256380470483</v>
+        <v>185.625623299501</v>
       </c>
       <c r="E115" t="n">
-        <v>190.8933105997472</v>
+        <v>190.8932954336949</v>
       </c>
       <c r="F115" t="n">
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169239280915949</v>
+        <v>0.005169079151165157</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3213,22 +3213,22 @@
         <v>46052</v>
       </c>
       <c r="B116" t="n">
-        <v>190.6838073730469</v>
+        <v>190.6837921142578</v>
       </c>
       <c r="C116" t="n">
-        <v>194.0359639826301</v>
+        <v>194.0359484555967</v>
       </c>
       <c r="D116" t="n">
-        <v>189.0276790286862</v>
+        <v>189.0276639024229</v>
       </c>
       <c r="E116" t="n">
-        <v>190.7636224379378</v>
+        <v>190.7636071727618</v>
       </c>
       <c r="F116" t="n">
         <v>179489500</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.007168415497976421</v>
+        <v>-0.00716841606749119</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766815185547</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557348322644</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4483900153819</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629659025267</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888093084756926</v>
+        <v>-0.0288807731158095</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839291451472381</v>
+        <v>-0.02839299457635047</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833557128906</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="C119" t="n">
-        <v>179.1607721437711</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086795929406</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410571553003</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0341021289659974</v>
+        <v>-0.03410221377522338</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787445068359</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4072143255947</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307227747363</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5216119878791</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.0132614035251003</v>
+        <v>-0.01326140468949821</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771728515625</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634574188361</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1924107166939</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775280578147</v>
+        <v>176.277498975506</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871779317924998</v>
+        <v>0.0787177112002726</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3372,7 +3372,7 @@
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0249714914147583</v>
+        <v>0.02497166051482758</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.099853515625</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306581643501</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808358171596</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E123" t="n">
-        <v>190.9332352083219</v>
+        <v>190.933219719687</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.00789295462474604</v>
+        <v>-0.007893035105149604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063232421875</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088208357837</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D124" t="n">
-        <v>188.329312674443</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007142509167</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800888303954661</v>
+        <v>0.00800904593061702</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410312537218</v>
+        <v>-0.01636418228460701</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130808403767</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7616860728079</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3256935584433</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0118155220086027</v>
+        <v>0.01181560567193918</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627283983140582</v>
+        <v>0.01627275579951704</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028137207031</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972046328596</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374116308485</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531547742145</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113849147715847</v>
+        <v>0.009113929721387581</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786827395534711</v>
+        <v>0.006786747007672789</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126708984375</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2687991412151</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396322236537</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187499528396</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660639760928495</v>
+        <v>0.01660648255510222</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119720458984</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6302923567135</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647274492447</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470399397241</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638994413631911</v>
+        <v>0.00163899427668035</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048614501953</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333155363547</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.4071960911633</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420134514761</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010806418782519</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716230855539603</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709167480469</v>
+        <v>174.9709320068359</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694550698242</v>
+        <v>175.5694703808103</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870713158056</v>
+        <v>168.3870860004334</v>
       </c>
       <c r="E4" t="n">
-        <v>174.741483653999</v>
+        <v>174.7414988927798</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417175785561</v>
+        <v>-0.001366330087374079</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519256591797</v>
+        <v>174.5519409179688</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672267555024</v>
+        <v>176.4672421817212</v>
       </c>
       <c r="D5" t="n">
-        <v>173.384789767114</v>
+        <v>173.3848049238756</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222540410346</v>
+        <v>174.4222692884882</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394632757571458</v>
+        <v>-0.002394632548741393</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545806884766</v>
+        <v>177.5545654296875</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531037491236</v>
+        <v>178.1530884388983</v>
       </c>
       <c r="D6" t="n">
-        <v>170.781182841084</v>
+        <v>170.7811681643912</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877371490149</v>
+        <v>172.1877223514448</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207335414736</v>
+        <v>0.01720189701660124</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531635496304</v>
+        <v>0.0102254031723028</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557464599609</v>
+        <v>181.15576171875</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435685875041</v>
+        <v>182.0435839210746</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618623689453</v>
+        <v>178.6618774176739</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348064912021</v>
+        <v>181.5348217819195</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009351751057110613</v>
+        <v>-0.0009350909542572561</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00787451516030313</v>
+        <v>-0.007874514497031027</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635455335401</v>
+        <v>-0.03324643662953308</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114196777344</v>
+        <v>166.6114044189453</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164970921864</v>
+        <v>168.6164816497661</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686393698748</v>
+        <v>163.6686243805947</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189434134908</v>
+        <v>167.6189280624296</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016265075109</v>
+        <v>-0.02703025175833773</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -828,7 +828,7 @@
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723568524209856</v>
+        <v>0.007723660814659139</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422393798828</v>
+        <v>170.3422546386719</v>
       </c>
       <c r="C17" t="n">
-        <v>170.561702379452</v>
+        <v>170.5617176578999</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332085052758</v>
+        <v>166.3320999523285</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763267714875</v>
+        <v>168.6763418810487</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634541386375</v>
+        <v>0.01455643629502945</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -876,7 +876,7 @@
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847530924081588</v>
+        <v>0.03847521621706362</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465515136719</v>
+        <v>176.7465362548828</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491190407138</v>
+        <v>179.8491035140756</v>
       </c>
       <c r="D19" t="n">
-        <v>176.058198218447</v>
+        <v>176.0581830190845</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505469868697</v>
+        <v>179.2505315119071</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460226669898541</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3949890136719</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731234709029</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.0282531820179</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.34510547722</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00366874201757672</v>
+        <v>0.003668914997253303</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251800537109</v>
+        <v>177.3251647949219</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225571584428</v>
+        <v>178.4225418052247</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929181271268</v>
+        <v>174.0929031464731</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501493971494</v>
+        <v>175.2501343169162</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003935227277223063</v>
+        <v>-0.0003936947256518719</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620361328125</v>
+        <v>174.4620208740234</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757693786965</v>
+        <v>177.0757538913052</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632311486472</v>
+        <v>173.9632159334845</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769643945311</v>
+        <v>176.5769489507663</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629078640273</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624671755319263</v>
+        <v>-0.02624663238682878</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653045654297</v>
+        <v>177.2652893066406</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291540783439</v>
+        <v>179.8291385988617</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162058826927</v>
+        <v>172.7161910154847</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629701066951</v>
+        <v>174.0629551235593</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068473920816773</v>
+        <v>0.004068387491782843</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7640991210938</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403244887289</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118813132914</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441426621237</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830697929731</v>
+        <v>0.002814003097804996</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053992000650995</v>
+        <v>0.02053983240613322</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.79248046875</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="C33" t="n">
-        <v>187.6903232769056</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604518817237</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972606974542</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537325381961498</v>
+        <v>0.0035374073593748</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812141321341782</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715850830078</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050419886609</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369484043502</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378401044004</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723425742952704</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108631272043314</v>
+        <v>-0.0110862321012164</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1317,22 +1317,22 @@
         <v>45937</v>
       </c>
       <c r="B37" t="n">
-        <v>184.5977325439453</v>
+        <v>184.5977172851562</v>
       </c>
       <c r="C37" t="n">
-        <v>188.6081286768816</v>
+        <v>188.6081130865945</v>
       </c>
       <c r="D37" t="n">
-        <v>183.5602249269612</v>
+        <v>183.5602097539322</v>
       </c>
       <c r="E37" t="n">
-        <v>185.7848907820332</v>
+        <v>185.784875425114</v>
       </c>
       <c r="F37" t="n">
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694945388425074</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199541139559646</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626288358566</v>
+        <v>0.01829618052309101</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886536282782095</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699035644531</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556185865847</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155435929421</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207340107304</v>
+        <v>187.52074924116</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817213093671711</v>
+        <v>0.02817212858411589</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402082090329285</v>
+        <v>-0.04402089854789248</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1533,22 +1533,22 @@
         <v>45950</v>
       </c>
       <c r="B46" t="n">
-        <v>182.2034606933594</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="C46" t="n">
-        <v>184.7573394499357</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D46" t="n">
-        <v>181.2956320849819</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E46" t="n">
-        <v>182.6922949953283</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="F46" t="n">
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165674177737388</v>
+        <v>-0.003165590696970089</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1572,7 +1572,7 @@
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103251299777958</v>
+        <v>-0.008103334367036585</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.84912109375</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015721983185</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375297972393</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070662621498</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004857597766183885</v>
+        <v>-0.00485768219622118</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1620,7 +1620,7 @@
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829004346624</v>
+        <v>0.01042837577039868</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495147705078</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644428640734</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513174538508</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E52" t="n">
-        <v>192.588592118433</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981974113173093</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989603835835264</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448386811519</v>
+        <v>-0.02004441147263381</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060577392578</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729406961805</v>
+        <v>207.4729563679188</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870481318289</v>
+        <v>201.5870633589687</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565693232556</v>
+        <v>205.9565848804529</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971380233034448</v>
+        <v>-0.001971304845645117</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1788,7 +1788,7 @@
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168005119548289</v>
+        <v>0.02167997402155764</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434387207031</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4350026612236</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847643800754</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949275919373</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751478380745641</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.03652470224768178</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003021240234</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699092076593</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823961188316</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580698535366</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721368699238781</v>
+        <v>0.0003720555463071484</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742492675781</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621214501376</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268115668235</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436639125443</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793249675415924</v>
+        <v>0.05793266405042918</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959044433116265</v>
+        <v>-0.02959051889910702</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368225097656</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218237722109</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6732056162565</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522318976041</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331505219175</v>
+        <v>0.003313252320373383</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133911132812</v>
+        <v>186.4134063720703</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824463944715</v>
+        <v>190.9824620272586</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105907203728</v>
+        <v>183.4106057333689</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933791327836</v>
+        <v>190.5933947337238</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581020576737093</v>
+        <v>-0.03581005074692667</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2004,7 +2004,7 @@
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0177137394870075</v>
+        <v>0.01771365618248799</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540069580078</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482645458532</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794576828592</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E66" t="n">
-        <v>185.525507871713</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877265156263563</v>
+        <v>-0.01877257113277342</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808138730923948</v>
+        <v>-0.02808154894469495</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845174000170858</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524841308594</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1189017022491</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166923711864</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068443722038</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009742993471366312</v>
+        <v>-0.009743078144453632</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652227239154</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3949890136719</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341727058355</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447513765687</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919407266003</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0259108417558972</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291778564453</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728535594688</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140165634392</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1959139436215</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372185796401415</v>
+        <v>0.01372168475193747</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.0180850950995245</v>
+        <v>-0.01808492693090802</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649711013028865</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.951904296875</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="C78" t="n">
-        <v>184.0892423581687</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398901129937</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1960032737075</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053512845051</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2340,7 +2340,7 @@
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00528960288028224</v>
+        <v>-0.005289519918164731</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114044189453</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3931976659576</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123291208211</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871831157045</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266452212921567</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256277519845034</v>
+        <v>0.007256189498619836</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3051147460938</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733214473424</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916907151964</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485164107673</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111747940743541</v>
+        <v>0.008111661183153096</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2532,7 +2532,7 @@
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814991702143256</v>
+        <v>-0.03814983424509077</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2589,22 +2589,22 @@
         <v>46013</v>
       </c>
       <c r="B90" t="n">
-        <v>183.2611541748047</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="C90" t="n">
-        <v>183.730058116363</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D90" t="n">
-        <v>181.9242862331203</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E90" t="n">
-        <v>183.4906129473229</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="F90" t="n">
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.014917857266596</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2628,7 +2628,7 @@
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005078265538064</v>
+        <v>0.03005069689074391</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2661,22 +2661,22 @@
         <v>46017</v>
       </c>
       <c r="B93" t="n">
-        <v>190.0851898193359</v>
+        <v>190.085205078125</v>
       </c>
       <c r="C93" t="n">
-        <v>192.2401507638228</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5610975436497</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E93" t="n">
-        <v>189.4766133088049</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="F93" t="n">
         <v>139740300</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01017970646506039</v>
+        <v>0.01017978755564442</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>120006100</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.01212401633949489</v>
+        <v>-0.01212409563967642</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021728515625</v>
+        <v>187.1021881103516</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5487999407664</v>
+        <v>188.5488153175326</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4935963146986</v>
+        <v>186.4936115238563</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005508490403</v>
+        <v>187.8005661647843</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612838827051545</v>
+        <v>-0.003612757568446812</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646209716797</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151405796458</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546497967401</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E96" t="n">
-        <v>189.127461449755</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545375898472038</v>
+        <v>-0.005545538552702456</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2757,22 +2757,22 @@
         <v>46024</v>
       </c>
       <c r="B97" t="n">
-        <v>188.4091186523438</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="C97" t="n">
-        <v>192.479580126264</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D97" t="n">
-        <v>187.8204844911982</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E97" t="n">
-        <v>189.3967976648124</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="F97" t="n">
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01260044853460296</v>
+        <v>0.0126006135839718</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2796,7 +2796,7 @@
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.003865453797424312</v>
+        <v>-0.00386553447189375</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8028869628906</v>
+        <v>186.8029022216797</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213703933745</v>
+        <v>191.7213860539245</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838692947835</v>
+        <v>186.3838845193456</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752284670132</v>
+        <v>190.0752439930999</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677861544826856</v>
+        <v>-0.004677780243029006</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2829,22 +2829,22 @@
         <v>46029</v>
       </c>
       <c r="B100" t="n">
-        <v>188.6685028076172</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="C100" t="n">
-        <v>190.9232211122124</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1244530144955</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E100" t="n">
-        <v>188.1297701943655</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="F100" t="n">
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.00998708250744107</v>
+        <v>0.009987081691657185</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080169677734</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074981045344</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685228499072</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152180029744644</v>
+        <v>-0.02152196030920583</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009727675505442068</v>
+        <v>-0.0009726849758688871</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952270507812</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="C107" t="n">
-        <v>189.99540517049</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455833269296</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385795892923</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383931140514608</v>
+        <v>-0.004383849373637116</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3036,7 +3036,7 @@
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381676302343995</v>
+        <v>-0.0438168415518142</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.0346832275391</v>
+        <v>186.03466796875</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784906596197</v>
+        <v>188.6784751839824</v>
       </c>
       <c r="D112" t="n">
-        <v>185.555808059744</v>
+        <v>185.5557928402329</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230748442759</v>
+        <v>186.7230595290241</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.00639415348837058</v>
+        <v>-0.006394234985120373</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099371233637481</v>
+        <v>0.01099379525930511</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728912353516</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009553855833</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3968053634026</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E114" t="n">
-        <v>190.8234748728661</v>
+        <v>190.823459633995</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591342985123156</v>
+        <v>0.01591334872193784</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3189,22 +3189,22 @@
         <v>46051</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0605621337891</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="C115" t="n">
-        <v>193.0282987969995</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D115" t="n">
-        <v>185.625623299501</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E115" t="n">
-        <v>190.8932954336949</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="F115" t="n">
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169079151165157</v>
+        <v>0.005169239280915949</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3213,22 +3213,22 @@
         <v>46052</v>
       </c>
       <c r="B116" t="n">
-        <v>190.6837921142578</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="C116" t="n">
-        <v>194.0359484555967</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D116" t="n">
-        <v>189.0276639024229</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E116" t="n">
-        <v>190.7636071727618</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="F116" t="n">
         <v>179489500</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.00716841606749119</v>
+        <v>-0.007168415497976421</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766967773438</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557504766133</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4484052141589</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629812920276</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.0288807731158095</v>
+        <v>-0.02888093084756926</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839299457635047</v>
+        <v>-0.02839291451472381</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833404541016</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="C119" t="n">
-        <v>179.160756412826</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086645338761</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410414348666</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221377522338</v>
+        <v>-0.0341021289659974</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787292480469</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4071986282528</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307075914073</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5215964583249</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.01326140468949821</v>
+        <v>-0.0132614035251003</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771423339844</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634266395524</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923819783884</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E121" t="n">
-        <v>176.277498975506</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0787177112002726</v>
+        <v>0.07871770419569057</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963287353516</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2078878887748</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205500126207</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298238555102</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497166051482758</v>
+        <v>0.024971658454912</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893035105149604</v>
+        <v>-0.007893114950312197</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5035858154297</v>
+        <v>186.5036010742188</v>
       </c>
       <c r="C125" t="n">
-        <v>193.1580126884611</v>
+        <v>193.158028491682</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745817463215</v>
+        <v>186.0745969700116</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793648877844</v>
+        <v>192.5793806436633</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636418228460701</v>
+        <v>-0.01636410180845216</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832244873047</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622780376601</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660713803529</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E126" t="n">
-        <v>187.042320465516</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209266545793198</v>
+        <v>-0.02209282728038808</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3492,7 +3492,7 @@
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560567193918</v>
+        <v>0.01181569032381558</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613342285156</v>
+        <v>187.4613189697266</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900957055448</v>
+        <v>187.9900804037161</v>
       </c>
       <c r="D129" t="n">
-        <v>185.2265733363672</v>
+        <v>185.226558259481</v>
       </c>
       <c r="E129" t="n">
-        <v>186.62329889396</v>
+        <v>186.6232837033845</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004255251289267958</v>
+        <v>-0.0004256064912840918</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3564,7 +3564,7 @@
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021825301539225</v>
+        <v>0.01021833524412785</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028289794922</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972200828311</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374267327081</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531700210539</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113929721387581</v>
+        <v>0.009113849147715847</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786747007672789</v>
+        <v>0.006786827395534711</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637395256691</v>
+        <v>182.1637238018573</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682453114839</v>
+        <v>175.9682301224481</v>
       </c>
       <c r="E135" t="n">
-        <v>180.8268714126474</v>
+        <v>180.82685580423</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164637217148226</v>
+        <v>-0.04164645489360941</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539855957031</v>
+        <v>182.0539703369141</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317086895539</v>
+        <v>183.0316933488174</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322921838959</v>
+        <v>174.2322775806792</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014235260267</v>
+        <v>174.6014088918714</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486242594537</v>
+        <v>0.02985486500292533</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3732,7 +3732,7 @@
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331646982798718</v>
+        <v>-0.01331638712945649</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119873046875</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6303076754259</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647422536165</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470550179114</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.00163899427668035</v>
+        <v>0.001638910718471109</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048614501953</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333155363547</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4071960911633</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420134514761</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010806418782519</v>
+        <v>-0.03010789985650675</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716230855539603</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H275"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7041,12 +7041,36 @@
         <v>219.3500061035156</v>
       </c>
       <c r="F275" t="n">
-        <v>189683500</v>
+        <v>190287400</v>
       </c>
       <c r="G275" t="n">
         <v>0.01335829298572921</v>
       </c>
       <c r="H275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B276" t="n">
+        <v>227.3800048828125</v>
+      </c>
+      <c r="C276" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="D276" t="n">
+        <v>221.5599975585938</v>
+      </c>
+      <c r="E276" t="n">
+        <v>222.9400024414062</v>
+      </c>
+      <c r="F276" t="n">
+        <v>109479900</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0.02299005944179355</v>
+      </c>
+      <c r="H276" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709320068359</v>
+        <v>174.9709014892578</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694703808103</v>
+        <v>175.5694397588381</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870860004334</v>
+        <v>168.3870566311777</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414988927798</v>
+        <v>174.7414684152183</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366330087374079</v>
+        <v>-0.001366504264196933</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519409179688</v>
+        <v>174.5519256591797</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672421817212</v>
+        <v>176.4672267555024</v>
       </c>
       <c r="D5" t="n">
-        <v>173.3848049238756</v>
+        <v>173.384789767114</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222692884882</v>
+        <v>174.4222540410346</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394632548741393</v>
+        <v>-0.002394545758820588</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545654296875</v>
+        <v>177.5545959472656</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1530884388983</v>
+        <v>178.1531190593489</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811681643912</v>
+        <v>170.7811975177769</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877223514448</v>
+        <v>172.1877519465851</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720189701660124</v>
+        <v>0.01720216077105197</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701324462891</v>
+        <v>179.3701019287109</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650013525793</v>
+        <v>181.4649704785855</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380681264219</v>
+        <v>176.138038158739</v>
       </c>
       <c r="E7" t="n">
-        <v>177.913712535141</v>
+        <v>177.9136822653545</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0102254031723028</v>
+        <v>0.0102250576604872</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253173828125</v>
+        <v>181.3253326416016</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9437957277396</v>
+        <v>181.9438110385745</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725521067403</v>
+        <v>178.3725671170498</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6194940740671</v>
+        <v>179.6195091893087</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090028150092892</v>
+        <v>0.01090053856170359</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.15576171875</v>
+        <v>181.1557464599609</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435839210746</v>
+        <v>182.0435685875041</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618774176739</v>
+        <v>178.6618623689453</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348217819195</v>
+        <v>181.5348064912021</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009350909542572561</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -684,7 +684,7 @@
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874514497031027</v>
+        <v>-0.007874430930079446</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400512695312</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.439558941325</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955557135668</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527215200144</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095443250276666</v>
+        <v>0.006095353599539832</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114044189453</v>
+        <v>166.6114349365234</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164816497661</v>
+        <v>168.6165125346066</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686243805947</v>
+        <v>163.668654359155</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189280624296</v>
+        <v>167.618958764552</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703025175833773</v>
+        <v>-0.0270299868441547</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982543945312</v>
+        <v>167.8982696533203</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417807313731</v>
+        <v>170.5417962304089</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406114031506</v>
+        <v>166.9406265749079</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401190912332</v>
+        <v>167.140134281122</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723660814659139</v>
+        <v>0.007723567816861676</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643629502945</v>
+        <v>0.01455634409096618</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847521621706362</v>
+        <v>0.03847512663982333</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465362548828</v>
+        <v>176.7465667724609</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491035140756</v>
+        <v>179.8491345673521</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0581830190845</v>
+        <v>176.0582134178096</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505315119071</v>
+        <v>179.2505624618324</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008458502230944687</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731234709029</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.0282531820179</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.34510547722</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668914997253303</v>
+        <v>0.003668655369389429</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947256518719</v>
+        <v>-0.000393608743619156</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -981,22 +981,22 @@
         <v>45917</v>
       </c>
       <c r="B23" t="n">
-        <v>169.8829803466797</v>
+        <v>169.8829956054688</v>
       </c>
       <c r="C23" t="n">
-        <v>172.7860287607356</v>
+        <v>172.7860442802747</v>
       </c>
       <c r="D23" t="n">
-        <v>168.007484117061</v>
+        <v>168.0074992073941</v>
       </c>
       <c r="E23" t="n">
-        <v>172.2273696616015</v>
+        <v>172.2273851309623</v>
       </c>
       <c r="F23" t="n">
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624663238682878</v>
+        <v>-0.02624654492487588</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1020,7 +1020,7 @@
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494055886175818</v>
+        <v>0.034940465904016</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477416992188</v>
+        <v>176.2477264404297</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543753314711</v>
+        <v>177.6543599509016</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612974471592</v>
+        <v>174.7612823170602</v>
       </c>
       <c r="E25" t="n">
-        <v>175.349898865447</v>
+        <v>175.3498836843894</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439756788046976</v>
+        <v>0.002439670001024075</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1068,7 +1068,7 @@
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928229701524732</v>
+        <v>0.03928238699195052</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035400390625</v>
+        <v>178.0035247802734</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9840093083128</v>
+        <v>181.9839937083107</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888599052367</v>
+        <v>175.7888448362941</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350878652714</v>
+        <v>181.5350723037516</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821196229186118</v>
+        <v>-0.02821204559530932</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470275878906</v>
+        <v>176.5470123291016</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3502935078314</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807727171775</v>
+        <v>174.9807575937583</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403383898065</v>
+        <v>179.3403228895943</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.008182492189240609</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2652893066406</v>
+        <v>177.2653198242188</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291385988617</v>
+        <v>179.8291695578261</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7161910154847</v>
+        <v>172.7162207499007</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629551235593</v>
+        <v>174.062985089831</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387491782843</v>
+        <v>0.004068647130534231</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1164,7 +1164,7 @@
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002814003097804996</v>
+        <v>0.002813830455718369</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153594970703</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602146114836</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890176259668</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987400973632</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053983240613322</v>
+        <v>0.02053991824341894</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041378766245</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.7924957275391</v>
+        <v>186.79248046875</v>
       </c>
       <c r="C33" t="n">
-        <v>187.690338609038</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604668683245</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972757932568</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0035374073593748</v>
+        <v>0.003537325381961498</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812141321341782</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715698242188</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050265070322</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369333277354</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378247179256</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723587692724298</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0110862321012164</v>
+        <v>-0.01108615148198644</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1317,22 +1317,22 @@
         <v>45937</v>
       </c>
       <c r="B37" t="n">
-        <v>184.5977172851562</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="C37" t="n">
-        <v>188.6081130865945</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D37" t="n">
-        <v>183.5602097539322</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E37" t="n">
-        <v>185.784875425114</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="F37" t="n">
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694945388425074</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199541139559646</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829618052309101</v>
+        <v>0.01829626288358566</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886536282782095</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699188232422</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556339904095</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155586605101</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E41" t="n">
-        <v>187.52074924116</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817212858411589</v>
+        <v>0.02817213093671711</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1437,22 +1437,22 @@
         <v>45944</v>
       </c>
       <c r="B42" t="n">
-        <v>179.5997161865234</v>
+        <v>179.5997009277344</v>
       </c>
       <c r="C42" t="n">
-        <v>184.3583198600852</v>
+        <v>184.3583041970053</v>
       </c>
       <c r="D42" t="n">
-        <v>179.2705030798172</v>
+        <v>179.2704878489981</v>
       </c>
       <c r="E42" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3283771191491</v>
       </c>
       <c r="F42" t="n">
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402089854789248</v>
+        <v>-0.04402090212326881</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001770019531</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281238318171</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D43" t="n">
-        <v>176.8662395170747</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3582990595379</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001111021714327642</v>
+        <v>-0.001110851888737052</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754425048828</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419301869027</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944368108431</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038770384366</v>
+        <v>0.01101038676736099</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820892333984</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599908268075</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493465774322</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755442021748715</v>
+        <v>0.007755441369297289</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590696970089</v>
+        <v>-0.003165673913464562</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1557,22 +1557,22 @@
         <v>45951</v>
       </c>
       <c r="B47" t="n">
-        <v>180.7270202636719</v>
+        <v>180.7270050048828</v>
       </c>
       <c r="C47" t="n">
-        <v>182.3531141136141</v>
+        <v>182.3530987175338</v>
       </c>
       <c r="D47" t="n">
-        <v>179.3702701372806</v>
+        <v>179.370254993042</v>
       </c>
       <c r="E47" t="n">
-        <v>182.3531141136141</v>
+        <v>182.3530987175338</v>
       </c>
       <c r="F47" t="n">
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103334367036585</v>
+        <v>-0.008103418112909044</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491058349609</v>
+        <v>179.84912109375</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015566720687</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375148363812</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070509305708</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485768219622118</v>
+        <v>-0.00485751374626664</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246398925781</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925557149365</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602938591047</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988793025541</v>
+        <v>179.988777912505</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042837577039868</v>
+        <v>0.01042820520129983</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1644,7 +1644,7 @@
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250748267812286</v>
+        <v>0.02250756853454439</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.545166015625</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482921843539</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989603608371594</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050598144531</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672482532724</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286015136062</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596525726598</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004441147263381</v>
+        <v>-0.02004448238730316</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060577392578</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729563679188</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870633589687</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565848804529</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971304845645117</v>
+        <v>-0.001971530859184778</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1788,7 +1788,7 @@
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02167997402155764</v>
+        <v>0.02168012836941968</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434234619141</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4349867997753</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847491650603</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949120548774</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751478380745641</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652470224768178</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7002868652344</v>
+        <v>187.7003173828125</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8698939350823</v>
+        <v>187.8699244802363</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823816093971</v>
+        <v>178.4824106282661</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580548583195</v>
+        <v>184.4580848487537</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003720555463071484</v>
+        <v>0.0003722181935406077</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793266405042918</v>
+        <v>0.05793249204463202</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983489990234</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529420926121</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427938118383</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935689756818</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959051889910702</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368072509766</v>
+        <v>193.3368225097656</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218083488666</v>
+        <v>195.4218237722109</v>
       </c>
       <c r="D63" t="n">
-        <v>190.673190567689</v>
+        <v>190.6732056162565</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522164876445</v>
+        <v>195.2522318976041</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313252320373383</v>
+        <v>0.00331341095243709</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4134063720703</v>
+        <v>186.4133758544922</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824620272586</v>
+        <v>190.9824307616844</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4106057333689</v>
+        <v>183.4105757073767</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933947337238</v>
+        <v>190.5933635318434</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005074692667</v>
+        <v>-0.03581028469071756</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154693603516</v>
+        <v>189.7154846191406</v>
       </c>
       <c r="C65" t="n">
-        <v>190.553458007553</v>
+        <v>190.5534733337414</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1483942490048</v>
+        <v>180.1484087383153</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229435613052</v>
+        <v>182.4229582335574</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771365618248799</v>
+        <v>0.01771390464612344</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540222167969</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482800008962</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794727552066</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255230789849</v>
+        <v>185.525507871713</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877257113277342</v>
+        <v>-0.01877273048260975</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2052,7 +2052,7 @@
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808154894469495</v>
+        <v>-0.02808146927787025</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0742034912109</v>
+        <v>186.0741882324219</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109971087465</v>
+        <v>187.4109817403353</v>
       </c>
       <c r="D68" t="n">
-        <v>182.3930205111681</v>
+        <v>182.39300555425</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483273978252</v>
+        <v>184.3483122805645</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174000170858</v>
+        <v>0.02845165566477292</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152479724769053</v>
+        <v>-0.03152471782905131</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524688720703</v>
+        <v>178.4524536132812</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188859589464</v>
+        <v>184.1188702156436</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166776199441</v>
+        <v>172.5166628687019</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068289121023</v>
+        <v>180.806813452001</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743078144453632</v>
+        <v>-0.009743162817541062</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.020516696793347</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3950042724609</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341879937998</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447659257062</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E72" t="n">
-        <v>174.491955735681</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067635257405</v>
+        <v>-0.0259108417558972</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291625976562</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728380763597</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140014756398</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958985688627</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372168475193747</v>
+        <v>0.01372168593222045</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492693090802</v>
+        <v>-0.01808492846544285</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649711013028865</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030535058927451</v>
+        <v>-0.01030543487972591</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.9518890380859</v>
+        <v>182.951904296875</v>
       </c>
       <c r="C78" t="n">
-        <v>184.089227004522</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398751387779</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1959881613664</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116062209880032</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2340,7 +2340,7 @@
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289519918164731</v>
+        <v>-0.00528960288028224</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114196777344</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3932136047752</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123443447362</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871989054384</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266452212921567</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256189498619836</v>
+        <v>0.007256277519845034</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3050994873047</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733061224419</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916756985292</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485012773324</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111661183153096</v>
+        <v>0.008111747940743541</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2532,7 +2532,7 @@
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814983424509077</v>
+        <v>-0.03814991702143256</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2589,22 +2589,22 @@
         <v>46013</v>
       </c>
       <c r="B90" t="n">
-        <v>183.2611694335938</v>
+        <v>183.2611541748047</v>
       </c>
       <c r="C90" t="n">
-        <v>183.7300734141942</v>
+        <v>183.730058116363</v>
       </c>
       <c r="D90" t="n">
-        <v>181.9243013805983</v>
+        <v>181.9242862331203</v>
       </c>
       <c r="E90" t="n">
-        <v>183.4906282252173</v>
+        <v>183.4906129473229</v>
       </c>
       <c r="F90" t="n">
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491794177123418</v>
+        <v>0.014917857266596</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2628,7 +2628,7 @@
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005069689074391</v>
+        <v>0.03005078265538064</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2661,22 +2661,22 @@
         <v>46017</v>
       </c>
       <c r="B93" t="n">
-        <v>190.085205078125</v>
+        <v>190.0851898193359</v>
       </c>
       <c r="C93" t="n">
-        <v>192.240166195598</v>
+        <v>192.2401507638228</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5611125998212</v>
+        <v>187.5610975436497</v>
       </c>
       <c r="E93" t="n">
-        <v>189.4766285187414</v>
+        <v>189.4766133088049</v>
       </c>
       <c r="F93" t="n">
         <v>139740300</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01017978755564442</v>
+        <v>0.01017970646506039</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>120006100</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.01212409563967642</v>
+        <v>-0.01212401633949489</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021881103516</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5488153175326</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4936115238563</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005661647843</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612757568446812</v>
+        <v>-0.003612838827051545</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646057128906</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151249886817</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546345387688</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E96" t="n">
-        <v>189.1274459397885</v>
+        <v>189.127461449755</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545538552702456</v>
+        <v>-0.005545375898472038</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2757,22 +2757,22 @@
         <v>46024</v>
       </c>
       <c r="B97" t="n">
-        <v>188.4091339111328</v>
+        <v>188.4091186523438</v>
       </c>
       <c r="C97" t="n">
-        <v>192.4795957147097</v>
+        <v>192.479580126264</v>
       </c>
       <c r="D97" t="n">
-        <v>187.8204997023152</v>
+        <v>187.8204844911982</v>
       </c>
       <c r="E97" t="n">
-        <v>189.3968130035911</v>
+        <v>189.3967976648124</v>
       </c>
       <c r="F97" t="n">
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0126006135839718</v>
+        <v>0.01260044853460296</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2796,7 +2796,7 @@
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386553447189375</v>
+        <v>-0.003865453797424312</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8029022216797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213860539245</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838845193456</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752439930999</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780243029006</v>
+        <v>-0.004677861544826856</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2829,22 +2829,22 @@
         <v>46029</v>
       </c>
       <c r="B100" t="n">
-        <v>188.6685180664062</v>
+        <v>188.6685028076172</v>
       </c>
       <c r="C100" t="n">
-        <v>190.9232365533545</v>
+        <v>190.9232211122124</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1244680675316</v>
+        <v>186.1244530144955</v>
       </c>
       <c r="E100" t="n">
-        <v>188.1297854095839</v>
+        <v>188.1297701943655</v>
       </c>
       <c r="F100" t="n">
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987081691657185</v>
+        <v>0.00998708250744107</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080017089844</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074824738404</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685072554968</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152196030920583</v>
+        <v>-0.02152180029744644</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009726849758688871</v>
+        <v>-0.0009727675505442068</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952423095703</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="C107" t="n">
-        <v>189.9954207742267</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455985734289</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385950815971</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849373637116</v>
+        <v>-0.004383931140514608</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3036,7 +3036,7 @@
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438168415518142</v>
+        <v>-0.04381676302343995</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.03466796875</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784751839824</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D112" t="n">
-        <v>185.5557928402329</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230595290241</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.006394234985120373</v>
+        <v>-0.00639415348837058</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099379525930511</v>
+        <v>0.01099371233637481</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728759765625</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009400606663</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3967902384632</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E114" t="n">
-        <v>190.823459633995</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591334872193784</v>
+        <v>0.01591342985123156</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3189,22 +3189,22 @@
         <v>46051</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0605773925781</v>
+        <v>192.0605621337891</v>
       </c>
       <c r="C115" t="n">
-        <v>193.0283141326731</v>
+        <v>193.0282987969995</v>
       </c>
       <c r="D115" t="n">
-        <v>185.6256380470483</v>
+        <v>185.625623299501</v>
       </c>
       <c r="E115" t="n">
-        <v>190.8933105997472</v>
+        <v>190.8932954336949</v>
       </c>
       <c r="F115" t="n">
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169239280915949</v>
+        <v>0.005169079151165157</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3213,22 +3213,22 @@
         <v>46052</v>
       </c>
       <c r="B116" t="n">
-        <v>190.6838073730469</v>
+        <v>190.6837921142578</v>
       </c>
       <c r="C116" t="n">
-        <v>194.0359639826301</v>
+        <v>194.0359484555967</v>
       </c>
       <c r="D116" t="n">
-        <v>189.0276790286862</v>
+        <v>189.0276639024229</v>
       </c>
       <c r="E116" t="n">
-        <v>190.7636224379378</v>
+        <v>190.7636071727618</v>
       </c>
       <c r="F116" t="n">
         <v>179489500</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.007168415497976421</v>
+        <v>-0.00716841606749119</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766815185547</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557348322644</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4483900153819</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629659025267</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888093084756926</v>
+        <v>-0.0288807731158095</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839291451472381</v>
+        <v>-0.02839299457635047</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833557128906</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="C119" t="n">
-        <v>179.1607721437711</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086795929406</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410571553003</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0341021289659974</v>
+        <v>-0.03410221377522338</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787445068359</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4072143255947</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307227747363</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5216119878791</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.0132614035251003</v>
+        <v>-0.01326140468949821</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771575927734</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634420291942</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923963475411</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775135166603</v>
+        <v>176.277498975506</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871770419569057</v>
+        <v>0.0787177112002726</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963439941406</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2079034382237</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205647824287</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298386502086</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.024971658454912</v>
+        <v>0.02497166051482758</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893114950312197</v>
+        <v>-0.007893035105149604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5036010742188</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="C125" t="n">
-        <v>193.158028491682</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745969700116</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793806436633</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410180845216</v>
+        <v>-0.01636418228460701</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832092285156</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622623874058</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660562233949</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E126" t="n">
-        <v>187.0423048169314</v>
+        <v>187.042320465516</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209282728038808</v>
+        <v>-0.02209266545793198</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3492,7 +3492,7 @@
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181569032381558</v>
+        <v>0.01181560567193918</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613189697266</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900804037161</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D129" t="n">
-        <v>185.226558259481</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E129" t="n">
-        <v>186.6232837033845</v>
+        <v>186.62329889396</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004256064912840918</v>
+        <v>-0.0004255251289267958</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3564,7 +3564,7 @@
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833524412785</v>
+        <v>0.01021825301539225</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028137207031</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972046328596</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374116308485</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531547742145</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113849147715847</v>
+        <v>0.009113929721387581</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786827395534711</v>
+        <v>0.006786747007672789</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637238018573</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682301224481</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E135" t="n">
-        <v>180.82685580423</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164645489360941</v>
+        <v>-0.04164637217148226</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539703369141</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0316933488174</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322775806792</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014088918714</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486500292533</v>
+        <v>0.02985486242594537</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3732,7 +3732,7 @@
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331638712945649</v>
+        <v>-0.01331646982798718</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119720458984</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6302923567135</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647274492447</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470399397241</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638910718471109</v>
+        <v>0.00163899427668035</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048614501953</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333155363547</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4071960911633</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.420134514761</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010789985650675</v>
+        <v>-0.03010806418782519</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716230855539603</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -7065,12 +7065,28 @@
         <v>222.9400024414062</v>
       </c>
       <c r="F276" t="n">
-        <v>109479900</v>
+        <v>109806100</v>
       </c>
       <c r="G276" t="n">
         <v>0.02299005944179355</v>
       </c>
       <c r="H276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="n">
+        <v>93296546</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H277"/>
+  <dimension ref="A1:H278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103271484375</v>
+        <v>175.2103424072266</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535459787435</v>
+        <v>182.0535618334976</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607001855326</v>
+        <v>175.0607154312909</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837099150805</v>
+        <v>181.9837257637527</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709014892578</v>
+        <v>174.9709167480469</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694397588381</v>
+        <v>175.5694550698242</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870566311777</v>
+        <v>168.3870713158056</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414684152183</v>
+        <v>174.741483653999</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366504264196933</v>
+        <v>-0.00136650414519035</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -564,7 +564,7 @@
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394545758820588</v>
+        <v>-0.002394632757571458</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545959472656</v>
+        <v>177.5545806884766</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531190593489</v>
+        <v>178.1531037491236</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811975177769</v>
+        <v>170.781182841084</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877519465851</v>
+        <v>172.1877371490149</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720216077105197</v>
+        <v>0.01720207335414736</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701019287109</v>
+        <v>179.3701324462891</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4649704785855</v>
+        <v>181.4650013525793</v>
       </c>
       <c r="D7" t="n">
-        <v>176.138038158739</v>
+        <v>176.1380681264219</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9136822653545</v>
+        <v>177.913712535141</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0102250576604872</v>
+        <v>0.01022531635496304</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253326416016</v>
+        <v>181.3253173828125</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438110385745</v>
+        <v>181.9437957277396</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725671170498</v>
+        <v>178.3725521067403</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195091893087</v>
+        <v>179.6194940740671</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090053856170359</v>
+        <v>0.01090028150092892</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557464599609</v>
+        <v>181.15576171875</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435685875041</v>
+        <v>182.0435839210746</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618623689453</v>
+        <v>178.6618774176739</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348064912021</v>
+        <v>181.5348217819195</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009352591784613784</v>
+        <v>-0.0009350909542572561</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874430930079446</v>
+        <v>-0.007874598727247717</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643662953308</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400512695312</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.439558941325</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955557135668</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527215200144</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095353599539832</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114349365234</v>
+        <v>166.6114196777344</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6165125346066</v>
+        <v>168.6164970921864</v>
       </c>
       <c r="D15" t="n">
-        <v>163.668654359155</v>
+        <v>163.6686393698748</v>
       </c>
       <c r="E15" t="n">
-        <v>167.618958764552</v>
+        <v>167.6189434134908</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0270299868441547</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982696533203</v>
+        <v>167.8982543945312</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417962304089</v>
+        <v>170.5417807313731</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406265749079</v>
+        <v>166.9406114031506</v>
       </c>
       <c r="E16" t="n">
-        <v>167.140134281122</v>
+        <v>167.1401190912332</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723567816861676</v>
+        <v>0.007723568524209856</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634409096618</v>
+        <v>0.01455643629502945</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465667724609</v>
+        <v>176.7465362548828</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491345673521</v>
+        <v>179.8491035140756</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0582134178096</v>
+        <v>176.0581830190845</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505624618324</v>
+        <v>179.2505315119071</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008458502230944687</v>
+        <v>-0.0008460227399664788</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3949890136719</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731234709029</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.0282531820179</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.34510547722</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668655369389429</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.000393608743619156</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -981,22 +981,22 @@
         <v>45917</v>
       </c>
       <c r="B23" t="n">
-        <v>169.8829956054688</v>
+        <v>169.8829803466797</v>
       </c>
       <c r="C23" t="n">
-        <v>172.7860442802747</v>
+        <v>172.7860287607356</v>
       </c>
       <c r="D23" t="n">
-        <v>168.0074992073941</v>
+        <v>168.007484117061</v>
       </c>
       <c r="E23" t="n">
-        <v>172.2273851309623</v>
+        <v>172.2273696616015</v>
       </c>
       <c r="F23" t="n">
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624654492487588</v>
+        <v>-0.02624663238682878</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1020,7 +1020,7 @@
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.034940465904016</v>
+        <v>0.03494055886175818</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477264404297</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543599509016</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612823170602</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E25" t="n">
-        <v>175.3498836843894</v>
+        <v>175.349898865447</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439670001024075</v>
+        <v>0.002439756788046976</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711578369141</v>
+        <v>183.1711730957031</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089135963474</v>
+        <v>184.1089289332547</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924356467209</v>
+        <v>174.2924501658818</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810218455756</v>
+        <v>174.8810364137678</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928238699195052</v>
+        <v>0.0392823835910463</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035247802734</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9839937083107</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888448362941</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350723037516</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204559530932</v>
+        <v>-0.02821204324514892</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470123291016</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3502935078314</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807575937583</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403228895943</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182492189240609</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653198242188</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291695578261</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162207499007</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.062985089831</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068647130534231</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830455718369</v>
+        <v>0.002813830697929731</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053991824341894</v>
+        <v>0.020540005843803</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715545654297</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050110254035</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369182511207</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378093314507</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587692724298</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965576171875</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7825209975275</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918479831437</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566599139491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108615148198644</v>
+        <v>-0.01108615057821005</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1317,22 +1317,22 @@
         <v>45937</v>
       </c>
       <c r="B37" t="n">
-        <v>184.5977325439453</v>
+        <v>184.5977172851562</v>
       </c>
       <c r="C37" t="n">
-        <v>188.6081286768816</v>
+        <v>188.6081130865945</v>
       </c>
       <c r="D37" t="n">
-        <v>183.5602249269612</v>
+        <v>183.5602097539322</v>
       </c>
       <c r="E37" t="n">
-        <v>185.7848907820332</v>
+        <v>185.784875425114</v>
       </c>
       <c r="F37" t="n">
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002695027603176414</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199541139559646</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626288358566</v>
+        <v>0.01829618052309101</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699035644531</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556185865847</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155435929421</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207340107304</v>
+        <v>187.52074924116</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817213093671711</v>
+        <v>0.02817221444483309</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1437,22 +1437,22 @@
         <v>45944</v>
       </c>
       <c r="B42" t="n">
-        <v>179.5997009277344</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="C42" t="n">
-        <v>184.3583041970053</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D42" t="n">
-        <v>179.2704878489981</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E42" t="n">
-        <v>184.3283771191491</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="F42" t="n">
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402090212326881</v>
+        <v>-0.04402089854789248</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001922607422</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281395182556</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D43" t="n">
-        <v>176.866254560341</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3583147400375</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110851888737052</v>
+        <v>-0.001111021714327642</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1500,7 +1500,7 @@
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038676736099</v>
+        <v>0.01101047275832534</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7821044921875</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6600061588844</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493615830456</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755441369297289</v>
+        <v>0.007755357241106875</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165673913464562</v>
+        <v>-0.003165590696970089</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1557,22 +1557,22 @@
         <v>45951</v>
       </c>
       <c r="B47" t="n">
-        <v>180.7270050048828</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="C47" t="n">
-        <v>182.3530987175338</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D47" t="n">
-        <v>179.370254993042</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E47" t="n">
-        <v>182.3530987175338</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="F47" t="n">
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103418112909044</v>
+        <v>-0.008103334367036585</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1596,7 +1596,7 @@
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485751374626664</v>
+        <v>-0.004857597766183885</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250756853454439</v>
+        <v>0.02250765250109055</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807910615919784</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495300292969</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644582837766</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513320204045</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886067715161</v>
+        <v>192.588592118433</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981974113173093</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.545166015625</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828666070652</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905729140704</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482921843539</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989603608371594</v>
+        <v>0.02989603835835264</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050750732422</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672637579894</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286166610889</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596680014167</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448238730316</v>
+        <v>-0.02004448386811519</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729250244422</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870329046891</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565537660584</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971530859184778</v>
+        <v>-0.001971380233034448</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1788,7 +1788,7 @@
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168012836941968</v>
+        <v>0.02168005119548289</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434387207031</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4350026612236</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847643800754</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949275919373</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751478380745641</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.03652470224768178</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003173828125</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699244802363</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4824106282661</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580848487537</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003722181935406077</v>
+        <v>0.0003720555463071484</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742645263672</v>
+        <v>198.5742492675781</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621367771523</v>
+        <v>199.4621214501376</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268264223904</v>
+        <v>193.3268115668235</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6436639125443</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793249204463202</v>
+        <v>0.05793258275705826</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959052117289374</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368225097656</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218237722109</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6732056162565</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522318976041</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00331341095243709</v>
+        <v>0.003313252582732629</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133758544922</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824307616844</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105757073767</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933635318434</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581028469071756</v>
+        <v>-0.03581005357317613</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154846191406</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="C65" t="n">
-        <v>190.5534733337414</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1484087383153</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229582335574</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771390464612344</v>
+        <v>0.0177137394870075</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540069580078</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482645458532</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794576828592</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E66" t="n">
-        <v>185.525507871713</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877273048260975</v>
+        <v>-0.01877257113277342</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146927787025</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0741882324219</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109817403353</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D68" t="n">
-        <v>182.39300555425</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483122805645</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165566477292</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2085,22 +2085,22 @@
         <v>45981</v>
       </c>
       <c r="B69" t="n">
-        <v>180.208251953125</v>
+        <v>180.2082366943359</v>
       </c>
       <c r="C69" t="n">
-        <v>195.5315406452363</v>
+        <v>195.5315240889771</v>
       </c>
       <c r="D69" t="n">
-        <v>179.4201468289569</v>
+        <v>179.4201316368992</v>
       </c>
       <c r="E69" t="n">
-        <v>195.4816571057099</v>
+        <v>195.4816405536745</v>
       </c>
       <c r="F69" t="n">
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152471782905131</v>
+        <v>-0.03152487925147596</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524536132812</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188702156436</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166628687019</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E70" t="n">
-        <v>180.806813452001</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743162817541062</v>
+        <v>-0.009742994296335628</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2148,7 +2148,7 @@
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.020516696793347</v>
+        <v>0.02051660953286172</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3949890136719</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341727058355</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447513765687</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919407266003</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0259108417558972</v>
+        <v>-0.02591067418159221</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372168593222045</v>
+        <v>0.01372151153989076</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492846544285</v>
+        <v>-0.01808484361385299</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649711013028865</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030543487972591</v>
+        <v>-0.01030535058927451</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.951904296875</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="C78" t="n">
-        <v>184.0892423581687</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398901129937</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1960032737075</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116062209880032</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2340,7 +2340,7 @@
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00528960288028224</v>
+        <v>-0.005289519918164731</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168212890625</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5610985176648</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741660895743</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E80" t="n">
-        <v>182.2136112701494</v>
+        <v>182.213626289633</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721399899417375</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125912631224192</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.8784332275391</v>
+        <v>175.87841796875</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0034500370577</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213802569945</v>
+        <v>174.6213651072644</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245903328353</v>
+        <v>177.5245749312296</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256277519845034</v>
+        <v>0.007256190132717499</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3051147460938</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733214473424</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916907151964</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485164107673</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111747940743541</v>
+        <v>0.008111748644499261</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814991702143256</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2589,22 +2589,22 @@
         <v>46013</v>
       </c>
       <c r="B90" t="n">
-        <v>183.2611541748047</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="C90" t="n">
-        <v>183.730058116363</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D90" t="n">
-        <v>181.9242862331203</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E90" t="n">
-        <v>183.4906129473229</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="F90" t="n">
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.014917857266596</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2628,7 +2628,7 @@
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005078265538064</v>
+        <v>0.03005069689074391</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2661,22 +2661,22 @@
         <v>46017</v>
       </c>
       <c r="B93" t="n">
-        <v>190.0851898193359</v>
+        <v>190.085205078125</v>
       </c>
       <c r="C93" t="n">
-        <v>192.2401507638228</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5610975436497</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E93" t="n">
-        <v>189.4766133088049</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="F93" t="n">
         <v>139740300</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01017970646506039</v>
+        <v>0.01017978755564442</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>120006100</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.01212401633949489</v>
+        <v>-0.01212409563967642</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646209716797</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151405796458</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546497967401</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E96" t="n">
-        <v>189.127461449755</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545375898472038</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2757,22 +2757,22 @@
         <v>46024</v>
       </c>
       <c r="B97" t="n">
-        <v>188.4091186523438</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="C97" t="n">
-        <v>192.479580126264</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D97" t="n">
-        <v>187.8204844911982</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E97" t="n">
-        <v>189.3967976648124</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="F97" t="n">
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01260044853460296</v>
+        <v>0.0126006135839718</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2796,7 +2796,7 @@
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.003865453797424312</v>
+        <v>-0.00386553447189375</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2829,22 +2829,22 @@
         <v>46029</v>
       </c>
       <c r="B100" t="n">
-        <v>188.6685028076172</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="C100" t="n">
-        <v>190.9232211122124</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1244530144955</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E100" t="n">
-        <v>188.1297701943655</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="F100" t="n">
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.00998708250744107</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080169677734</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074981045344</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685228499072</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152180029744644</v>
+        <v>-0.02152196030920583</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009727675505442068</v>
+        <v>-0.0009726849758688871</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133270263672</v>
+        <v>186.6133117675781</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571344016907</v>
+        <v>189.2571189267257</v>
       </c>
       <c r="D106" t="n">
-        <v>185.895006678512</v>
+        <v>185.8949914784577</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0646079796491</v>
+        <v>186.0645927657271</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134974210895835</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3012,7 +3012,7 @@
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383931140514608</v>
+        <v>-0.004383849732090828</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.654296875</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381676302343995</v>
+        <v>-0.04381668089652369</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948280612693632</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728912353516</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009553855833</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3968053634026</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E114" t="n">
-        <v>190.8234748728661</v>
+        <v>190.823459633995</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591342985123156</v>
+        <v>0.01591334872193784</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3189,22 +3189,22 @@
         <v>46051</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0605621337891</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="C115" t="n">
-        <v>193.0282987969995</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D115" t="n">
-        <v>185.625623299501</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E115" t="n">
-        <v>190.8932954336949</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="F115" t="n">
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169079151165157</v>
+        <v>0.005169239280915949</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3213,22 +3213,22 @@
         <v>46052</v>
       </c>
       <c r="B116" t="n">
-        <v>190.6837921142578</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="C116" t="n">
-        <v>194.0359484555967</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D116" t="n">
-        <v>189.0276639024229</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E116" t="n">
-        <v>190.7636071727618</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="F116" t="n">
         <v>179489500</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.00716841606749119</v>
+        <v>-0.007168415497976421</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766967773438</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557504766133</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4484052141589</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629812920276</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.0288807731158095</v>
+        <v>-0.02888093084756926</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839299457635047</v>
+        <v>-0.02839291451472381</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833404541016</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="C119" t="n">
-        <v>179.160756412826</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086645338761</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410414348666</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221377522338</v>
+        <v>-0.0341021289659974</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787292480469</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4071986282528</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307075914073</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5215964583249</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.01326140468949821</v>
+        <v>-0.0132614035251003</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771423339844</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634266395524</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923819783884</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E121" t="n">
-        <v>176.277498975506</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0787177112002726</v>
+        <v>0.07871770419569057</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963287353516</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2078878887748</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205500126207</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298238555102</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497166051482758</v>
+        <v>0.024971658454912</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893035105149604</v>
+        <v>-0.007893114950312197</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832244873047</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622780376601</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660713803529</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E126" t="n">
-        <v>187.042320465516</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209266545793198</v>
+        <v>-0.02209274727292232</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560567193918</v>
+        <v>0.01181560666047221</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768615722656</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856654675195</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059147845697</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344488846578</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021825301539225</v>
+        <v>0.01021833441238607</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028289794922</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972200828311</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374267327081</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531700210539</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113929721387581</v>
+        <v>0.009113767839714404</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786747007672789</v>
+        <v>0.006786827395534711</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583740234375</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364236513225</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8897126034445</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164813019665</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456121004512637</v>
+        <v>-0.05456128825383422</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164637217148226</v>
+        <v>-0.04164629289442512</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539855957031</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317086895539</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322921838959</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014235260267</v>
+        <v>174.601438160182</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486242594537</v>
+        <v>0.02985494874285899</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296691894531</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776756968921</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069714269912</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0733135069376</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331646982798718</v>
+        <v>-0.01331663634113589</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660656891157819</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119873046875</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6303076754259</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647422536165</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470550179114</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.00163899427668035</v>
+        <v>0.001638910718471109</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048614501953</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333155363547</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4071960911633</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420134514761</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010806418782519</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716230855539603</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7076,17 +7076,49 @@
       <c r="A277" s="2" t="n">
         <v>46287</v>
       </c>
-      <c r="B277" t="inlineStr"/>
-      <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
+      <c r="B277" t="n">
+        <v>228.8699951171875</v>
+      </c>
+      <c r="C277" t="n">
+        <v>229.9799957275391</v>
+      </c>
+      <c r="D277" t="n">
+        <v>226.5</v>
+      </c>
+      <c r="E277" t="n">
+        <v>226.8500061035156</v>
+      </c>
       <c r="F277" t="n">
-        <v>93296546</v>
+        <v>95746700</v>
       </c>
       <c r="G277" t="n">
-        <v>0</v>
+        <v>0.006552863938686704</v>
       </c>
       <c r="H277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B278" t="n">
+        <v>225.5099945068359</v>
+      </c>
+      <c r="C278" t="n">
+        <v>228.9499969482422</v>
+      </c>
+      <c r="D278" t="n">
+        <v>224.0200042724609</v>
+      </c>
+      <c r="E278" t="n">
+        <v>228.0299987792969</v>
+      </c>
+      <c r="F278" t="n">
+        <v>89306700</v>
+      </c>
+      <c r="G278" t="n">
+        <v>-0.01468082615473976</v>
+      </c>
+      <c r="H278" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H278"/>
+  <dimension ref="A1:H279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103424072266</v>
+        <v>175.2103271484375</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535618334976</v>
+        <v>182.0535459787435</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607154312909</v>
+        <v>175.0607001855326</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837257637527</v>
+        <v>181.9837099150805</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -540,7 +540,7 @@
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.00136650414519035</v>
+        <v>-0.001366417175785561</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545806884766</v>
+        <v>177.5545654296875</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531037491236</v>
+        <v>178.1530884388983</v>
       </c>
       <c r="D6" t="n">
-        <v>170.781182841084</v>
+        <v>170.7811681643912</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877371490149</v>
+        <v>172.1877223514448</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207335414736</v>
+        <v>0.01720198593724254</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701324462891</v>
+        <v>179.3701171875</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650013525793</v>
+        <v>181.4649859155824</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380681264219</v>
+        <v>176.1380531425805</v>
       </c>
       <c r="E7" t="n">
-        <v>177.913712535141</v>
+        <v>177.9136974002478</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531635496304</v>
+        <v>0.01022531723371234</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253173828125</v>
+        <v>181.3253326416016</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9437957277396</v>
+        <v>181.9438110385745</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725521067403</v>
+        <v>178.3725671170498</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6194940740671</v>
+        <v>179.6195091893087</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090028150092892</v>
+        <v>0.01090045256567307</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009350909542572561</v>
+        <v>-0.0009351750270146786</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874598727247717</v>
+        <v>-0.007874514497031027</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538909912109</v>
+        <v>173.7538757324219</v>
       </c>
       <c r="C11" t="n">
-        <v>177.714180280125</v>
+        <v>177.7141646735497</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264119284913</v>
+        <v>172.7263967599338</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6742848307548</v>
+        <v>177.674269227683</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635455335401</v>
+        <v>-0.03324652152828622</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -732,7 +732,7 @@
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952001095973654</v>
+        <v>-0.0195199248555431</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400512695312</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.439558941325</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955557135668</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527215200144</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095443250276666</v>
+        <v>0.006095353599539832</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016265075109</v>
+        <v>-0.02703007595174933</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982543945312</v>
+        <v>167.8982696533203</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417807313731</v>
+        <v>170.5417962304089</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406114031506</v>
+        <v>166.9406265749079</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401190912332</v>
+        <v>167.140134281122</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723568524209856</v>
+        <v>0.007723660107302521</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422546386719</v>
+        <v>170.3422698974609</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617176578999</v>
+        <v>170.5617329363479</v>
       </c>
       <c r="D17" t="n">
-        <v>166.3320999523285</v>
+        <v>166.332114851899</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763418810487</v>
+        <v>168.6763569906099</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643629502945</v>
+        <v>0.01455643497212367</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512663982333</v>
+        <v>0.03847512319332802</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460227399664788</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731541223449</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028283464474</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451359862166</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003669001328727717</v>
+        <v>0.003668914997253303</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807076698219</v>
+        <v>-0.0003936947256518719</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711730957031</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089289332547</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924501658818</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810364137678</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0392823835910463</v>
+        <v>0.03928229701524732</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204324514892</v>
+        <v>-0.02821196229186118</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653045654297</v>
+        <v>177.2652893066406</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291540783439</v>
+        <v>179.8291385988617</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162058826927</v>
+        <v>172.7161910154847</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629701066951</v>
+        <v>174.0629551235593</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068473920816773</v>
+        <v>0.004068387491782843</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7640991210938</v>
+        <v>177.7641296386719</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403244887289</v>
+        <v>179.3403552769049</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118813132914</v>
+        <v>174.5119112725463</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441426621237</v>
+        <v>177.7441731762758</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830697929731</v>
+        <v>0.002814089176637058</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153747558594</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602300506758</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890327563757</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987552370008</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.020540005843803</v>
+        <v>0.02053974480577181</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041378766245</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.79248046875</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="C33" t="n">
-        <v>187.6903232769056</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604518817237</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972606974542</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537325381961498</v>
+        <v>0.0035374073593748</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385375976562</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="C34" t="n">
-        <v>190.59337868299</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105195355423</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E34" t="n">
-        <v>189.146847340247</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812223009789566</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715698242188</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050265070322</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369333277354</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378247179256</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.00672366812316183</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965576171875</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825209975275</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918479831437</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566599139491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108615057821005</v>
+        <v>-0.01108615148198644</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1317,22 +1317,22 @@
         <v>45937</v>
       </c>
       <c r="B37" t="n">
-        <v>184.5977172851562</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="C37" t="n">
-        <v>188.6081130865945</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D37" t="n">
-        <v>183.5602097539322</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E37" t="n">
-        <v>185.784875425114</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="F37" t="n">
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002695027603176414</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1356,7 +1356,7 @@
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199541139559646</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886536282782095</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1428,7 +1428,7 @@
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817221444483309</v>
+        <v>0.02817212858411589</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001770019531</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281238318171</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D43" t="n">
-        <v>176.8662395170747</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3582990595379</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001111021714327642</v>
+        <v>-0.001110936754343372</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754577636719</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419455690647</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944521048813</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101047275832534</v>
+        <v>0.01101030171288664</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755357241106875</v>
+        <v>0.007755442021748715</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.84912109375</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015721983185</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375297972393</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070662621498</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004857597766183885</v>
+        <v>-0.00485768219622118</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988793025541</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042820520129983</v>
+        <v>0.01042837577039868</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250765250109055</v>
+        <v>0.02250748267812286</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910615919784</v>
+        <v>0.02807919058326869</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495147705078</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644428640734</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513174538508</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E52" t="n">
-        <v>192.588592118433</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981974113173093</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1716,7 +1716,7 @@
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989603835835264</v>
+        <v>0.02989595999882533</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050598144531</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672482532724</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286015136062</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596525726598</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448386811519</v>
+        <v>-0.02004440999182711</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971380233034448</v>
+        <v>-0.001971455471800998</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434234619141</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4349867997753</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847491650603</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949120548774</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751478380745641</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652470224768178</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742492675781</v>
+        <v>198.5742797851562</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621214501376</v>
+        <v>199.462152104167</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268115668235</v>
+        <v>193.3268412779572</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436639125443</v>
+        <v>194.6436938260565</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793258275705826</v>
+        <v>0.05793274534380033</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959052117289374</v>
+        <v>-0.02959067030875928</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3367919921875</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4217929255223</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6731755191215</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522010776849</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313252582732629</v>
+        <v>0.003313331767584859</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005357317613</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.926513671875</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.358293814419</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2205942185541</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.9416897271721</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808163091331894</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0742034912109</v>
+        <v>186.0741882324219</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109971087465</v>
+        <v>187.4109817403353</v>
       </c>
       <c r="D68" t="n">
-        <v>182.3930205111681</v>
+        <v>182.39300555425</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483273978252</v>
+        <v>184.3483122805645</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845174240124138</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2085,22 +2085,22 @@
         <v>45981</v>
       </c>
       <c r="B69" t="n">
-        <v>180.2082366943359</v>
+        <v>180.208251953125</v>
       </c>
       <c r="C69" t="n">
-        <v>195.5315240889771</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D69" t="n">
-        <v>179.4201316368992</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E69" t="n">
-        <v>195.4816405536745</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="F69" t="n">
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152487925147596</v>
+        <v>-0.03152471782905131</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524688720703</v>
+        <v>178.4524536132812</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188859589464</v>
+        <v>184.1188702156436</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166776199441</v>
+        <v>172.5166628687019</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068289121023</v>
+        <v>180.806813452001</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009742994296335628</v>
+        <v>-0.009743162817541062</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051660953286172</v>
+        <v>0.02051661128715887</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.734203281764</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447804748437</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919707447618</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067418159221</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372151153989076</v>
+        <v>0.01372159873604817</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168365478516</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5611139779305</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741810893209</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E80" t="n">
-        <v>182.213626289633</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721399899417375</v>
+        <v>0.01721391514737669</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864265695677</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920356049676</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E81" t="n">
-        <v>185.12679644575</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125912631224192</v>
+        <v>-0.003125748033105724</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509674072266</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469957406681</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150239281505</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5381918075859</v>
+        <v>184.538176449994</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433411769608655</v>
+        <v>-0.006433576610347602</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770933102352</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114044189453</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3931976659576</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123291208211</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871831157045</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266452212921567</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.87841796875</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034500370577</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213651072644</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245749312296</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256190132717499</v>
+        <v>0.007256189498619836</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2508,7 +2508,7 @@
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111748644499261</v>
+        <v>0.008111661183153096</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814983424509077</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021728515625</v>
+        <v>187.1021881103516</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5487999407664</v>
+        <v>188.5488153175326</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4935963146986</v>
+        <v>186.4936115238563</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005508490403</v>
+        <v>187.8005661647843</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612838827051545</v>
+        <v>-0.003612757568446812</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545538552702456</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8028869628906</v>
+        <v>186.8029022216797</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213703933745</v>
+        <v>191.7213860539245</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838692947835</v>
+        <v>186.3838845193456</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752284670132</v>
+        <v>190.0752439930999</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677861544826856</v>
+        <v>-0.004677780243029006</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987164191344933</v>
+        <v>0.009987081691657185</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133117675781</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571189267257</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D106" t="n">
-        <v>185.8949914784577</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0645927657271</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974210895835</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952270507812</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="C107" t="n">
-        <v>189.99540517049</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455833269296</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385795892923</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849732090828</v>
+        <v>-0.004383849373637116</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.654296875</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542325986551</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953640623503</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753422141945</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381668089652369</v>
+        <v>-0.0438168415518142</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948280612693632</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.0346832275391</v>
+        <v>186.03466796875</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784906596197</v>
+        <v>188.6784751839824</v>
       </c>
       <c r="D112" t="n">
-        <v>185.555808059744</v>
+        <v>185.5557928402329</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230748442759</v>
+        <v>186.7230595290241</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.00639415348837058</v>
+        <v>-0.006394234985120373</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099371233637481</v>
+        <v>0.01099379525930511</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5035858154297</v>
+        <v>186.5036010742188</v>
       </c>
       <c r="C125" t="n">
-        <v>193.1580126884611</v>
+        <v>193.158028491682</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745817463215</v>
+        <v>186.0745969700116</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793648877844</v>
+        <v>192.5793806436633</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636418228460701</v>
+        <v>-0.01636410180845216</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209274727292232</v>
+        <v>-0.02209282728038808</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130808403767</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7616860728079</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3256935584433</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560666047221</v>
+        <v>0.01181569032381558</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627283983140582</v>
+        <v>0.01627275579951704</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613342285156</v>
+        <v>187.4613189697266</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900957055448</v>
+        <v>187.9900804037161</v>
       </c>
       <c r="D129" t="n">
-        <v>185.2265733363672</v>
+        <v>185.226558259481</v>
       </c>
       <c r="E129" t="n">
-        <v>186.62329889396</v>
+        <v>186.6232837033845</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004255251289267958</v>
+        <v>-0.0004256064912840918</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768768310547</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856807673048</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059297314624</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344638821937</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833441238607</v>
+        <v>0.01021833524412785</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113767839714404</v>
+        <v>0.009113849147715847</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583587646484</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364076167612</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8896973916963</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164652690549</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456128825383422</v>
+        <v>-0.05456121004512637</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637395256691</v>
+        <v>182.1637238018573</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682453114839</v>
+        <v>175.9682301224481</v>
       </c>
       <c r="E135" t="n">
-        <v>180.8268714126474</v>
+        <v>180.82685580423</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164629289442512</v>
+        <v>-0.04164645489360941</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0540008544922</v>
+        <v>182.0539703369141</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317240302905</v>
+        <v>183.0316933488174</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2323067871125</v>
+        <v>174.2322775806792</v>
       </c>
       <c r="E136" t="n">
-        <v>174.601438160182</v>
+        <v>174.6014088918714</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985494874285899</v>
+        <v>0.02985486500292533</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296539306641</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776603660684</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069564334623</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0732983803544</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331663634113589</v>
+        <v>-0.01331638712945649</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660656891157819</v>
+        <v>0.01660648255510222</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010789985650675</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7113,12 +7113,36 @@
         <v>228.0299987792969</v>
       </c>
       <c r="F278" t="n">
-        <v>89306700</v>
+        <v>89547300</v>
       </c>
       <c r="G278" t="n">
         <v>-0.01468082615473976</v>
       </c>
       <c r="H278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B279" t="n">
+        <v>224.5800018310547</v>
+      </c>
+      <c r="C279" t="n">
+        <v>224.9400024414062</v>
+      </c>
+      <c r="D279" t="n">
+        <v>221.0899963378906</v>
+      </c>
+      <c r="E279" t="n">
+        <v>222.0800018310547</v>
+      </c>
+      <c r="F279" t="n">
+        <v>77305200</v>
+      </c>
+      <c r="G279" t="n">
+        <v>-0.004123953254555501</v>
+      </c>
+      <c r="H279" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H279"/>
+  <dimension ref="A1:H280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709167480469</v>
+        <v>174.9709014892578</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694550698242</v>
+        <v>175.5694397588381</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870713158056</v>
+        <v>168.3870566311777</v>
       </c>
       <c r="E4" t="n">
-        <v>174.741483653999</v>
+        <v>174.7414684152183</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417175785561</v>
+        <v>-0.001366504264196933</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519256591797</v>
+        <v>174.5519409179688</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672267555024</v>
+        <v>176.4672421817212</v>
       </c>
       <c r="D5" t="n">
-        <v>173.384789767114</v>
+        <v>173.3848049238756</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222540410346</v>
+        <v>174.4222692884882</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394632757571458</v>
+        <v>-0.002394458551239653</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545654296875</v>
+        <v>177.5545806884766</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1530884388983</v>
+        <v>178.1531037491236</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811681643912</v>
+        <v>170.781182841084</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877223514448</v>
+        <v>172.1877371490149</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720198593724254</v>
+        <v>0.0172019844334983</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531723371234</v>
+        <v>0.01022523041638013</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538757324219</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141646735497</v>
+        <v>177.714180280125</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7263967599338</v>
+        <v>172.7264119284913</v>
       </c>
       <c r="E11" t="n">
-        <v>177.674269227683</v>
+        <v>177.6742848307548</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324652152828622</v>
+        <v>-0.03324643662953308</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622131347656</v>
+        <v>170.3621978759766</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583050821389</v>
+        <v>171.9582896803931</v>
       </c>
       <c r="D12" t="n">
-        <v>166.810924534394</v>
+        <v>166.8109095936823</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841224963229</v>
+        <v>169.5841073072249</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0195199248555431</v>
+        <v>-0.01952009877813865</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026062011719</v>
+        <v>170.2025909423828</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882358353705</v>
+        <v>171.9882204164984</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668725173688</v>
+        <v>168.4668574141896</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415322614545</v>
+        <v>170.6415169633154</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368681625865349</v>
+        <v>-0.0009368682464988565</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400512695312</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.439558941325</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955557135668</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527215200144</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095353599539832</v>
+        <v>0.006095533447482593</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703007595174933</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982696533203</v>
+        <v>167.8982391357422</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417962304089</v>
+        <v>170.5417652323373</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406265749079</v>
+        <v>166.9405962313932</v>
       </c>
       <c r="E16" t="n">
-        <v>167.140134281122</v>
+        <v>167.1401039013443</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723660107302521</v>
+        <v>0.007723476941117413</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422698974609</v>
+        <v>170.3422546386719</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617329363479</v>
+        <v>170.5617176578999</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332114851899</v>
+        <v>166.3320999523285</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763569906099</v>
+        <v>168.6763418810487</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643497212367</v>
+        <v>0.01455652849910916</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512319332802</v>
+        <v>0.03847512663982333</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008460227399664788</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668914997253303</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947256518719</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187866210938</v>
+        <v>175.8187561035156</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767318043244</v>
+        <v>176.6767011378293</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466271367534</v>
+        <v>172.5465971871373</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641783462465</v>
+        <v>173.5641482200099</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494055886175818</v>
+        <v>0.03494037922293813</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439756788046976</v>
+        <v>0.002439930785601563</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711578369141</v>
+        <v>183.1711730957031</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089135963474</v>
+        <v>184.1089289332547</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924356467209</v>
+        <v>174.2924501658818</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810218455756</v>
+        <v>174.8810364137678</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928229701524732</v>
+        <v>0.0392823835910463</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035400390625</v>
+        <v>178.0035247802734</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9840093083128</v>
+        <v>181.9839937083107</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888599052367</v>
+        <v>175.7888448362941</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350878652714</v>
+        <v>181.5350723037516</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821196229186118</v>
+        <v>-0.02821212654859018</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470275878906</v>
+        <v>176.5470428466797</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3503245099793</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807727171775</v>
+        <v>174.9807878405966</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403383898065</v>
+        <v>179.3403538900187</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.008182320745567351</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2652893066406</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291385988617</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7161910154847</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629551235593</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387491782843</v>
+        <v>0.004068387140155894</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641296386719</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403552769049</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5119112725463</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441731762758</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002814089176637058</v>
+        <v>0.002813916776754244</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153594970703</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602146114836</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890176259668</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987400973632</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053974480577181</v>
+        <v>0.02053991824341894</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041378766245</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.7924957275391</v>
+        <v>186.79248046875</v>
       </c>
       <c r="C33" t="n">
-        <v>187.690338609038</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604668683245</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972757932568</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0035374073593748</v>
+        <v>0.003537325381961498</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385528564453</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="C34" t="n">
-        <v>190.593394116267</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105347272827</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E34" t="n">
-        <v>189.1468626563914</v>
+        <v>189.146847340247</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223009789566</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715545654297</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050110254035</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369182511207</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378093314507</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.00672366812316183</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965270996094</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7824902019781</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918178290645</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566294029491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108615148198644</v>
+        <v>-0.01108631362422263</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694780736732239</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097412109375</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="C39" t="n">
-        <v>194.8332119113436</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033405552435</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705422839889</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829618052309101</v>
+        <v>0.01829626140377161</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1404,7 +1404,7 @@
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886535894656951</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754425048828</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419301869027</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944368108431</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101030171288664</v>
+        <v>0.01101038676736099</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755442021748715</v>
+        <v>0.007755357241106875</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246398925781</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925557149365</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602938591047</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988793025541</v>
+        <v>179.988777912505</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042837577039868</v>
+        <v>0.01042829092822517</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250748267812286</v>
+        <v>0.02250765250109055</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323333740234</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="C51" t="n">
-        <v>191.5411089646758</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D51" t="n">
-        <v>187.9796341631504</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359184602369</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807902404094098</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981990486196963</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989595999882533</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050750732422</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672637579894</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286166610889</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596680014167</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004440999182711</v>
+        <v>-0.02004441147263381</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971455471800998</v>
+        <v>-0.001971380233034448</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434387207031</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4350026612236</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847643800754</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949275919373</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751478380745641</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.03652478060097764</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7002868652344</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8698939350823</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823816093971</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580548583195</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003720555463071484</v>
+        <v>0.0003722182238108385</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742797851562</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="C61" t="n">
-        <v>199.462152104167</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268412779572</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436938260565</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793274534380033</v>
+        <v>0.05793257804752372</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959067030875928</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133911132812</v>
+        <v>186.4134063720703</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824463944715</v>
+        <v>190.9824620272586</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105907203728</v>
+        <v>183.4106057333689</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933791327836</v>
+        <v>190.5933947337238</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581012967027952</v>
+        <v>-0.03581005074692667</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154693603516</v>
+        <v>189.7154846191406</v>
       </c>
       <c r="C65" t="n">
-        <v>190.553458007553</v>
+        <v>190.5534733337414</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1483942490048</v>
+        <v>180.1484087383153</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229435613052</v>
+        <v>182.4229582335574</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0177137394870075</v>
+        <v>0.01771373803705711</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540222167969</v>
+        <v>186.1540374755859</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482800008962</v>
+        <v>188.5482954559393</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794727552066</v>
+        <v>183.879487827554</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255230789849</v>
+        <v>185.5255382862568</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877257113277342</v>
+        <v>-0.01877256962289819</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.926513671875</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.358293814419</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2205942185541</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9416897271721</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808163091331894</v>
+        <v>-0.02808162861150654</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0741882324219</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109817403353</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D68" t="n">
-        <v>182.39300555425</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483122805645</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174240124138</v>
+        <v>0.02845174000170858</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152471782905131</v>
+        <v>-0.03152479724769053</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524536132812</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188702156436</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166628687019</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E70" t="n">
-        <v>180.806813452001</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743162817541062</v>
+        <v>-0.009743078144453632</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1136779785156</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614042749852</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0581789881563</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0609943264491</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051661128715887</v>
+        <v>0.02051643852050034</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341879937998</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447659257062</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E72" t="n">
-        <v>174.491955735681</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067635257405</v>
+        <v>-0.02591051094922314</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159873604817</v>
+        <v>0.01372159755577274</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808484361385299</v>
+        <v>-0.01808492693090802</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263061523438</v>
+        <v>181.0262908935547</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162648499111</v>
+        <v>185.2162492379485</v>
       </c>
       <c r="D76" t="n">
-        <v>179.569788944198</v>
+        <v>179.5697738081794</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255769560617</v>
+        <v>181.325561672047</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559426101467649</v>
+        <v>0.008559341089538375</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2292,7 +2292,7 @@
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030535058927451</v>
+        <v>-0.01030526716745872</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841613769531</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2289086763207</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876631773748</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4607020047171</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289519918164731</v>
+        <v>-0.005289603321452563</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721400043751253</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125830460996126</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2421,22 +2421,22 @@
         <v>46002</v>
       </c>
       <c r="B83" t="n">
-        <v>180.5075988769531</v>
+        <v>180.5076141357422</v>
       </c>
       <c r="C83" t="n">
-        <v>180.8967030087509</v>
+        <v>180.896718300432</v>
       </c>
       <c r="D83" t="n">
-        <v>176.2076633109278</v>
+        <v>176.2076782062319</v>
       </c>
       <c r="E83" t="n">
-        <v>179.8591224369562</v>
+        <v>179.8591376409278</v>
       </c>
       <c r="F83" t="n">
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550770804044477</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2460,7 +2460,7 @@
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266451936799664</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682952880859</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8880102762506</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4730132178061</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428571096804</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005069689074391</v>
+        <v>0.03005061362821149</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.003171176350336591</v>
+        <v>-0.00317109577323571</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021881103516</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5488153175326</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4936115238563</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005661647843</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612757568446812</v>
+        <v>-0.003612838827051545</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545538552702456</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808319091797</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779786425506</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154296257417</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123337767646</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386553447189375</v>
+        <v>-0.00386561545941666</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8029022216797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213860539245</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838845193456</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752439930999</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780243029006</v>
+        <v>-0.004677780623340899</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987081691657185</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080017089844</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074824738404</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685072554968</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152196030920583</v>
+        <v>-0.02152187943302564</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009726849758688871</v>
+        <v>-0.0009727675505442068</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.376220703125</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708543554723</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718432388734</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5681140987238</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.004704210650191332</v>
+        <v>0.00470412795042785</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2964,7 +2964,7 @@
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436954843994676</v>
+        <v>-0.01436946731018618</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.654296875</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438168415518142</v>
+        <v>-0.04381675942490471</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948280612693632</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.03466796875</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784751839824</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D112" t="n">
-        <v>185.5557928402329</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230595290241</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.006394234985120373</v>
+        <v>-0.00639415348837058</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099379525930511</v>
+        <v>0.01099371233637481</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728759765625</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009400606663</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3967902384632</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E114" t="n">
-        <v>190.823459633995</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591334872193784</v>
+        <v>0.01591342985123156</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169239280915949</v>
+        <v>0.00516915900963677</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3261,22 +3261,22 @@
         <v>46056</v>
       </c>
       <c r="B118" t="n">
-        <v>179.9189758300781</v>
+        <v>179.9189910888672</v>
       </c>
       <c r="C118" t="n">
-        <v>185.8351396091497</v>
+        <v>185.835155369684</v>
       </c>
       <c r="D118" t="n">
-        <v>175.8185703987175</v>
+        <v>175.8185853097543</v>
       </c>
       <c r="E118" t="n">
-        <v>185.8052108647954</v>
+        <v>185.8052266227915</v>
       </c>
       <c r="F118" t="n">
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839291451472381</v>
+        <v>-0.02839283211347909</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3300,7 +3300,7 @@
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0341021289659974</v>
+        <v>-0.03410221088304122</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963439941406</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2079034382237</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205647824287</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298386502086</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.024971658454912</v>
+        <v>0.02497157596478594</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893114950312197</v>
+        <v>-0.007893035105149604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063385009766</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088363522974</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D124" t="n">
-        <v>188.3293278304631</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007297023972</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800904593061702</v>
+        <v>0.008008964809924857</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5036010742188</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="C125" t="n">
-        <v>193.158028491682</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745969700116</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793806436633</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410180845216</v>
+        <v>-0.01636410312537218</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209282728038808</v>
+        <v>-0.02209274727292232</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181569032381558</v>
+        <v>0.01181560666047221</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613189697266</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900804037161</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D129" t="n">
-        <v>185.226558259481</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E129" t="n">
-        <v>186.6232837033845</v>
+        <v>186.62329889396</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004256064912840918</v>
+        <v>-0.0004255251289267958</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3564,7 +3564,7 @@
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833524412785</v>
+        <v>0.01021825301539225</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637238018573</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682301224481</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E135" t="n">
-        <v>180.82685580423</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164645489360941</v>
+        <v>-0.04164637217148226</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539703369141</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0316933488174</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322775806792</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014088918714</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486500292533</v>
+        <v>0.02985486242594537</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3732,7 +3732,7 @@
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331638712945649</v>
+        <v>-0.01331646982798718</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126861572266</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2688145383873</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396472340209</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187649948852</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660639760928495</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638910718471109</v>
+        <v>0.001638994413631911</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010789985650675</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3813,22 +3813,22 @@
         <v>46090</v>
       </c>
       <c r="B141" t="n">
-        <v>182.2235870361328</v>
+        <v>182.2236022949219</v>
       </c>
       <c r="C141" t="n">
-        <v>182.4829897940845</v>
+        <v>182.4830050745951</v>
       </c>
       <c r="D141" t="n">
-        <v>175.1501427003192</v>
+        <v>175.1501573668019</v>
       </c>
       <c r="E141" t="n">
-        <v>176.4171820751478</v>
+        <v>176.4171968477281</v>
       </c>
       <c r="F141" t="n">
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716221787178097</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3852,7 +3852,7 @@
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690076858506</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -7137,12 +7137,36 @@
         <v>222.0800018310547</v>
       </c>
       <c r="F279" t="n">
-        <v>77305200</v>
+        <v>77469900</v>
       </c>
       <c r="G279" t="n">
         <v>-0.004123953254555501</v>
       </c>
       <c r="H279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B280" t="n">
+        <v>225.0700073242188</v>
+      </c>
+      <c r="C280" t="n">
+        <v>226.9400024414062</v>
+      </c>
+      <c r="D280" t="n">
+        <v>223.1300048828125</v>
+      </c>
+      <c r="E280" t="n">
+        <v>225.1300048828125</v>
+      </c>
+      <c r="F280" t="n">
+        <v>89808400</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0.002181875007431389</v>
+      </c>
+      <c r="H280" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701171875</v>
+        <v>179.3701324462891</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4649859155824</v>
+        <v>181.4650013525793</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380531425805</v>
+        <v>176.1380681264219</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9136974002478</v>
+        <v>177.913712535141</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022523041638013</v>
+        <v>0.01022531635496304</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -636,7 +636,7 @@
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090045256567307</v>
+        <v>0.0109003665696572</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187561035156</v>
+        <v>175.8187713623047</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767011378293</v>
+        <v>176.6767164710769</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5465971871373</v>
+        <v>172.5466121619453</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641482200099</v>
+        <v>173.5641632831282</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494037922293813</v>
+        <v>0.03494046904234804</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439930785601563</v>
+        <v>0.00243984378681672</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035247802734</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9839937083107</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888448362941</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350723037516</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821212654859018</v>
+        <v>-0.02821204324514892</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1116,7 +1116,7 @@
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182320745567351</v>
+        <v>-0.008182405765993161</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153747558594</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602300506758</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890327563757</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987552370008</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053991824341894</v>
+        <v>0.02053983240613322</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041378766245</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699188232422</v>
+        <v>187.8699340820312</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556339904095</v>
+        <v>189.6556493942343</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155586605101</v>
+        <v>185.5155737280782</v>
       </c>
       <c r="E41" t="n">
-        <v>187.52074924116</v>
+        <v>187.5207644715895</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817212858411589</v>
+        <v>0.02817221209222476</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402089854789248</v>
+        <v>-0.04402097619247958</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136779785156</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614042749852</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581789881563</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0609943264491</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051643852050034</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2172,7 +2172,7 @@
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591051094922314</v>
+        <v>-0.0259105925654145</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0262908935547</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162492379485</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D76" t="n">
-        <v>179.5697738081794</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E76" t="n">
-        <v>181.325561672047</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559341089538375</v>
+        <v>0.008559426101467649</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526716745872</v>
+        <v>-0.01030543487972591</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116053693065423</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545806884766</v>
+        <v>177.5545959472656</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531037491236</v>
+        <v>178.1531190593489</v>
       </c>
       <c r="D6" t="n">
-        <v>170.781182841084</v>
+        <v>170.7811975177769</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877371490149</v>
+        <v>172.1877519465851</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0172019844334983</v>
+        <v>0.01720207185039535</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531635496304</v>
+        <v>0.01022522953763838</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.15576171875</v>
+        <v>181.1557464599609</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435839210746</v>
+        <v>182.0435685875041</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618774176739</v>
+        <v>178.6618623689453</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348217819195</v>
+        <v>181.5348064912021</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009351750270146786</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874514497031027</v>
+        <v>-0.00787451516030313</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="C11" t="n">
-        <v>177.714180280125</v>
+        <v>177.7141958867003</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264119284913</v>
+        <v>172.7264270970488</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6742848307548</v>
+        <v>177.6743004338266</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643662953308</v>
+        <v>-0.03324626965459365</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3621978759766</v>
+        <v>170.3622131347656</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9582896803931</v>
+        <v>171.9583050821389</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109095936823</v>
+        <v>166.810924534394</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841073072249</v>
+        <v>169.5841224963229</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952009877813865</v>
+        <v>-0.01952009706391489</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2025909423828</v>
+        <v>170.2026062011719</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882204164984</v>
+        <v>171.9882358353705</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668574141896</v>
+        <v>168.4668725173688</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415169633154</v>
+        <v>170.6415322614545</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368682464988565</v>
+        <v>-0.0009368681625865349</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400817871094</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.4395894944585</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955858311417</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527518438138</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095533447482593</v>
+        <v>0.006095532901013501</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114196777344</v>
+        <v>166.6114044189453</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164970921864</v>
+        <v>168.6164816497661</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686393698748</v>
+        <v>163.6686243805947</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189434134908</v>
+        <v>167.6189280624296</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016265075109</v>
+        <v>-0.02703033845731617</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982391357422</v>
+        <v>167.8982543945312</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417652323373</v>
+        <v>170.5417807313731</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9405962313932</v>
+        <v>166.9406114031506</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401039013443</v>
+        <v>167.1401190912332</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723476941117413</v>
+        <v>0.007723660814659139</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455652849910916</v>
+        <v>0.01455643629502945</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465362548828</v>
+        <v>176.7465515136719</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491035140756</v>
+        <v>179.8491190407138</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0581830190845</v>
+        <v>176.058198218447</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505315119071</v>
+        <v>179.2505469868697</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460227399664788</v>
+        <v>-0.0008459364815304182</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731541223449</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028283464474</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451359862166</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003669001328727717</v>
+        <v>0.003668828349043585</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807076698219</v>
+        <v>-0.0003936947256518719</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620208740234</v>
+        <v>174.4620361328125</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757538913052</v>
+        <v>177.0757693786965</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632159334845</v>
+        <v>173.9632311486472</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769489507663</v>
+        <v>176.5769643945311</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614620612602058</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624663238682878</v>
+        <v>-0.02624671755319263</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711730957031</v>
+        <v>183.171142578125</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089289332547</v>
+        <v>184.10889825944</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924501658818</v>
+        <v>174.29242112756</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810364137678</v>
+        <v>174.8810072773835</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0392823835910463</v>
+        <v>0.03928221043944835</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204324514892</v>
+        <v>-0.0282118813385599</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470428466797</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503245099793</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807878405966</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403538900187</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182405765993161</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1140,7 +1140,7 @@
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387140155894</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813916776754244</v>
+        <v>0.002813830697929731</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153594970703</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602146114836</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890176259668</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987400973632</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053983240613322</v>
+        <v>0.020540005843803</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041378766245</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385375976562</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="C34" t="n">
-        <v>190.59337868299</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105195355423</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E34" t="n">
-        <v>189.146847340247</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812305418101074</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723587148282584</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199532691778505</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626140377161</v>
+        <v>0.01829634376427292</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699340820312</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556493942343</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155737280782</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207644715895</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817221209222476</v>
+        <v>0.02817204507600701</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402097619247958</v>
+        <v>-0.04402082090329285</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820892333984</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599908268075</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493465774322</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755357241106875</v>
+        <v>0.007755441369297289</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590696970089</v>
+        <v>-0.003165673913464562</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250765250109055</v>
+        <v>0.02250756853454439</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807902404094098</v>
+        <v>0.02807910846500516</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989595999882533</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050598144531</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672482532724</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286015136062</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596525726598</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004441147263381</v>
+        <v>-0.02004440999182711</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729406961805</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870481318289</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565693232556</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971380233034448</v>
+        <v>-0.001971530859184778</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1788,7 +1788,7 @@
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168005119548289</v>
+        <v>0.02168012836941968</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434234619141</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4349867997753</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847491650603</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949120548774</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751478380745641</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304626464844</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476539294223</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345289438528</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505251524069</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652478060097764</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003722182238108385</v>
+        <v>0.0003721368699238781</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4134063720703</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824620272586</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4106057333689</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933947337238</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005074692667</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154846191406</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="C65" t="n">
-        <v>190.5534733337414</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1484087383153</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229582335574</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771373803705711</v>
+        <v>0.0177137394870075</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540374755859</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482954559393</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D66" t="n">
-        <v>183.879487827554</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255382862568</v>
+        <v>185.525507871713</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877256962289819</v>
+        <v>-0.01877265156263563</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2052,7 +2052,7 @@
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808162861150654</v>
+        <v>-0.02808146927787025</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2085,22 +2085,22 @@
         <v>45981</v>
       </c>
       <c r="B69" t="n">
-        <v>180.208251953125</v>
+        <v>180.2082672119141</v>
       </c>
       <c r="C69" t="n">
-        <v>195.5315406452363</v>
+        <v>195.5315572014955</v>
       </c>
       <c r="D69" t="n">
-        <v>179.4201468289569</v>
+        <v>179.4201620210147</v>
       </c>
       <c r="E69" t="n">
-        <v>195.4816571057099</v>
+        <v>195.4816736577453</v>
       </c>
       <c r="F69" t="n">
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152479724769053</v>
+        <v>-0.0315247152439051</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2124,7 +2124,7 @@
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743078144453632</v>
+        <v>-0.009743161992557425</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.734203281764</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447804748437</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919707447618</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0259105925654145</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159755577274</v>
+        <v>0.01372168475193747</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492693090802</v>
+        <v>-0.01808501178249078</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649711013028865</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607818603516</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139471586436</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.6819333075974</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472262869623</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030543487972591</v>
+        <v>-0.01030526629882311</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053693065423</v>
+        <v>0.02116036298998392</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H280"/>
+  <dimension ref="A1:H281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545959472656</v>
+        <v>177.5545806884766</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531190593489</v>
+        <v>178.1531037491236</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811975177769</v>
+        <v>170.781182841084</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877519465851</v>
+        <v>172.1877371490149</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207185039535</v>
+        <v>0.0172019844334983</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022522953763838</v>
+        <v>0.01022531635496304</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141958867003</v>
+        <v>177.714180280125</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264270970488</v>
+        <v>172.7264119284913</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6743004338266</v>
+        <v>177.6742848307548</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324626965459365</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -732,7 +732,7 @@
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952009706391489</v>
+        <v>-0.01952001095973654</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114044189453</v>
+        <v>166.6114196777344</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164816497661</v>
+        <v>168.6164970921864</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686243805947</v>
+        <v>163.6686393698748</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189280624296</v>
+        <v>167.6189434134908</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703033845731617</v>
+        <v>-0.02703024934973741</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -828,7 +828,7 @@
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723660814659139</v>
+        <v>0.007723568524209856</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422546386719</v>
+        <v>170.3422393798828</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617176578999</v>
+        <v>170.561702379452</v>
       </c>
       <c r="D17" t="n">
-        <v>166.3320999523285</v>
+        <v>166.332085052758</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763418810487</v>
+        <v>168.6763267714875</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643629502945</v>
+        <v>0.01455634541386375</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -876,7 +876,7 @@
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512663982333</v>
+        <v>0.03847521966356759</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465515136719</v>
+        <v>176.7465362548828</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491190407138</v>
+        <v>179.8491035140756</v>
       </c>
       <c r="D19" t="n">
-        <v>176.058198218447</v>
+        <v>176.0581830190845</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505469868697</v>
+        <v>179.2505315119071</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008459364815304182</v>
+        <v>-0.0008460227399664788</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668828349043585</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947256518719</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620361328125</v>
+        <v>174.4620208740234</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757693786965</v>
+        <v>177.0757538913052</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632311486472</v>
+        <v>173.9632159334845</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769643945311</v>
+        <v>176.5769489507663</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614620612602058</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624671755319263</v>
+        <v>-0.02624663238682878</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.171142578125</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="C26" t="n">
-        <v>184.10889825944</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D26" t="n">
-        <v>174.29242112756</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810072773835</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928221043944835</v>
+        <v>0.03928229701524732</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0282118813385599</v>
+        <v>-0.02821196229186118</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153747558594</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602300506758</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890327563757</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987552370008</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.020540005843803</v>
+        <v>0.02053992000650995</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041378766245</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385528564453</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="C34" t="n">
-        <v>190.593394116267</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105347272827</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E34" t="n">
-        <v>189.1468626563914</v>
+        <v>189.146847340247</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812305418101074</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587148282584</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965270996094</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7824902019781</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918178290645</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566294029491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108631362422263</v>
+        <v>-0.0110862321012164</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694780736732239</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829634376427292</v>
+        <v>0.01829626140377161</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886535894656951</v>
+        <v>-0.04886543837402468</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699035644531</v>
+        <v>187.8699340820312</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556185865847</v>
+        <v>189.6556493942343</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155435929421</v>
+        <v>185.5155737280782</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207340107304</v>
+        <v>187.5207644715895</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817204507600701</v>
+        <v>0.02817229795294884</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402082090329285</v>
+        <v>-0.04402097619247958</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491058349609</v>
+        <v>179.84912109375</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015566720687</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375148363812</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070509305708</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485768219622118</v>
+        <v>-0.004857597766183885</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.724609375</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988762799469</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829092822517</v>
+        <v>0.01042812035913343</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250756853454439</v>
+        <v>0.02250773835753361</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323181152344</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="C51" t="n">
-        <v>191.541093665248</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D51" t="n">
-        <v>187.979619148197</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359033209746</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910846500516</v>
+        <v>0.02807910615919784</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981990486196963</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989595999882533</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004440999182711</v>
+        <v>-0.02004433759634028</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855438232422</v>
+        <v>206.3855590820312</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348755139714</v>
+        <v>210.8348911017148</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0686914304077</v>
+        <v>205.0687065918373</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826726752522</v>
+        <v>207.5826880225491</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168012836941968</v>
+        <v>0.02168020390572556</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958816719273994</v>
+        <v>-0.03958823819926593</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.0365248560924305</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003021240234</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699092076593</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823961188316</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580698535366</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721368699238781</v>
+        <v>0.0003721369001874475</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793257804752372</v>
+        <v>0.05793266405042918</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540069580078</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482645458532</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794576828592</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E66" t="n">
-        <v>185.525507871713</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877265156263563</v>
+        <v>-0.01877257113277342</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146927787025</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174000170858</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2085,22 +2085,22 @@
         <v>45981</v>
       </c>
       <c r="B69" t="n">
-        <v>180.2082672119141</v>
+        <v>180.208251953125</v>
       </c>
       <c r="C69" t="n">
-        <v>195.5315572014955</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D69" t="n">
-        <v>179.4201620210147</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E69" t="n">
-        <v>195.4816736577453</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="F69" t="n">
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.0315247152439051</v>
+        <v>-0.03152479724769053</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2124,7 +2124,7 @@
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743161992557425</v>
+        <v>-0.009743078144453632</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.02051660953286172</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341879937998</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447659257062</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E72" t="n">
-        <v>174.491955735681</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067635257405</v>
+        <v>-0.02591067418159221</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291625976562</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728380763597</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140014756398</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958985688627</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372168475193747</v>
+        <v>0.01372151153989076</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808501178249078</v>
+        <v>-0.01808484361385299</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899749755859</v>
+        <v>179.4899597167969</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690716163194</v>
+        <v>179.8690563253026</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648835948944</v>
+        <v>173.2648688653124</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3423041351479</v>
+        <v>174.3422893139723</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649702371590833</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263061523438</v>
+        <v>181.0263214111328</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162648499111</v>
+        <v>185.2162804618737</v>
       </c>
       <c r="D76" t="n">
-        <v>179.569788944198</v>
+        <v>179.5698040802165</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255769560617</v>
+        <v>181.3255922400764</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559426101467649</v>
+        <v>0.008559596852994122</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607818603516</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139471586436</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819333075974</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472262869623</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526629882311</v>
+        <v>-0.0103055183015206</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116036298998392</v>
+        <v>0.02116053693065423</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2421,22 +2421,22 @@
         <v>46002</v>
       </c>
       <c r="B83" t="n">
-        <v>180.5076141357422</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="C83" t="n">
-        <v>180.896718300432</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D83" t="n">
-        <v>176.2076782062319</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E83" t="n">
-        <v>179.8591376409278</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="F83" t="n">
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770804044477</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2460,7 +2460,7 @@
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266451936799664</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814983424509077</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491794177123418</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682800292969</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8879950077845</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4729984678863</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428423541149</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005061362821149</v>
+        <v>0.03005069689074391</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.00317109577323571</v>
+        <v>-0.003171176350336591</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124481201172</v>
+        <v>182.7124633789062</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293738083791</v>
+        <v>184.029389177148</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779146434709</v>
+        <v>180.3779297072971</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8897012556695</v>
+        <v>183.889716612774</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436946731018618</v>
+        <v>-0.01436938499763141</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134974032598635</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.654296875</v>
+        <v>177.6543121337891</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542325986551</v>
+        <v>181.9542482267672</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953640623503</v>
+        <v>177.1953792817215</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753422141945</v>
+        <v>181.4753578011745</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381675942490471</v>
+        <v>-0.0438166772979951</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920440673828</v>
+        <v>182.8920288085938</v>
       </c>
       <c r="C109" t="n">
-        <v>184.9472325313386</v>
+        <v>184.947217101084</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835164834521</v>
+        <v>177.9835016341843</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6320081827799</v>
+        <v>178.6319932794081</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948280612693632</v>
+        <v>0.02948263181397048</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291414334357983</v>
+        <v>0.008291498456701074</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728912353516</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009553855833</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3968053634026</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E114" t="n">
-        <v>190.8234748728661</v>
+        <v>190.823459633995</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591342985123156</v>
+        <v>0.01591334872193784</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.00516915900963677</v>
+        <v>0.005169239280915949</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3261,22 +3261,22 @@
         <v>46056</v>
       </c>
       <c r="B118" t="n">
-        <v>179.9189910888672</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="C118" t="n">
-        <v>185.835155369684</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D118" t="n">
-        <v>175.8185853097543</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E118" t="n">
-        <v>185.8052266227915</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="F118" t="n">
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839283211347909</v>
+        <v>-0.02839291451472381</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3300,7 +3300,7 @@
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221088304122</v>
+        <v>-0.0341021289659974</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771575927734</v>
+        <v>184.9771728515625</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634420291942</v>
+        <v>186.5634574188361</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923963475411</v>
+        <v>174.1924107166939</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775135166603</v>
+        <v>176.2775280578147</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871770419569057</v>
+        <v>0.07871779317924998</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3372,7 +3372,7 @@
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497157596478594</v>
+        <v>0.0249714914147583</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.0998382568359</v>
+        <v>188.099853515625</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306425866914</v>
+        <v>192.0306581643501</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808205923615</v>
+        <v>187.6808358171596</v>
       </c>
       <c r="E123" t="n">
-        <v>190.933219719687</v>
+        <v>190.9332352083219</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893035105149604</v>
+        <v>-0.00789295462474604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3420,7 +3420,7 @@
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.008008964809924857</v>
+        <v>0.00800888303954661</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832092285156</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622623874058</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660562233949</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E126" t="n">
-        <v>187.0423048169314</v>
+        <v>187.042320465516</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209274727292232</v>
+        <v>-0.02209266545793198</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3492,7 +3492,7 @@
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560666047221</v>
+        <v>0.0118155220086027</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3813,22 +3813,22 @@
         <v>46090</v>
       </c>
       <c r="B141" t="n">
-        <v>182.2236022949219</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="C141" t="n">
-        <v>182.4830050745951</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D141" t="n">
-        <v>175.1501573668019</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E141" t="n">
-        <v>176.4171968477281</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="F141" t="n">
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716221787178097</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690076858506</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7161,12 +7161,36 @@
         <v>225.1300048828125</v>
       </c>
       <c r="F280" t="n">
-        <v>89808400</v>
+        <v>89947700</v>
       </c>
       <c r="G280" t="n">
         <v>0.002181875007431389</v>
       </c>
       <c r="H280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B281" t="n">
+        <v>228.8600006103516</v>
+      </c>
+      <c r="C281" t="n">
+        <v>233.2100067138672</v>
+      </c>
+      <c r="D281" t="n">
+        <v>228.0399932861328</v>
+      </c>
+      <c r="E281" t="n">
+        <v>229.75</v>
+      </c>
+      <c r="F281" t="n">
+        <v>141544300</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0.0168391752023771</v>
+      </c>
+      <c r="H281" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H281"/>
+  <dimension ref="A1:H282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709014892578</v>
+        <v>174.9709167480469</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694397588381</v>
+        <v>175.5694550698242</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870566311777</v>
+        <v>168.3870713158056</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414684152183</v>
+        <v>174.741483653999</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366504264196933</v>
+        <v>-0.001366417175785561</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519409179688</v>
+        <v>174.5519256591797</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672421817212</v>
+        <v>176.4672267555024</v>
       </c>
       <c r="D5" t="n">
-        <v>173.3848049238756</v>
+        <v>173.384789767114</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222692884882</v>
+        <v>174.4222540410346</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394458551239653</v>
+        <v>-0.002394632757571458</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -588,7 +588,7 @@
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0172019844334983</v>
+        <v>0.01720207335414736</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253326416016</v>
+        <v>181.3253173828125</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438110385745</v>
+        <v>181.9437957277396</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725671170498</v>
+        <v>178.3725521067403</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195091893087</v>
+        <v>179.6194940740671</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0109003665696572</v>
+        <v>0.01090028150092892</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009352591784613784</v>
+        <v>-0.0009351751057110613</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400817871094</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395894944585</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955858311417</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527518438138</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095532901013501</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703024934973741</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847521966356759</v>
+        <v>0.03847530924081588</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465362548828</v>
+        <v>176.7465515136719</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491035140756</v>
+        <v>179.8491190407138</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0581830190845</v>
+        <v>176.058198218447</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505315119071</v>
+        <v>179.2505469868697</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460227399664788</v>
+        <v>-0.0008460226669898541</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.39501953125</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731541223449</v>
+        <v>178.1731234709029</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028283464474</v>
+        <v>176.0282531820179</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451359862166</v>
+        <v>177.34510547722</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003669001328727717</v>
+        <v>0.00366874201757672</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251647949219</v>
+        <v>177.3251800537109</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225418052247</v>
+        <v>178.4225571584428</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929031464731</v>
+        <v>174.0929181271268</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501343169162</v>
+        <v>175.2501493971494</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807076698219</v>
+        <v>-0.0003935227277223063</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620208740234</v>
+        <v>174.4620361328125</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757538913052</v>
+        <v>177.0757693786965</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632159334845</v>
+        <v>173.9632311486472</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769489507663</v>
+        <v>176.5769643945311</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614629078640273</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624663238682878</v>
+        <v>-0.02624671755319263</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187713623047</v>
+        <v>175.8187866210938</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767164710769</v>
+        <v>176.6767318043244</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466121619453</v>
+        <v>172.5466271367534</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641632831282</v>
+        <v>173.5641783462465</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494046904234804</v>
+        <v>0.03494055886175818</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00243984378681672</v>
+        <v>0.002439756788046976</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715698242188</v>
+        <v>187.1715850830078</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050265070322</v>
+        <v>189.9050419886609</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369333277354</v>
+        <v>184.9369484043502</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378247179256</v>
+        <v>188.7378401044004</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723425742952704</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0110862321012164</v>
+        <v>-0.01108631272043314</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199532691778505</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097564697266</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="C39" t="n">
-        <v>194.833227386451</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033556943829</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705575158363</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626140377161</v>
+        <v>0.01829626288358566</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1404,7 +1404,7 @@
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886543837402468</v>
+        <v>-0.04886536282782095</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699340820312</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556493942343</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155737280782</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207644715895</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817229795294884</v>
+        <v>0.02817213093671711</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402097619247958</v>
+        <v>-0.04402082090329285</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001922607422</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281395182556</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D43" t="n">
-        <v>176.866254560341</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3583147400375</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110936754343372</v>
+        <v>-0.001111021714327642</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754577636719</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419455690647</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944521048813</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038676736099</v>
+        <v>0.01101038770384366</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7821044921875</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6600061588844</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493615830456</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755441369297289</v>
+        <v>0.007755442021748715</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1533,22 +1533,22 @@
         <v>45950</v>
       </c>
       <c r="B46" t="n">
-        <v>182.2034759521484</v>
+        <v>182.2034606933594</v>
       </c>
       <c r="C46" t="n">
-        <v>184.7573549226016</v>
+        <v>184.7573394499357</v>
       </c>
       <c r="D46" t="n">
-        <v>181.2956472677441</v>
+        <v>181.2956320849819</v>
       </c>
       <c r="E46" t="n">
-        <v>182.6923102950553</v>
+        <v>182.6922949953283</v>
       </c>
       <c r="F46" t="n">
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165673913464562</v>
+        <v>-0.003165674177737388</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1572,7 +1572,7 @@
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103334367036585</v>
+        <v>-0.008103251299777958</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.724609375</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925250516066</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602637385785</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988762799469</v>
+        <v>179.988793025541</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042812035913343</v>
+        <v>0.01042829004346624</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250773835753361</v>
+        <v>0.02250748267812286</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910615919784</v>
+        <v>0.02807919058326869</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495300292969</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644582837766</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513320204045</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886067715161</v>
+        <v>192.588592118433</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981974113173093</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989603835835264</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050750732422</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672637579894</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286166610889</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596680014167</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004433759634028</v>
+        <v>-0.02004448386811519</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729250244422</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870329046891</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565537660584</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971530859184778</v>
+        <v>-0.001971380233034448</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855590820312</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348911017148</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0687065918373</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826880225491</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168020390572556</v>
+        <v>0.02168005119548289</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958823819926593</v>
+        <v>-0.03958816719273994</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304626464844</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476539294223</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345289438528</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505251524069</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.0365248560924305</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7002868652344</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8698939350823</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823816093971</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580548583195</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721369001874475</v>
+        <v>0.0003721368699238781</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742645263672</v>
+        <v>198.5742492675781</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621367771523</v>
+        <v>199.4621214501376</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268264223904</v>
+        <v>193.3268115668235</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6436639125443</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793266405042918</v>
+        <v>0.05793249675415924</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983337402344</v>
+        <v>192.6983489990234</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529266552934</v>
+        <v>194.9529420926121</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427786999811</v>
+        <v>190.8427938118383</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935535589016</v>
+        <v>194.6935689756818</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959044433116265</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368072509766</v>
+        <v>193.3368225097656</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218083488666</v>
+        <v>195.4218237722109</v>
       </c>
       <c r="D63" t="n">
-        <v>190.673190567689</v>
+        <v>190.6732056162565</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522164876445</v>
+        <v>195.2522318976041</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331767584859</v>
+        <v>0.003313331505219175</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581012967027952</v>
+        <v>-0.03581020576737093</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540222167969</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482800008962</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794727552066</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255230789849</v>
+        <v>185.525507871713</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877257113277342</v>
+        <v>-0.01877265156263563</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2052,7 +2052,7 @@
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808138730923948</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524688720703</v>
+        <v>178.4524841308594</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188859589464</v>
+        <v>184.1189017022491</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166776199441</v>
+        <v>172.5166923711864</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068289121023</v>
+        <v>180.8068443722038</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743078144453632</v>
+        <v>-0.009742993471366312</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2148,7 +2148,7 @@
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051660953286172</v>
+        <v>0.02051652227239154</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.39501953125</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C72" t="n">
-        <v>177.734203281764</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447804748437</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919707447618</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067418159221</v>
+        <v>-0.0259108417558972</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291778564453</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728535594688</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140165634392</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1959139436215</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372151153989076</v>
+        <v>0.01372185796401415</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808484361385299</v>
+        <v>-0.0180850950995245</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899597167969</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690563253026</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648688653124</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3422893139723</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649702371590833</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263214111328</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162804618737</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D76" t="n">
-        <v>179.5698040802165</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255922400764</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559596852994122</v>
+        <v>0.008559426101467649</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.0103055183015206</v>
+        <v>-0.01030535058927451</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.9518890380859</v>
+        <v>182.951904296875</v>
       </c>
       <c r="C78" t="n">
-        <v>184.089227004522</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398751387779</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1959881613664</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053693065423</v>
+        <v>0.02116053512845051</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841461181641</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2288932293168</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876480440623</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4606866221248</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289603321452563</v>
+        <v>-0.00528960288028224</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721400043751253</v>
+        <v>0.01721391514737669</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864265695677</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920356049676</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E81" t="n">
-        <v>185.12679644575</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125830460996126</v>
+        <v>-0.003125748033105724</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509674072266</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469957406681</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150239281505</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5381918075859</v>
+        <v>184.538176449994</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433411769608655</v>
+        <v>-0.006433576610347602</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770933102352</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114196777344</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3932136047752</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123443447362</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871989054384</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266452212921567</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256189498619836</v>
+        <v>0.007256277519845034</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3050994873047</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733061224419</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916756985292</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485012773324</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111661183153096</v>
+        <v>0.008111747940743541</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814991702143256</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2589,22 +2589,22 @@
         <v>46013</v>
       </c>
       <c r="B90" t="n">
-        <v>183.2611694335938</v>
+        <v>183.2611541748047</v>
       </c>
       <c r="C90" t="n">
-        <v>183.7300734141942</v>
+        <v>183.730058116363</v>
       </c>
       <c r="D90" t="n">
-        <v>181.9243013805983</v>
+        <v>181.9242862331203</v>
       </c>
       <c r="E90" t="n">
-        <v>183.4906282252173</v>
+        <v>183.4906129473229</v>
       </c>
       <c r="F90" t="n">
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.014917857266596</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2628,7 +2628,7 @@
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005069689074391</v>
+        <v>0.03005078265538064</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2661,22 +2661,22 @@
         <v>46017</v>
       </c>
       <c r="B93" t="n">
-        <v>190.085205078125</v>
+        <v>190.0851898193359</v>
       </c>
       <c r="C93" t="n">
-        <v>192.240166195598</v>
+        <v>192.2401507638228</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5611125998212</v>
+        <v>187.5610975436497</v>
       </c>
       <c r="E93" t="n">
-        <v>189.4766285187414</v>
+        <v>189.4766133088049</v>
       </c>
       <c r="F93" t="n">
         <v>139740300</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01017978755564442</v>
+        <v>0.01017970646506039</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>120006100</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.01212409563967642</v>
+        <v>-0.01212401633949489</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646057128906</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151249886817</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546345387688</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E96" t="n">
-        <v>189.1274459397885</v>
+        <v>189.127461449755</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545375898472038</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2757,22 +2757,22 @@
         <v>46024</v>
       </c>
       <c r="B97" t="n">
-        <v>188.4091339111328</v>
+        <v>188.4091186523438</v>
       </c>
       <c r="C97" t="n">
-        <v>192.4795957147097</v>
+        <v>192.479580126264</v>
       </c>
       <c r="D97" t="n">
-        <v>187.8204997023152</v>
+        <v>187.8204844911982</v>
       </c>
       <c r="E97" t="n">
-        <v>189.3968130035911</v>
+        <v>189.3967976648124</v>
       </c>
       <c r="F97" t="n">
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0126006135839718</v>
+        <v>0.01260044853460296</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808166503906</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779629368336</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154145267434</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123182227279</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386561545941666</v>
+        <v>-0.003865453797424312</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780623340899</v>
+        <v>-0.004677861544826856</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2829,22 +2829,22 @@
         <v>46029</v>
       </c>
       <c r="B100" t="n">
-        <v>188.6685180664062</v>
+        <v>188.6685028076172</v>
       </c>
       <c r="C100" t="n">
-        <v>190.9232365533545</v>
+        <v>190.9232211122124</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1244680675316</v>
+        <v>186.1244530144955</v>
       </c>
       <c r="E100" t="n">
-        <v>188.1297854095839</v>
+        <v>188.1297701943655</v>
       </c>
       <c r="F100" t="n">
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987164191344933</v>
+        <v>0.00998708250744107</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2868,7 +2868,7 @@
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152187943302564</v>
+        <v>-0.02152180029744644</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.3762054443359</v>
+        <v>185.376220703125</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708389078061</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718281779948</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5680989064521</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.00470412795042785</v>
+        <v>0.004704210650191332</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124633789062</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="C105" t="n">
-        <v>184.029389177148</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779297072971</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E105" t="n">
-        <v>183.889716612774</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436938499763141</v>
+        <v>-0.01436954843994676</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974032598635</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952423095703</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="C107" t="n">
-        <v>189.9954207742267</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455985734289</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385950815971</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849373637116</v>
+        <v>-0.004383931140514608</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6543121337891</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542482267672</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953792817215</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753578011745</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438166772979951</v>
+        <v>-0.04381676302343995</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920288085938</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="C109" t="n">
-        <v>184.947217101084</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835016341843</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6319932794081</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948263181397048</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291498456701074</v>
+        <v>0.008291414334357983</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728759765625</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009400606663</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3967902384632</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E114" t="n">
-        <v>190.823459633995</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591334872193784</v>
+        <v>0.01591342985123156</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3189,22 +3189,22 @@
         <v>46051</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0605773925781</v>
+        <v>192.0605621337891</v>
       </c>
       <c r="C115" t="n">
-        <v>193.0283141326731</v>
+        <v>193.0282987969995</v>
       </c>
       <c r="D115" t="n">
-        <v>185.6256380470483</v>
+        <v>185.625623299501</v>
       </c>
       <c r="E115" t="n">
-        <v>190.8933105997472</v>
+        <v>190.8932954336949</v>
       </c>
       <c r="F115" t="n">
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169239280915949</v>
+        <v>0.005169079151165157</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3213,22 +3213,22 @@
         <v>46052</v>
       </c>
       <c r="B116" t="n">
-        <v>190.6838073730469</v>
+        <v>190.6837921142578</v>
       </c>
       <c r="C116" t="n">
-        <v>194.0359639826301</v>
+        <v>194.0359484555967</v>
       </c>
       <c r="D116" t="n">
-        <v>189.0276790286862</v>
+        <v>189.0276639024229</v>
       </c>
       <c r="E116" t="n">
-        <v>190.7636224379378</v>
+        <v>190.7636071727618</v>
       </c>
       <c r="F116" t="n">
         <v>179489500</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.007168415497976421</v>
+        <v>-0.00716841606749119</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766815185547</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557348322644</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4483900153819</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629659025267</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888093084756926</v>
+        <v>-0.0288807731158095</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839291451472381</v>
+        <v>-0.02839299457635047</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833557128906</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="C119" t="n">
-        <v>179.1607721437711</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086795929406</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410571553003</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0341021289659974</v>
+        <v>-0.03410221377522338</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787445068359</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4072143255947</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307227747363</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5216119878791</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.0132614035251003</v>
+        <v>-0.01326140468949821</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771728515625</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634574188361</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1924107166939</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775280578147</v>
+        <v>176.277498975506</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871779317924998</v>
+        <v>0.0787177112002726</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3372,7 +3372,7 @@
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0249714914147583</v>
+        <v>0.02497166051482758</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.099853515625</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306581643501</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808358171596</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E123" t="n">
-        <v>190.9332352083219</v>
+        <v>190.933219719687</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.00789295462474604</v>
+        <v>-0.007893035105149604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063232421875</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088208357837</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D124" t="n">
-        <v>188.329312674443</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007142509167</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800888303954661</v>
+        <v>0.00800904593061702</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410312537218</v>
+        <v>-0.01636418228460701</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130808403767</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7616860728079</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3256935584433</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0118155220086027</v>
+        <v>0.01181560567193918</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627283983140582</v>
+        <v>0.01627275579951704</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028137207031</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972046328596</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374116308485</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531547742145</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113849147715847</v>
+        <v>0.009113929721387581</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786827395534711</v>
+        <v>0.006786747007672789</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126708984375</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2687991412151</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396322236537</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187499528396</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660639760928495</v>
+        <v>0.01660648255510222</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119720458984</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6302923567135</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647274492447</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470399397241</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638994413631911</v>
+        <v>0.00163899427668035</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048614501953</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333155363547</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.4071960911633</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420134514761</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010806418782519</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716230855539603</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7185,12 +7185,36 @@
         <v>229.75</v>
       </c>
       <c r="F281" t="n">
-        <v>141544300</v>
+        <v>142344300</v>
       </c>
       <c r="G281" t="n">
         <v>0.0168391752023771</v>
       </c>
       <c r="H281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B282" t="n">
+        <v>227.2100067138672</v>
+      </c>
+      <c r="C282" t="n">
+        <v>232.8200073242188</v>
+      </c>
+      <c r="D282" t="n">
+        <v>227.0299987792969</v>
+      </c>
+      <c r="E282" t="n">
+        <v>230.9700012207031</v>
+      </c>
+      <c r="F282" t="n">
+        <v>101203000</v>
+      </c>
+      <c r="G282" t="n">
+        <v>-0.007209621131189281</v>
+      </c>
+      <c r="H282" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701324462891</v>
+        <v>179.3701171875</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650013525793</v>
+        <v>181.4649859155824</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380681264219</v>
+        <v>176.1380531425805</v>
       </c>
       <c r="E7" t="n">
-        <v>177.913712535141</v>
+        <v>177.9136974002478</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531635496304</v>
+        <v>0.01022523041638013</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253173828125</v>
+        <v>181.3253326416016</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9437957277396</v>
+        <v>181.9438110385745</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725521067403</v>
+        <v>178.3725671170498</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6194940740671</v>
+        <v>179.6195091893087</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090028150092892</v>
+        <v>0.01090045256567307</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009351751057110613</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538909912109</v>
+        <v>173.7538757324219</v>
       </c>
       <c r="C11" t="n">
-        <v>177.714180280125</v>
+        <v>177.7141646735497</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264119284913</v>
+        <v>172.7263967599338</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6742848307548</v>
+        <v>177.674269227683</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635455335401</v>
+        <v>-0.03324643945211436</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622131347656</v>
+        <v>170.3622283935547</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583050821389</v>
+        <v>171.9583204838847</v>
       </c>
       <c r="D12" t="n">
-        <v>166.810924534394</v>
+        <v>166.8109394751057</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841224963229</v>
+        <v>169.5841376854209</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952001095973654</v>
+        <v>-0.01951983703713334</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368681625865349</v>
+        <v>-0.0009369576454122397</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982543945312</v>
+        <v>167.8982696533203</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417807313731</v>
+        <v>170.5417962304089</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406114031506</v>
+        <v>166.9406265749079</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401190912332</v>
+        <v>167.140134281122</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723568524209856</v>
+        <v>0.007723660107302521</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422393798828</v>
+        <v>170.3422546386719</v>
       </c>
       <c r="C17" t="n">
-        <v>170.561702379452</v>
+        <v>170.5617176578999</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332085052758</v>
+        <v>166.3320999523285</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763267714875</v>
+        <v>168.6763418810487</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634541386375</v>
+        <v>0.01455634409096618</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -876,7 +876,7 @@
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847530924081588</v>
+        <v>0.03847521621706362</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465515136719</v>
+        <v>176.7465362548828</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491190407138</v>
+        <v>179.8491035140756</v>
       </c>
       <c r="D19" t="n">
-        <v>176.058198218447</v>
+        <v>176.0581830190845</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505469868697</v>
+        <v>179.2505315119071</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460226669898541</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3949890136719</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731234709029</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.0282531820179</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.34510547722</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00366874201757672</v>
+        <v>0.003668914997253303</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251800537109</v>
+        <v>177.3251495361328</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225571584428</v>
+        <v>178.4225264520066</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929181271268</v>
+        <v>174.0928881658194</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501493971494</v>
+        <v>175.250119236683</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003935227277223063</v>
+        <v>-0.0003937807415412831</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620361328125</v>
+        <v>174.4620208740234</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757693786965</v>
+        <v>177.0757538913052</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632311486472</v>
+        <v>173.9632159334845</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769643945311</v>
+        <v>176.5769489507663</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629078640273</v>
+        <v>-0.01614620751539797</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624671755319263</v>
+        <v>-0.02624663238682878</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477416992188</v>
+        <v>176.2477264404297</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543753314711</v>
+        <v>177.6543599509016</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612974471592</v>
+        <v>174.7612823170602</v>
       </c>
       <c r="E25" t="n">
-        <v>175.349898865447</v>
+        <v>175.3498836843894</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439756788046976</v>
+        <v>0.002439670001024075</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711578369141</v>
+        <v>183.1711730957031</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089135963474</v>
+        <v>184.1089289332547</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924356467209</v>
+        <v>174.2924501658818</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810218455756</v>
+        <v>174.8810364137678</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928229701524732</v>
+        <v>0.03928247356775705</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821196229186118</v>
+        <v>-0.02821204324514892</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470275878906</v>
+        <v>176.5470123291016</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3502935078314</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807727171775</v>
+        <v>174.9807575937583</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403383898065</v>
+        <v>179.3403228895943</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.008182577209651543</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653045654297</v>
+        <v>177.2653198242188</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291540783439</v>
+        <v>179.8291695578261</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162058826927</v>
+        <v>172.7162207499007</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629701066951</v>
+        <v>174.062985089831</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068473920816773</v>
+        <v>0.004068647130534231</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7640991210938</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403244887289</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118813132914</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441426621237</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830697929731</v>
+        <v>0.002813830455718369</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053992000650995</v>
+        <v>0.02053983240613322</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340637207031</v>
+        <v>186.1340484619141</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022276338177</v>
+        <v>186.9022123120565</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462469572146</v>
+        <v>181.0462321155116</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448190078555</v>
+        <v>181.6448041170831</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041597539022</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.79248046875</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="C33" t="n">
-        <v>187.6903232769056</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604518817237</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972606974542</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537325381961498</v>
+        <v>0.003537489626782131</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812141321341782</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715850830078</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050419886609</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369484043502</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378401044004</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723425742952704</v>
+        <v>-0.006723587692724298</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965576171875</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7825209975275</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918479831437</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566599139491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108631272043314</v>
+        <v>-0.01108606995897354</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694945166262119</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886536282782095</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699035644531</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556185865847</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155435929421</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207340107304</v>
+        <v>187.52074924116</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817213093671711</v>
+        <v>0.02817212858411589</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402082090329285</v>
+        <v>-0.04402089854789248</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001770019531</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281238318171</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D43" t="n">
-        <v>176.8662395170747</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3582990595379</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001111021714327642</v>
+        <v>-0.001110936754343372</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1500,7 +1500,7 @@
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038770384366</v>
+        <v>0.01101030171288664</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1533,22 +1533,22 @@
         <v>45950</v>
       </c>
       <c r="B46" t="n">
-        <v>182.2034606933594</v>
+        <v>182.2034759521484</v>
       </c>
       <c r="C46" t="n">
-        <v>184.7573394499357</v>
+        <v>184.7573549226016</v>
       </c>
       <c r="D46" t="n">
-        <v>181.2956320849819</v>
+        <v>181.2956472677441</v>
       </c>
       <c r="E46" t="n">
-        <v>182.6922949953283</v>
+        <v>182.6923102950553</v>
       </c>
       <c r="F46" t="n">
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165674177737388</v>
+        <v>-0.003165590696970089</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1572,7 +1572,7 @@
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103251299777958</v>
+        <v>-0.008103334367036585</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.84912109375</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015721983185</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375297972393</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070662621498</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004857597766183885</v>
+        <v>-0.00485768219622118</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246398925781</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925557149365</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602938591047</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988793025541</v>
+        <v>179.988777912505</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829004346624</v>
+        <v>0.01042829092822517</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250748267812286</v>
+        <v>0.02250765250109055</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807910615919784</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.545166015625</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482921843539</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989603835835264</v>
+        <v>0.02989611444324924</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050598144531</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672482532724</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286015136062</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596525726598</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448386811519</v>
+        <v>-0.02004448238730316</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971380233034448</v>
+        <v>-0.001971455471800998</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151184082031</v>
+        <v>198.2151031494141</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824975937368</v>
+        <v>203.4824819294599</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569251230167</v>
+        <v>197.4569099225941</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5148147488263</v>
+        <v>202.5147991590425</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958816719273994</v>
+        <v>-0.03958824112615977</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751463119384</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304931640625</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476859949454</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.934559185592</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505570232203</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.03652469938585123</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003021240234</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699092076593</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823961188316</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580698535366</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721368699238781</v>
+        <v>0.0003719741924403941</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742492675781</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621214501376</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268115668235</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436639125443</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793249675415924</v>
+        <v>0.05793266405042918</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983489990234</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529420926121</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427938118383</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935689756818</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959044433116265</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368225097656</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218237722109</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6732056162565</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522318976041</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331505219175</v>
+        <v>0.003313252582732629</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581020576737093</v>
+        <v>-0.03581005357317613</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540069580078</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482645458532</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794576828592</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E66" t="n">
-        <v>185.525507871713</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877265156263563</v>
+        <v>-0.01877257113277342</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2052,7 +2052,7 @@
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808138730923948</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524841308594</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1189017022491</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166923711864</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068443722038</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009742993471366312</v>
+        <v>-0.009743078144453632</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652227239154</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3949890136719</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341727058355</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447513765687</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919407266003</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0259108417558972</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291778564453</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728535594688</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140165634392</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1959139436215</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372185796401415</v>
+        <v>0.01372159873604817</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.0180850950995245</v>
+        <v>-0.01808492846544285</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607818603516</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.0139471586436</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819333075974</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6472262869623</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030535058927451</v>
+        <v>-0.01030526629882311</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.951904296875</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="C78" t="n">
-        <v>184.0892423581687</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398901129937</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1960032737075</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053512845051</v>
+        <v>0.02116036298998392</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2340,7 +2340,7 @@
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00528960288028224</v>
+        <v>-0.005289519918164731</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168212890625</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5610985176648</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741660895743</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E80" t="n">
-        <v>182.2136112701494</v>
+        <v>182.213626289633</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721399899417375</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125912631224192</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.8784332275391</v>
+        <v>175.87841796875</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0034500370577</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213802569945</v>
+        <v>174.6213651072644</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245903328353</v>
+        <v>177.5245749312296</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256277519845034</v>
+        <v>0.007256190132717499</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3051147460938</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733214473424</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916907151964</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485164107673</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111747940743541</v>
+        <v>0.008111748644499261</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814991702143256</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2589,22 +2589,22 @@
         <v>46013</v>
       </c>
       <c r="B90" t="n">
-        <v>183.2611541748047</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="C90" t="n">
-        <v>183.730058116363</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D90" t="n">
-        <v>181.9242862331203</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E90" t="n">
-        <v>183.4906129473229</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="F90" t="n">
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.014917857266596</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2628,7 +2628,7 @@
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005078265538064</v>
+        <v>0.03005069689074391</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2661,22 +2661,22 @@
         <v>46017</v>
       </c>
       <c r="B93" t="n">
-        <v>190.0851898193359</v>
+        <v>190.085205078125</v>
       </c>
       <c r="C93" t="n">
-        <v>192.2401507638228</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5610975436497</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E93" t="n">
-        <v>189.4766133088049</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="F93" t="n">
         <v>139740300</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01017970646506039</v>
+        <v>0.01017978755564442</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>120006100</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.01212401633949489</v>
+        <v>-0.01212409563967642</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646209716797</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151405796458</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546497967401</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E96" t="n">
-        <v>189.127461449755</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545375898472038</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2757,22 +2757,22 @@
         <v>46024</v>
       </c>
       <c r="B97" t="n">
-        <v>188.4091186523438</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="C97" t="n">
-        <v>192.479580126264</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D97" t="n">
-        <v>187.8204844911982</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E97" t="n">
-        <v>189.3967976648124</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="F97" t="n">
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01260044853460296</v>
+        <v>0.0126006135839718</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2796,7 +2796,7 @@
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.003865453797424312</v>
+        <v>-0.00386553447189375</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2829,22 +2829,22 @@
         <v>46029</v>
       </c>
       <c r="B100" t="n">
-        <v>188.6685028076172</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="C100" t="n">
-        <v>190.9232211122124</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1244530144955</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E100" t="n">
-        <v>188.1297701943655</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="F100" t="n">
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.00998708250744107</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080169677734</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074981045344</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685228499072</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152180029744644</v>
+        <v>-0.02152196030920583</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009727675505442068</v>
+        <v>-0.0009726849758688871</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133270263672</v>
+        <v>186.6133117675781</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571344016907</v>
+        <v>189.2571189267257</v>
       </c>
       <c r="D106" t="n">
-        <v>185.895006678512</v>
+        <v>185.8949914784577</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0646079796491</v>
+        <v>186.0645927657271</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134974210895835</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3012,7 +3012,7 @@
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383931140514608</v>
+        <v>-0.004383849732090828</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.654296875</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381676302343995</v>
+        <v>-0.04381668089652369</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948280612693632</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728912353516</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009553855833</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3968053634026</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E114" t="n">
-        <v>190.8234748728661</v>
+        <v>190.823459633995</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591342985123156</v>
+        <v>0.01591334872193784</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3189,22 +3189,22 @@
         <v>46051</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0605621337891</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="C115" t="n">
-        <v>193.0282987969995</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D115" t="n">
-        <v>185.625623299501</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E115" t="n">
-        <v>190.8932954336949</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="F115" t="n">
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169079151165157</v>
+        <v>0.005169239280915949</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3213,22 +3213,22 @@
         <v>46052</v>
       </c>
       <c r="B116" t="n">
-        <v>190.6837921142578</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="C116" t="n">
-        <v>194.0359484555967</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D116" t="n">
-        <v>189.0276639024229</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E116" t="n">
-        <v>190.7636071727618</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="F116" t="n">
         <v>179489500</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.00716841606749119</v>
+        <v>-0.007168415497976421</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766967773438</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557504766133</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4484052141589</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629812920276</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.0288807731158095</v>
+        <v>-0.02888093084756926</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839299457635047</v>
+        <v>-0.02839291451472381</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833404541016</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="C119" t="n">
-        <v>179.160756412826</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086645338761</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410414348666</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221377522338</v>
+        <v>-0.0341021289659974</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787292480469</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4071986282528</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307075914073</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5215964583249</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.01326140468949821</v>
+        <v>-0.0132614035251003</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771423339844</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634266395524</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923819783884</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E121" t="n">
-        <v>176.277498975506</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0787177112002726</v>
+        <v>0.07871770419569057</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963287353516</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2078878887748</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205500126207</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298238555102</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497166051482758</v>
+        <v>0.024971658454912</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893035105149604</v>
+        <v>-0.007893114950312197</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832244873047</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622780376601</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660713803529</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E126" t="n">
-        <v>187.042320465516</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209266545793198</v>
+        <v>-0.02209274727292232</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560567193918</v>
+        <v>0.01181560666047221</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768615722656</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856654675195</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059147845697</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344488846578</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021825301539225</v>
+        <v>0.01021833441238607</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028289794922</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972200828311</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374267327081</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531700210539</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113929721387581</v>
+        <v>0.009113767839714404</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786747007672789</v>
+        <v>0.006786827395534711</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583740234375</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364236513225</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8897126034445</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164813019665</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456121004512637</v>
+        <v>-0.05456128825383422</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164637217148226</v>
+        <v>-0.04164629289442512</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539855957031</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317086895539</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322921838959</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014235260267</v>
+        <v>174.601438160182</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486242594537</v>
+        <v>0.02985494874285899</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296691894531</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776756968921</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069714269912</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0733135069376</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331646982798718</v>
+        <v>-0.01331663634113589</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660656891157819</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119873046875</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6303076754259</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647422536165</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470550179114</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.00163899427668035</v>
+        <v>0.001638910718471109</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048614501953</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333155363547</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4071960911633</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420134514761</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010806418782519</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716230855539603</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7209,12 +7209,36 @@
         <v>230.9700012207031</v>
       </c>
       <c r="F282" t="n">
-        <v>101203000</v>
+        <v>101494900</v>
       </c>
       <c r="G282" t="n">
         <v>-0.007209621131189281</v>
       </c>
       <c r="H282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B283" t="n">
+        <v>228.3800048828125</v>
+      </c>
+      <c r="C283" t="n">
+        <v>232.3699951171875</v>
+      </c>
+      <c r="D283" t="n">
+        <v>228.1699981689453</v>
+      </c>
+      <c r="E283" t="n">
+        <v>229.2700042724609</v>
+      </c>
+      <c r="F283" t="n">
+        <v>121269300</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0.00514941302923666</v>
+      </c>
+      <c r="H283" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H283"/>
+  <dimension ref="A1:H284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103271484375</v>
+        <v>175.2103118896484</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535459787435</v>
+        <v>182.0535301239894</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607001855326</v>
+        <v>175.0606849397743</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837099150805</v>
+        <v>181.9836940664082</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709167480469</v>
+        <v>174.9709014892578</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694550698242</v>
+        <v>175.5694397588381</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870713158056</v>
+        <v>168.3870566311777</v>
       </c>
       <c r="E4" t="n">
-        <v>174.741483653999</v>
+        <v>174.7414684152183</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417175785561</v>
+        <v>-0.001366417294784594</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -564,7 +564,7 @@
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394632757571458</v>
+        <v>-0.002394545758820588</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545806884766</v>
+        <v>177.5545959472656</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531037491236</v>
+        <v>178.1531190593489</v>
       </c>
       <c r="D6" t="n">
-        <v>170.781182841084</v>
+        <v>170.7811975177769</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877371490149</v>
+        <v>172.1877519465851</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207335414736</v>
+        <v>0.01720216077105197</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022523041638013</v>
+        <v>0.01022514359906279</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557464599609</v>
+        <v>181.1557312011719</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435685875041</v>
+        <v>182.0435532539336</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618623689453</v>
+        <v>178.6618473202167</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348064912021</v>
+        <v>181.5347912004848</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009352591784613784</v>
+        <v>-0.0009353433299080782</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00787451516030313</v>
+        <v>-0.007874347363113654</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643945211436</v>
+        <v>-0.03324652152828622</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622283935547</v>
+        <v>170.3622131347656</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583204838847</v>
+        <v>171.9583050821389</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109394751057</v>
+        <v>166.810924534394</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841376854209</v>
+        <v>169.5841224963229</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01951983703713334</v>
+        <v>-0.0195199248555431</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026062011719</v>
+        <v>170.2026214599609</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882358353705</v>
+        <v>171.9882512542426</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668725173688</v>
+        <v>168.4668876205481</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415322614545</v>
+        <v>170.6415475595936</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009369576454122397</v>
+        <v>-0.0009367785958406261</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400817871094</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.4395894944585</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955858311417</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527518438138</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095443250276666</v>
+        <v>0.00609544270381579</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114196777344</v>
+        <v>166.6114349365234</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164970921864</v>
+        <v>168.6165125346066</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686393698748</v>
+        <v>163.668654359155</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189434134908</v>
+        <v>167.618958764552</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016265075109</v>
+        <v>-0.02703016024215876</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982696533203</v>
+        <v>167.8982543945312</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417962304089</v>
+        <v>170.5417807313731</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406265749079</v>
+        <v>166.9406114031506</v>
       </c>
       <c r="E16" t="n">
-        <v>167.140134281122</v>
+        <v>167.1401190912332</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723660107302521</v>
+        <v>0.007723476233777449</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422546386719</v>
+        <v>170.3422393798828</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617176578999</v>
+        <v>170.561702379452</v>
       </c>
       <c r="D17" t="n">
-        <v>166.3320999523285</v>
+        <v>166.332085052758</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763418810487</v>
+        <v>168.6763267714875</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634409096618</v>
+        <v>0.01455634541386375</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847521621706362</v>
+        <v>0.03847521966356759</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465362548828</v>
+        <v>176.7465667724609</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491035140756</v>
+        <v>179.8491345673521</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0581830190845</v>
+        <v>176.0582134178096</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505315119071</v>
+        <v>179.2505624618324</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008458502230944687</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731234709029</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.0282531820179</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.34510547722</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668914997253303</v>
+        <v>0.003668655369389429</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807415412831</v>
+        <v>-0.0003936947595158946</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711730957031</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089289332547</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924501658818</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810364137678</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928247356775705</v>
+        <v>0.03928238699195052</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204324514892</v>
+        <v>-0.02821196229186118</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153594970703</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602146114836</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890176259668</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987400973632</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053983240613322</v>
+        <v>0.02053991824341894</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041597539022</v>
+        <v>0.02601032967798278</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.7924957275391</v>
+        <v>186.79248046875</v>
       </c>
       <c r="C33" t="n">
-        <v>187.690338609038</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604668683245</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972757932568</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537489626782131</v>
+        <v>0.003537407649362168</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812141321341782</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965576171875</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825209975275</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918479831437</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566599139491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108606995897354</v>
+        <v>-0.01108615148198644</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694945166262119</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699188232422</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556339904095</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155586605101</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E41" t="n">
-        <v>187.52074924116</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817212858411589</v>
+        <v>0.02817204507600701</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1437,22 +1437,22 @@
         <v>45944</v>
       </c>
       <c r="B42" t="n">
-        <v>179.5997161865234</v>
+        <v>179.5997009277344</v>
       </c>
       <c r="C42" t="n">
-        <v>184.3583198600852</v>
+        <v>184.3583041970053</v>
       </c>
       <c r="D42" t="n">
-        <v>179.2705030798172</v>
+        <v>179.2704878489981</v>
       </c>
       <c r="E42" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3283771191491</v>
       </c>
       <c r="F42" t="n">
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402089854789248</v>
+        <v>-0.04402090212326881</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1476,7 +1476,7 @@
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110936754343372</v>
+        <v>-0.001110851888737052</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754425048828</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419301869027</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944368108431</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101030171288664</v>
+        <v>0.01101038676736099</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755442021748715</v>
+        <v>0.007755357241106875</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1557,22 +1557,22 @@
         <v>45951</v>
       </c>
       <c r="B47" t="n">
-        <v>180.7270202636719</v>
+        <v>180.7270050048828</v>
       </c>
       <c r="C47" t="n">
-        <v>182.3531141136141</v>
+        <v>182.3530987175338</v>
       </c>
       <c r="D47" t="n">
-        <v>179.3702701372806</v>
+        <v>179.370254993042</v>
       </c>
       <c r="E47" t="n">
-        <v>182.3531141136141</v>
+        <v>182.3530987175338</v>
       </c>
       <c r="F47" t="n">
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103334367036585</v>
+        <v>-0.008103418112909044</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1596,7 +1596,7 @@
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485768219622118</v>
+        <v>-0.00485759817631104</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250765250109055</v>
+        <v>0.02250756853454439</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323333740234</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="C51" t="n">
-        <v>191.5411089646758</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D51" t="n">
-        <v>187.9796341631504</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359184602369</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910615919784</v>
+        <v>0.02807910846500516</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495147705078</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644428640734</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513174538508</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E52" t="n">
-        <v>192.588592118433</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981974113173093</v>
+        <v>0.04981990486196963</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1716,7 +1716,7 @@
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989611444324924</v>
+        <v>0.02989603608371594</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855438232422</v>
+        <v>206.3855285644531</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348755139714</v>
+        <v>210.834859926228</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0686914304077</v>
+        <v>205.068676268978</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826726752522</v>
+        <v>207.5826573279554</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168005119548289</v>
+        <v>0.02167997565918256</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958824112615977</v>
+        <v>-0.03958817011962867</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304931640625</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476859949454</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.934559185592</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505570232203</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652469938585123</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7002868652344</v>
+        <v>187.7003173828125</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8698939350823</v>
+        <v>187.8699244802363</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823816093971</v>
+        <v>178.4824106282661</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580548583195</v>
+        <v>184.4580848487537</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003719741924403941</v>
+        <v>0.0003722181935406077</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793266405042918</v>
+        <v>0.05793249204463202</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3367919921875</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4217929255223</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6731755191215</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522010776849</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313252582732629</v>
+        <v>0.003313331767584859</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133911132812</v>
+        <v>186.4133758544922</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824463944715</v>
+        <v>190.9824307616844</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105907203728</v>
+        <v>183.4105757073767</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933791327836</v>
+        <v>190.5933635318434</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005357317613</v>
+        <v>-0.03581020859363238</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154693603516</v>
+        <v>189.7154846191406</v>
       </c>
       <c r="C65" t="n">
-        <v>190.553458007553</v>
+        <v>190.5534733337414</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1483942490048</v>
+        <v>180.1484087383153</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229435613052</v>
+        <v>182.4229582335574</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0177137394870075</v>
+        <v>0.01771390464612344</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540222167969</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482800008962</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794727552066</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255230789849</v>
+        <v>185.525507871713</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877257113277342</v>
+        <v>-0.01877273048260975</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808146927787025</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0742034912109</v>
+        <v>186.0741882324219</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109971087465</v>
+        <v>187.4109817403353</v>
       </c>
       <c r="D68" t="n">
-        <v>182.3930205111681</v>
+        <v>182.39300555425</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483273978252</v>
+        <v>184.3483122805645</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845165566477292</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152479724769053</v>
+        <v>-0.03152471782905131</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3950042724609</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341879937998</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447659257062</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E72" t="n">
-        <v>174.491955735681</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067635257405</v>
+        <v>-0.02591076013973348</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159873604817</v>
+        <v>0.0137217719481173</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492846544285</v>
+        <v>-0.01808501178249078</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899749755859</v>
+        <v>179.489990234375</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690716163194</v>
+        <v>179.8690869073362</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648835948944</v>
+        <v>173.2648983244765</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3423041351479</v>
+        <v>174.3423189563235</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649728438465226</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263061523438</v>
+        <v>181.0262908935547</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162648499111</v>
+        <v>185.2162492379485</v>
       </c>
       <c r="D76" t="n">
-        <v>179.569788944198</v>
+        <v>179.5697738081794</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255769560617</v>
+        <v>181.325561672047</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559426101467649</v>
+        <v>0.008559255349970263</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607818603516</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139471586436</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819333075974</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472262869623</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526629882311</v>
+        <v>-0.01030526716745872</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.9518890380859</v>
+        <v>182.951904296875</v>
       </c>
       <c r="C78" t="n">
-        <v>184.089227004522</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398751387779</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1959881613664</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116036298998392</v>
+        <v>0.02116053512845051</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2340,7 +2340,7 @@
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289519918164731</v>
+        <v>-0.00528960288028224</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.87841796875</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034500370577</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213651072644</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245749312296</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256190132717499</v>
+        <v>0.007256277519845034</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3050994873047</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733061224419</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916756985292</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485012773324</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111748644499261</v>
+        <v>0.008111747940743541</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814991702143256</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682952880859</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8880102762506</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4730132178061</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428571096804</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005069689074391</v>
+        <v>0.03005061362821149</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.003171176350336591</v>
+        <v>-0.00317109577323571</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646057128906</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151249886817</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546345387688</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E96" t="n">
-        <v>189.1274459397885</v>
+        <v>189.127461449755</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545375898472038</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2772,7 +2772,7 @@
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0126006135839718</v>
+        <v>0.01260053054261179</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080017089844</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074824738404</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685072554968</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152196030920583</v>
+        <v>-0.02152187943302564</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009726849758688871</v>
+        <v>-0.0009727675505442068</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124481201172</v>
+        <v>182.7124328613281</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293738083791</v>
+        <v>184.0293584396101</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779146434709</v>
+        <v>180.3778995796448</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8897012556695</v>
+        <v>183.8896858985649</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436954843994676</v>
+        <v>-0.01436963075249476</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133117675781</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571189267257</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D106" t="n">
-        <v>185.8949914784577</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0645927657271</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974210895835</v>
+        <v>0.02134991091711691</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3012,7 +3012,7 @@
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849732090828</v>
+        <v>-0.004383931140514608</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.654296875</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542325986551</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953640623503</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753422141945</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381668089652369</v>
+        <v>-0.04381676302343995</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948280612693632</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728759765625</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009400606663</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3967902384632</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E114" t="n">
-        <v>190.823459633995</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591334872193784</v>
+        <v>0.01591342985123156</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169239280915949</v>
+        <v>0.00516915900963677</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766815185547</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557348322644</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4483900153819</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629659025267</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888093084756926</v>
+        <v>-0.02888085082614911</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839291451472381</v>
+        <v>-0.02839299457635047</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833557128906</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="C119" t="n">
-        <v>179.1607721437711</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086795929406</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410571553003</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0341021289659974</v>
+        <v>-0.03410221377522338</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787445068359</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4072143255947</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307227747363</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5216119878791</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.0132614035251003</v>
+        <v>-0.01326140468949821</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771575927734</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634420291942</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923963475411</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775135166603</v>
+        <v>176.277498975506</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871770419569057</v>
+        <v>0.0787177112002726</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3372,7 +3372,7 @@
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.024971658454912</v>
+        <v>0.02497174300496052</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063385009766</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088363522974</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D124" t="n">
-        <v>188.3293278304631</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007297023972</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800904593061702</v>
+        <v>0.008008964809924857</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636418228460701</v>
+        <v>-0.01636410312537218</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832092285156</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622623874058</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660562233949</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E126" t="n">
-        <v>187.0423048169314</v>
+        <v>187.042320465516</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209274727292232</v>
+        <v>-0.02209266545793198</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3492,7 +3492,7 @@
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560666047221</v>
+        <v>0.0118155220086027</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028137207031</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972046328596</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374116308485</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531547742145</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113767839714404</v>
+        <v>0.009113848413379699</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786827395534711</v>
+        <v>0.006786747007672789</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119720458984</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6302923567135</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647274492447</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470399397241</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638910718471109</v>
+        <v>0.00163899427668035</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010798076634313</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -7233,12 +7233,36 @@
         <v>229.2700042724609</v>
       </c>
       <c r="F283" t="n">
-        <v>121269300</v>
+        <v>121732200</v>
       </c>
       <c r="G283" t="n">
         <v>0.00514941302923666</v>
       </c>
       <c r="H283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B284" t="n">
+        <v>230.8600006103516</v>
+      </c>
+      <c r="C284" t="n">
+        <v>232.2899932861328</v>
+      </c>
+      <c r="D284" t="n">
+        <v>228.1600036621094</v>
+      </c>
+      <c r="E284" t="n">
+        <v>229.9799957275391</v>
+      </c>
+      <c r="F284" t="n">
+        <v>98369800</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0.01085907555178323</v>
+      </c>
+      <c r="H284" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H284"/>
+  <dimension ref="A1:H285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103118896484</v>
+        <v>175.2103271484375</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535301239894</v>
+        <v>182.0535459787435</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0606849397743</v>
+        <v>175.0607001855326</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9836940664082</v>
+        <v>181.9837099150805</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709014892578</v>
+        <v>174.9709167480469</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694397588381</v>
+        <v>175.5694550698242</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870566311777</v>
+        <v>168.3870713158056</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414684152183</v>
+        <v>174.741483653999</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417294784594</v>
+        <v>-0.001366417175785561</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -564,7 +564,7 @@
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394545758820588</v>
+        <v>-0.002394632757571458</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545959472656</v>
+        <v>177.5545654296875</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531190593489</v>
+        <v>178.1530884388983</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811975177769</v>
+        <v>170.7811681643912</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877519465851</v>
+        <v>172.1877223514448</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720216077105197</v>
+        <v>0.01720198593724254</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701171875</v>
+        <v>179.3701477050781</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4649859155824</v>
+        <v>181.4650167895762</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380531425805</v>
+        <v>176.1380831102634</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9136974002478</v>
+        <v>177.9137276700343</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022514359906279</v>
+        <v>0.01022548911089305</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -636,7 +636,7 @@
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090045256567307</v>
+        <v>0.01090028057365577</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557312011719</v>
+        <v>181.1557464599609</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435532539336</v>
+        <v>182.0435685875041</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618473202167</v>
+        <v>178.6618623689453</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5347912004848</v>
+        <v>181.5348064912021</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009353433299080782</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874347363113654</v>
+        <v>-0.00787451516030313</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538757324219</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141646735497</v>
+        <v>177.714180280125</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7263967599338</v>
+        <v>172.7264119284913</v>
       </c>
       <c r="E11" t="n">
-        <v>177.674269227683</v>
+        <v>177.6742848307548</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324652152828622</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -732,7 +732,7 @@
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0195199248555431</v>
+        <v>-0.01952001095973654</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026214599609</v>
+        <v>170.2026062011719</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882512542426</v>
+        <v>171.9882358353705</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668876205481</v>
+        <v>168.4668725173688</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415475595936</v>
+        <v>170.6415322614545</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009367785958406261</v>
+        <v>-0.0009368681625865349</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400817871094</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395894944585</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955858311417</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527518438138</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00609544270381579</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114349365234</v>
+        <v>166.6114196777344</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6165125346066</v>
+        <v>168.6164970921864</v>
       </c>
       <c r="D15" t="n">
-        <v>163.668654359155</v>
+        <v>163.6686393698748</v>
       </c>
       <c r="E15" t="n">
-        <v>167.618958764552</v>
+        <v>167.6189434134908</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016024215876</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982543945312</v>
+        <v>167.8982391357422</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417807313731</v>
+        <v>170.5417652323373</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406114031506</v>
+        <v>166.9405962313932</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401190912332</v>
+        <v>167.1401039013443</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723476233777449</v>
+        <v>0.007723476941117413</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422393798828</v>
+        <v>170.3422546386719</v>
       </c>
       <c r="C17" t="n">
-        <v>170.561702379452</v>
+        <v>170.5617176578999</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332085052758</v>
+        <v>166.3320999523285</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763267714875</v>
+        <v>168.6763418810487</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634541386375</v>
+        <v>0.01455652849910916</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847521966356759</v>
+        <v>0.03847521621706362</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465667724609</v>
+        <v>176.7465362548828</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491345673521</v>
+        <v>179.8491035140756</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0582134178096</v>
+        <v>176.0581830190845</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505624618324</v>
+        <v>179.2505315119071</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008458502230944687</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3949890136719</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731234709029</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.0282531820179</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.34510547722</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668655369389429</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251495361328</v>
+        <v>177.3251647949219</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225264520066</v>
+        <v>178.4225418052247</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0928881658194</v>
+        <v>174.0929031464731</v>
       </c>
       <c r="E21" t="n">
-        <v>175.250119236683</v>
+        <v>175.2501343169162</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947595158946</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -972,7 +972,7 @@
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614620751539797</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187866210938</v>
+        <v>175.8187713623047</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767318043244</v>
+        <v>176.6767164710769</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466271367534</v>
+        <v>172.5466121619453</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641783462465</v>
+        <v>173.5641632831282</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494055886175818</v>
+        <v>0.03494046904234804</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477264404297</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543599509016</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612823170602</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E25" t="n">
-        <v>175.3498836843894</v>
+        <v>175.349898865447</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439670001024075</v>
+        <v>0.00243984378681672</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1068,7 +1068,7 @@
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928238699195052</v>
+        <v>0.03928229701524732</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470123291016</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3502935078314</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807575937583</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403228895943</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182577209651543</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653198242188</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291695578261</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162207499007</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.062985089831</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068647130534231</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830455718369</v>
+        <v>0.002813830697929731</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153747558594</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602300506758</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890327563757</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987552370008</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053991824341894</v>
+        <v>0.02053992000650995</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340484619141</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022123120565</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462321155116</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448041170831</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601032967798278</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1236,7 +1236,7 @@
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537407649362168</v>
+        <v>0.003537325381961498</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715545654297</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050110254035</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369182511207</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378093314507</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587692724298</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108615148198644</v>
+        <v>-0.0110862321012164</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097412109375</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="C39" t="n">
-        <v>194.8332119113436</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033405552435</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705422839889</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626288358566</v>
+        <v>0.01829626140377161</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886543837402468</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699035644531</v>
+        <v>187.8699340820312</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556185865847</v>
+        <v>189.6556493942343</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155435929421</v>
+        <v>185.5155737280782</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207340107304</v>
+        <v>187.5207644715895</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817204507600701</v>
+        <v>0.02817229795294884</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1437,22 +1437,22 @@
         <v>45944</v>
       </c>
       <c r="B42" t="n">
-        <v>179.5997009277344</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="C42" t="n">
-        <v>184.3583041970053</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D42" t="n">
-        <v>179.2704878489981</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E42" t="n">
-        <v>184.3283771191491</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="F42" t="n">
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402090212326881</v>
+        <v>-0.04402097619247958</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1476,7 +1476,7 @@
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110851888737052</v>
+        <v>-0.001110936754343372</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820892333984</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599908268075</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493465774322</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755357241106875</v>
+        <v>0.007755441369297289</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590696970089</v>
+        <v>-0.003165673913464562</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1557,22 +1557,22 @@
         <v>45951</v>
       </c>
       <c r="B47" t="n">
-        <v>180.7270050048828</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="C47" t="n">
-        <v>182.3530987175338</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D47" t="n">
-        <v>179.370254993042</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E47" t="n">
-        <v>182.3530987175338</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="F47" t="n">
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103418112909044</v>
+        <v>-0.008103334367036585</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491058349609</v>
+        <v>179.84912109375</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015566720687</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375148363812</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070509305708</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485759817631104</v>
+        <v>-0.004857597766183885</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.724609375</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988762799469</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829092822517</v>
+        <v>0.01042812035913343</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250756853454439</v>
+        <v>0.02250773835753361</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323181152344</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="C51" t="n">
-        <v>191.541093665248</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D51" t="n">
-        <v>187.979619148197</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359033209746</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910846500516</v>
+        <v>0.02807910615919784</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981990486196963</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.545166015625</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828666070652</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905729140704</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482921843539</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989603608371594</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448238730316</v>
+        <v>-0.02004433759634028</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729406961805</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870481318289</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565693232556</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971455471800998</v>
+        <v>-0.001971530859184778</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855285644531</v>
+        <v>206.3855590820312</v>
       </c>
       <c r="C56" t="n">
-        <v>210.834859926228</v>
+        <v>210.8348911017148</v>
       </c>
       <c r="D56" t="n">
-        <v>205.068676268978</v>
+        <v>205.0687065918373</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826573279554</v>
+        <v>207.5826880225491</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02167997565918256</v>
+        <v>0.02168020390572556</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151031494141</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824819294599</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569099225941</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5147991590425</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958817011962867</v>
+        <v>-0.03958823819926593</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751463119384</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.0365248560924305</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003173828125</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699244802363</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4824106282661</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580848487537</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003722181935406077</v>
+        <v>0.0003721369001874475</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793249204463202</v>
+        <v>0.05793266405042918</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133758544922</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824307616844</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105757073767</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933635318434</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581020859363238</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154846191406</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="C65" t="n">
-        <v>190.5534733337414</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1484087383153</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229582335574</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771390464612344</v>
+        <v>0.0177137394870075</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540069580078</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482645458532</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794576828592</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E66" t="n">
-        <v>185.525507871713</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877273048260975</v>
+        <v>-0.01877257113277342</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146927787025</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0741882324219</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109817403353</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D68" t="n">
-        <v>182.39300555425</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483122805645</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165566477292</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152471782905131</v>
+        <v>-0.03152479724769053</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.02051660953286172</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3949890136719</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341727058355</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447513765687</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919407266003</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591076013973348</v>
+        <v>-0.02591067418159221</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291625976562</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728380763597</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140014756398</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958985688627</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0137217719481173</v>
+        <v>0.01372151153989076</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808501178249078</v>
+        <v>-0.01808484361385299</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.489990234375</v>
+        <v>179.4899597167969</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690869073362</v>
+        <v>179.8690563253026</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648983244765</v>
+        <v>173.2648688653124</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3423189563235</v>
+        <v>174.3422893139723</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649728438465226</v>
+        <v>0.01649702371590833</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0262908935547</v>
+        <v>181.0263214111328</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162492379485</v>
+        <v>185.2162804618737</v>
       </c>
       <c r="D76" t="n">
-        <v>179.5697738081794</v>
+        <v>179.5698040802165</v>
       </c>
       <c r="E76" t="n">
-        <v>181.325561672047</v>
+        <v>181.3255922400764</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559255349970263</v>
+        <v>0.008559596852994122</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526716745872</v>
+        <v>-0.0103055183015206</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.951904296875</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="C78" t="n">
-        <v>184.0892423581687</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398901129937</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1960032737075</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053512845051</v>
+        <v>0.02116053693065423</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841613769531</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2289086763207</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876631773748</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4607020047171</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00528960288028224</v>
+        <v>-0.005289603321452563</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168365478516</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5611139779305</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741810893209</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E80" t="n">
-        <v>182.213626289633</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721399899417375</v>
+        <v>0.01721400043751253</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2388,7 +2388,7 @@
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125912631224192</v>
+        <v>-0.003125830460996126</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114044189453</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3931976659576</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123291208211</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871831157045</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266452212921567</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256277519845034</v>
+        <v>0.007256189498619836</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3051147460938</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733214473424</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916907151964</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485164107673</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111747940743541</v>
+        <v>0.008111661183153096</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814991702143256</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491794177123418</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682800292969</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8879950077845</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4729984678863</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428423541149</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005061362821149</v>
+        <v>0.03005069689074391</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.00317109577323571</v>
+        <v>-0.003171176350336591</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646209716797</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151405796458</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546497967401</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E96" t="n">
-        <v>189.127461449755</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545375898472038</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2772,7 +2772,7 @@
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01260053054261179</v>
+        <v>0.0126006135839718</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808319091797</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779786425506</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154296257417</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123337767646</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386553447189375</v>
+        <v>-0.00386561545941666</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677861544826856</v>
+        <v>-0.004677780623340899</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.376220703125</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708543554723</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718432388734</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5681140987238</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.004704210650191332</v>
+        <v>0.00470412795042785</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124328613281</v>
+        <v>182.7124633789062</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293584396101</v>
+        <v>184.029389177148</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3778995796448</v>
+        <v>180.3779297072971</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8896858985649</v>
+        <v>183.889716612774</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436963075249476</v>
+        <v>-0.01436938499763141</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134991091711691</v>
+        <v>0.02134974032598635</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952270507812</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="C107" t="n">
-        <v>189.99540517049</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455833269296</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385795892923</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383931140514608</v>
+        <v>-0.004383849373637116</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.6543121337891</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542482267672</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953792817215</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753578011745</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381676302343995</v>
+        <v>-0.0438166772979951</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920440673828</v>
+        <v>182.8920288085938</v>
       </c>
       <c r="C109" t="n">
-        <v>184.9472325313386</v>
+        <v>184.947217101084</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835164834521</v>
+        <v>177.9835016341843</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6320081827799</v>
+        <v>178.6319932794081</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948263181397048</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291414334357983</v>
+        <v>0.008291498456701074</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728912353516</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009553855833</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3968053634026</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E114" t="n">
-        <v>190.8234748728661</v>
+        <v>190.823459633995</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591342985123156</v>
+        <v>0.01591334872193784</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.00516915900963677</v>
+        <v>0.005169239280915949</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766967773438</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557504766133</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4484052141589</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629812920276</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888085082614911</v>
+        <v>-0.02888093084756926</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839299457635047</v>
+        <v>-0.02839291451472381</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833404541016</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="C119" t="n">
-        <v>179.160756412826</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086645338761</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410414348666</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221377522338</v>
+        <v>-0.0341021289659974</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787292480469</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4071986282528</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307075914073</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5215964583249</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.01326140468949821</v>
+        <v>-0.0132614035251003</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771423339844</v>
+        <v>184.9771728515625</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634266395524</v>
+        <v>186.5634574188361</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923819783884</v>
+        <v>174.1924107166939</v>
       </c>
       <c r="E121" t="n">
-        <v>176.277498975506</v>
+        <v>176.2775280578147</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0787177112002726</v>
+        <v>0.07871779317924998</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963439941406</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2079034382237</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205647824287</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298386502086</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497174300496052</v>
+        <v>0.0249714914147583</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.0998382568359</v>
+        <v>188.099853515625</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306425866914</v>
+        <v>192.0306581643501</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808205923615</v>
+        <v>187.6808358171596</v>
       </c>
       <c r="E123" t="n">
-        <v>190.933219719687</v>
+        <v>190.9332352083219</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893114950312197</v>
+        <v>-0.00789295462474604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3420,7 +3420,7 @@
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.008008964809924857</v>
+        <v>0.00800888303954661</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768768310547</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856807673048</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059297314624</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344638821937</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833441238607</v>
+        <v>0.01021825301539225</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028289794922</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972200828311</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374267327081</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531700210539</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113848413379699</v>
+        <v>0.009113849147715847</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786747007672789</v>
+        <v>0.006786827395534711</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583587646484</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364076167612</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8896973916963</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164652690549</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456128825383422</v>
+        <v>-0.05456121004512637</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164629289442512</v>
+        <v>-0.04164637217148226</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0540008544922</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317240302905</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2323067871125</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E136" t="n">
-        <v>174.601438160182</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985494874285899</v>
+        <v>0.02985486242594537</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296539306641</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776603660684</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069564334623</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0732983803544</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331663634113589</v>
+        <v>-0.01331646982798718</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126861572266</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2688145383873</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396472340209</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187649948852</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660656891157819</v>
+        <v>0.01660639760928495</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119873046875</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6303076754259</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647422536165</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470550179114</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.00163899427668035</v>
+        <v>0.001638994413631911</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010798076634313</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -7257,12 +7257,36 @@
         <v>229.9799957275391</v>
       </c>
       <c r="F284" t="n">
-        <v>98369800</v>
+        <v>98591400</v>
       </c>
       <c r="G284" t="n">
         <v>0.01085907555178323</v>
       </c>
       <c r="H284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B285" t="n">
+        <v>233.9499969482422</v>
+      </c>
+      <c r="C285" t="n">
+        <v>237.8800048828125</v>
+      </c>
+      <c r="D285" t="n">
+        <v>233.6000061035156</v>
+      </c>
+      <c r="E285" t="n">
+        <v>236.0599975585938</v>
+      </c>
+      <c r="F285" t="n">
+        <v>134914600</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0.01338471943914588</v>
+      </c>
+      <c r="H285" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103271484375</v>
+        <v>175.2103118896484</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535459787435</v>
+        <v>182.0535301239894</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607001855326</v>
+        <v>175.0606849397743</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837099150805</v>
+        <v>181.9836940664082</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709167480469</v>
+        <v>174.9709014892578</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694550698242</v>
+        <v>175.5694397588381</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870713158056</v>
+        <v>168.3870566311777</v>
       </c>
       <c r="E4" t="n">
-        <v>174.741483653999</v>
+        <v>174.7414684152183</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417175785561</v>
+        <v>-0.001366417294784594</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -564,7 +564,7 @@
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394632757571458</v>
+        <v>-0.002394545758820588</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545654296875</v>
+        <v>177.5545959472656</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1530884388983</v>
+        <v>178.1531190593489</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811681643912</v>
+        <v>170.7811975177769</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877223514448</v>
+        <v>172.1877519465851</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720198593724254</v>
+        <v>0.01720216077105197</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701477050781</v>
+        <v>179.3701171875</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650167895762</v>
+        <v>181.4649859155824</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380831102634</v>
+        <v>176.1380531425805</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9137276700343</v>
+        <v>177.9136974002478</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022548911089305</v>
+        <v>0.01022514359906279</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -636,7 +636,7 @@
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090028057365577</v>
+        <v>0.01090045256567307</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557464599609</v>
+        <v>181.1557312011719</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435685875041</v>
+        <v>182.0435532539336</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618623689453</v>
+        <v>178.6618473202167</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348064912021</v>
+        <v>181.5347912004848</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009352591784613784</v>
+        <v>-0.0009353433299080782</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00787451516030313</v>
+        <v>-0.007874347363113654</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538909912109</v>
+        <v>173.7538757324219</v>
       </c>
       <c r="C11" t="n">
-        <v>177.714180280125</v>
+        <v>177.7141646735497</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264119284913</v>
+        <v>172.7263967599338</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6742848307548</v>
+        <v>177.674269227683</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635455335401</v>
+        <v>-0.03324652152828622</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -732,7 +732,7 @@
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952001095973654</v>
+        <v>-0.0195199248555431</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026062011719</v>
+        <v>170.2026214599609</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882358353705</v>
+        <v>171.9882512542426</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668725173688</v>
+        <v>168.4668876205481</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415322614545</v>
+        <v>170.6415475595936</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368681625865349</v>
+        <v>-0.0009367785958406261</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400817871094</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.4395894944585</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955858311417</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527518438138</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095443250276666</v>
+        <v>0.00609544270381579</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114196777344</v>
+        <v>166.6114349365234</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164970921864</v>
+        <v>168.6165125346066</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686393698748</v>
+        <v>163.668654359155</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189434134908</v>
+        <v>167.618958764552</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016265075109</v>
+        <v>-0.02703016024215876</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982391357422</v>
+        <v>167.8982543945312</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417652323373</v>
+        <v>170.5417807313731</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9405962313932</v>
+        <v>166.9406114031506</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401039013443</v>
+        <v>167.1401190912332</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723476941117413</v>
+        <v>0.007723476233777449</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422546386719</v>
+        <v>170.3422393798828</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617176578999</v>
+        <v>170.561702379452</v>
       </c>
       <c r="D17" t="n">
-        <v>166.3320999523285</v>
+        <v>166.332085052758</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763418810487</v>
+        <v>168.6763267714875</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455652849910916</v>
+        <v>0.01455634541386375</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847521621706362</v>
+        <v>0.03847521966356759</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465362548828</v>
+        <v>176.7465667724609</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491035140756</v>
+        <v>179.8491345673521</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0581830190845</v>
+        <v>176.0582134178096</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505315119071</v>
+        <v>179.2505624618324</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008458502230944687</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.39501953125</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731541223449</v>
+        <v>178.1731234709029</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028283464474</v>
+        <v>176.0282531820179</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451359862166</v>
+        <v>177.34510547722</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003669001328727717</v>
+        <v>0.003668655369389429</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807076698219</v>
+        <v>-0.000393608743619156</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187713623047</v>
+        <v>175.8187866210938</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767164710769</v>
+        <v>176.6767318043244</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466121619453</v>
+        <v>172.5466271367534</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641632831282</v>
+        <v>173.5641783462465</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494046904234804</v>
+        <v>0.03494055886175818</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477416992188</v>
+        <v>176.2477264404297</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543753314711</v>
+        <v>177.6543599509016</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612974471592</v>
+        <v>174.7612823170602</v>
       </c>
       <c r="E25" t="n">
-        <v>175.349898865447</v>
+        <v>175.3498836843894</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00243984378681672</v>
+        <v>0.002439670001024075</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1068,7 +1068,7 @@
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928229701524732</v>
+        <v>0.03928238699195052</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470275878906</v>
+        <v>176.5470123291016</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3502935078314</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807727171775</v>
+        <v>174.9807575937583</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403383898065</v>
+        <v>179.3403228895943</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.008182577209651543</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653045654297</v>
+        <v>177.2653198242188</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291540783439</v>
+        <v>179.8291695578261</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162058826927</v>
+        <v>172.7162207499007</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629701066951</v>
+        <v>174.062985089831</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068473920816773</v>
+        <v>0.004068647130534231</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7640991210938</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403244887289</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118813132914</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441426621237</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830697929731</v>
+        <v>0.002813830455718369</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153594970703</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602146114836</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890176259668</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987400973632</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053992000650995</v>
+        <v>0.02053991824341894</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340637207031</v>
+        <v>186.1340484619141</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022276338177</v>
+        <v>186.9022123120565</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462469572146</v>
+        <v>181.0462321155116</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448190078555</v>
+        <v>181.6448041170831</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601032967798278</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1236,7 +1236,7 @@
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537325381961498</v>
+        <v>0.003537407649362168</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199532691778505</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097564697266</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="C39" t="n">
-        <v>194.833227386451</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033556943829</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705575158363</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626140377161</v>
+        <v>0.01829626288358566</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886543837402468</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699340820312</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556493942343</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155737280782</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207644715895</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817229795294884</v>
+        <v>0.02817204507600701</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1437,22 +1437,22 @@
         <v>45944</v>
       </c>
       <c r="B42" t="n">
-        <v>179.5997161865234</v>
+        <v>179.5997009277344</v>
       </c>
       <c r="C42" t="n">
-        <v>184.3583198600852</v>
+        <v>184.3583041970053</v>
       </c>
       <c r="D42" t="n">
-        <v>179.2705030798172</v>
+        <v>179.2704878489981</v>
       </c>
       <c r="E42" t="n">
-        <v>184.3283927796865</v>
+        <v>184.3283771191491</v>
       </c>
       <c r="F42" t="n">
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402097619247958</v>
+        <v>-0.04402090212326881</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1476,7 +1476,7 @@
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110936754343372</v>
+        <v>-0.001110851888737052</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7821044921875</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6600061588844</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493615830456</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755441369297289</v>
+        <v>0.007755357241106875</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165673913464562</v>
+        <v>-0.003165590696970089</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1557,22 +1557,22 @@
         <v>45951</v>
       </c>
       <c r="B47" t="n">
-        <v>180.7270202636719</v>
+        <v>180.7270050048828</v>
       </c>
       <c r="C47" t="n">
-        <v>182.3531141136141</v>
+        <v>182.3530987175338</v>
       </c>
       <c r="D47" t="n">
-        <v>179.3702701372806</v>
+        <v>179.370254993042</v>
       </c>
       <c r="E47" t="n">
-        <v>182.3531141136141</v>
+        <v>182.3530987175338</v>
       </c>
       <c r="F47" t="n">
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103334367036585</v>
+        <v>-0.008103418112909044</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.84912109375</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015721983185</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375297972393</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070662621498</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004857597766183885</v>
+        <v>-0.00485759817631104</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.724609375</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925250516066</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602637385785</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988762799469</v>
+        <v>179.988777912505</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042812035913343</v>
+        <v>0.01042829092822517</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250773835753361</v>
+        <v>0.02250756853454439</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323333740234</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="C51" t="n">
-        <v>191.5411089646758</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D51" t="n">
-        <v>187.9796341631504</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359184602369</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910615919784</v>
+        <v>0.02807910846500516</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981990486196963</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.545166015625</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482921843539</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989603608371594</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004433759634028</v>
+        <v>-0.02004448238730316</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729250244422</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870329046891</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565537660584</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971530859184778</v>
+        <v>-0.001971455471800998</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855590820312</v>
+        <v>206.3855285644531</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348911017148</v>
+        <v>210.834859926228</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0687065918373</v>
+        <v>205.068676268978</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826880225491</v>
+        <v>207.5826573279554</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168020390572556</v>
+        <v>0.02167997565918256</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151184082031</v>
+        <v>198.2151031494141</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824975937368</v>
+        <v>203.4824819294599</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569251230167</v>
+        <v>197.4569099225941</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5148147488263</v>
+        <v>202.5147991590425</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958823819926593</v>
+        <v>-0.03958817011962867</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751463119384</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304626464844</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476539294223</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345289438528</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505251524069</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.0365248560924305</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7002868652344</v>
+        <v>187.7003173828125</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8698939350823</v>
+        <v>187.8699244802363</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823816093971</v>
+        <v>178.4824106282661</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580548583195</v>
+        <v>184.4580848487537</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721369001874475</v>
+        <v>0.0003722181935406077</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793266405042918</v>
+        <v>0.05793249204463202</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133911132812</v>
+        <v>186.4133758544922</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824463944715</v>
+        <v>190.9824307616844</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105907203728</v>
+        <v>183.4105757073767</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933791327836</v>
+        <v>190.5933635318434</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581012967027952</v>
+        <v>-0.03581020859363238</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2004,7 +2004,7 @@
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0177137394870075</v>
+        <v>0.01771382279154077</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540222167969</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482800008962</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794727552066</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255230789849</v>
+        <v>185.525507871713</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877257113277342</v>
+        <v>-0.01877265156263563</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808146927787025</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845174000170858</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051660953286172</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.39501953125</v>
+        <v>177.3949890136719</v>
       </c>
       <c r="C72" t="n">
-        <v>177.734203281764</v>
+        <v>177.7341727058355</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447804748437</v>
+        <v>169.1447513765687</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919707447618</v>
+        <v>174.4919407266003</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067418159221</v>
+        <v>-0.02591076013973348</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372151153989076</v>
+        <v>0.0137217719481173</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808484361385299</v>
+        <v>-0.01808501178249078</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899597167969</v>
+        <v>179.489990234375</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690563253026</v>
+        <v>179.8690869073362</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648688653124</v>
+        <v>173.2648983244765</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3422893139723</v>
+        <v>174.3423189563235</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649702371590833</v>
+        <v>0.01649728438465226</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263214111328</v>
+        <v>181.0262908935547</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162804618737</v>
+        <v>185.2162492379485</v>
       </c>
       <c r="D76" t="n">
-        <v>179.5698040802165</v>
+        <v>179.5697738081794</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255922400764</v>
+        <v>181.325561672047</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559596852994122</v>
+        <v>0.008559255349970263</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.0103055183015206</v>
+        <v>-0.01030526716745872</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.9518890380859</v>
+        <v>182.951904296875</v>
       </c>
       <c r="C78" t="n">
-        <v>184.089227004522</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398751387779</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1959881613664</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053693065423</v>
+        <v>0.02116053512845051</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841461181641</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2288932293168</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876480440623</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4606866221248</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289603321452563</v>
+        <v>-0.00528960288028224</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168212890625</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5610985176648</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741660895743</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E80" t="n">
-        <v>182.2136112701494</v>
+        <v>182.213626289633</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721400043751253</v>
+        <v>0.01721399899417375</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2388,7 +2388,7 @@
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125830460996126</v>
+        <v>-0.003125912631224192</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114196777344</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3932136047752</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123443447362</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871989054384</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266452212921567</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256189498619836</v>
+        <v>0.007256277519845034</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3050994873047</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733061224419</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916756985292</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485012773324</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111661183153096</v>
+        <v>0.008111747940743541</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814991702143256</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682952880859</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8880102762506</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4730132178061</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428571096804</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005069689074391</v>
+        <v>0.03005061362821149</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.003171176350336591</v>
+        <v>-0.00317109577323571</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646057128906</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151249886817</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546345387688</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E96" t="n">
-        <v>189.1274459397885</v>
+        <v>189.127461449755</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545375898472038</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2772,7 +2772,7 @@
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0126006135839718</v>
+        <v>0.01260053054261179</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808166503906</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779629368336</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154145267434</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123182227279</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386561545941666</v>
+        <v>-0.00386553447189375</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780623340899</v>
+        <v>-0.004677861544826856</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.3762054443359</v>
+        <v>185.376220703125</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708389078061</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718281779948</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5680989064521</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.00470412795042785</v>
+        <v>0.004704210650191332</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124633789062</v>
+        <v>182.7124328613281</v>
       </c>
       <c r="C105" t="n">
-        <v>184.029389177148</v>
+        <v>184.0293584396101</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779297072971</v>
+        <v>180.3778995796448</v>
       </c>
       <c r="E105" t="n">
-        <v>183.889716612774</v>
+        <v>183.8896858985649</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436938499763141</v>
+        <v>-0.01436963075249476</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974032598635</v>
+        <v>0.02134991091711691</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952423095703</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="C107" t="n">
-        <v>189.9954207742267</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455985734289</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385950815971</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849373637116</v>
+        <v>-0.004383931140514608</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6543121337891</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542482267672</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953792817215</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753578011745</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438166772979951</v>
+        <v>-0.04381676302343995</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920288085938</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="C109" t="n">
-        <v>184.947217101084</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835016341843</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6319932794081</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948263181397048</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291498456701074</v>
+        <v>0.008291414334357983</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728759765625</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009400606663</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3967902384632</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E114" t="n">
-        <v>190.823459633995</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591334872193784</v>
+        <v>0.01591342985123156</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169239280915949</v>
+        <v>0.00516915900963677</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766815185547</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557348322644</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4483900153819</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629659025267</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888093084756926</v>
+        <v>-0.02888085082614911</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839291451472381</v>
+        <v>-0.02839299457635047</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833557128906</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="C119" t="n">
-        <v>179.1607721437711</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086795929406</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410571553003</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0341021289659974</v>
+        <v>-0.03410221377522338</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787445068359</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4072143255947</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307227747363</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5216119878791</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.0132614035251003</v>
+        <v>-0.01326140468949821</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771728515625</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634574188361</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1924107166939</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775280578147</v>
+        <v>176.277498975506</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871779317924998</v>
+        <v>0.0787177112002726</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963287353516</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2078878887748</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205500126207</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298238555102</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0249714914147583</v>
+        <v>0.02497174300496052</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.099853515625</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306581643501</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808358171596</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E123" t="n">
-        <v>190.9332352083219</v>
+        <v>190.933219719687</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.00789295462474604</v>
+        <v>-0.007893114950312197</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3420,7 +3420,7 @@
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800888303954661</v>
+        <v>0.008008964809924857</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768615722656</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856654675195</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059147845697</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344488846578</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021825301539225</v>
+        <v>0.01021833441238607</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028137207031</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972046328596</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374116308485</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531547742145</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113849147715847</v>
+        <v>0.009113848413379699</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786827395534711</v>
+        <v>0.006786747007672789</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583740234375</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364236513225</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8897126034445</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164813019665</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456121004512637</v>
+        <v>-0.05456128825383422</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164637217148226</v>
+        <v>-0.04164629289442512</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539855957031</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317086895539</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322921838959</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014235260267</v>
+        <v>174.601438160182</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486242594537</v>
+        <v>0.02985494874285899</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296691894531</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776756968921</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069714269912</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0733135069376</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331646982798718</v>
+        <v>-0.01331663634113589</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126708984375</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2687991412151</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396322236537</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187499528396</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660639760928495</v>
+        <v>0.01660656891157819</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119720458984</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6302923567135</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647274492447</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470399397241</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638994413631911</v>
+        <v>0.00163899427668035</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010798076634313</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H285"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103118896484</v>
+        <v>175.2103271484375</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535301239894</v>
+        <v>182.0535459787435</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0606849397743</v>
+        <v>175.0607001855326</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9836940664082</v>
+        <v>181.9837099150805</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -540,7 +540,7 @@
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417294784594</v>
+        <v>-0.001366504264196933</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545959472656</v>
+        <v>177.5545806884766</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531190593489</v>
+        <v>178.1531037491236</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811975177769</v>
+        <v>170.781182841084</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877519465851</v>
+        <v>172.1877371490149</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720216077105197</v>
+        <v>0.01720207335414736</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022514359906279</v>
+        <v>0.01022523041638013</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557312011719</v>
+        <v>181.1557464599609</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435532539336</v>
+        <v>182.0435685875041</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618473202167</v>
+        <v>178.6618623689453</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5347912004848</v>
+        <v>181.5348064912021</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009353433299080782</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -684,7 +684,7 @@
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874347363113654</v>
+        <v>-0.007874430930079446</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622131347656</v>
+        <v>170.3621978759766</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583050821389</v>
+        <v>171.9582896803931</v>
       </c>
       <c r="D12" t="n">
-        <v>166.810924534394</v>
+        <v>166.8109095936823</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841224963229</v>
+        <v>169.5841073072249</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0195199248555431</v>
+        <v>-0.01952001267395287</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009367785958406261</v>
+        <v>-0.0009366891129908295</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400817871094</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395894944585</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955858311417</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527518438138</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00609544270381579</v>
+        <v>0.006095353053086949</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016024215876</v>
+        <v>-0.02703007354316445</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422393798828</v>
+        <v>170.3422546386719</v>
       </c>
       <c r="C17" t="n">
-        <v>170.561702379452</v>
+        <v>170.5617176578999</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332085052758</v>
+        <v>166.3320999523285</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763267714875</v>
+        <v>168.6763418810487</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634541386375</v>
+        <v>0.01455643629502945</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -876,7 +876,7 @@
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847521966356759</v>
+        <v>0.03847512663982333</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -981,22 +981,22 @@
         <v>45917</v>
       </c>
       <c r="B23" t="n">
-        <v>169.8829803466797</v>
+        <v>169.8829956054688</v>
       </c>
       <c r="C23" t="n">
-        <v>172.7860287607356</v>
+        <v>172.7860442802747</v>
       </c>
       <c r="D23" t="n">
-        <v>168.007484117061</v>
+        <v>168.0074992073941</v>
       </c>
       <c r="E23" t="n">
-        <v>172.2273696616015</v>
+        <v>172.2273851309623</v>
       </c>
       <c r="F23" t="n">
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624663238682878</v>
+        <v>-0.02624654492487588</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1020,7 +1020,7 @@
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494055886175818</v>
+        <v>0.034940465904016</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035400390625</v>
+        <v>178.0035247802734</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9840093083128</v>
+        <v>181.9839937083107</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888599052367</v>
+        <v>175.7888448362941</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350878652714</v>
+        <v>181.5350723037516</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821196229186118</v>
+        <v>-0.02821204559530932</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1116,7 +1116,7 @@
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182577209651543</v>
+        <v>-0.008182492189240609</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340484619141</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022123120565</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462321155116</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448041170831</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601032967798278</v>
+        <v>0.02601041378766245</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1236,7 +1236,7 @@
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537407649362168</v>
+        <v>0.003537325381961498</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715698242188</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050265070322</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369333277354</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378247179256</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723587692724298</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0110862321012164</v>
+        <v>-0.01108615148198644</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886536282782095</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1428,7 +1428,7 @@
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817204507600701</v>
+        <v>0.02817213093671711</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820892333984</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599908268075</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493465774322</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755357241106875</v>
+        <v>0.007755441369297289</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590696970089</v>
+        <v>-0.003165673913464562</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491058349609</v>
+        <v>179.84912109375</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015566720687</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375148363812</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070509305708</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485759817631104</v>
+        <v>-0.00485751374626664</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1620,7 +1620,7 @@
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829092822517</v>
+        <v>0.01042820520129983</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323181152344</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="C51" t="n">
-        <v>191.541093665248</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D51" t="n">
-        <v>187.979619148197</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359033209746</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910846500516</v>
+        <v>0.02807919058326869</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981990486196963</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729406961805</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870481318289</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565693232556</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971455471800998</v>
+        <v>-0.001971530859184778</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855285644531</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="C56" t="n">
-        <v>210.834859926228</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D56" t="n">
-        <v>205.068676268978</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826573279554</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02167997565918256</v>
+        <v>0.02168012836941968</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151031494141</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824819294599</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569099225941</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5147991590425</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958817011962867</v>
+        <v>-0.03958816719273994</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751463119384</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368072509766</v>
+        <v>193.3368225097656</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218083488666</v>
+        <v>195.4218237722109</v>
       </c>
       <c r="D63" t="n">
-        <v>190.673190567689</v>
+        <v>190.6732056162565</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522164876445</v>
+        <v>195.2522318976041</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331767584859</v>
+        <v>0.00331341095243709</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581020859363238</v>
+        <v>-0.03581028469071756</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154693603516</v>
+        <v>189.7154846191406</v>
       </c>
       <c r="C65" t="n">
-        <v>190.553458007553</v>
+        <v>190.5534733337414</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1483942490048</v>
+        <v>180.1484087383153</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229435613052</v>
+        <v>182.4229582335574</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771382279154077</v>
+        <v>0.01771390464612344</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2028,7 +2028,7 @@
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877265156263563</v>
+        <v>-0.01877273048260975</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0742034912109</v>
+        <v>186.0741882324219</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109971087465</v>
+        <v>187.4109817403353</v>
       </c>
       <c r="D68" t="n">
-        <v>182.3930205111681</v>
+        <v>182.39300555425</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483273978252</v>
+        <v>184.3483122805645</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174000170858</v>
+        <v>0.02845165566477292</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152479724769053</v>
+        <v>-0.03152471782905131</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524688720703</v>
+        <v>178.4524536132812</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188859589464</v>
+        <v>184.1188702156436</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166776199441</v>
+        <v>172.5166628687019</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068289121023</v>
+        <v>180.806813452001</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743078144453632</v>
+        <v>-0.009743162817541062</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.020516696793347</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2172,7 +2172,7 @@
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591076013973348</v>
+        <v>-0.0259108417558972</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291625976562</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728380763597</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140014756398</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958985688627</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0137217719481173</v>
+        <v>0.01372168593222045</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808501178249078</v>
+        <v>-0.01808492846544285</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.489990234375</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690869073362</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648983244765</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3423189563235</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649728438465226</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0262908935547</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162492379485</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D76" t="n">
-        <v>179.5697738081794</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E76" t="n">
-        <v>181.325561672047</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559255349970263</v>
+        <v>0.008559426101467649</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526716745872</v>
+        <v>-0.01030543487972591</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053512845051</v>
+        <v>0.02116062209880032</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168365478516</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5611139779305</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741810893209</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E80" t="n">
-        <v>182.213626289633</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721399899417375</v>
+        <v>0.01721391514737669</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864265695677</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920356049676</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E81" t="n">
-        <v>185.12679644575</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125912631224192</v>
+        <v>-0.003125748033105724</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509674072266</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469957406681</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150239281505</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5381918075859</v>
+        <v>184.538176449994</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433411769608655</v>
+        <v>-0.006433576610347602</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770933102352</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2589,22 +2589,22 @@
         <v>46013</v>
       </c>
       <c r="B90" t="n">
-        <v>183.2611694335938</v>
+        <v>183.2611541748047</v>
       </c>
       <c r="C90" t="n">
-        <v>183.7300734141942</v>
+        <v>183.730058116363</v>
       </c>
       <c r="D90" t="n">
-        <v>181.9243013805983</v>
+        <v>181.9242862331203</v>
       </c>
       <c r="E90" t="n">
-        <v>183.4906282252173</v>
+        <v>183.4906129473229</v>
       </c>
       <c r="F90" t="n">
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491794177123418</v>
+        <v>0.014917857266596</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682800292969</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8879950077845</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4729984678863</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428423541149</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005061362821149</v>
+        <v>0.03005078265538064</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.00317109577323571</v>
+        <v>-0.003171176350336591</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2661,22 +2661,22 @@
         <v>46017</v>
       </c>
       <c r="B93" t="n">
-        <v>190.085205078125</v>
+        <v>190.0851898193359</v>
       </c>
       <c r="C93" t="n">
-        <v>192.240166195598</v>
+        <v>192.2401507638228</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5611125998212</v>
+        <v>187.5610975436497</v>
       </c>
       <c r="E93" t="n">
-        <v>189.4766285187414</v>
+        <v>189.4766133088049</v>
       </c>
       <c r="F93" t="n">
         <v>139740300</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01017978755564442</v>
+        <v>0.01017970646506039</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>120006100</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.01212409563967642</v>
+        <v>-0.01212401633949489</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -2757,22 +2757,22 @@
         <v>46024</v>
       </c>
       <c r="B97" t="n">
-        <v>188.4091339111328</v>
+        <v>188.4091186523438</v>
       </c>
       <c r="C97" t="n">
-        <v>192.4795957147097</v>
+        <v>192.479580126264</v>
       </c>
       <c r="D97" t="n">
-        <v>187.8204997023152</v>
+        <v>187.8204844911982</v>
       </c>
       <c r="E97" t="n">
-        <v>189.3968130035911</v>
+        <v>189.3967976648124</v>
       </c>
       <c r="F97" t="n">
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01260053054261179</v>
+        <v>0.01260044853460296</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2796,7 +2796,7 @@
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386553447189375</v>
+        <v>-0.003865453797424312</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2829,22 +2829,22 @@
         <v>46029</v>
       </c>
       <c r="B100" t="n">
-        <v>188.6685180664062</v>
+        <v>188.6685028076172</v>
       </c>
       <c r="C100" t="n">
-        <v>190.9232365533545</v>
+        <v>190.9232211122124</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1244680675316</v>
+        <v>186.1244530144955</v>
       </c>
       <c r="E100" t="n">
-        <v>188.1297854095839</v>
+        <v>188.1297701943655</v>
       </c>
       <c r="F100" t="n">
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987164191344933</v>
+        <v>0.00998708250744107</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2868,7 +2868,7 @@
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152187943302564</v>
+        <v>-0.02152180029744644</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124328613281</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293584396101</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3778995796448</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8896858985649</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436963075249476</v>
+        <v>-0.01436954843994676</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134991091711691</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3189,22 +3189,22 @@
         <v>46051</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0605773925781</v>
+        <v>192.0605621337891</v>
       </c>
       <c r="C115" t="n">
-        <v>193.0283141326731</v>
+        <v>193.0282987969995</v>
       </c>
       <c r="D115" t="n">
-        <v>185.6256380470483</v>
+        <v>185.625623299501</v>
       </c>
       <c r="E115" t="n">
-        <v>190.8933105997472</v>
+        <v>190.8932954336949</v>
       </c>
       <c r="F115" t="n">
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.00516915900963677</v>
+        <v>0.005169079151165157</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3213,22 +3213,22 @@
         <v>46052</v>
       </c>
       <c r="B116" t="n">
-        <v>190.6838073730469</v>
+        <v>190.6837921142578</v>
       </c>
       <c r="C116" t="n">
-        <v>194.0359639826301</v>
+        <v>194.0359484555967</v>
       </c>
       <c r="D116" t="n">
-        <v>189.0276790286862</v>
+        <v>189.0276639024229</v>
       </c>
       <c r="E116" t="n">
-        <v>190.7636224379378</v>
+        <v>190.7636071727618</v>
       </c>
       <c r="F116" t="n">
         <v>179489500</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.007168415497976421</v>
+        <v>-0.00716841606749119</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -3252,7 +3252,7 @@
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888085082614911</v>
+        <v>-0.0288807731158095</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963439941406</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2079034382237</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205647824287</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298386502086</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497174300496052</v>
+        <v>0.02497166051482758</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893114950312197</v>
+        <v>-0.007893035105149604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063232421875</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088208357837</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D124" t="n">
-        <v>188.329312674443</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007142509167</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.008008964809924857</v>
+        <v>0.00800904593061702</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410312537218</v>
+        <v>-0.01636418228460701</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130808403767</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7616860728079</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3256935584433</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0118155220086027</v>
+        <v>0.01181560567193918</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627283983140582</v>
+        <v>0.01627275579951704</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768768310547</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856807673048</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059297314624</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344638821937</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833441238607</v>
+        <v>0.01021825301539225</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113848413379699</v>
+        <v>0.009113929721387581</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583587646484</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364076167612</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8896973916963</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164652690549</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456128825383422</v>
+        <v>-0.05456121004512637</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164629289442512</v>
+        <v>-0.04164637217148226</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0540008544922</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317240302905</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2323067871125</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E136" t="n">
-        <v>174.601438160182</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985494874285899</v>
+        <v>0.02985486242594537</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296539306641</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776603660684</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069564334623</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0732983803544</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331663634113589</v>
+        <v>-0.01331646982798718</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660656891157819</v>
+        <v>0.01660648255510222</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048614501953</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333155363547</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4071960911633</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.420134514761</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010798076634313</v>
+        <v>-0.03010806418782519</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716230855539603</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7281,12 +7281,36 @@
         <v>236.0599975585938</v>
       </c>
       <c r="F285" t="n">
-        <v>134914600</v>
+        <v>135167800</v>
       </c>
       <c r="G285" t="n">
         <v>0.01338471943914588</v>
       </c>
       <c r="H285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B286" t="n">
+        <v>238.8999938964844</v>
+      </c>
+      <c r="C286" t="n">
+        <v>240.1000061035156</v>
+      </c>
+      <c r="D286" t="n">
+        <v>235.1499938964844</v>
+      </c>
+      <c r="E286" t="n">
+        <v>236.0899963378906</v>
+      </c>
+      <c r="F286" t="n">
+        <v>126639900</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0.02115835440398528</v>
+      </c>
+      <c r="H286" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:H287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709014892578</v>
+        <v>174.9709167480469</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694397588381</v>
+        <v>175.5694550698242</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870566311777</v>
+        <v>168.3870713158056</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414684152183</v>
+        <v>174.741483653999</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366504264196933</v>
+        <v>-0.001366417175785561</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -564,7 +564,7 @@
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394545758820588</v>
+        <v>-0.002394632757571458</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701171875</v>
+        <v>179.3701324462891</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4649859155824</v>
+        <v>181.4650013525793</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380531425805</v>
+        <v>176.1380681264219</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9136974002478</v>
+        <v>177.913712535141</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022523041638013</v>
+        <v>0.01022531635496304</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253326416016</v>
+        <v>181.3253173828125</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438110385745</v>
+        <v>181.9437957277396</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725671170498</v>
+        <v>178.3725521067403</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195091893087</v>
+        <v>179.6194940740671</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090045256567307</v>
+        <v>0.01090028150092892</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557464599609</v>
+        <v>181.15576171875</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435685875041</v>
+        <v>182.0435839210746</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618623689453</v>
+        <v>178.6618774176739</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348064912021</v>
+        <v>181.5348217819195</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009352591784613784</v>
+        <v>-0.0009350909542572561</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874430930079446</v>
+        <v>-0.007874598727247717</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538757324219</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141646735497</v>
+        <v>177.714180280125</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7263967599338</v>
+        <v>172.7264119284913</v>
       </c>
       <c r="E11" t="n">
-        <v>177.674269227683</v>
+        <v>177.6742848307548</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324652152828622</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -732,7 +732,7 @@
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952001267395287</v>
+        <v>-0.01952009877813865</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026214599609</v>
+        <v>170.2026062011719</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882512542426</v>
+        <v>171.9882358353705</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668876205481</v>
+        <v>168.4668725173688</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415475595936</v>
+        <v>170.6415322614545</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009366891129908295</v>
+        <v>-0.000936778679744843</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -780,7 +780,7 @@
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095353053086949</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114349365234</v>
+        <v>166.6114196777344</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6165125346066</v>
+        <v>168.6164970921864</v>
       </c>
       <c r="D15" t="n">
-        <v>163.668654359155</v>
+        <v>163.6686393698748</v>
       </c>
       <c r="E15" t="n">
-        <v>167.618958764552</v>
+        <v>167.6189434134908</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703007354316445</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -828,7 +828,7 @@
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723476233777449</v>
+        <v>0.007723568524209856</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465667724609</v>
+        <v>176.7465515136719</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491345673521</v>
+        <v>179.8491190407138</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0582134178096</v>
+        <v>176.058198218447</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505624618324</v>
+        <v>179.2505469868697</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008458502230944687</v>
+        <v>-0.0008459364815304182</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3949890136719</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731234709029</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.0282531820179</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.34510547722</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668655369389429</v>
+        <v>0.003668828349043585</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251647949219</v>
+        <v>177.3251800537109</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225418052247</v>
+        <v>178.4225571584428</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929031464731</v>
+        <v>174.0929181271268</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501343169162</v>
+        <v>175.2501493971494</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.000393608743619156</v>
+        <v>-0.0003936087097625718</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620208740234</v>
+        <v>174.4620361328125</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757538913052</v>
+        <v>177.0757693786965</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632159334845</v>
+        <v>173.9632311486472</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769489507663</v>
+        <v>176.5769643945311</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614629078640273</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -981,22 +981,22 @@
         <v>45917</v>
       </c>
       <c r="B23" t="n">
-        <v>169.8829956054688</v>
+        <v>169.8829803466797</v>
       </c>
       <c r="C23" t="n">
-        <v>172.7860442802747</v>
+        <v>172.7860287607356</v>
       </c>
       <c r="D23" t="n">
-        <v>168.0074992073941</v>
+        <v>168.007484117061</v>
       </c>
       <c r="E23" t="n">
-        <v>172.2273851309623</v>
+        <v>172.2273696616015</v>
       </c>
       <c r="F23" t="n">
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624654492487588</v>
+        <v>-0.02624671755319263</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1020,7 +1020,7 @@
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.034940465904016</v>
+        <v>0.03494055886175818</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477264404297</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543599509016</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612823170602</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E25" t="n">
-        <v>175.3498836843894</v>
+        <v>175.349898865447</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439670001024075</v>
+        <v>0.002439756788046976</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711578369141</v>
+        <v>183.1711730957031</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089135963474</v>
+        <v>184.1089289332547</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924356467209</v>
+        <v>174.2924501658818</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810218455756</v>
+        <v>174.8810364137678</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928238699195052</v>
+        <v>0.0392823835910463</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035247802734</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9839937083107</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888448362941</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350723037516</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204559530932</v>
+        <v>-0.02821204324514892</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470123291016</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3502935078314</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807575937583</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403228895943</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182492189240609</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653198242188</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291695578261</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162207499007</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.062985089831</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068647130534231</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830455718369</v>
+        <v>0.002813830697929731</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053991824341894</v>
+        <v>0.020540005843803</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715545654297</v>
+        <v>187.1715850830078</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050110254035</v>
+        <v>189.9050419886609</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369182511207</v>
+        <v>184.9369484043502</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378093314507</v>
+        <v>188.7378401044004</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587692724298</v>
+        <v>-0.006723425742952704</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108615148198644</v>
+        <v>-0.01108631272043314</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626288358566</v>
+        <v>0.01829618052309101</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1437,22 +1437,22 @@
         <v>45944</v>
       </c>
       <c r="B42" t="n">
-        <v>179.5997009277344</v>
+        <v>179.5997161865234</v>
       </c>
       <c r="C42" t="n">
-        <v>184.3583041970053</v>
+        <v>184.3583198600852</v>
       </c>
       <c r="D42" t="n">
-        <v>179.2704878489981</v>
+        <v>179.2705030798172</v>
       </c>
       <c r="E42" t="n">
-        <v>184.3283771191491</v>
+        <v>184.3283927796865</v>
       </c>
       <c r="F42" t="n">
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402090212326881</v>
+        <v>-0.04402082090329285</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001922607422</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281395182556</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D43" t="n">
-        <v>176.866254560341</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3583147400375</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110851888737052</v>
+        <v>-0.001111021714327642</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1500,7 +1500,7 @@
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038676736099</v>
+        <v>0.01101047275832534</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7821044921875</v>
+        <v>182.7820739746094</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6600061588844</v>
+        <v>183.6599754947305</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3203666523256</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493615830456</v>
+        <v>179.7493315718189</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755441369297289</v>
+        <v>0.007755273112916461</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165673913464562</v>
+        <v>-0.003165507480461738</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1557,22 +1557,22 @@
         <v>45951</v>
       </c>
       <c r="B47" t="n">
-        <v>180.7270050048828</v>
+        <v>180.7270202636719</v>
       </c>
       <c r="C47" t="n">
-        <v>182.3530987175338</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="D47" t="n">
-        <v>179.370254993042</v>
+        <v>179.3702701372806</v>
       </c>
       <c r="E47" t="n">
-        <v>182.3530987175338</v>
+        <v>182.3531141136141</v>
       </c>
       <c r="F47" t="n">
         <v>124240200</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.008103418112909044</v>
+        <v>-0.008103334367036585</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.84912109375</v>
+        <v>179.8491363525391</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015721983185</v>
+        <v>183.0015877245683</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375297972393</v>
+        <v>176.3375447580973</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070662621498</v>
+        <v>180.7070815937288</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485751374626664</v>
+        <v>-0.004857513336146591</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1620,7 +1620,7 @@
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042820520129983</v>
+        <v>0.01042811947438915</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323333740234</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="C51" t="n">
-        <v>191.5411089646758</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D51" t="n">
-        <v>187.9796341631504</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359184602369</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807910846500516</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495300292969</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644582837766</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513320204045</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886067715161</v>
+        <v>192.588592118433</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981982498653692</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.545166015625</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828666070652</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905729140704</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482921843539</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989603608371594</v>
+        <v>0.02989603835835264</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050750732422</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672637579894</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286166610889</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596680014167</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448238730316</v>
+        <v>-0.02004448386811519</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729250244422</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870329046891</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565537660584</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971530859184778</v>
+        <v>-0.001971380233034448</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1788,7 +1788,7 @@
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168012836941968</v>
+        <v>0.02168005119548289</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003173828125</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699244802363</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4824106282661</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580848487537</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003722181935406077</v>
+        <v>0.0003721368699238781</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742645263672</v>
+        <v>198.5742492675781</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621367771523</v>
+        <v>199.4621214501376</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268264223904</v>
+        <v>193.3268115668235</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6436639125443</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793249204463202</v>
+        <v>0.05793249675415924</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959052117289374</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368225097656</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218237722109</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6732056162565</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522318976041</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00331341095243709</v>
+        <v>0.003313331767584859</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133758544922</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824307616844</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105757073767</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933635318434</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581028469071756</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154846191406</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="C65" t="n">
-        <v>190.5534733337414</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1484087383153</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229582335574</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771390464612344</v>
+        <v>0.0177137394870075</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540069580078</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482645458532</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794576828592</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E66" t="n">
-        <v>185.525507871713</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877273048260975</v>
+        <v>-0.01877257113277342</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146927787025</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0741882324219</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109817403353</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D68" t="n">
-        <v>182.39300555425</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483122805645</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165566477292</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2085,22 +2085,22 @@
         <v>45981</v>
       </c>
       <c r="B69" t="n">
-        <v>180.208251953125</v>
+        <v>180.2082366943359</v>
       </c>
       <c r="C69" t="n">
-        <v>195.5315406452363</v>
+        <v>195.5315240889771</v>
       </c>
       <c r="D69" t="n">
-        <v>179.4201468289569</v>
+        <v>179.4201316368992</v>
       </c>
       <c r="E69" t="n">
-        <v>195.4816571057099</v>
+        <v>195.4816405536745</v>
       </c>
       <c r="F69" t="n">
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152471782905131</v>
+        <v>-0.03152487925147596</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524536132812</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188702156436</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166628687019</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E70" t="n">
-        <v>180.806813452001</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743162817541062</v>
+        <v>-0.009742994296335628</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2148,7 +2148,7 @@
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.020516696793347</v>
+        <v>0.02051660953286172</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3949890136719</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341727058355</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447513765687</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919407266003</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0259108417558972</v>
+        <v>-0.02591075796874476</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372168593222045</v>
+        <v>0.01372168475193747</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492846544285</v>
+        <v>-0.01808492693090802</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649711013028865</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168212890625</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5610985176648</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741660895743</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E80" t="n">
-        <v>182.2136112701494</v>
+        <v>182.213626289633</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721399899417375</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125912631224192</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2589,22 +2589,22 @@
         <v>46013</v>
       </c>
       <c r="B90" t="n">
-        <v>183.2611541748047</v>
+        <v>183.2611694335938</v>
       </c>
       <c r="C90" t="n">
-        <v>183.730058116363</v>
+        <v>183.7300734141942</v>
       </c>
       <c r="D90" t="n">
-        <v>181.9242862331203</v>
+        <v>181.9243013805983</v>
       </c>
       <c r="E90" t="n">
-        <v>183.4906129473229</v>
+        <v>183.4906282252173</v>
       </c>
       <c r="F90" t="n">
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.014917857266596</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682952880859</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8880102762506</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4730132178061</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428571096804</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005078265538064</v>
+        <v>0.03005061362821149</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.003171176350336591</v>
+        <v>-0.00317109577323571</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2661,22 +2661,22 @@
         <v>46017</v>
       </c>
       <c r="B93" t="n">
-        <v>190.0851898193359</v>
+        <v>190.085205078125</v>
       </c>
       <c r="C93" t="n">
-        <v>192.2401507638228</v>
+        <v>192.240166195598</v>
       </c>
       <c r="D93" t="n">
-        <v>187.5610975436497</v>
+        <v>187.5611125998212</v>
       </c>
       <c r="E93" t="n">
-        <v>189.4766133088049</v>
+        <v>189.4766285187414</v>
       </c>
       <c r="F93" t="n">
         <v>139740300</v>
       </c>
       <c r="G93" t="n">
-        <v>0.01017970646506039</v>
+        <v>0.01017978755564442</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>120006100</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.01212401633949489</v>
+        <v>-0.01212409563967642</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -2757,22 +2757,22 @@
         <v>46024</v>
       </c>
       <c r="B97" t="n">
-        <v>188.4091186523438</v>
+        <v>188.4091339111328</v>
       </c>
       <c r="C97" t="n">
-        <v>192.479580126264</v>
+        <v>192.4795957147097</v>
       </c>
       <c r="D97" t="n">
-        <v>187.8204844911982</v>
+        <v>187.8204997023152</v>
       </c>
       <c r="E97" t="n">
-        <v>189.3967976648124</v>
+        <v>189.3968130035911</v>
       </c>
       <c r="F97" t="n">
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01260044853460296</v>
+        <v>0.01260053054261179</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2796,7 +2796,7 @@
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.003865453797424312</v>
+        <v>-0.00386553447189375</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2829,22 +2829,22 @@
         <v>46029</v>
       </c>
       <c r="B100" t="n">
-        <v>188.6685028076172</v>
+        <v>188.6685180664062</v>
       </c>
       <c r="C100" t="n">
-        <v>190.9232211122124</v>
+        <v>190.9232365533545</v>
       </c>
       <c r="D100" t="n">
-        <v>186.1244530144955</v>
+        <v>186.1244680675316</v>
       </c>
       <c r="E100" t="n">
-        <v>188.1297701943655</v>
+        <v>188.1297854095839</v>
       </c>
       <c r="F100" t="n">
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.00998708250744107</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2868,7 +2868,7 @@
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152180029744644</v>
+        <v>-0.02152187943302564</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124481201172</v>
+        <v>182.7124328613281</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293738083791</v>
+        <v>184.0293584396101</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779146434709</v>
+        <v>180.3778995796448</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8897012556695</v>
+        <v>183.8896858985649</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436954843994676</v>
+        <v>-0.01436963075249476</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134991091711691</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3189,22 +3189,22 @@
         <v>46051</v>
       </c>
       <c r="B115" t="n">
-        <v>192.0605621337891</v>
+        <v>192.0605773925781</v>
       </c>
       <c r="C115" t="n">
-        <v>193.0282987969995</v>
+        <v>193.0283141326731</v>
       </c>
       <c r="D115" t="n">
-        <v>185.625623299501</v>
+        <v>185.6256380470483</v>
       </c>
       <c r="E115" t="n">
-        <v>190.8932954336949</v>
+        <v>190.8933105997472</v>
       </c>
       <c r="F115" t="n">
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169079151165157</v>
+        <v>0.00516915900963677</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3213,22 +3213,22 @@
         <v>46052</v>
       </c>
       <c r="B116" t="n">
-        <v>190.6837921142578</v>
+        <v>190.6838073730469</v>
       </c>
       <c r="C116" t="n">
-        <v>194.0359484555967</v>
+        <v>194.0359639826301</v>
       </c>
       <c r="D116" t="n">
-        <v>189.0276639024229</v>
+        <v>189.0276790286862</v>
       </c>
       <c r="E116" t="n">
-        <v>190.7636071727618</v>
+        <v>190.7636224379378</v>
       </c>
       <c r="F116" t="n">
         <v>179489500</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.00716841606749119</v>
+        <v>-0.007168415497976421</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -3252,7 +3252,7 @@
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.0288807731158095</v>
+        <v>-0.02888085082614911</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963287353516</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2078878887748</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205500126207</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298238555102</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497166051482758</v>
+        <v>0.02497174300496052</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893035105149604</v>
+        <v>-0.007893114950312197</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063385009766</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088363522974</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D124" t="n">
-        <v>188.3293278304631</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007297023972</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800904593061702</v>
+        <v>0.008008964809924857</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636418228460701</v>
+        <v>-0.01636410312537218</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560567193918</v>
+        <v>0.0118155220086027</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768615722656</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856654675195</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059147845697</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344488846578</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021825301539225</v>
+        <v>0.01021833441238607</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113929721387581</v>
+        <v>0.009113848413379699</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583740234375</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364236513225</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8897126034445</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164813019665</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456121004512637</v>
+        <v>-0.05456128825383422</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164637217148226</v>
+        <v>-0.04164629289442512</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539855957031</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317086895539</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322921838959</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014235260267</v>
+        <v>174.601438160182</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486242594537</v>
+        <v>0.02985494874285899</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296691894531</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776756968921</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069714269912</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0733135069376</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331646982798718</v>
+        <v>-0.01331663634113589</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660656891157819</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048614501953</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333155363547</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4071960911633</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420134514761</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010806418782519</v>
+        <v>-0.03010798076634313</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716230855539603</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7305,12 +7305,36 @@
         <v>236.0899963378906</v>
       </c>
       <c r="F286" t="n">
-        <v>126639900</v>
+        <v>127171500</v>
       </c>
       <c r="G286" t="n">
         <v>0.02115835440398528</v>
       </c>
       <c r="H286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B287" t="n">
+        <v>239.2400054931641</v>
+      </c>
+      <c r="C287" t="n">
+        <v>243.3699951171875</v>
+      </c>
+      <c r="D287" t="n">
+        <v>238.9299926757812</v>
+      </c>
+      <c r="E287" t="n">
+        <v>242.1000061035156</v>
+      </c>
+      <c r="F287" t="n">
+        <v>100868800</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0.001423238197431731</v>
+      </c>
+      <c r="H287" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H287"/>
+  <dimension ref="A1:H288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545806884766</v>
+        <v>177.5545654296875</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531037491236</v>
+        <v>178.1530884388983</v>
       </c>
       <c r="D6" t="n">
-        <v>170.781182841084</v>
+        <v>170.7811681643912</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877371490149</v>
+        <v>172.1877223514448</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207335414736</v>
+        <v>0.01720198593724254</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701324462891</v>
+        <v>179.3701171875</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650013525793</v>
+        <v>181.4649859155824</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380681264219</v>
+        <v>176.1380531425805</v>
       </c>
       <c r="E7" t="n">
-        <v>177.913712535141</v>
+        <v>177.9136974002478</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531635496304</v>
+        <v>0.01022531723371234</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253173828125</v>
+        <v>181.3253326416016</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9437957277396</v>
+        <v>181.9438110385745</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725521067403</v>
+        <v>178.3725671170498</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6194940740671</v>
+        <v>179.6195091893087</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090028150092892</v>
+        <v>0.01090045256567307</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009350909542572561</v>
+        <v>-0.0009351750270146786</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874598727247717</v>
+        <v>-0.007874514497031027</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538909912109</v>
+        <v>173.7538757324219</v>
       </c>
       <c r="C11" t="n">
-        <v>177.714180280125</v>
+        <v>177.7141646735497</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264119284913</v>
+        <v>172.7263967599338</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6742848307548</v>
+        <v>177.674269227683</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635455335401</v>
+        <v>-0.03324652152828622</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3621978759766</v>
+        <v>170.3622131347656</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9582896803931</v>
+        <v>171.9583050821389</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109095936823</v>
+        <v>166.810924534394</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841073072249</v>
+        <v>169.5841224963229</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952009877813865</v>
+        <v>-0.0195199248555431</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.000936778679744843</v>
+        <v>-0.0009368681625865349</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400512695312</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.439558941325</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955557135668</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527215200144</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095443250276666</v>
+        <v>0.006095353599539832</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016265075109</v>
+        <v>-0.02703007595174933</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982543945312</v>
+        <v>167.8982696533203</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417807313731</v>
+        <v>170.5417962304089</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406114031506</v>
+        <v>166.9406265749079</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401190912332</v>
+        <v>167.140134281122</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723568524209856</v>
+        <v>0.007723660107302521</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422546386719</v>
+        <v>170.3422698974609</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617176578999</v>
+        <v>170.5617329363479</v>
       </c>
       <c r="D17" t="n">
-        <v>166.3320999523285</v>
+        <v>166.332114851899</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763418810487</v>
+        <v>168.6763569906099</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643629502945</v>
+        <v>0.01455643497212367</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512663982333</v>
+        <v>0.03847512319332802</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465515136719</v>
+        <v>176.7465362548828</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491190407138</v>
+        <v>179.8491035140756</v>
       </c>
       <c r="D19" t="n">
-        <v>176.058198218447</v>
+        <v>176.0581830190845</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505469868697</v>
+        <v>179.2505315119071</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008459364815304182</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -924,7 +924,7 @@
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668828349043585</v>
+        <v>0.003668914997253303</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251800537109</v>
+        <v>177.3251647949219</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225571584428</v>
+        <v>178.4225418052247</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929181271268</v>
+        <v>174.0929031464731</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501493971494</v>
+        <v>175.2501343169162</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936087097625718</v>
+        <v>-0.0003936947256518719</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620361328125</v>
+        <v>174.4620208740234</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757693786965</v>
+        <v>177.0757538913052</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632311486472</v>
+        <v>173.9632159334845</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769643945311</v>
+        <v>176.5769489507663</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629078640273</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624671755319263</v>
+        <v>-0.02624663238682878</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653045654297</v>
+        <v>177.2652893066406</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291540783439</v>
+        <v>179.8291385988617</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162058826927</v>
+        <v>172.7161910154847</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629701066951</v>
+        <v>174.0629551235593</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068473920816773</v>
+        <v>0.004068387491782843</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7640991210938</v>
+        <v>177.7641296386719</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403244887289</v>
+        <v>179.3403552769049</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118813132914</v>
+        <v>174.5119112725463</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441426621237</v>
+        <v>177.7441731762758</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830697929731</v>
+        <v>0.002814089176637058</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153747558594</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602300506758</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890327563757</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987552370008</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.020540005843803</v>
+        <v>0.02053974480577181</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041378766245</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.79248046875</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="C33" t="n">
-        <v>187.6903232769056</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604518817237</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972606974542</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537325381961498</v>
+        <v>0.0035374073593748</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385375976562</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="C34" t="n">
-        <v>190.59337868299</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105195355423</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E34" t="n">
-        <v>189.146847340247</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812223009789566</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715850830078</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050419886609</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369484043502</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378401044004</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723425742952704</v>
+        <v>-0.00672366812316183</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1308,7 +1308,7 @@
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108631272043314</v>
+        <v>-0.01108615148198644</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699035644531</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556185865847</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155435929421</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207340107304</v>
+        <v>187.52074924116</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817213093671711</v>
+        <v>0.02817221444483309</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402082090329285</v>
+        <v>-0.04402089854789248</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001770019531</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281238318171</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D43" t="n">
-        <v>176.8662395170747</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3582990595379</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001111021714327642</v>
+        <v>-0.001110936754343372</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754577636719</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419455690647</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944521048813</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101047275832534</v>
+        <v>0.01101030171288664</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820739746094</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599754947305</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203666523256</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493315718189</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755273112916461</v>
+        <v>0.007755442021748715</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165507480461738</v>
+        <v>-0.003165590696970089</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491363525391</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015877245683</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375447580973</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070815937288</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004857513336146591</v>
+        <v>-0.00485768219622118</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988793025541</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042811947438915</v>
+        <v>0.01042837577039868</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1644,7 +1644,7 @@
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250756853454439</v>
+        <v>0.02250748267812286</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323181152344</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="C51" t="n">
-        <v>191.541093665248</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D51" t="n">
-        <v>187.979619148197</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359033209746</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910846500516</v>
+        <v>0.02807919058326869</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495147705078</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644428640734</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513174538508</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E52" t="n">
-        <v>192.588592118433</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982498653692</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1716,7 +1716,7 @@
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989603835835264</v>
+        <v>0.02989595999882533</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050598144531</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672482532724</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286015136062</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596525726598</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448386811519</v>
+        <v>-0.02004440999182711</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971380233034448</v>
+        <v>-0.001971455471800998</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003021240234</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699092076593</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823961188316</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580698535366</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721368699238781</v>
+        <v>0.0003720555463071484</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742492675781</v>
+        <v>198.5742797851562</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621214501376</v>
+        <v>199.462152104167</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268115668235</v>
+        <v>193.3268412779572</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436639125443</v>
+        <v>194.6436938260565</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793249675415924</v>
+        <v>0.05793274534380033</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959052117289374</v>
+        <v>-0.02959067030875928</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.926513671875</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.358293814419</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2205942185541</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.9416897271721</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808163091331894</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0742034912109</v>
+        <v>186.0741882324219</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109971087465</v>
+        <v>187.4109817403353</v>
       </c>
       <c r="D68" t="n">
-        <v>182.3930205111681</v>
+        <v>182.39300555425</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483273978252</v>
+        <v>184.3483122805645</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845174240124138</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2085,22 +2085,22 @@
         <v>45981</v>
       </c>
       <c r="B69" t="n">
-        <v>180.2082366943359</v>
+        <v>180.208251953125</v>
       </c>
       <c r="C69" t="n">
-        <v>195.5315240889771</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D69" t="n">
-        <v>179.4201316368992</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E69" t="n">
-        <v>195.4816405536745</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="F69" t="n">
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152487925147596</v>
+        <v>-0.03152471782905131</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524688720703</v>
+        <v>178.4524536132812</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188859589464</v>
+        <v>184.1188702156436</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166776199441</v>
+        <v>172.5166628687019</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068289121023</v>
+        <v>180.806813452001</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009742994296335628</v>
+        <v>-0.009743162817541062</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051660953286172</v>
+        <v>0.02051661128715887</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2172,7 +2172,7 @@
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591075796874476</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291625976562</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728380763597</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140014756398</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958985688627</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372168475193747</v>
+        <v>0.01372159873604817</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492693090802</v>
+        <v>-0.01808484361385299</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030543487972591</v>
+        <v>-0.01030535058927451</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.951904296875</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="C78" t="n">
-        <v>184.0892423581687</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398901129937</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1960032737075</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116062209880032</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2340,7 +2340,7 @@
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00528960288028224</v>
+        <v>-0.005289519918164731</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168365478516</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5611139779305</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741810893209</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E80" t="n">
-        <v>182.213626289633</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721399899417375</v>
+        <v>0.01721391514737669</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864265695677</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920356049676</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E81" t="n">
-        <v>185.12679644575</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125912631224192</v>
+        <v>-0.003125748033105724</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509674072266</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469957406681</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150239281505</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5381918075859</v>
+        <v>184.538176449994</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433411769608655</v>
+        <v>-0.006433576610347602</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770933102352</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114044189453</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3931976659576</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123291208211</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871831157045</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266452212921567</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256277519845034</v>
+        <v>0.007256189498619836</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3051147460938</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733214473424</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916907151964</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485164107673</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111747940743541</v>
+        <v>0.008111661183153096</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2532,7 +2532,7 @@
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814991702143256</v>
+        <v>-0.03814983424509077</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682800292969</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8879950077845</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4729984678863</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428423541149</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005061362821149</v>
+        <v>0.03005069689074391</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.00317109577323571</v>
+        <v>-0.003171176350336591</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021728515625</v>
+        <v>187.1021881103516</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5487999407664</v>
+        <v>188.5488153175326</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4935963146986</v>
+        <v>186.4936115238563</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005508490403</v>
+        <v>187.8005661647843</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612838827051545</v>
+        <v>-0.003612757568446812</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646209716797</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151405796458</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546497967401</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E96" t="n">
-        <v>189.127461449755</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545375898472038</v>
+        <v>-0.005545538552702456</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2772,7 +2772,7 @@
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01260053054261179</v>
+        <v>0.0126006135839718</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8028869628906</v>
+        <v>186.8029022216797</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213703933745</v>
+        <v>191.7213860539245</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838692947835</v>
+        <v>186.3838845193456</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752284670132</v>
+        <v>190.0752439930999</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677861544826856</v>
+        <v>-0.004677780243029006</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987164191344933</v>
+        <v>0.009987081691657185</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080169677734</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074981045344</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685228499072</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152187943302564</v>
+        <v>-0.02152196030920583</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009727675505442068</v>
+        <v>-0.0009726849758688871</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124328613281</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293584396101</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3778995796448</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8896858985649</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436963075249476</v>
+        <v>-0.01436954843994676</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134991091711691</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952270507812</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="C107" t="n">
-        <v>189.99540517049</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455833269296</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385795892923</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383931140514608</v>
+        <v>-0.004383849373637116</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3036,7 +3036,7 @@
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381676302343995</v>
+        <v>-0.0438168415518142</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.0346832275391</v>
+        <v>186.03466796875</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784906596197</v>
+        <v>188.6784751839824</v>
       </c>
       <c r="D112" t="n">
-        <v>185.555808059744</v>
+        <v>185.5557928402329</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230748442759</v>
+        <v>186.7230595290241</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.00639415348837058</v>
+        <v>-0.006394234985120373</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099371233637481</v>
+        <v>0.01099379525930511</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728912353516</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009553855833</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3968053634026</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E114" t="n">
-        <v>190.8234748728661</v>
+        <v>190.823459633995</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591342985123156</v>
+        <v>0.01591334872193784</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.00516915900963677</v>
+        <v>0.005169239280915949</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766967773438</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557504766133</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4484052141589</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629812920276</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888085082614911</v>
+        <v>-0.02888093084756926</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839299457635047</v>
+        <v>-0.02839291451472381</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833404541016</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="C119" t="n">
-        <v>179.160756412826</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086645338761</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410414348666</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221377522338</v>
+        <v>-0.0341021289659974</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787292480469</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4071986282528</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307075914073</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5215964583249</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.01326140468949821</v>
+        <v>-0.0132614035251003</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771423339844</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634266395524</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923819783884</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E121" t="n">
-        <v>176.277498975506</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0787177112002726</v>
+        <v>0.07871770419569057</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3372,7 +3372,7 @@
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497174300496052</v>
+        <v>0.024971658454912</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063232421875</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088208357837</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D124" t="n">
-        <v>188.329312674443</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007142509167</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.008008964809924857</v>
+        <v>0.00800904593061702</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5035858154297</v>
+        <v>186.5036010742188</v>
       </c>
       <c r="C125" t="n">
-        <v>193.1580126884611</v>
+        <v>193.158028491682</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745817463215</v>
+        <v>186.0745969700116</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793648877844</v>
+        <v>192.5793806436633</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410312537218</v>
+        <v>-0.01636410180845216</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832244873047</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622780376601</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660713803529</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E126" t="n">
-        <v>187.042320465516</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209266545793198</v>
+        <v>-0.02209282728038808</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130808403767</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7616860728079</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3256935584433</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0118155220086027</v>
+        <v>0.01181569032381558</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627283983140582</v>
+        <v>0.01627275579951704</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613342285156</v>
+        <v>187.4613189697266</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900957055448</v>
+        <v>187.9900804037161</v>
       </c>
       <c r="D129" t="n">
-        <v>185.2265733363672</v>
+        <v>185.226558259481</v>
       </c>
       <c r="E129" t="n">
-        <v>186.62329889396</v>
+        <v>186.6232837033845</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004255251289267958</v>
+        <v>-0.0004256064912840918</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768768310547</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856807673048</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059297314624</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344638821937</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833441238607</v>
+        <v>0.01021833524412785</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028289794922</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972200828311</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374267327081</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531700210539</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113848413379699</v>
+        <v>0.009113849147715847</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786747007672789</v>
+        <v>0.006786827395534711</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583587646484</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364076167612</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8896973916963</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164652690549</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456128825383422</v>
+        <v>-0.05456121004512637</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637395256691</v>
+        <v>182.1637238018573</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682453114839</v>
+        <v>175.9682301224481</v>
       </c>
       <c r="E135" t="n">
-        <v>180.8268714126474</v>
+        <v>180.82685580423</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164629289442512</v>
+        <v>-0.04164645489360941</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0540008544922</v>
+        <v>182.0539703369141</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317240302905</v>
+        <v>183.0316933488174</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2323067871125</v>
+        <v>174.2322775806792</v>
       </c>
       <c r="E136" t="n">
-        <v>174.601438160182</v>
+        <v>174.6014088918714</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985494874285899</v>
+        <v>0.02985486500292533</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296539306641</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776603660684</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069564334623</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0732983803544</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331663634113589</v>
+        <v>-0.01331638712945649</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660656891157819</v>
+        <v>0.01660648255510222</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119873046875</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6303076754259</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647422536165</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470550179114</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.00163899427668035</v>
+        <v>0.001638910718471109</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3804,7 +3804,7 @@
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010798076634313</v>
+        <v>-0.03010789985650675</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7329,12 +7329,36 @@
         <v>242.1000061035156</v>
       </c>
       <c r="F287" t="n">
-        <v>100868800</v>
+        <v>101701900</v>
       </c>
       <c r="G287" t="n">
         <v>0.001423238197431731</v>
       </c>
       <c r="H287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B288" t="n">
+        <v>237.4700012207031</v>
+      </c>
+      <c r="C288" t="n">
+        <v>239.0800018310547</v>
+      </c>
+      <c r="D288" t="n">
+        <v>236.3800048828125</v>
+      </c>
+      <c r="E288" t="n">
+        <v>237.6900024414062</v>
+      </c>
+      <c r="F288" t="n">
+        <v>81485100</v>
+      </c>
+      <c r="G288" t="n">
+        <v>-0.00739844604505957</v>
+      </c>
+      <c r="H288" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H288"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545654296875</v>
+        <v>177.5545806884766</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1530884388983</v>
+        <v>178.1531037491236</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811681643912</v>
+        <v>170.781182841084</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877223514448</v>
+        <v>172.1877371490149</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720198593724254</v>
+        <v>0.01720207335414736</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531723371234</v>
+        <v>0.01022523041638013</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.15576171875</v>
+        <v>181.1557464599609</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435839210746</v>
+        <v>182.0435685875041</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618774176739</v>
+        <v>178.6618623689453</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348217819195</v>
+        <v>181.5348064912021</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009351750270146786</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874514497031027</v>
+        <v>-0.00787451516030313</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324652152828622</v>
+        <v>-0.03324643945211436</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622131347656</v>
+        <v>170.3622283935547</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583050821389</v>
+        <v>171.9583204838847</v>
       </c>
       <c r="D12" t="n">
-        <v>166.810924534394</v>
+        <v>166.8109394751057</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841224963229</v>
+        <v>169.5841376854209</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0195199248555431</v>
+        <v>-0.01951983703713334</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368681625865349</v>
+        <v>-0.0009369576454122397</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400512695312</v>
+        <v>171.2400817871094</v>
       </c>
       <c r="C14" t="n">
-        <v>171.439558941325</v>
+        <v>171.4395894944585</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955557135668</v>
+        <v>168.9955858311417</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527215200144</v>
+        <v>170.1527518438138</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095353599539832</v>
+        <v>0.006095532901013501</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703007595174933</v>
+        <v>-0.02703024934973741</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422698974609</v>
+        <v>170.3422546386719</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617329363479</v>
+        <v>170.5617176578999</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332114851899</v>
+        <v>166.3320999523285</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763569906099</v>
+        <v>168.6763418810487</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643497212367</v>
+        <v>0.01455634409096618</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512319332802</v>
+        <v>0.03847512663982333</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008460227399664788</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251647949219</v>
+        <v>177.3251495361328</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225418052247</v>
+        <v>178.4225264520066</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929031464731</v>
+        <v>174.0928881658194</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501343169162</v>
+        <v>175.250119236683</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947256518719</v>
+        <v>-0.0003937807415412831</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -972,7 +972,7 @@
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614620751539797</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477416992188</v>
+        <v>176.2477264404297</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543753314711</v>
+        <v>177.6543599509016</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612974471592</v>
+        <v>174.7612823170602</v>
       </c>
       <c r="E25" t="n">
-        <v>175.349898865447</v>
+        <v>175.3498836843894</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439756788046976</v>
+        <v>0.002439670001024075</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1068,7 +1068,7 @@
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0392823835910463</v>
+        <v>0.03928247356775705</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470275878906</v>
+        <v>176.5470123291016</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3502935078314</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807727171775</v>
+        <v>174.9807575937583</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403383898065</v>
+        <v>179.3403228895943</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.008182577209651543</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2652893066406</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291385988617</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7161910154847</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629551235593</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387491782843</v>
+        <v>0.004068560701492752</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641296386719</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403552769049</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5119112725463</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441731762758</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002814089176637058</v>
+        <v>0.002813916776754244</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053974480577181</v>
+        <v>0.02053983240613322</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340637207031</v>
+        <v>186.1340484619141</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022276338177</v>
+        <v>186.9022123120565</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462469572146</v>
+        <v>181.0462321155116</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448190078555</v>
+        <v>181.6448041170831</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041597539022</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1236,7 +1236,7 @@
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0035374073593748</v>
+        <v>0.003537489626782131</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385528564453</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="C34" t="n">
-        <v>190.593394116267</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105347272827</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E34" t="n">
-        <v>189.1468626563914</v>
+        <v>189.146847340247</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223009789566</v>
+        <v>0.008812141321341782</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.00672366812316183</v>
+        <v>-0.006723587692724298</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965576171875</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7825209975275</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918479831437</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566599139491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108615148198644</v>
+        <v>-0.01108606995897354</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694945166262119</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199532691778505</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829618052309101</v>
+        <v>0.01829626288358566</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886536282782095</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1428,7 +1428,7 @@
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817221444483309</v>
+        <v>0.02817212858411589</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246398925781</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925557149365</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602938591047</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988793025541</v>
+        <v>179.988777912505</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042837577039868</v>
+        <v>0.01042829092822517</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250748267812286</v>
+        <v>0.02250765250109055</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807910615919784</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495300292969</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644582837766</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513320204045</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886067715161</v>
+        <v>192.588592118433</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981974113173093</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.545166015625</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482921843539</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989595999882533</v>
+        <v>0.02989611444324924</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004440999182711</v>
+        <v>-0.02004448238730316</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151184082031</v>
+        <v>198.2151031494141</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824975937368</v>
+        <v>203.4824819294599</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569251230167</v>
+        <v>197.4569099225941</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5148147488263</v>
+        <v>202.5147991590425</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958816719273994</v>
+        <v>-0.03958824112615977</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751463119384</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304931640625</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476859949454</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.934559185592</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505570232203</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.03652469938585123</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003720555463071484</v>
+        <v>0.0003719741924403941</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742797851562</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="C61" t="n">
-        <v>199.462152104167</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268412779572</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436938260565</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793274534380033</v>
+        <v>0.05793266405042918</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959067030875928</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368072509766</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218083488666</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D63" t="n">
-        <v>190.673190567689</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522164876445</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331767584859</v>
+        <v>0.003313252582732629</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581012967027952</v>
+        <v>-0.03581005357317613</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.926513671875</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.358293814419</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2205942185541</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9416897271721</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808163091331894</v>
+        <v>-0.02808154894469495</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0741882324219</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109817403353</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D68" t="n">
-        <v>182.39300555425</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483122805645</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174240124138</v>
+        <v>0.02845174000170858</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152471782905131</v>
+        <v>-0.03152479724769053</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524536132812</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188702156436</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166628687019</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E70" t="n">
-        <v>180.806813452001</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743162817541062</v>
+        <v>-0.009743078144453632</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2148,7 +2148,7 @@
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051661128715887</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808484361385299</v>
+        <v>-0.01808492846544285</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649711013028865</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607818603516</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.0139471586436</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819333075974</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6472262869623</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030535058927451</v>
+        <v>-0.01030526629882311</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116036298998392</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168212890625</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5610985176648</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741660895743</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E80" t="n">
-        <v>182.2136112701494</v>
+        <v>182.213626289633</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721399899417375</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125912631224192</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114196777344</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3932136047752</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123443447362</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871989054384</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266452212921567</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.8784332275391</v>
+        <v>175.87841796875</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0034500370577</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213802569945</v>
+        <v>174.6213651072644</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245903328353</v>
+        <v>177.5245749312296</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256189498619836</v>
+        <v>0.007256190132717499</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2508,7 +2508,7 @@
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111661183153096</v>
+        <v>0.008111748644499261</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814983424509077</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491794177123418</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021881103516</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5488153175326</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4936115238563</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005661647843</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612757568446812</v>
+        <v>-0.003612838827051545</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545538552702456</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8029022216797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213860539245</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838845193456</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752439930999</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780243029006</v>
+        <v>-0.004677861544826856</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987081691657185</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133270263672</v>
+        <v>186.6133117675781</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571344016907</v>
+        <v>189.2571189267257</v>
       </c>
       <c r="D106" t="n">
-        <v>185.895006678512</v>
+        <v>185.8949914784577</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0646079796491</v>
+        <v>186.0645927657271</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134974210895835</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952423095703</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="C107" t="n">
-        <v>189.9954207742267</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455985734289</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385950815971</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849373637116</v>
+        <v>-0.004383849732090828</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.654296875</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438168415518142</v>
+        <v>-0.04381668089652369</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948280612693632</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.03466796875</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784751839824</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D112" t="n">
-        <v>185.5557928402329</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230595290241</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.006394234985120373</v>
+        <v>-0.00639415348837058</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099379525930511</v>
+        <v>0.01099371233637481</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5036010742188</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="C125" t="n">
-        <v>193.158028491682</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745969700116</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793806436633</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410180845216</v>
+        <v>-0.01636418228460701</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209282728038808</v>
+        <v>-0.02209274727292232</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181569032381558</v>
+        <v>0.01181560666047221</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613189697266</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900804037161</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D129" t="n">
-        <v>185.226558259481</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E129" t="n">
-        <v>186.6232837033845</v>
+        <v>186.62329889396</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004256064912840918</v>
+        <v>-0.0004255251289267958</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768615722656</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856654675195</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059147845697</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344488846578</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833524412785</v>
+        <v>0.01021833441238607</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113849147715847</v>
+        <v>0.009113767839714404</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583740234375</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364236513225</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8897126034445</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164813019665</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456121004512637</v>
+        <v>-0.05456128825383422</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637238018573</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682301224481</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E135" t="n">
-        <v>180.82685580423</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164645489360941</v>
+        <v>-0.04164629289442512</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539703369141</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0316933488174</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322775806792</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014088918714</v>
+        <v>174.601438160182</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486500292533</v>
+        <v>0.02985494874285899</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296691894531</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776756968921</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069714269912</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0733135069376</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331638712945649</v>
+        <v>-0.01331663634113589</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660656891157819</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010789985650675</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7353,12 +7353,36 @@
         <v>237.6900024414062</v>
       </c>
       <c r="F288" t="n">
-        <v>81485100</v>
+        <v>81772400</v>
       </c>
       <c r="G288" t="n">
         <v>-0.00739844604505957</v>
       </c>
       <c r="H288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B289" t="n">
+        <v>230.4799957275391</v>
+      </c>
+      <c r="C289" t="n">
+        <v>237.0700073242188</v>
+      </c>
+      <c r="D289" t="n">
+        <v>229.8500061035156</v>
+      </c>
+      <c r="E289" t="n">
+        <v>234.9199981689453</v>
+      </c>
+      <c r="F289" t="n">
+        <v>118311700</v>
+      </c>
+      <c r="G289" t="n">
+        <v>-0.02943532007088168</v>
+      </c>
+      <c r="H289" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701171875</v>
+        <v>179.3701324462891</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4649859155824</v>
+        <v>181.4650013525793</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380531425805</v>
+        <v>176.1380681264219</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9136974002478</v>
+        <v>177.913712535141</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022523041638013</v>
+        <v>0.01022531635496304</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -636,7 +636,7 @@
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090045256567307</v>
+        <v>0.0109003665696572</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538757324219</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141646735497</v>
+        <v>177.714180280125</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7263967599338</v>
+        <v>172.7264119284913</v>
       </c>
       <c r="E11" t="n">
-        <v>177.674269227683</v>
+        <v>177.6742848307548</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643945211436</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -732,7 +732,7 @@
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01951983703713334</v>
+        <v>-0.01951992314133455</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026062011719</v>
+        <v>170.2025909423828</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882358353705</v>
+        <v>171.9882204164984</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668725173688</v>
+        <v>168.4668574141896</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415322614545</v>
+        <v>170.6415169633154</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009369576454122397</v>
+        <v>-0.000937047212150155</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400817871094</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395894944585</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955858311417</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527518438138</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095532901013501</v>
+        <v>0.006095533447482593</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114196777344</v>
+        <v>166.6114349365234</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164970921864</v>
+        <v>168.6165125346066</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686393698748</v>
+        <v>163.668654359155</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189434134908</v>
+        <v>167.618958764552</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703024934973741</v>
+        <v>-0.02703007354316445</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982696533203</v>
+        <v>167.8982391357422</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417962304089</v>
+        <v>170.5417652323373</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406265749079</v>
+        <v>166.9405962313932</v>
       </c>
       <c r="E16" t="n">
-        <v>167.140134281122</v>
+        <v>167.1401039013443</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723660107302521</v>
+        <v>0.007723384650693443</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634409096618</v>
+        <v>0.01455652849910916</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668914997253303</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251495361328</v>
+        <v>177.3251647949219</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225264520066</v>
+        <v>178.4225418052247</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0928881658194</v>
+        <v>174.0929031464731</v>
       </c>
       <c r="E21" t="n">
-        <v>175.250119236683</v>
+        <v>175.2501343169162</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807415412831</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -972,7 +972,7 @@
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614620751539797</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187866210938</v>
+        <v>175.8187713623047</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767318043244</v>
+        <v>176.6767164710769</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466271367534</v>
+        <v>172.5466121619453</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641783462465</v>
+        <v>173.5641632831282</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494055886175818</v>
+        <v>0.03494046904234804</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477264404297</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543599509016</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612823170602</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E25" t="n">
-        <v>175.3498836843894</v>
+        <v>175.349898865447</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439670001024075</v>
+        <v>0.00243984378681672</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711730957031</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089289332547</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924501658818</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810364137678</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928247356775705</v>
+        <v>0.03928229701524732</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204324514892</v>
+        <v>-0.02821196229186118</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470123291016</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3502935078314</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807575937583</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403228895943</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182577209651543</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1140,7 +1140,7 @@
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068560701492752</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813916776754244</v>
+        <v>0.002813830697929731</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053983240613322</v>
+        <v>0.02053992000650995</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340484619141</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022123120565</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462321155116</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448041170831</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041597539022</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.7924957275391</v>
+        <v>186.79248046875</v>
       </c>
       <c r="C33" t="n">
-        <v>187.690338609038</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604668683245</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972757932568</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537489626782131</v>
+        <v>0.003537325381961498</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812141321341782</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715545654297</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050110254035</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369182511207</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378093314507</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587692724298</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965576171875</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825209975275</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918479831437</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566599139491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108606995897354</v>
+        <v>-0.0110862321012164</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694945166262119</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097412109375</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="C39" t="n">
-        <v>194.8332119113436</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033405552435</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705422839889</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626288358566</v>
+        <v>0.01829626140377161</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886543837402468</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699188232422</v>
+        <v>187.8699340820312</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556339904095</v>
+        <v>189.6556493942343</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155586605101</v>
+        <v>185.5155737280782</v>
       </c>
       <c r="E41" t="n">
-        <v>187.52074924116</v>
+        <v>187.5207644715895</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817212858411589</v>
+        <v>0.02817229795294884</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402089854789248</v>
+        <v>-0.04402097619247958</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754425048828</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419301869027</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944368108431</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101030171288664</v>
+        <v>0.01101038676736099</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820892333984</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599908268075</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493465774322</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755442021748715</v>
+        <v>0.007755441369297289</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590696970089</v>
+        <v>-0.003165673913464562</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491058349609</v>
+        <v>179.84912109375</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015566720687</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375148363812</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070509305708</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485768219622118</v>
+        <v>-0.004857597766183885</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.724609375</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988762799469</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829092822517</v>
+        <v>0.01042812035913343</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1644,7 +1644,7 @@
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250765250109055</v>
+        <v>0.02250773835753361</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495147705078</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644428640734</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513174538508</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E52" t="n">
-        <v>192.588592118433</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981974113173093</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.545166015625</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828666070652</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905729140704</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482921843539</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989611444324924</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448238730316</v>
+        <v>-0.02004433759634028</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729406961805</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870481318289</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565693232556</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971455471800998</v>
+        <v>-0.001971530859184778</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855438232422</v>
+        <v>206.3855590820312</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348755139714</v>
+        <v>210.8348911017148</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0686914304077</v>
+        <v>205.0687065918373</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826726752522</v>
+        <v>207.5826880225491</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168005119548289</v>
+        <v>0.02168020390572556</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151031494141</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824819294599</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569099225941</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5147991590425</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958824112615977</v>
+        <v>-0.03958823819926593</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751463119384</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304931640625</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476859949454</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D59" t="n">
-        <v>185.934559185592</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505570232203</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652469938585123</v>
+        <v>-0.0365248560924305</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003719741924403941</v>
+        <v>0.0003721369001874475</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3367919921875</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4217929255223</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6731755191215</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522010776849</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313252582732629</v>
+        <v>0.003313331767584859</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005357317613</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808154894469495</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174000170858</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.02051660953286172</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341879937998</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447659257062</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E72" t="n">
-        <v>174.491955735681</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067635257405</v>
+        <v>-0.02591067418159221</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159873604817</v>
+        <v>0.01372151153989076</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492846544285</v>
+        <v>-0.01808484361385299</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899749755859</v>
+        <v>179.4899597167969</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690716163194</v>
+        <v>179.8690563253026</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648835948944</v>
+        <v>173.2648688653124</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3423041351479</v>
+        <v>174.3422893139723</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649702371590833</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263061523438</v>
+        <v>181.0263214111328</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162648499111</v>
+        <v>185.2162804618737</v>
       </c>
       <c r="D76" t="n">
-        <v>179.569788944198</v>
+        <v>179.5698040802165</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255769560617</v>
+        <v>181.3255922400764</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559426101467649</v>
+        <v>0.008559596852994122</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607818603516</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139471586436</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819333075974</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472262869623</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526629882311</v>
+        <v>-0.0103055183015206</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116036298998392</v>
+        <v>0.02116053693065423</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841613769531</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2289086763207</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876631773748</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4607020047171</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289519918164731</v>
+        <v>-0.005289603321452563</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168365478516</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5611139779305</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741810893209</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E80" t="n">
-        <v>182.213626289633</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721399899417375</v>
+        <v>0.01721400043751253</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2388,7 +2388,7 @@
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125912631224192</v>
+        <v>-0.003125830460996126</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114044189453</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3931976659576</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123291208211</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871831157045</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266452212921567</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.87841796875</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034500370577</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213651072644</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245749312296</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256190132717499</v>
+        <v>0.007256189498619836</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2508,7 +2508,7 @@
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111748644499261</v>
+        <v>0.008111661183153096</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808319091797</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779786425506</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154296257417</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123337767646</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386553447189375</v>
+        <v>-0.00386561545941666</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677861544826856</v>
+        <v>-0.004677780623340899</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080017089844</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074824738404</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685072554968</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152196030920583</v>
+        <v>-0.02152187943302564</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009726849758688871</v>
+        <v>-0.0009727675505442068</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.376220703125</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708543554723</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718432388734</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5681140987238</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.004704210650191332</v>
+        <v>0.00470412795042785</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124481201172</v>
+        <v>182.7124633789062</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293738083791</v>
+        <v>184.029389177148</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779146434709</v>
+        <v>180.3779297072971</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8897012556695</v>
+        <v>183.889716612774</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436954843994676</v>
+        <v>-0.01436938499763141</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133117675781</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571189267257</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D106" t="n">
-        <v>185.8949914784577</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0645927657271</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974210895835</v>
+        <v>0.02134974032598635</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952270507812</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="C107" t="n">
-        <v>189.99540517049</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455833269296</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385795892923</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849732090828</v>
+        <v>-0.004383849373637116</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.654296875</v>
+        <v>177.6543121337891</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542325986551</v>
+        <v>181.9542482267672</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953640623503</v>
+        <v>177.1953792817215</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753422141945</v>
+        <v>181.4753578011745</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381668089652369</v>
+        <v>-0.0438166772979951</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920440673828</v>
+        <v>182.8920288085938</v>
       </c>
       <c r="C109" t="n">
-        <v>184.9472325313386</v>
+        <v>184.947217101084</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835164834521</v>
+        <v>177.9835016341843</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6320081827799</v>
+        <v>178.6319932794081</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948280612693632</v>
+        <v>0.02948263181397048</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291414334357983</v>
+        <v>0.008291498456701074</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771575927734</v>
+        <v>184.9771728515625</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634420291942</v>
+        <v>186.5634574188361</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923963475411</v>
+        <v>174.1924107166939</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775135166603</v>
+        <v>176.2775280578147</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871770419569057</v>
+        <v>0.07871779317924998</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963439941406</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2079034382237</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205647824287</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298386502086</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.024971658454912</v>
+        <v>0.0249714914147583</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.0998382568359</v>
+        <v>188.099853515625</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306425866914</v>
+        <v>192.0306581643501</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808205923615</v>
+        <v>187.6808358171596</v>
       </c>
       <c r="E123" t="n">
-        <v>190.933219719687</v>
+        <v>190.9332352083219</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893114950312197</v>
+        <v>-0.00789295462474604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063385009766</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088363522974</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D124" t="n">
-        <v>188.3293278304631</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007297023972</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800904593061702</v>
+        <v>0.00800888303954661</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636418228460701</v>
+        <v>-0.01636410312537218</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832092285156</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622623874058</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660562233949</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E126" t="n">
-        <v>187.0423048169314</v>
+        <v>187.042320465516</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209274727292232</v>
+        <v>-0.02209266545793198</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3492,7 +3492,7 @@
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560666047221</v>
+        <v>0.0118155220086027</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768768310547</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856807673048</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059297314624</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344638821937</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833441238607</v>
+        <v>0.01021825301539225</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113767839714404</v>
+        <v>0.009113849147715847</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583587646484</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364076167612</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8896973916963</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164652690549</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456128825383422</v>
+        <v>-0.05456121004512637</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164629289442512</v>
+        <v>-0.04164637217148226</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0540008544922</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317240302905</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2323067871125</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E136" t="n">
-        <v>174.601438160182</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985494874285899</v>
+        <v>0.02985486242594537</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296539306641</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776603660684</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069564334623</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0732983803544</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331663634113589</v>
+        <v>-0.01331646982798718</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126861572266</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2688145383873</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396472340209</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187649948852</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660656891157819</v>
+        <v>0.01660639760928495</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638910718471109</v>
+        <v>0.001638994413631911</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -7377,12 +7377,36 @@
         <v>234.9199981689453</v>
       </c>
       <c r="F289" t="n">
-        <v>118311700</v>
+        <v>118697400</v>
       </c>
       <c r="G289" t="n">
         <v>-0.02943532007088168</v>
       </c>
       <c r="H289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B290" t="n">
+        <v>229.2799987792969</v>
+      </c>
+      <c r="C290" t="n">
+        <v>233.9199981689453</v>
+      </c>
+      <c r="D290" t="n">
+        <v>229.1100006103516</v>
+      </c>
+      <c r="E290" t="n">
+        <v>233.8399963378906</v>
+      </c>
+      <c r="F290" t="n">
+        <v>84470000</v>
+      </c>
+      <c r="G290" t="n">
+        <v>-0.005206512367610272</v>
+      </c>
+      <c r="H290" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519256591797</v>
+        <v>174.5519409179688</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672267555024</v>
+        <v>176.4672421817212</v>
       </c>
       <c r="D5" t="n">
-        <v>173.384789767114</v>
+        <v>173.3848049238756</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222540410346</v>
+        <v>174.4222692884882</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394632757571458</v>
+        <v>-0.002394545549998073</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -588,7 +588,7 @@
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207335414736</v>
+        <v>0.0172019844334983</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253326416016</v>
+        <v>181.3253173828125</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438110385745</v>
+        <v>181.9437957277396</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725671170498</v>
+        <v>178.3725521067403</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195091893087</v>
+        <v>179.6194940740671</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0109003665696572</v>
+        <v>0.01090028150092892</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009352591784613784</v>
+        <v>-0.0009351751057110613</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00787451516030313</v>
+        <v>-0.007874430930079446</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635455335401</v>
+        <v>-0.03324643662953308</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622283935547</v>
+        <v>170.3621978759766</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583204838847</v>
+        <v>171.9582896803931</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109394751057</v>
+        <v>166.8109095936823</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841376854209</v>
+        <v>169.5841073072249</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01951992314133455</v>
+        <v>-0.01952009877813865</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2025909423828</v>
+        <v>170.2026062011719</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882204164984</v>
+        <v>171.9882358353705</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668574141896</v>
+        <v>168.4668725173688</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415169633154</v>
+        <v>170.6415322614545</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.000937047212150155</v>
+        <v>-0.000936778679744843</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -780,7 +780,7 @@
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095533447482593</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114349365234</v>
+        <v>166.6114044189453</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6165125346066</v>
+        <v>168.6164816497661</v>
       </c>
       <c r="D15" t="n">
-        <v>163.668654359155</v>
+        <v>163.6686243805947</v>
       </c>
       <c r="E15" t="n">
-        <v>167.618958764552</v>
+        <v>167.6189280624296</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703007354316445</v>
+        <v>-0.02703025175833773</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -828,7 +828,7 @@
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723384650693443</v>
+        <v>0.007723569231558258</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422546386719</v>
+        <v>170.3422393798828</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617176578999</v>
+        <v>170.561702379452</v>
       </c>
       <c r="D17" t="n">
-        <v>166.3320999523285</v>
+        <v>166.332085052758</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763418810487</v>
+        <v>168.6763267714875</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455652849910916</v>
+        <v>0.01455643761793546</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512663982333</v>
+        <v>0.03847530924081588</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460227399664788</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731541223449</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028283464474</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451359862166</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003669001328727717</v>
+        <v>0.003668914997253303</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807076698219</v>
+        <v>-0.0003936947256518719</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187713623047</v>
+        <v>175.8187866210938</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767164710769</v>
+        <v>176.6767318043244</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466121619453</v>
+        <v>172.5466271367534</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641632831282</v>
+        <v>173.5641783462465</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494046904234804</v>
+        <v>0.03494055886175818</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00243984378681672</v>
+        <v>0.002439756788046976</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653045654297</v>
+        <v>177.2652893066406</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291540783439</v>
+        <v>179.8291385988617</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162058826927</v>
+        <v>172.7161910154847</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629701066951</v>
+        <v>174.0629551235593</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068473920816773</v>
+        <v>0.004068387491782843</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7640991210938</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403244887289</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118813132914</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441426621237</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830697929731</v>
+        <v>0.002814003097804996</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053992000650995</v>
+        <v>0.02053983240613322</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.79248046875</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="C33" t="n">
-        <v>187.6903232769056</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604518817237</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972606974542</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537325381961498</v>
+        <v>0.0035374073593748</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812141321341782</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1317,22 +1317,22 @@
         <v>45937</v>
       </c>
       <c r="B37" t="n">
-        <v>184.5977325439453</v>
+        <v>184.5977172851562</v>
       </c>
       <c r="C37" t="n">
-        <v>188.6081286768816</v>
+        <v>188.6081130865945</v>
       </c>
       <c r="D37" t="n">
-        <v>183.5602249269612</v>
+        <v>183.5602097539322</v>
       </c>
       <c r="E37" t="n">
-        <v>185.7848907820332</v>
+        <v>185.784875425114</v>
       </c>
       <c r="F37" t="n">
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694945388425074</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1356,7 +1356,7 @@
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199532691778505</v>
+        <v>0.02199541139559646</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097564697266</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="C39" t="n">
-        <v>194.833227386451</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033556943829</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705575158363</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626140377161</v>
+        <v>0.01829618052309101</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886543837402468</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699340820312</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556493942343</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155737280782</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207644715895</v>
+        <v>187.52074924116</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817229795294884</v>
+        <v>0.02817212858411589</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402097619247958</v>
+        <v>-0.04402089854789248</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001922607422</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281395182556</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D43" t="n">
-        <v>176.866254560341</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3583147400375</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110936754343372</v>
+        <v>-0.001111021714327642</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754577636719</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419455690647</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944521048813</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038676736099</v>
+        <v>0.01101038770384366</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7821044921875</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6600061588844</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493615830456</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755441369297289</v>
+        <v>0.007755442021748715</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165673913464562</v>
+        <v>-0.003165590696970089</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.84912109375</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015721983185</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375297972393</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070662621498</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004857597766183885</v>
+        <v>-0.00485768219622118</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.724609375</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925250516066</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602637385785</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988762799469</v>
+        <v>179.988793025541</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042812035913343</v>
+        <v>0.01042837577039868</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250773835753361</v>
+        <v>0.02250748267812286</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910615919784</v>
+        <v>0.02807919058326869</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050750732422</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672637579894</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286166610889</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596680014167</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004433759634028</v>
+        <v>-0.02004441147263381</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060577392578</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729250244422</v>
+        <v>207.4729563679188</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870329046891</v>
+        <v>201.5870633589687</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565537660584</v>
+        <v>205.9565848804529</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971530859184778</v>
+        <v>-0.001971304845645117</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855590820312</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348911017148</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0687065918373</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826880225491</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168020390572556</v>
+        <v>0.02167997402155764</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958823819926593</v>
+        <v>-0.03958816719273994</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434387207031</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4350026612236</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847643800754</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949275919373</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751478380745641</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304626464844</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476539294223</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345289438528</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505251524069</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.0365248560924305</v>
+        <v>-0.03652470224768178</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721369001874475</v>
+        <v>0.0003720555463071484</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983337402344</v>
+        <v>192.6983489990234</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529266552934</v>
+        <v>194.9529420926121</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427786999811</v>
+        <v>190.8427938118383</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935535589016</v>
+        <v>194.6935689756818</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959051889910702</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1956,7 +1956,7 @@
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331767584859</v>
+        <v>0.003313252320373383</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133911132812</v>
+        <v>186.4134063720703</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824463944715</v>
+        <v>190.9824620272586</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105907203728</v>
+        <v>183.4106057333689</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933791327836</v>
+        <v>190.5933947337238</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581012967027952</v>
+        <v>-0.03581005074692667</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2004,7 +2004,7 @@
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0177137394870075</v>
+        <v>0.01771365618248799</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808154894469495</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845174000170858</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051660953286172</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.734203281764</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447804748437</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919707447618</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067418159221</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372151153989076</v>
+        <v>0.01372168475193747</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808484361385299</v>
+        <v>-0.01808492693090802</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899597167969</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690563253026</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648688653124</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3422893139723</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649702371590833</v>
+        <v>0.01649711013028865</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263214111328</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162804618737</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D76" t="n">
-        <v>179.5698040802165</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255922400764</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559596852994122</v>
+        <v>0.008559426101467649</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.0103055183015206</v>
+        <v>-0.01030535058927451</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053693065423</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841461181641</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2288932293168</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876480440623</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4606866221248</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289603321452563</v>
+        <v>-0.005289519918164731</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721400043751253</v>
+        <v>0.01721391514737669</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864265695677</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920356049676</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E81" t="n">
-        <v>185.12679644575</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125830460996126</v>
+        <v>-0.003125748033105724</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509674072266</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469957406681</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150239281505</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5381918075859</v>
+        <v>184.538176449994</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433411769608655</v>
+        <v>-0.006433576610347602</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770933102352</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814983424509077</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021728515625</v>
+        <v>187.1021881103516</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5487999407664</v>
+        <v>188.5488153175326</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4935963146986</v>
+        <v>186.4936115238563</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005508490403</v>
+        <v>187.8005661647843</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612838827051545</v>
+        <v>-0.003612757568446812</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545538552702456</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808166503906</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779629368336</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154145267434</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123182227279</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386561545941666</v>
+        <v>-0.00386553447189375</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8028869628906</v>
+        <v>186.8029022216797</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213703933745</v>
+        <v>191.7213860539245</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838692947835</v>
+        <v>186.3838845193456</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752284670132</v>
+        <v>190.0752439930999</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780623340899</v>
+        <v>-0.004677780243029006</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987164191344933</v>
+        <v>0.009987081691657185</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080169677734</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074981045344</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685228499072</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152187943302564</v>
+        <v>-0.02152196030920583</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009727675505442068</v>
+        <v>-0.0009726849758688871</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.3762054443359</v>
+        <v>185.376220703125</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708389078061</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718281779948</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5680989064521</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.00470412795042785</v>
+        <v>0.004704210650191332</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124633789062</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="C105" t="n">
-        <v>184.029389177148</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779297072971</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E105" t="n">
-        <v>183.889716612774</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436938499763141</v>
+        <v>-0.01436954843994676</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974032598635</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6543121337891</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542482267672</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953792817215</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753578011745</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438166772979951</v>
+        <v>-0.0438168415518142</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920288085938</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="C109" t="n">
-        <v>184.947217101084</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835016341843</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6319932794081</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948263181397048</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291498456701074</v>
+        <v>0.008291414334357983</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.0346832275391</v>
+        <v>186.03466796875</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784906596197</v>
+        <v>188.6784751839824</v>
       </c>
       <c r="D112" t="n">
-        <v>185.555808059744</v>
+        <v>185.5557928402329</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230748442759</v>
+        <v>186.7230595290241</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.00639415348837058</v>
+        <v>-0.006394234985120373</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099371233637481</v>
+        <v>0.01099379525930511</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771728515625</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634574188361</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1924107166939</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775280578147</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871779317924998</v>
+        <v>0.07871770419569057</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963287353516</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2078878887748</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205500126207</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298238555102</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0249714914147583</v>
+        <v>0.024971658454912</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.099853515625</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306581643501</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808358171596</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E123" t="n">
-        <v>190.9332352083219</v>
+        <v>190.933219719687</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.00789295462474604</v>
+        <v>-0.007893114950312197</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063232421875</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088208357837</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D124" t="n">
-        <v>188.329312674443</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007142509167</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800888303954661</v>
+        <v>0.00800904593061702</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5035858154297</v>
+        <v>186.5036010742188</v>
       </c>
       <c r="C125" t="n">
-        <v>193.1580126884611</v>
+        <v>193.158028491682</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745817463215</v>
+        <v>186.0745969700116</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793648877844</v>
+        <v>192.5793806436633</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410312537218</v>
+        <v>-0.01636410180845216</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832244873047</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622780376601</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660713803529</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E126" t="n">
-        <v>187.042320465516</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209266545793198</v>
+        <v>-0.02209282728038808</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130808403767</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7616860728079</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3256935584433</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0118155220086027</v>
+        <v>0.01181569032381558</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627283983140582</v>
+        <v>0.01627275579951704</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613342285156</v>
+        <v>187.4613189697266</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900957055448</v>
+        <v>187.9900804037161</v>
       </c>
       <c r="D129" t="n">
-        <v>185.2265733363672</v>
+        <v>185.226558259481</v>
       </c>
       <c r="E129" t="n">
-        <v>186.62329889396</v>
+        <v>186.6232837033845</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004255251289267958</v>
+        <v>-0.0004256064912840918</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3564,7 +3564,7 @@
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021825301539225</v>
+        <v>0.01021833524412785</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637395256691</v>
+        <v>182.1637238018573</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682453114839</v>
+        <v>175.9682301224481</v>
       </c>
       <c r="E135" t="n">
-        <v>180.8268714126474</v>
+        <v>180.82685580423</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164637217148226</v>
+        <v>-0.04164645489360941</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539855957031</v>
+        <v>182.0539703369141</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317086895539</v>
+        <v>183.0316933488174</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322921838959</v>
+        <v>174.2322775806792</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014235260267</v>
+        <v>174.6014088918714</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486242594537</v>
+        <v>0.02985486500292533</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3732,7 +3732,7 @@
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331646982798718</v>
+        <v>-0.01331638712945649</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126708984375</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2687991412151</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396322236537</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187499528396</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660639760928495</v>
+        <v>0.01660648255510222</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638994413631911</v>
+        <v>0.001638910718471109</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010789985650675</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709167480469</v>
+        <v>174.9709014892578</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694550698242</v>
+        <v>175.5694397588381</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870713158056</v>
+        <v>168.3870566311777</v>
       </c>
       <c r="E4" t="n">
-        <v>174.741483653999</v>
+        <v>174.7414684152183</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417175785561</v>
+        <v>-0.001366504264196933</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519409179688</v>
+        <v>174.5519256591797</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672421817212</v>
+        <v>176.4672267555024</v>
       </c>
       <c r="D5" t="n">
-        <v>173.3848049238756</v>
+        <v>173.384789767114</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222692884882</v>
+        <v>174.4222540410346</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394545549998073</v>
+        <v>-0.002394545758820588</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -588,7 +588,7 @@
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0172019844334983</v>
+        <v>0.01720207335414736</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253173828125</v>
+        <v>181.3253479003906</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9437957277396</v>
+        <v>181.9438263494094</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725521067403</v>
+        <v>178.3725821273594</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6194940740671</v>
+        <v>179.6195243045502</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090028150092892</v>
+        <v>0.01090045163838549</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009351751057110613</v>
+        <v>-0.0009353432511975956</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874430930079446</v>
+        <v>-0.00787451516030313</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643662953308</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3621978759766</v>
+        <v>170.3622283935547</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9582896803931</v>
+        <v>171.9583204838847</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109095936823</v>
+        <v>166.8109394751057</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841073072249</v>
+        <v>169.5841376854209</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952009877813865</v>
+        <v>-0.01951992314133455</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026062011719</v>
+        <v>170.2025909423828</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882358353705</v>
+        <v>171.9882204164984</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668725173688</v>
+        <v>168.4668574141896</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415322614545</v>
+        <v>170.6415169633154</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.000936778679744843</v>
+        <v>-0.000937047212150155</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -780,7 +780,7 @@
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095443250276666</v>
+        <v>0.006095533447482593</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114044189453</v>
+        <v>166.6114196777344</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164816497661</v>
+        <v>168.6164970921864</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686243805947</v>
+        <v>163.6686393698748</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189280624296</v>
+        <v>167.6189434134908</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703025175833773</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982391357422</v>
+        <v>167.8982543945312</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417652323373</v>
+        <v>170.5417807313731</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9405962313932</v>
+        <v>166.9406114031506</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401039013443</v>
+        <v>167.1401190912332</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723569231558258</v>
+        <v>0.007723568524209856</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422393798828</v>
+        <v>170.3422546386719</v>
       </c>
       <c r="C17" t="n">
-        <v>170.561702379452</v>
+        <v>170.5617176578999</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332085052758</v>
+        <v>166.3320999523285</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763267714875</v>
+        <v>168.6763418810487</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643761793546</v>
+        <v>0.01455643629502945</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847530924081588</v>
+        <v>0.03847512663982333</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008460227399664788</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668914997253303</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947256518719</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620208740234</v>
+        <v>174.4620361328125</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757538913052</v>
+        <v>177.0757693786965</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632159334845</v>
+        <v>173.9632311486472</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769489507663</v>
+        <v>176.5769643945311</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614620612602058</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -981,22 +981,22 @@
         <v>45917</v>
       </c>
       <c r="B23" t="n">
-        <v>169.8829803466797</v>
+        <v>169.8829650878906</v>
       </c>
       <c r="C23" t="n">
-        <v>172.7860287607356</v>
+        <v>172.7860132411964</v>
       </c>
       <c r="D23" t="n">
-        <v>168.007484117061</v>
+        <v>168.0074690267279</v>
       </c>
       <c r="E23" t="n">
-        <v>172.2273696616015</v>
+        <v>172.2273541922408</v>
       </c>
       <c r="F23" t="n">
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624663238682878</v>
+        <v>-0.02624680501513788</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187866210938</v>
+        <v>175.8187713623047</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767318043244</v>
+        <v>176.6767164710769</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466271367534</v>
+        <v>172.5466121619453</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641783462465</v>
+        <v>173.5641632831282</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494055886175818</v>
+        <v>0.03494056200009887</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439756788046976</v>
+        <v>0.00243984378681672</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2652893066406</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291385988617</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7161910154847</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629551235593</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387491782843</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1164,7 +1164,7 @@
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002814003097804996</v>
+        <v>0.002813916776754244</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153594970703</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602146114836</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890176259668</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987400973632</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053983240613322</v>
+        <v>0.02053991824341894</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041378766245</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.7924957275391</v>
+        <v>186.79248046875</v>
       </c>
       <c r="C33" t="n">
-        <v>187.690338609038</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604668683245</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972757932568</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0035374073593748</v>
+        <v>0.003537325381961498</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385375976562</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="C34" t="n">
-        <v>190.59337868299</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105195355423</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E34" t="n">
-        <v>189.146847340247</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812141321341782</v>
+        <v>0.008812305418101074</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723587148282584</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1317,22 +1317,22 @@
         <v>45937</v>
       </c>
       <c r="B37" t="n">
-        <v>184.5977172851562</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="C37" t="n">
-        <v>188.6081130865945</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D37" t="n">
-        <v>183.5602097539322</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E37" t="n">
-        <v>185.784875425114</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="F37" t="n">
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694945388425074</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1356,7 +1356,7 @@
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199541139559646</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001770019531</v>
+        <v>179.4002075195312</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281238318171</v>
+        <v>184.428155204694</v>
       </c>
       <c r="D43" t="n">
-        <v>176.8662395170747</v>
+        <v>176.8662696036074</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3582990595379</v>
+        <v>184.358330420537</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001111021714327642</v>
+        <v>-0.001110851794359102</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754425048828</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419301869027</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944368108431</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038770384366</v>
+        <v>0.0110103007764113</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820892333984</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599908268075</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493465774322</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755442021748715</v>
+        <v>0.007755441369297289</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590696970089</v>
+        <v>-0.003165673913464562</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491058349609</v>
+        <v>179.84912109375</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015566720687</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375148363812</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070509305708</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485768219622118</v>
+        <v>-0.004857597766183885</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246398925781</v>
+        <v>181.724609375</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925557149365</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602938591047</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988793025541</v>
+        <v>179.988762799469</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042837577039868</v>
+        <v>0.01042812035913343</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250748267812286</v>
+        <v>0.02250773835753361</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323333740234</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="C51" t="n">
-        <v>191.5411089646758</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D51" t="n">
-        <v>187.9796341631504</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359184602369</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807902404094098</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981990486196963</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989595999882533</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050598144531</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672482532724</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286015136062</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596525726598</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004441147263381</v>
+        <v>-0.02004440999182711</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060577392578</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729563679188</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870633589687</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565848804529</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971304845645117</v>
+        <v>-0.001971530859184778</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855438232422</v>
+        <v>206.3855590820312</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348755139714</v>
+        <v>210.8348911017148</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0686914304077</v>
+        <v>205.0687065918373</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826726752522</v>
+        <v>207.5826880225491</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02167997402155764</v>
+        <v>0.02168020390572556</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958816719273994</v>
+        <v>-0.03958823819926593</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434234619141</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4349867997753</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847491650603</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949120548774</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751478380745641</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652470224768178</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983489990234</v>
+        <v>192.6983184814453</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529420926121</v>
+        <v>194.9529112179747</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427938118383</v>
+        <v>190.8427635881239</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935689756818</v>
+        <v>194.6935381421213</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959051889910702</v>
+        <v>-0.02959067258255743</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368072509766</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218083488666</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D63" t="n">
-        <v>190.673190567689</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522164876445</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313252320373383</v>
+        <v>0.003313332029950544</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4134063720703</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824620272586</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4106057333689</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933947337238</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005074692667</v>
+        <v>-0.03581005357317613</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2004,7 +2004,7 @@
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771365618248799</v>
+        <v>0.0177137394870075</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808154894469495</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174000170858</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.02051660953286172</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341879937998</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447659257062</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E72" t="n">
-        <v>174.491955735681</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067635257405</v>
+        <v>-0.02591067418159221</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291625976562</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728380763597</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140014756398</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958985688627</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372168475193747</v>
+        <v>0.01372151153989076</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492693090802</v>
+        <v>-0.01808484361385299</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899749755859</v>
+        <v>179.4899597167969</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690716163194</v>
+        <v>179.8690563253026</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648835948944</v>
+        <v>173.2648688653124</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3423041351479</v>
+        <v>174.3422893139723</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649711013028865</v>
+        <v>0.01649702371590833</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2268,7 +2268,7 @@
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559426101467649</v>
+        <v>0.008559511841057521</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607818603516</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.0139471586436</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819333075974</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6472262869623</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030535058927451</v>
+        <v>-0.01030526629882311</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116036298998392</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841613769531</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2289086763207</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876631773748</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4607020047171</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289519918164731</v>
+        <v>-0.005289603321452563</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721400043751253</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125830460996126</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814983424509077</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491794177123418</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021881103516</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5488153175326</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4936115238563</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005661647843</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612757568446812</v>
+        <v>-0.003612838827051545</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545538552702456</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808319091797</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779786425506</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154296257417</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123337767646</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386553447189375</v>
+        <v>-0.00386561545941666</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8029022216797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213860539245</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838845193456</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752439930999</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780243029006</v>
+        <v>-0.004677780623340899</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987081691657185</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080017089844</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074824738404</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685072554968</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152196030920583</v>
+        <v>-0.02152187943302564</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009726849758688871</v>
+        <v>-0.0009727675505442068</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.376220703125</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708543554723</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718432388734</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5681140987238</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.004704210650191332</v>
+        <v>0.00470412795042785</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124481201172</v>
+        <v>182.7124633789062</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293738083791</v>
+        <v>184.029389177148</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779146434709</v>
+        <v>180.3779297072971</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8897012556695</v>
+        <v>183.889716612774</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436954843994676</v>
+        <v>-0.01436938499763141</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134974032598635</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.6543121337891</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542482267672</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953792817215</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753578011745</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438168415518142</v>
+        <v>-0.0438166772979951</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920440673828</v>
+        <v>182.8920288085938</v>
       </c>
       <c r="C109" t="n">
-        <v>184.9472325313386</v>
+        <v>184.947217101084</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835164834521</v>
+        <v>177.9835016341843</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6320081827799</v>
+        <v>178.6319932794081</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948263181397048</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291414334357983</v>
+        <v>0.008291498456701074</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.03466796875</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784751839824</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D112" t="n">
-        <v>185.5557928402329</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230595290241</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.006394234985120373</v>
+        <v>-0.00639415348837058</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099379525930511</v>
+        <v>0.01099371233637481</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771575927734</v>
+        <v>184.9771728515625</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634420291942</v>
+        <v>186.5634574188361</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923963475411</v>
+        <v>174.1924107166939</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775135166603</v>
+        <v>176.2775280578147</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871770419569057</v>
+        <v>0.07871779317924998</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963439941406</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2079034382237</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205647824287</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298386502086</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.024971658454912</v>
+        <v>0.0249714914147583</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.0998382568359</v>
+        <v>188.099853515625</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306425866914</v>
+        <v>192.0306581643501</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808205923615</v>
+        <v>187.6808358171596</v>
       </c>
       <c r="E123" t="n">
-        <v>190.933219719687</v>
+        <v>190.9332352083219</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893114950312197</v>
+        <v>-0.00789295462474604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063385009766</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088363522974</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D124" t="n">
-        <v>188.3293278304631</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007297023972</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800904593061702</v>
+        <v>0.00800888303954661</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5036010742188</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="C125" t="n">
-        <v>193.158028491682</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745969700116</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793806436633</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410180845216</v>
+        <v>-0.01636410312537218</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832092285156</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622623874058</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660562233949</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E126" t="n">
-        <v>187.0423048169314</v>
+        <v>187.042320465516</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209282728038808</v>
+        <v>-0.02209266545793198</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181569032381558</v>
+        <v>0.0118155220086027</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613189697266</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900804037161</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D129" t="n">
-        <v>185.226558259481</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E129" t="n">
-        <v>186.6232837033845</v>
+        <v>186.62329889396</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004256064912840918</v>
+        <v>-0.0004255251289267958</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3564,7 +3564,7 @@
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833524412785</v>
+        <v>0.01021825301539225</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637238018573</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682301224481</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E135" t="n">
-        <v>180.82685580423</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164645489360941</v>
+        <v>-0.04164637217148226</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539703369141</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0316933488174</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322775806792</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014088918714</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486500292533</v>
+        <v>0.02985486242594537</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3732,7 +3732,7 @@
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331638712945649</v>
+        <v>-0.01331646982798718</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126861572266</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2688145383873</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396472340209</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187649948852</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660639760928495</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638910718471109</v>
+        <v>0.001638994413631911</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010789985650675</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H290"/>
+  <dimension ref="A1:H291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519256591797</v>
+        <v>174.5519409179688</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672267555024</v>
+        <v>176.4672421817212</v>
       </c>
       <c r="D5" t="n">
-        <v>173.384789767114</v>
+        <v>173.3848049238756</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222540410346</v>
+        <v>174.4222692884882</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394545758820588</v>
+        <v>-0.002394458551239653</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -588,7 +588,7 @@
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207335414736</v>
+        <v>0.0172019844334983</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701324462891</v>
+        <v>179.3701171875</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650013525793</v>
+        <v>181.4649859155824</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380681264219</v>
+        <v>176.1380531425805</v>
       </c>
       <c r="E7" t="n">
-        <v>177.913712535141</v>
+        <v>177.9136974002478</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531635496304</v>
+        <v>0.01022523041638013</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253479003906</v>
+        <v>181.3253326416016</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438263494094</v>
+        <v>181.9438110385745</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725821273594</v>
+        <v>178.3725671170498</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195243045502</v>
+        <v>179.6195091893087</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090045163838549</v>
+        <v>0.01090045256567307</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009353432511975956</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00787451516030313</v>
+        <v>-0.007874430930079446</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635455335401</v>
+        <v>-0.03324643662953308</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622283935547</v>
+        <v>170.3621978759766</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583204838847</v>
+        <v>171.9582896803931</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109394751057</v>
+        <v>166.8109095936823</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841376854209</v>
+        <v>169.5841073072249</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01951992314133455</v>
+        <v>-0.01952009877813865</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.000937047212150155</v>
+        <v>-0.0009368682464988565</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982543945312</v>
+        <v>167.8982238769531</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417807313731</v>
+        <v>170.5417497333015</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406114031506</v>
+        <v>166.9405810596359</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401190912332</v>
+        <v>167.1400887114555</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723568524209856</v>
+        <v>0.00772338535802497</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643629502945</v>
+        <v>0.01455662070320596</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620361328125</v>
+        <v>174.4620208740234</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757693786965</v>
+        <v>177.0757538913052</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632311486472</v>
+        <v>173.9632159334845</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769643945311</v>
+        <v>176.5769489507663</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614620612602058</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -981,22 +981,22 @@
         <v>45917</v>
       </c>
       <c r="B23" t="n">
-        <v>169.8829650878906</v>
+        <v>169.8829803466797</v>
       </c>
       <c r="C23" t="n">
-        <v>172.7860132411964</v>
+        <v>172.7860287607356</v>
       </c>
       <c r="D23" t="n">
-        <v>168.0074690267279</v>
+        <v>168.007484117061</v>
       </c>
       <c r="E23" t="n">
-        <v>172.2273541922408</v>
+        <v>172.2273696616015</v>
       </c>
       <c r="F23" t="n">
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624680501513788</v>
+        <v>-0.02624663238682878</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187713623047</v>
+        <v>175.8187561035156</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767164710769</v>
+        <v>176.6767011378293</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466121619453</v>
+        <v>172.5465971871373</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641632831282</v>
+        <v>173.5641482200099</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494056200009887</v>
+        <v>0.03494037922293813</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00243984378681672</v>
+        <v>0.002439930785601563</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711578369141</v>
+        <v>183.1711730957031</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089135963474</v>
+        <v>184.1089289332547</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924356467209</v>
+        <v>174.2924501658818</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810218455756</v>
+        <v>174.8810364137678</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928229701524732</v>
+        <v>0.0392823835910463</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035400390625</v>
+        <v>178.0035247802734</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9840093083128</v>
+        <v>181.9839937083107</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888599052367</v>
+        <v>175.7888448362941</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350878652714</v>
+        <v>181.5350723037516</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821196229186118</v>
+        <v>-0.02821212654859018</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470275878906</v>
+        <v>176.5470428466797</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3503245099793</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807727171775</v>
+        <v>174.9807878405966</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403383898065</v>
+        <v>179.3403538900187</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.008182320745567351</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1140,7 +1140,7 @@
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068473920816773</v>
+        <v>0.004068387140155894</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385528564453</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="C34" t="n">
-        <v>190.593394116267</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105347272827</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E34" t="n">
-        <v>189.1468626563914</v>
+        <v>189.146847340247</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812305418101074</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587148282584</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965270996094</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7824902019781</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918178290645</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566294029491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0110862321012164</v>
+        <v>-0.01108631362422263</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694780736732239</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097412109375</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="C39" t="n">
-        <v>194.8332119113436</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033405552435</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705422839889</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829618052309101</v>
+        <v>0.01829626140377161</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1404,7 +1404,7 @@
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886535894656951</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4002075195312</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="C43" t="n">
-        <v>184.428155204694</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D43" t="n">
-        <v>176.8662696036074</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E43" t="n">
-        <v>184.358330420537</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110851794359102</v>
+        <v>-0.001110936754343372</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1500,7 +1500,7 @@
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0110103007764113</v>
+        <v>0.01101038676736099</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7821044921875</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6600061588844</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203965919317</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493615830456</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755441369297289</v>
+        <v>0.007755357241106875</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165673913464562</v>
+        <v>-0.003165590696970089</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.84912109375</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015721983185</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375297972393</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070662621498</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004857597766183885</v>
+        <v>-0.00485768219622118</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.724609375</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925250516066</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602637385785</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988762799469</v>
+        <v>179.988777912505</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042812035913343</v>
+        <v>0.01042829092822517</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1644,7 +1644,7 @@
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250773835753361</v>
+        <v>0.02250765250109055</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989595999882533</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050750732422</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672637579894</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286166610889</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596680014167</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004440999182711</v>
+        <v>-0.02004441147263381</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060272216797</v>
+        <v>202.0060424804688</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729250244422</v>
+        <v>207.4729406961805</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870329046891</v>
+        <v>201.5870481318289</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565537660584</v>
+        <v>205.9565693232556</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971530859184778</v>
+        <v>-0.001971380233034448</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1773,22 +1773,22 @@
         <v>45964</v>
       </c>
       <c r="B56" t="n">
-        <v>206.3855590820312</v>
+        <v>206.3855438232422</v>
       </c>
       <c r="C56" t="n">
-        <v>210.8348911017148</v>
+        <v>210.8348755139714</v>
       </c>
       <c r="D56" t="n">
-        <v>205.0687065918373</v>
+        <v>205.0686914304077</v>
       </c>
       <c r="E56" t="n">
-        <v>207.5826880225491</v>
+        <v>207.5826726752522</v>
       </c>
       <c r="F56" t="n">
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168020390572556</v>
+        <v>0.02168005119548289</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958823819926593</v>
+        <v>-0.03958816719273994</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434387207031</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4350026612236</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847643800754</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949275919373</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751478380745641</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.03652478060097764</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7002868652344</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8698939350823</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823816093971</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580548583195</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003720555463071484</v>
+        <v>0.0003722182238108385</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793266405042918</v>
+        <v>0.05793257804752372</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983184814453</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529112179747</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427635881239</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935381421213</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959067258255743</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3367919921875</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4217929255223</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6731755191215</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522010776849</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313332029950544</v>
+        <v>0.003313331767584859</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133911132812</v>
+        <v>186.4134063720703</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824463944715</v>
+        <v>190.9824620272586</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105907203728</v>
+        <v>183.4106057333689</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933791327836</v>
+        <v>190.5933947337238</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005357317613</v>
+        <v>-0.03581005074692667</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154693603516</v>
+        <v>189.7154846191406</v>
       </c>
       <c r="C65" t="n">
-        <v>190.553458007553</v>
+        <v>190.5534733337414</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1483942490048</v>
+        <v>180.1484087383153</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229435613052</v>
+        <v>182.4229582335574</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0177137394870075</v>
+        <v>0.01771373803705711</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540222167969</v>
+        <v>186.1540374755859</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482800008962</v>
+        <v>188.5482954559393</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794727552066</v>
+        <v>183.879487827554</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255230789849</v>
+        <v>185.5255382862568</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877257113277342</v>
+        <v>-0.01877256962289819</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808162861150654</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845174000170858</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136779785156</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614042749852</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581789881563</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0609943264491</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051660953286172</v>
+        <v>0.02051643852050034</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2172,7 +2172,7 @@
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067418159221</v>
+        <v>-0.02591051094922314</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372151153989076</v>
+        <v>0.01372159755577274</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808484361385299</v>
+        <v>-0.01808492693090802</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2229,22 +2229,22 @@
         <v>45992</v>
       </c>
       <c r="B75" t="n">
-        <v>179.4899597167969</v>
+        <v>179.4899749755859</v>
       </c>
       <c r="C75" t="n">
-        <v>179.8690563253026</v>
+        <v>179.8690716163194</v>
       </c>
       <c r="D75" t="n">
-        <v>173.2648688653124</v>
+        <v>173.2648835948944</v>
       </c>
       <c r="E75" t="n">
-        <v>174.3422893139723</v>
+        <v>174.3423041351479</v>
       </c>
       <c r="F75" t="n">
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649702371590833</v>
+        <v>0.01649711013028865</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0263061523438</v>
+        <v>181.0262908935547</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162648499111</v>
+        <v>185.2162492379485</v>
       </c>
       <c r="D76" t="n">
-        <v>179.569788944198</v>
+        <v>179.5697738081794</v>
       </c>
       <c r="E76" t="n">
-        <v>181.3255769560617</v>
+        <v>181.325561672047</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559511841057521</v>
+        <v>0.008559341089538375</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607818603516</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139471586436</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819333075974</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472262869623</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526629882311</v>
+        <v>-0.01030526716745872</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116036298998392</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2421,22 +2421,22 @@
         <v>46002</v>
       </c>
       <c r="B83" t="n">
-        <v>180.5075988769531</v>
+        <v>180.5076141357422</v>
       </c>
       <c r="C83" t="n">
-        <v>180.8967030087509</v>
+        <v>180.896718300432</v>
       </c>
       <c r="D83" t="n">
-        <v>176.2076633109278</v>
+        <v>176.2076782062319</v>
       </c>
       <c r="E83" t="n">
-        <v>179.8591224369562</v>
+        <v>179.8591376409278</v>
       </c>
       <c r="F83" t="n">
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770804044477</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2460,7 +2460,7 @@
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266451936799664</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814983424509077</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682952880859</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8880102762506</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4730132178061</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428571096804</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005069689074391</v>
+        <v>0.03005061362821149</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.003171176350336591</v>
+        <v>-0.00317109577323571</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124633789062</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="C105" t="n">
-        <v>184.029389177148</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779297072971</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E105" t="n">
-        <v>183.889716612774</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436938499763141</v>
+        <v>-0.01436946731018618</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974032598635</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6543121337891</v>
+        <v>177.654296875</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542482267672</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953792817215</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753578011745</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438166772979951</v>
+        <v>-0.04381675942490471</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3045,22 +3045,22 @@
         <v>46043</v>
       </c>
       <c r="B109" t="n">
-        <v>182.8920288085938</v>
+        <v>182.8920440673828</v>
       </c>
       <c r="C109" t="n">
-        <v>184.947217101084</v>
+        <v>184.9472325313386</v>
       </c>
       <c r="D109" t="n">
-        <v>177.9835016341843</v>
+        <v>177.9835164834521</v>
       </c>
       <c r="E109" t="n">
-        <v>178.6319932794081</v>
+        <v>178.6320081827799</v>
       </c>
       <c r="F109" t="n">
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948263181397048</v>
+        <v>0.02948280612693632</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3084,7 +3084,7 @@
         <v>139636600</v>
       </c>
       <c r="G110" t="n">
-        <v>0.008291498456701074</v>
+        <v>0.008291414334357983</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728759765625</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009400606663</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3967902384632</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E114" t="n">
-        <v>190.823459633995</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591334872193784</v>
+        <v>0.01591342985123156</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169239280915949</v>
+        <v>0.00516915900963677</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3261,22 +3261,22 @@
         <v>46056</v>
       </c>
       <c r="B118" t="n">
-        <v>179.9189758300781</v>
+        <v>179.9189910888672</v>
       </c>
       <c r="C118" t="n">
-        <v>185.8351396091497</v>
+        <v>185.835155369684</v>
       </c>
       <c r="D118" t="n">
-        <v>175.8185703987175</v>
+        <v>175.8185853097543</v>
       </c>
       <c r="E118" t="n">
-        <v>185.8052108647954</v>
+        <v>185.8052266227915</v>
       </c>
       <c r="F118" t="n">
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839291451472381</v>
+        <v>-0.02839283211347909</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3300,7 +3300,7 @@
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0341021289659974</v>
+        <v>-0.03410221088304122</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771728515625</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634574188361</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1924107166939</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775280578147</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871779317924998</v>
+        <v>0.07871770419569057</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3372,7 +3372,7 @@
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0249714914147583</v>
+        <v>0.02497157596478594</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3381,22 +3381,22 @@
         <v>46063</v>
       </c>
       <c r="B123" t="n">
-        <v>188.099853515625</v>
+        <v>188.0998382568359</v>
       </c>
       <c r="C123" t="n">
-        <v>192.0306581643501</v>
+        <v>192.0306425866914</v>
       </c>
       <c r="D123" t="n">
-        <v>187.6808358171596</v>
+        <v>187.6808205923615</v>
       </c>
       <c r="E123" t="n">
-        <v>190.9332352083219</v>
+        <v>190.933219719687</v>
       </c>
       <c r="F123" t="n">
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.00789295462474604</v>
+        <v>-0.007893035105149604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3420,7 +3420,7 @@
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800888303954661</v>
+        <v>0.008008964809924857</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832244873047</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622780376601</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660713803529</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E126" t="n">
-        <v>187.042320465516</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209266545793198</v>
+        <v>-0.02209274727292232</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3492,7 +3492,7 @@
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0118155220086027</v>
+        <v>0.01181560666047221</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3813,22 +3813,22 @@
         <v>46090</v>
       </c>
       <c r="B141" t="n">
-        <v>182.2235870361328</v>
+        <v>182.2236022949219</v>
       </c>
       <c r="C141" t="n">
-        <v>182.4829897940845</v>
+        <v>182.4830050745951</v>
       </c>
       <c r="D141" t="n">
-        <v>175.1501427003192</v>
+        <v>175.1501573668019</v>
       </c>
       <c r="E141" t="n">
-        <v>176.4171820751478</v>
+        <v>176.4171968477281</v>
       </c>
       <c r="F141" t="n">
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716221787178097</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160690076858506</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7401,12 +7401,36 @@
         <v>233.8399963378906</v>
       </c>
       <c r="F290" t="n">
-        <v>84470000</v>
+        <v>84645600</v>
       </c>
       <c r="G290" t="n">
         <v>-0.005206512367610272</v>
       </c>
       <c r="H290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B291" t="n">
+        <v>226.3200073242188</v>
+      </c>
+      <c r="C291" t="n">
+        <v>228.8600006103516</v>
+      </c>
+      <c r="D291" t="n">
+        <v>224.8999938964844</v>
+      </c>
+      <c r="E291" t="n">
+        <v>228.7299957275391</v>
+      </c>
+      <c r="F291" t="n">
+        <v>70089000</v>
+      </c>
+      <c r="G291" t="n">
+        <v>-0.01290994186513139</v>
+      </c>
+      <c r="H291" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709014892578</v>
+        <v>174.9709167480469</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694397588381</v>
+        <v>175.5694550698242</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870566311777</v>
+        <v>168.3870713158056</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414684152183</v>
+        <v>174.741483653999</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366504264196933</v>
+        <v>-0.001366417175785561</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519409179688</v>
+        <v>174.5519256591797</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672421817212</v>
+        <v>176.4672267555024</v>
       </c>
       <c r="D5" t="n">
-        <v>173.3848049238756</v>
+        <v>173.384789767114</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222692884882</v>
+        <v>174.4222540410346</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394458551239653</v>
+        <v>-0.002394632757571458</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -588,7 +588,7 @@
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0172019844334983</v>
+        <v>0.01720207335414736</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874430930079446</v>
+        <v>-0.00787451516030313</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538909912109</v>
+        <v>173.7538757324219</v>
       </c>
       <c r="C11" t="n">
-        <v>177.714180280125</v>
+        <v>177.7141646735497</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264119284913</v>
+        <v>172.7263967599338</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6742848307548</v>
+        <v>177.674269227683</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643662953308</v>
+        <v>-0.03324643945211436</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3621978759766</v>
+        <v>170.3622283935547</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9582896803931</v>
+        <v>171.9583204838847</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109095936823</v>
+        <v>166.8109394751057</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841073072249</v>
+        <v>169.5841376854209</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952009877813865</v>
+        <v>-0.01951983703713334</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2025909423828</v>
+        <v>170.2026062011719</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882204164984</v>
+        <v>171.9882358353705</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668574141896</v>
+        <v>168.4668725173688</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415169633154</v>
+        <v>170.6415322614545</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368682464988565</v>
+        <v>-0.0009369576454122397</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -780,7 +780,7 @@
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095533447482593</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982238769531</v>
+        <v>167.8982696533203</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417497333015</v>
+        <v>170.5417962304089</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9405810596359</v>
+        <v>166.9406265749079</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1400887114555</v>
+        <v>167.140134281122</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00772338535802497</v>
+        <v>0.007723660107302521</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455662070320596</v>
+        <v>0.01455634409096618</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512663982333</v>
+        <v>0.03847521621706362</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460227399664788</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731541223449</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028283464474</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451359862166</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003669001328727717</v>
+        <v>0.003668914997253303</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251647949219</v>
+        <v>177.3251495361328</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225418052247</v>
+        <v>178.4225264520066</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929031464731</v>
+        <v>174.0928881658194</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501343169162</v>
+        <v>175.250119236683</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807076698219</v>
+        <v>-0.0003937807415412831</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -972,7 +972,7 @@
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614620751539797</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187561035156</v>
+        <v>175.8187866210938</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767011378293</v>
+        <v>176.6767318043244</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5465971871373</v>
+        <v>172.5466271367534</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641482200099</v>
+        <v>173.5641783462465</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494037922293813</v>
+        <v>0.03494055886175818</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477416992188</v>
+        <v>176.2477264404297</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543753314711</v>
+        <v>177.6543599509016</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612974471592</v>
+        <v>174.7612823170602</v>
       </c>
       <c r="E25" t="n">
-        <v>175.349898865447</v>
+        <v>175.3498836843894</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439930785601563</v>
+        <v>0.002439670001024075</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1068,7 +1068,7 @@
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0392823835910463</v>
+        <v>0.03928247356775705</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035247802734</v>
+        <v>178.0035400390625</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9839937083107</v>
+        <v>181.9840093083128</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888448362941</v>
+        <v>175.7888599052367</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350723037516</v>
+        <v>181.5350878652714</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821212654859018</v>
+        <v>-0.02821204324514892</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470428466797</v>
+        <v>176.5470123291016</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503245099793</v>
+        <v>179.3502935078314</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807878405966</v>
+        <v>174.9807575937583</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403538900187</v>
+        <v>179.3403228895943</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182320745567351</v>
+        <v>-0.008182577209651543</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653045654297</v>
+        <v>177.2653198242188</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291540783439</v>
+        <v>179.8291695578261</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162058826927</v>
+        <v>172.7162207499007</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629701066951</v>
+        <v>174.062985089831</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387140155894</v>
+        <v>0.004068647130534231</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1164,7 +1164,7 @@
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813916776754244</v>
+        <v>0.002813830455718369</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153747558594</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602300506758</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890327563757</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987552370008</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053991824341894</v>
+        <v>0.02053983240613322</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340637207031</v>
+        <v>186.1340484619141</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022276338177</v>
+        <v>186.9022123120565</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462469572146</v>
+        <v>181.0462321155116</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448190078555</v>
+        <v>181.6448041170831</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041378766245</v>
+        <v>0.02601041597539022</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.79248046875</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="C33" t="n">
-        <v>187.6903232769056</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604518817237</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972606974542</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537325381961498</v>
+        <v>0.003537489626782131</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812141321341782</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715698242188</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050265070322</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369333277354</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378247179256</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723587692724298</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965270996094</v>
+        <v>185.0965576171875</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7824902019781</v>
+        <v>186.7825209975275</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918178290645</v>
+        <v>182.8918479831437</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566294029491</v>
+        <v>185.0566599139491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108631362422263</v>
+        <v>-0.01108606995897354</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694780736732239</v>
+        <v>-0.002694945166262119</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199532691778505</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097564697266</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="C39" t="n">
-        <v>194.833227386451</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033556943829</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705575158363</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626140377161</v>
+        <v>0.01829626288358566</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1404,7 +1404,7 @@
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886535894656951</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754577636719</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419455690647</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944521048813</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038676736099</v>
+        <v>0.01101030171288664</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755357241106875</v>
+        <v>0.007755442021748715</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323181152344</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="C51" t="n">
-        <v>191.541093665248</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D51" t="n">
-        <v>187.979619148197</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359033209746</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807902404094098</v>
+        <v>0.02807910615919784</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495300292969</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644582837766</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513320204045</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886067715161</v>
+        <v>192.588592118433</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981990486196963</v>
+        <v>0.04981974113173093</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.545166015625</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482921843539</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989611444324924</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050598144531</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672482532724</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286015136062</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596525726598</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004441147263381</v>
+        <v>-0.02004448238730316</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971380233034448</v>
+        <v>-0.001971455471800998</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151184082031</v>
+        <v>198.2151031494141</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824975937368</v>
+        <v>203.4824819294599</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569251230167</v>
+        <v>197.4569099225941</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5148147488263</v>
+        <v>202.5147991590425</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958816719273994</v>
+        <v>-0.03958824112615977</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434234619141</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4349867997753</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847491650603</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949120548774</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751478380745641</v>
+        <v>-0.01751463119384</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304626464844</v>
+        <v>187.6304931640625</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476539294223</v>
+        <v>197.1476859949454</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345289438528</v>
+        <v>185.934559185592</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505251524069</v>
+        <v>195.9505570232203</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652478060097764</v>
+        <v>-0.03652469938585123</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003021240234</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699092076593</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823961188316</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580698535366</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003722182238108385</v>
+        <v>0.0003719741924403941</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793257804752372</v>
+        <v>0.05793266405042918</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368072509766</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218083488666</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D63" t="n">
-        <v>190.673190567689</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522164876445</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331767584859</v>
+        <v>0.003313252582732629</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4134063720703</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824620272586</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4106057333689</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933947337238</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005074692667</v>
+        <v>-0.03581005357317613</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154846191406</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="C65" t="n">
-        <v>190.5534733337414</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1484087383153</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229582335574</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771373803705711</v>
+        <v>0.0177137394870075</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540374755859</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482954559393</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D66" t="n">
-        <v>183.879487827554</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255382862568</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877256962289819</v>
+        <v>-0.01877257113277342</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808162861150654</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174000170858</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136779785156</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614042749852</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581789881563</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0609943264491</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051643852050034</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.734203281764</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447804748437</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919707447618</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591051094922314</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291625976562</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728380763597</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140014756398</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958985688627</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159755577274</v>
+        <v>0.01372159873604817</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492693090802</v>
+        <v>-0.01808492846544285</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649711013028865</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2253,22 +2253,22 @@
         <v>45993</v>
       </c>
       <c r="B76" t="n">
-        <v>181.0262908935547</v>
+        <v>181.0263061523438</v>
       </c>
       <c r="C76" t="n">
-        <v>185.2162492379485</v>
+        <v>185.2162648499111</v>
       </c>
       <c r="D76" t="n">
-        <v>179.5697738081794</v>
+        <v>179.569788944198</v>
       </c>
       <c r="E76" t="n">
-        <v>181.325561672047</v>
+        <v>181.3255769560617</v>
       </c>
       <c r="F76" t="n">
         <v>182632200</v>
       </c>
       <c r="G76" t="n">
-        <v>0.008559341089538375</v>
+        <v>0.008559426101467649</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607818603516</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.0139471586436</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819333075974</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6472262869623</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526716745872</v>
+        <v>-0.01030526629882311</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116036298998392</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841461181641</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2288932293168</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876480440623</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4606866221248</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289603321452563</v>
+        <v>-0.005289519918164731</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168212890625</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5610985176648</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741660895743</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E80" t="n">
-        <v>182.2136112701494</v>
+        <v>182.213626289633</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721400043751253</v>
+        <v>0.01721399899417375</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2388,7 +2388,7 @@
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125830460996126</v>
+        <v>-0.003125912631224192</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2421,22 +2421,22 @@
         <v>46002</v>
       </c>
       <c r="B83" t="n">
-        <v>180.5076141357422</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="C83" t="n">
-        <v>180.896718300432</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D83" t="n">
-        <v>176.2076782062319</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E83" t="n">
-        <v>179.8591376409278</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="F83" t="n">
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770804044477</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114196777344</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3932136047752</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123443447362</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871989054384</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266451936799664</v>
+        <v>-0.03266452212921567</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.8784332275391</v>
+        <v>175.87841796875</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0034500370577</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213802569945</v>
+        <v>174.6213651072644</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245903328353</v>
+        <v>177.5245749312296</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256189498619836</v>
+        <v>0.007256190132717499</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2508,7 +2508,7 @@
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111661183153096</v>
+        <v>0.008111748644499261</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814983424509077</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491794177123418</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682800292969</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8879950077845</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4729984678863</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428423541149</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005061362821149</v>
+        <v>0.03005069689074391</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.00317109577323571</v>
+        <v>-0.003171176350336591</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808166503906</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779629368336</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154145267434</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123182227279</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386561545941666</v>
+        <v>-0.00386553447189375</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780623340899</v>
+        <v>-0.004677861544826856</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080169677734</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074981045344</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685228499072</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152187943302564</v>
+        <v>-0.02152196030920583</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009727675505442068</v>
+        <v>-0.0009726849758688871</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.3762054443359</v>
+        <v>185.376220703125</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708389078061</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718281779948</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5680989064521</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.00470412795042785</v>
+        <v>0.004704210650191332</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2964,7 +2964,7 @@
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436946731018618</v>
+        <v>-0.01436954843994676</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133270263672</v>
+        <v>186.6133117675781</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571344016907</v>
+        <v>189.2571189267257</v>
       </c>
       <c r="D106" t="n">
-        <v>185.895006678512</v>
+        <v>185.8949914784577</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0646079796491</v>
+        <v>186.0645927657271</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134974210895835</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952423095703</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="C107" t="n">
-        <v>189.9954207742267</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455985734289</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385950815971</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849373637116</v>
+        <v>-0.004383849732090828</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3036,7 +3036,7 @@
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381675942490471</v>
+        <v>-0.04381668089652369</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728912353516</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009553855833</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3968053634026</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E114" t="n">
-        <v>190.8234748728661</v>
+        <v>190.823459633995</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591342985123156</v>
+        <v>0.01591334872193784</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.00516915900963677</v>
+        <v>0.005169239280915949</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3261,22 +3261,22 @@
         <v>46056</v>
       </c>
       <c r="B118" t="n">
-        <v>179.9189910888672</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="C118" t="n">
-        <v>185.835155369684</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D118" t="n">
-        <v>175.8185853097543</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E118" t="n">
-        <v>185.8052266227915</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="F118" t="n">
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839283211347909</v>
+        <v>-0.02839291451472381</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3300,7 +3300,7 @@
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221088304122</v>
+        <v>-0.0341021289659974</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963287353516</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2078878887748</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205500126207</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298238555102</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497157596478594</v>
+        <v>0.024971658454912</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893035105149604</v>
+        <v>-0.007893114950312197</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063232421875</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088208357837</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D124" t="n">
-        <v>188.329312674443</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007142509167</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.008008964809924857</v>
+        <v>0.00800904593061702</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410312537218</v>
+        <v>-0.01636418228460701</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768615722656</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856654675195</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059147845697</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344488846578</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021825301539225</v>
+        <v>0.01021833441238607</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113849147715847</v>
+        <v>0.009113767839714404</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583740234375</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364236513225</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8897126034445</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164813019665</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456121004512637</v>
+        <v>-0.05456128825383422</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164637217148226</v>
+        <v>-0.04164629289442512</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539855957031</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317086895539</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322921838959</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014235260267</v>
+        <v>174.601438160182</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486242594537</v>
+        <v>0.02985494874285899</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296691894531</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776756968921</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069714269912</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0733135069376</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331646982798718</v>
+        <v>-0.01331663634113589</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126708984375</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2687991412151</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396322236537</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187499528396</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660639760928495</v>
+        <v>0.01660656891157819</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638994413631911</v>
+        <v>0.001638910718471109</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3813,22 +3813,22 @@
         <v>46090</v>
       </c>
       <c r="B141" t="n">
-        <v>182.2236022949219</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="C141" t="n">
-        <v>182.4830050745951</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D141" t="n">
-        <v>175.1501573668019</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E141" t="n">
-        <v>176.4171968477281</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="F141" t="n">
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716221787178097</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690076858506</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7425,12 +7425,36 @@
         <v>228.7299957275391</v>
       </c>
       <c r="F291" t="n">
-        <v>70089000</v>
+        <v>70690300</v>
       </c>
       <c r="G291" t="n">
         <v>-0.01290994186513139</v>
       </c>
       <c r="H291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B292" t="n">
+        <v>228.5200042724609</v>
+      </c>
+      <c r="C292" t="n">
+        <v>228.6399993896484</v>
+      </c>
+      <c r="D292" t="n">
+        <v>223.0599975585938</v>
+      </c>
+      <c r="E292" t="n">
+        <v>224.3399963378906</v>
+      </c>
+      <c r="F292" t="n">
+        <v>83846800</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0.009720735582561923</v>
+      </c>
+      <c r="H292" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545806884766</v>
+        <v>177.5545654296875</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531037491236</v>
+        <v>178.1530884388983</v>
       </c>
       <c r="D6" t="n">
-        <v>170.781182841084</v>
+        <v>170.7811681643912</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877371490149</v>
+        <v>172.1877223514448</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207335414736</v>
+        <v>0.01720198593724254</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022523041638013</v>
+        <v>0.01022531723371234</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557464599609</v>
+        <v>181.15576171875</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435685875041</v>
+        <v>182.0435839210746</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618623689453</v>
+        <v>178.6618774176739</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348064912021</v>
+        <v>181.5348217819195</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009352591784613784</v>
+        <v>-0.0009351750270146786</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.00787451516030313</v>
+        <v>-0.007874514497031027</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643945211436</v>
+        <v>-0.03324652152828622</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622283935547</v>
+        <v>170.3622131347656</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583204838847</v>
+        <v>171.9583050821389</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109394751057</v>
+        <v>166.810924534394</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841376854209</v>
+        <v>169.5841224963229</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01951983703713334</v>
+        <v>-0.0195199248555431</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009369576454122397</v>
+        <v>-0.0009368681625865349</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400512695312</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.439558941325</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955557135668</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527215200144</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095443250276666</v>
+        <v>0.006095353599539832</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016265075109</v>
+        <v>-0.02703007595174933</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422546386719</v>
+        <v>170.3422698974609</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617176578999</v>
+        <v>170.5617329363479</v>
       </c>
       <c r="D17" t="n">
-        <v>166.3320999523285</v>
+        <v>166.332114851899</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763418810487</v>
+        <v>168.6763569906099</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634409096618</v>
+        <v>0.01455643497212367</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847521621706362</v>
+        <v>0.03847503361609572</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008460227399664788</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251495361328</v>
+        <v>177.3251647949219</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225264520066</v>
+        <v>178.4225418052247</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0928881658194</v>
+        <v>174.0929031464731</v>
       </c>
       <c r="E21" t="n">
-        <v>175.250119236683</v>
+        <v>175.2501343169162</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807415412831</v>
+        <v>-0.0003936947256518719</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -972,7 +972,7 @@
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614620751539797</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477264404297</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543599509016</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612823170602</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E25" t="n">
-        <v>175.3498836843894</v>
+        <v>175.349898865447</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439670001024075</v>
+        <v>0.002439756788046976</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711730957031</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089289332547</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924501658818</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810364137678</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928247356775705</v>
+        <v>0.03928229701524732</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204324514892</v>
+        <v>-0.02821196229186118</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470123291016</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3502935078314</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807575937583</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403228895943</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182577209651543</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653198242188</v>
+        <v>177.2652893066406</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291695578261</v>
+        <v>179.8291385988617</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162207499007</v>
+        <v>172.7161910154847</v>
       </c>
       <c r="E29" t="n">
-        <v>174.062985089831</v>
+        <v>174.0629551235593</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068647130534231</v>
+        <v>0.004068387491782843</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7641296386719</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403552769049</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5119112725463</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441731762758</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830455718369</v>
+        <v>0.002814089176637058</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053983240613322</v>
+        <v>0.02053974480577181</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340484619141</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022123120565</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462321155116</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448041170831</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041597539022</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1236,7 +1236,7 @@
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537489626782131</v>
+        <v>0.0035374073593748</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385375976562</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="C34" t="n">
-        <v>190.59337868299</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105195355423</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E34" t="n">
-        <v>189.146847340247</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812141321341782</v>
+        <v>0.008812223009789566</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587692724298</v>
+        <v>-0.00672366812316183</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965576171875</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825209975275</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918479831437</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566599139491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108606995897354</v>
+        <v>-0.01108615148198644</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694945166262119</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626288358566</v>
+        <v>0.01829618052309101</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988793025541</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829092822517</v>
+        <v>0.01042837577039868</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250765250109055</v>
+        <v>0.02250748267812286</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910615919784</v>
+        <v>0.02807919058326869</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495147705078</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644428640734</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513174538508</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E52" t="n">
-        <v>192.588592118433</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981974113173093</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.545166015625</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828666070652</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905729140704</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482921843539</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989611444324924</v>
+        <v>0.02989595999882533</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448238730316</v>
+        <v>-0.02004440999182711</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151031494141</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824819294599</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569099225941</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5147991590425</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958824112615977</v>
+        <v>-0.03958816719273994</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751463119384</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304931640625</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476859949454</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.934559185592</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505570232203</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652469938585123</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003719741924403941</v>
+        <v>0.0003720555463071484</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742645263672</v>
+        <v>198.5742797851562</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621367771523</v>
+        <v>199.462152104167</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268264223904</v>
+        <v>193.3268412779572</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6436938260565</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793266405042918</v>
+        <v>0.05793274534380033</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959067030875928</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3367919921875</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4217929255223</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6731755191215</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522010776849</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313252582732629</v>
+        <v>0.003313331767584859</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005357317613</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.926513671875</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.358293814419</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2205942185541</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.9416897271721</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808163091331894</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0742034912109</v>
+        <v>186.0741882324219</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109971087465</v>
+        <v>187.4109817403353</v>
       </c>
       <c r="D68" t="n">
-        <v>182.3930205111681</v>
+        <v>182.39300555425</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483273978252</v>
+        <v>184.3483122805645</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845174240124138</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152479724769053</v>
+        <v>-0.03152471782905131</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524688720703</v>
+        <v>178.4524536132812</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188859589464</v>
+        <v>184.1188702156436</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166776199441</v>
+        <v>172.5166628687019</v>
       </c>
       <c r="E70" t="n">
-        <v>180.8068289121023</v>
+        <v>180.806813452001</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743078144453632</v>
+        <v>-0.009743162817541062</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2148,7 +2148,7 @@
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.02051661128715887</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492846544285</v>
+        <v>-0.01808484361385299</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649711013028865</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607818603516</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139471586436</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819333075974</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472262869623</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526629882311</v>
+        <v>-0.01030535058927451</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116036298998392</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168365478516</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5611139779305</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741810893209</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E80" t="n">
-        <v>182.213626289633</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721399899417375</v>
+        <v>0.01721391514737669</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864265695677</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920356049676</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E81" t="n">
-        <v>185.12679644575</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125912631224192</v>
+        <v>-0.003125748033105724</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509674072266</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469957406681</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150239281505</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5381918075859</v>
+        <v>184.538176449994</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433411769608655</v>
+        <v>-0.006433576610347602</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770933102352</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114044189453</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3931976659576</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123291208211</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871831157045</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266452212921567</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.87841796875</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034500370577</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213651072644</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245749312296</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256190132717499</v>
+        <v>0.007256189498619836</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2508,7 +2508,7 @@
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111748644499261</v>
+        <v>0.008111661183153096</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814983424509077</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021728515625</v>
+        <v>187.1021881103516</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5487999407664</v>
+        <v>188.5488153175326</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4935963146986</v>
+        <v>186.4936115238563</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005508490403</v>
+        <v>187.8005661647843</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612838827051545</v>
+        <v>-0.003612757568446812</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545538552702456</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8028869628906</v>
+        <v>186.8029022216797</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213703933745</v>
+        <v>191.7213860539245</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838692947835</v>
+        <v>186.3838845193456</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752284670132</v>
+        <v>190.0752439930999</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677861544826856</v>
+        <v>-0.004677780243029006</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987164191344933</v>
+        <v>0.009987081691657185</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133117675781</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571189267257</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D106" t="n">
-        <v>185.8949914784577</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0645927657271</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974210895835</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952270507812</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="C107" t="n">
-        <v>189.99540517049</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455833269296</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385795892923</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849732090828</v>
+        <v>-0.004383849373637116</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.654296875</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542325986551</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953640623503</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753422141945</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381668089652369</v>
+        <v>-0.0438168415518142</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948280612693632</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.0346832275391</v>
+        <v>186.03466796875</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784906596197</v>
+        <v>188.6784751839824</v>
       </c>
       <c r="D112" t="n">
-        <v>185.555808059744</v>
+        <v>185.5557928402329</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230748442759</v>
+        <v>186.7230595290241</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.00639415348837058</v>
+        <v>-0.006394234985120373</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099371233637481</v>
+        <v>0.01099379525930511</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5035858154297</v>
+        <v>186.5036010742188</v>
       </c>
       <c r="C125" t="n">
-        <v>193.1580126884611</v>
+        <v>193.158028491682</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745817463215</v>
+        <v>186.0745969700116</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793648877844</v>
+        <v>192.5793806436633</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636418228460701</v>
+        <v>-0.01636410180845216</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209274727292232</v>
+        <v>-0.02209282728038808</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130808403767</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7616860728079</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3256935584433</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560666047221</v>
+        <v>0.01181569032381558</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627283983140582</v>
+        <v>0.01627275579951704</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613342285156</v>
+        <v>187.4613189697266</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900957055448</v>
+        <v>187.9900804037161</v>
       </c>
       <c r="D129" t="n">
-        <v>185.2265733363672</v>
+        <v>185.226558259481</v>
       </c>
       <c r="E129" t="n">
-        <v>186.62329889396</v>
+        <v>186.6232837033845</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004255251289267958</v>
+        <v>-0.0004256064912840918</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768768310547</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856807673048</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059297314624</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344638821937</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833441238607</v>
+        <v>0.01021833524412785</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113767839714404</v>
+        <v>0.009113849147715847</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583587646484</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364076167612</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8896973916963</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164652690549</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456128825383422</v>
+        <v>-0.05456121004512637</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637395256691</v>
+        <v>182.1637238018573</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682453114839</v>
+        <v>175.9682301224481</v>
       </c>
       <c r="E135" t="n">
-        <v>180.8268714126474</v>
+        <v>180.82685580423</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164629289442512</v>
+        <v>-0.04164645489360941</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0540008544922</v>
+        <v>182.0539703369141</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317240302905</v>
+        <v>183.0316933488174</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2323067871125</v>
+        <v>174.2322775806792</v>
       </c>
       <c r="E136" t="n">
-        <v>174.601438160182</v>
+        <v>174.6014088918714</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985494874285899</v>
+        <v>0.02985486500292533</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296539306641</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776603660684</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069564334623</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0732983803544</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331663634113589</v>
+        <v>-0.01331638712945649</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660656891157819</v>
+        <v>0.01660648255510222</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010789985650675</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7449,12 +7449,36 @@
         <v>224.3399963378906</v>
       </c>
       <c r="F292" t="n">
-        <v>83846800</v>
+        <v>84036900</v>
       </c>
       <c r="G292" t="n">
         <v>0.009720735582561923</v>
       </c>
       <c r="H292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B293" t="n">
+        <v>221.3000030517578</v>
+      </c>
+      <c r="C293" t="n">
+        <v>226</v>
+      </c>
+      <c r="D293" t="n">
+        <v>219.6399993896484</v>
+      </c>
+      <c r="E293" t="n">
+        <v>225.5299987792969</v>
+      </c>
+      <c r="F293" t="n">
+        <v>117249000</v>
+      </c>
+      <c r="G293" t="n">
+        <v>-0.03159461353805515</v>
+      </c>
+      <c r="H293" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519256591797</v>
+        <v>174.5519104003906</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672267555024</v>
+        <v>176.4672113292837</v>
       </c>
       <c r="D5" t="n">
-        <v>173.384789767114</v>
+        <v>173.3847746103523</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222540410346</v>
+        <v>174.4222387935811</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394632757571458</v>
+        <v>-0.002394719965144843</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -588,7 +588,7 @@
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720198593724254</v>
+        <v>0.01720207485789937</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701171875</v>
+        <v>179.3701324462891</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4649859155824</v>
+        <v>181.4650013525793</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380531425805</v>
+        <v>176.1380681264219</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9136974002478</v>
+        <v>177.913712535141</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531723371234</v>
+        <v>0.0102254031723028</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -636,7 +636,7 @@
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090045256567307</v>
+        <v>0.0109003665696572</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874514497031027</v>
+        <v>-0.007874598727247717</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324652152828622</v>
+        <v>-0.03324643945211436</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026062011719</v>
+        <v>170.2026214599609</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882358353705</v>
+        <v>171.9882512542426</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668725173688</v>
+        <v>168.4668876205481</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415322614545</v>
+        <v>170.6415475595936</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368681625865349</v>
+        <v>-0.0009367785958406261</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400512695312</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.439558941325</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955557135668</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527215200144</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095353599539832</v>
+        <v>0.006095353053086949</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114196777344</v>
+        <v>166.6114044189453</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164970921864</v>
+        <v>168.6164816497661</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686393698748</v>
+        <v>163.6686243805947</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189434134908</v>
+        <v>167.6189280624296</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703007595174933</v>
+        <v>-0.02703025175833773</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -828,7 +828,7 @@
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723660107302521</v>
+        <v>0.00772375239776002</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711578369141</v>
+        <v>183.1711730957031</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089135963474</v>
+        <v>184.1089289332547</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924356467209</v>
+        <v>174.2924501658818</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810218455756</v>
+        <v>174.8810364137678</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928229701524732</v>
+        <v>0.0392823835910463</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821196229186118</v>
+        <v>-0.02821204324514892</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886536282782095</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1428,7 +1428,7 @@
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817212858411589</v>
+        <v>0.02817221444483309</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -7473,12 +7473,36 @@
         <v>225.5299987792969</v>
       </c>
       <c r="F293" t="n">
-        <v>117249000</v>
+        <v>118730100</v>
       </c>
       <c r="G293" t="n">
         <v>-0.03159461353805515</v>
       </c>
       <c r="H293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B294" t="n">
+        <v>217.2299957275391</v>
+      </c>
+      <c r="C294" t="n">
+        <v>218.4700012207031</v>
+      </c>
+      <c r="D294" t="n">
+        <v>212.8500061035156</v>
+      </c>
+      <c r="E294" t="n">
+        <v>215.3000030517578</v>
+      </c>
+      <c r="F294" t="n">
+        <v>126789100</v>
+      </c>
+      <c r="G294" t="n">
+        <v>-0.01839135683729232</v>
+      </c>
+      <c r="H294" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H294"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519104003906</v>
+        <v>174.5519256591797</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672113292837</v>
+        <v>176.4672267555024</v>
       </c>
       <c r="D5" t="n">
-        <v>173.3847746103523</v>
+        <v>173.384789767114</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222387935811</v>
+        <v>174.4222540410346</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394719965144843</v>
+        <v>-0.002394632757571458</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545654296875</v>
+        <v>177.5545806884766</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1530884388983</v>
+        <v>178.1531037491236</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811681643912</v>
+        <v>170.781182841084</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877223514448</v>
+        <v>172.1877371490149</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207485789937</v>
+        <v>0.01720207335414736</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701324462891</v>
+        <v>179.3701477050781</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650013525793</v>
+        <v>181.4650167895762</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380681264219</v>
+        <v>176.1380831102634</v>
       </c>
       <c r="E7" t="n">
-        <v>177.913712535141</v>
+        <v>177.9137276700343</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0102254031723028</v>
+        <v>0.01022540229354618</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -636,7 +636,7 @@
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0109003665696572</v>
+        <v>0.01090028057365577</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.15576171875</v>
+        <v>181.1557464599609</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435839210746</v>
+        <v>182.0435685875041</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618774176739</v>
+        <v>178.6618623689453</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348217819195</v>
+        <v>181.5348064912021</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009351750270146786</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.7292175292969</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187007491465</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.978421739232</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776364561519</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874598727247717</v>
+        <v>-0.007874599390526926</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538757324219</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141646735497</v>
+        <v>177.714180280125</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7263967599338</v>
+        <v>172.7264119284913</v>
       </c>
       <c r="E11" t="n">
-        <v>177.674269227683</v>
+        <v>177.6742848307548</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643945211436</v>
+        <v>-0.03324627247716094</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -732,7 +732,7 @@
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0195199248555431</v>
+        <v>-0.01952001095973654</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -741,22 +741,22 @@
         <v>45903</v>
       </c>
       <c r="B13" t="n">
-        <v>170.2026214599609</v>
+        <v>170.2026062011719</v>
       </c>
       <c r="C13" t="n">
-        <v>171.9882512542426</v>
+        <v>171.9882358353705</v>
       </c>
       <c r="D13" t="n">
-        <v>168.4668876205481</v>
+        <v>168.4668725173688</v>
       </c>
       <c r="E13" t="n">
-        <v>170.6415475595936</v>
+        <v>170.6415322614545</v>
       </c>
       <c r="F13" t="n">
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009367785958406261</v>
+        <v>-0.0009368681625865349</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400817871094</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.4395894944585</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955858311417</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527518438138</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095353053086949</v>
+        <v>0.006095532901013501</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114044189453</v>
+        <v>166.6114196777344</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164816497661</v>
+        <v>168.6164970921864</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686243805947</v>
+        <v>163.6686393698748</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189280624296</v>
+        <v>167.6189434134908</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703025175833773</v>
+        <v>-0.02703024934973741</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982696533203</v>
+        <v>167.8982391357422</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417962304089</v>
+        <v>170.5417652323373</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406265749079</v>
+        <v>166.9405962313932</v>
       </c>
       <c r="E16" t="n">
-        <v>167.140134281122</v>
+        <v>167.1401039013443</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00772375239776002</v>
+        <v>0.007723476941117413</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643497212367</v>
+        <v>0.01455661938028308</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847503361609572</v>
+        <v>0.03847512319332802</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460227399664788</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668914997253303</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947256518719</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187866210938</v>
+        <v>175.8187713623047</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767318043244</v>
+        <v>176.6767164710769</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466271367534</v>
+        <v>172.5466121619453</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641783462465</v>
+        <v>173.5641632831282</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494055886175818</v>
+        <v>0.03494046904234804</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439756788046976</v>
+        <v>0.00243984378681672</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470275878906</v>
+        <v>176.5470428466797</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3503245099793</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807727171775</v>
+        <v>174.9807878405966</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403383898065</v>
+        <v>179.3403538900187</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.008182405765993161</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2652893066406</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291385988617</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7161910154847</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629551235593</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387491782843</v>
+        <v>0.004068387140155894</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641296386719</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403552769049</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5119112725463</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441731762758</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002814089176637058</v>
+        <v>0.002813916776754244</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1188,7 +1188,7 @@
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053974480577181</v>
+        <v>0.02053983240613322</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.7924957275391</v>
+        <v>186.79248046875</v>
       </c>
       <c r="C33" t="n">
-        <v>187.690338609038</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604668683245</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972757932568</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0035374073593748</v>
+        <v>0.003537325381961498</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385528564453</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="C34" t="n">
-        <v>190.593394116267</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105347272827</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E34" t="n">
-        <v>189.1468626563914</v>
+        <v>189.146847340247</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223009789566</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715545654297</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050110254035</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369182511207</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378093314507</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.00672366812316183</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965270996094</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7824902019781</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918178290645</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566294029491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108615148198644</v>
+        <v>-0.01108631362422263</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694780736732239</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097412109375</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="C39" t="n">
-        <v>194.8332119113436</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033405552435</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705422839889</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829618052309101</v>
+        <v>0.01829626140377161</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886536282782095</v>
+        <v>-0.04886535894656951</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699188232422</v>
+        <v>187.8699340820312</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556339904095</v>
+        <v>189.6556493942343</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155586605101</v>
+        <v>185.5155737280782</v>
       </c>
       <c r="E41" t="n">
-        <v>187.52074924116</v>
+        <v>187.5207644715895</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817221444483309</v>
+        <v>0.02817221209222476</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402089854789248</v>
+        <v>-0.04402097619247958</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754425048828</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419301869027</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944368108431</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101030171288664</v>
+        <v>0.01101038676736099</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755442021748715</v>
+        <v>0.007755357241106875</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246398925781</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925557149365</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602938591047</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988793025541</v>
+        <v>179.988777912505</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042837577039868</v>
+        <v>0.01042829092822517</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250748267812286</v>
+        <v>0.02250765250109055</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323333740234</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="C51" t="n">
-        <v>191.5411089646758</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D51" t="n">
-        <v>187.9796341631504</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359184602369</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807902404094098</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981990486196963</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989595999882533</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050750732422</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672637579894</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286166610889</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596680014167</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004440999182711</v>
+        <v>-0.02004441147263381</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971455471800998</v>
+        <v>-0.001971380233034448</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434387207031</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4350026612236</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847643800754</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949275919373</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751478380745641</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304626464844</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476539294223</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.9345289438528</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505251524069</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.03652478060097764</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7002868652344</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8698939350823</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823816093971</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580548583195</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003720555463071484</v>
+        <v>0.0003722182238108385</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742797851562</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="C61" t="n">
-        <v>199.462152104167</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268412779572</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436938260565</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793274534380033</v>
+        <v>0.05793257804752372</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959067030875928</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133911132812</v>
+        <v>186.4134063720703</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824463944715</v>
+        <v>190.9824620272586</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105907203728</v>
+        <v>183.4106057333689</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933791327836</v>
+        <v>190.5933947337238</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581012967027952</v>
+        <v>-0.03581005074692667</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154693603516</v>
+        <v>189.7154846191406</v>
       </c>
       <c r="C65" t="n">
-        <v>190.553458007553</v>
+        <v>190.5534733337414</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1483942490048</v>
+        <v>180.1484087383153</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229435613052</v>
+        <v>182.4229582335574</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0177137394870075</v>
+        <v>0.01771373803705711</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540222167969</v>
+        <v>186.1540374755859</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482800008962</v>
+        <v>188.5482954559393</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794727552066</v>
+        <v>183.879487827554</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255230789849</v>
+        <v>185.5255382862568</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877257113277342</v>
+        <v>-0.01877256962289819</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.926513671875</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.358293814419</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2205942185541</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9416897271721</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808163091331894</v>
+        <v>-0.02808162861150654</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2061,22 +2061,22 @@
         <v>45980</v>
       </c>
       <c r="B68" t="n">
-        <v>186.0741882324219</v>
+        <v>186.0742034912109</v>
       </c>
       <c r="C68" t="n">
-        <v>187.4109817403353</v>
+        <v>187.4109971087465</v>
       </c>
       <c r="D68" t="n">
-        <v>182.39300555425</v>
+        <v>182.3930205111681</v>
       </c>
       <c r="E68" t="n">
-        <v>184.3483122805645</v>
+        <v>184.3483273978252</v>
       </c>
       <c r="F68" t="n">
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174240124138</v>
+        <v>0.02845174000170858</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2100,7 +2100,7 @@
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152471782905131</v>
+        <v>-0.03152479724769053</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2109,22 +2109,22 @@
         <v>45982</v>
       </c>
       <c r="B70" t="n">
-        <v>178.4524536132812</v>
+        <v>178.4524688720703</v>
       </c>
       <c r="C70" t="n">
-        <v>184.1188702156436</v>
+        <v>184.1188859589464</v>
       </c>
       <c r="D70" t="n">
-        <v>172.5166628687019</v>
+        <v>172.5166776199441</v>
       </c>
       <c r="E70" t="n">
-        <v>180.806813452001</v>
+        <v>180.8068289121023</v>
       </c>
       <c r="F70" t="n">
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743162817541062</v>
+        <v>-0.009743078144453632</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2148,7 +2148,7 @@
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051661128715887</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C72" t="n">
-        <v>177.7341879937998</v>
+        <v>177.734203281764</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447659257062</v>
+        <v>169.1447804748437</v>
       </c>
       <c r="E72" t="n">
-        <v>174.491955735681</v>
+        <v>174.4919707447618</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591067635257405</v>
+        <v>-0.0259105925654145</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159873604817</v>
+        <v>0.01372159755577274</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2220,7 +2220,7 @@
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808484361385299</v>
+        <v>-0.01808492693090802</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607513427734</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.013916155068</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819028715845</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6471955161887</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030535058927451</v>
+        <v>-0.01030543487972591</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116053693065423</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841613769531</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2289086763207</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876631773748</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4607020047171</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289519918164731</v>
+        <v>-0.005289603321452563</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721400043751253</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125830460996126</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2421,22 +2421,22 @@
         <v>46002</v>
       </c>
       <c r="B83" t="n">
-        <v>180.5075988769531</v>
+        <v>180.5076141357422</v>
       </c>
       <c r="C83" t="n">
-        <v>180.8967030087509</v>
+        <v>180.896718300432</v>
       </c>
       <c r="D83" t="n">
-        <v>176.2076633109278</v>
+        <v>176.2076782062319</v>
       </c>
       <c r="E83" t="n">
-        <v>179.8591224369562</v>
+        <v>179.8591376409278</v>
       </c>
       <c r="F83" t="n">
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550770804044477</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2460,7 +2460,7 @@
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266451936799664</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682952880859</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8880102762506</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4730132178061</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428571096804</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005069689074391</v>
+        <v>0.03005061362821149</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.003171176350336591</v>
+        <v>-0.00317109577323571</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021881103516</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5488153175326</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4936115238563</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005661647843</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612757568446812</v>
+        <v>-0.003612838827051545</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545538552702456</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808319091797</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779786425506</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154296257417</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123337767646</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386553447189375</v>
+        <v>-0.00386561545941666</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8029022216797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213860539245</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838845193456</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752439930999</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780243029006</v>
+        <v>-0.004677780623340899</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987081691657185</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080017089844</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074824738404</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685072554968</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152196030920583</v>
+        <v>-0.02152187943302564</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009726849758688871</v>
+        <v>-0.0009727675505442068</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.376220703125</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708543554723</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718432388734</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5681140987238</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.004704210650191332</v>
+        <v>0.00470412795042785</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2964,7 +2964,7 @@
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436954843994676</v>
+        <v>-0.01436946731018618</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.654296875</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438168415518142</v>
+        <v>-0.04381675942490471</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948280612693632</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.03466796875</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784751839824</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D112" t="n">
-        <v>185.5557928402329</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230595290241</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.006394234985120373</v>
+        <v>-0.00639415348837058</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099379525930511</v>
+        <v>0.01099371233637481</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728759765625</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009400606663</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3967902384632</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E114" t="n">
-        <v>190.823459633995</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591334872193784</v>
+        <v>0.01591342985123156</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169239280915949</v>
+        <v>0.00516915900963677</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3261,22 +3261,22 @@
         <v>46056</v>
       </c>
       <c r="B118" t="n">
-        <v>179.9189758300781</v>
+        <v>179.9189910888672</v>
       </c>
       <c r="C118" t="n">
-        <v>185.8351396091497</v>
+        <v>185.835155369684</v>
       </c>
       <c r="D118" t="n">
-        <v>175.8185703987175</v>
+        <v>175.8185853097543</v>
       </c>
       <c r="E118" t="n">
-        <v>185.8052108647954</v>
+        <v>185.8052266227915</v>
       </c>
       <c r="F118" t="n">
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839291451472381</v>
+        <v>-0.02839283211347909</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3300,7 +3300,7 @@
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0341021289659974</v>
+        <v>-0.03410221088304122</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963439941406</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2079034382237</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205647824287</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298386502086</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.024971658454912</v>
+        <v>0.02497157596478594</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893114950312197</v>
+        <v>-0.007893035105149604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063385009766</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088363522974</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D124" t="n">
-        <v>188.3293278304631</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007297023972</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800904593061702</v>
+        <v>0.008008964809924857</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5036010742188</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="C125" t="n">
-        <v>193.158028491682</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745969700116</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793806436633</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410180845216</v>
+        <v>-0.01636410312537218</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209282728038808</v>
+        <v>-0.02209274727292232</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181569032381558</v>
+        <v>0.01181560666047221</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613189697266</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900804037161</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D129" t="n">
-        <v>185.226558259481</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E129" t="n">
-        <v>186.6232837033845</v>
+        <v>186.62329889396</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004256064912840918</v>
+        <v>-0.0004255251289267958</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3564,7 +3564,7 @@
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833524412785</v>
+        <v>0.01021825301539225</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637238018573</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682301224481</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E135" t="n">
-        <v>180.82685580423</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164645489360941</v>
+        <v>-0.04164637217148226</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539703369141</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0316933488174</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322775806792</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014088918714</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486500292533</v>
+        <v>0.02985486242594537</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3732,7 +3732,7 @@
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331638712945649</v>
+        <v>-0.01331646982798718</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126861572266</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2688145383873</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396472340209</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187649948852</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660639760928495</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638910718471109</v>
+        <v>0.001638994413631911</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010789985650675</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3813,22 +3813,22 @@
         <v>46090</v>
       </c>
       <c r="B141" t="n">
-        <v>182.2235870361328</v>
+        <v>182.2236022949219</v>
       </c>
       <c r="C141" t="n">
-        <v>182.4829897940845</v>
+        <v>182.4830050745951</v>
       </c>
       <c r="D141" t="n">
-        <v>175.1501427003192</v>
+        <v>175.1501573668019</v>
       </c>
       <c r="E141" t="n">
-        <v>176.4171820751478</v>
+        <v>176.4171968477281</v>
       </c>
       <c r="F141" t="n">
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716221787178097</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3852,7 +3852,7 @@
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690076858506</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -7497,12 +7497,36 @@
         <v>215.3000030517578</v>
       </c>
       <c r="F294" t="n">
-        <v>126789100</v>
+        <v>127087900</v>
       </c>
       <c r="G294" t="n">
         <v>-0.01839135683729232</v>
       </c>
       <c r="H294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B295" t="n">
+        <v>214.1300048828125</v>
+      </c>
+      <c r="C295" t="n">
+        <v>218.6799926757812</v>
+      </c>
+      <c r="D295" t="n">
+        <v>213.3200073242188</v>
+      </c>
+      <c r="E295" t="n">
+        <v>216.5599975585938</v>
+      </c>
+      <c r="F295" t="n">
+        <v>120855100</v>
+      </c>
+      <c r="G295" t="n">
+        <v>-0.01427054691201457</v>
+      </c>
+      <c r="H295" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701477050781</v>
+        <v>179.3701324462891</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650167895762</v>
+        <v>181.4650013525793</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380831102634</v>
+        <v>176.1380681264219</v>
       </c>
       <c r="E7" t="n">
-        <v>177.9137276700343</v>
+        <v>177.913712535141</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022540229354618</v>
+        <v>0.01022531635496304</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253326416016</v>
+        <v>181.3253173828125</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438110385745</v>
+        <v>181.9437957277396</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725671170498</v>
+        <v>178.3725521067403</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195091893087</v>
+        <v>179.6194940740671</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090028057365577</v>
+        <v>0.01090028150092892</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557464599609</v>
+        <v>181.15576171875</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435685875041</v>
+        <v>182.0435839210746</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618623689453</v>
+        <v>178.6618774176739</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348064912021</v>
+        <v>181.5348217819195</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009352591784613784</v>
+        <v>-0.0009350909542572561</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292175292969</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187007491465</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.978421739232</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776364561519</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874599390526926</v>
+        <v>-0.007874598727247717</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324627247716094</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622131347656</v>
+        <v>170.3621978759766</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583050821389</v>
+        <v>171.9582896803931</v>
       </c>
       <c r="D12" t="n">
-        <v>166.810924534394</v>
+        <v>166.8109095936823</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841224963229</v>
+        <v>169.5841073072249</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952001095973654</v>
+        <v>-0.01952009877813865</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368681625865349</v>
+        <v>-0.000936778679744843</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400817871094</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395894944585</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955858311417</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527518438138</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095532901013501</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703024934973741</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982391357422</v>
+        <v>167.8982543945312</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417652323373</v>
+        <v>170.5417807313731</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9405962313932</v>
+        <v>166.9406114031506</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401039013443</v>
+        <v>167.1401190912332</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723476941117413</v>
+        <v>0.007723568524209856</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -837,22 +837,22 @@
         <v>45909</v>
       </c>
       <c r="B17" t="n">
-        <v>170.3422698974609</v>
+        <v>170.3422546386719</v>
       </c>
       <c r="C17" t="n">
-        <v>170.5617329363479</v>
+        <v>170.5617176578999</v>
       </c>
       <c r="D17" t="n">
-        <v>166.332114851899</v>
+        <v>166.3320999523285</v>
       </c>
       <c r="E17" t="n">
-        <v>168.6763569906099</v>
+        <v>168.6763418810487</v>
       </c>
       <c r="F17" t="n">
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455661938028308</v>
+        <v>0.01455643629502945</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8962097167969</v>
+        <v>176.8961944580078</v>
       </c>
       <c r="C18" t="n">
-        <v>178.851406558282</v>
+        <v>178.8513911308407</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407591182253</v>
+        <v>175.0407440194845</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078951884048</v>
+        <v>176.2078799889887</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512319332802</v>
+        <v>0.03847512663982333</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465362548828</v>
+        <v>176.7465515136719</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491035140756</v>
+        <v>179.8491190407138</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0581830190845</v>
+        <v>176.058198218447</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505315119071</v>
+        <v>179.2505469868697</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008459364815304182</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731541223449</v>
+        <v>178.1731387966239</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028283464474</v>
+        <v>176.028268323246</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451359862166</v>
+        <v>177.3451207317183</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003669001328727717</v>
+        <v>0.003668828349043585</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251647949219</v>
+        <v>177.3251800537109</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225418052247</v>
+        <v>178.4225571584428</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929031464731</v>
+        <v>174.0929181271268</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501343169162</v>
+        <v>175.2501493971494</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807076698219</v>
+        <v>-0.0003936087097625718</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620208740234</v>
+        <v>174.4620361328125</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757538913052</v>
+        <v>177.0757693786965</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632159334845</v>
+        <v>173.9632311486472</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769489507663</v>
+        <v>176.5769643945311</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614629078640273</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624663238682878</v>
+        <v>-0.02624671755319263</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187713623047</v>
+        <v>175.8187866210938</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767164710769</v>
+        <v>176.6767318043244</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466121619453</v>
+        <v>172.5466271367534</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641632831282</v>
+        <v>173.5641783462465</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494046904234804</v>
+        <v>0.03494055886175818</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00243984378681672</v>
+        <v>0.002439756788046976</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470428466797</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503245099793</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807878405966</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403538900187</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182405765993161</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1140,7 +1140,7 @@
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387140155894</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813916776754244</v>
+        <v>0.002813830697929731</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153594970703</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602146114836</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890176259668</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987400973632</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053983240613322</v>
+        <v>0.020540005843803</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041378766245</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715698242188</v>
+        <v>187.1715850830078</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050265070322</v>
+        <v>189.9050419886609</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369333277354</v>
+        <v>184.9369484043502</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378247179256</v>
+        <v>188.7378401044004</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723425742952704</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965270996094</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7824902019781</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918178290645</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566294029491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108631362422263</v>
+        <v>-0.01108631272043314</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694780736732239</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097564697266</v>
+        <v>192.1097412109375</v>
       </c>
       <c r="C39" t="n">
-        <v>194.833227386451</v>
+        <v>194.8332119113436</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033556943829</v>
+        <v>190.6033405552435</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705575158363</v>
+        <v>191.7705422839889</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626140377161</v>
+        <v>0.01829618052309101</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886535894656951</v>
+        <v>-0.04886536282782095</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699340820312</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556493942343</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155737280782</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207644715895</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817221209222476</v>
+        <v>0.02817213093671711</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402097619247958</v>
+        <v>-0.04402082090329285</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001922607422</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281395182556</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D43" t="n">
-        <v>176.866254560341</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3583147400375</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110936754343372</v>
+        <v>-0.001111021714327642</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1500,7 +1500,7 @@
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038676736099</v>
+        <v>0.01101047275832534</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820892333984</v>
+        <v>182.7820739746094</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599908268075</v>
+        <v>183.6599754947305</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3203666523256</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493465774322</v>
+        <v>179.7493315718189</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755357241106875</v>
+        <v>0.007755273112916461</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590696970089</v>
+        <v>-0.003165507480461738</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491058349609</v>
+        <v>179.8491363525391</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015566720687</v>
+        <v>183.0015877245683</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375148363812</v>
+        <v>176.3375447580973</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070509305708</v>
+        <v>180.7070815937288</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485768219622118</v>
+        <v>-0.004857513336146591</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1620,7 +1620,7 @@
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829092822517</v>
+        <v>0.01042811947438915</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250765250109055</v>
+        <v>0.02250756853454439</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807902404094098</v>
+        <v>0.02807910846500516</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495300292969</v>
+        <v>200.5495147705078</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644582837766</v>
+        <v>202.6644428640734</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513320204045</v>
+        <v>191.4513174538508</v>
       </c>
       <c r="E52" t="n">
-        <v>192.5886067715161</v>
+        <v>192.588592118433</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981990486196963</v>
+        <v>0.04981982498653692</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989603835835264</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1740,7 +1740,7 @@
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004441147263381</v>
+        <v>-0.02004448386811519</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434234619141</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4349867997753</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847491650603</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949120548774</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751478380745641</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304626464844</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476539294223</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345289438528</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505251524069</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652478060097764</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003722182238108385</v>
+        <v>0.0003721368699238781</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742645263672</v>
+        <v>198.5742492675781</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621367771523</v>
+        <v>199.4621214501376</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268264223904</v>
+        <v>193.3268115668235</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436788693004</v>
+        <v>194.6436639125443</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793257804752372</v>
+        <v>0.05793249675415924</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959052117289374</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4134063720703</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824620272586</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4106057333689</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933947337238</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005074692667</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -1989,22 +1989,22 @@
         <v>45975</v>
       </c>
       <c r="B65" t="n">
-        <v>189.7154846191406</v>
+        <v>189.7154693603516</v>
       </c>
       <c r="C65" t="n">
-        <v>190.5534733337414</v>
+        <v>190.553458007553</v>
       </c>
       <c r="D65" t="n">
-        <v>180.1484087383153</v>
+        <v>180.1483942490048</v>
       </c>
       <c r="E65" t="n">
-        <v>182.4229582335574</v>
+        <v>182.4229435613052</v>
       </c>
       <c r="F65" t="n">
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771373803705711</v>
+        <v>0.0177137394870075</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540374755859</v>
+        <v>186.1540222167969</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482954559393</v>
+        <v>188.5482800008962</v>
       </c>
       <c r="D66" t="n">
-        <v>183.879487827554</v>
+        <v>183.8794727552066</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255382862568</v>
+        <v>185.5255230789849</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877256962289819</v>
+        <v>-0.01877257113277342</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265289306641</v>
+        <v>180.9265441894531</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583093626339</v>
+        <v>184.3583249108488</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206093334711</v>
+        <v>179.2206244483882</v>
       </c>
       <c r="E67" t="n">
-        <v>182.941705155915</v>
+        <v>182.9417205846578</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808162861150654</v>
+        <v>-0.02808146697607095</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845174000170858</v>
+        <v>0.02845165326524768</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2085,22 +2085,22 @@
         <v>45981</v>
       </c>
       <c r="B69" t="n">
-        <v>180.208251953125</v>
+        <v>180.2082366943359</v>
       </c>
       <c r="C69" t="n">
-        <v>195.5315406452363</v>
+        <v>195.5315240889771</v>
       </c>
       <c r="D69" t="n">
-        <v>179.4201468289569</v>
+        <v>179.4201316368992</v>
       </c>
       <c r="E69" t="n">
-        <v>195.4816571057099</v>
+        <v>195.4816405536745</v>
       </c>
       <c r="F69" t="n">
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152479724769053</v>
+        <v>-0.03152487925147596</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2124,7 +2124,7 @@
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743078144453632</v>
+        <v>-0.009742994296335628</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1136932373047</v>
+        <v>182.1137084960938</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614196131816</v>
+        <v>183.0614349513779</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0581937395723</v>
+        <v>176.0582084909882</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610093294625</v>
+        <v>179.0610243324759</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051652402668092</v>
+        <v>0.02051660953286172</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2157,22 +2157,22 @@
         <v>45986</v>
       </c>
       <c r="B72" t="n">
-        <v>177.39501953125</v>
+        <v>177.3950042724609</v>
       </c>
       <c r="C72" t="n">
-        <v>177.734203281764</v>
+        <v>177.7341879937998</v>
       </c>
       <c r="D72" t="n">
-        <v>169.1447804748437</v>
+        <v>169.1447659257062</v>
       </c>
       <c r="E72" t="n">
-        <v>174.4919707447618</v>
+        <v>174.491955735681</v>
       </c>
       <c r="F72" t="n">
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.0259105925654145</v>
+        <v>-0.02591075796874476</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2196,7 +2196,7 @@
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159755577274</v>
+        <v>0.01372168475193747</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.9518890380859</v>
+        <v>182.951904296875</v>
       </c>
       <c r="C78" t="n">
-        <v>184.089227004522</v>
+        <v>184.0892423581687</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398751387779</v>
+        <v>179.5398901129937</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1959881613664</v>
+        <v>181.1960032737075</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116053693065423</v>
+        <v>0.02116062209880032</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841461181641</v>
+        <v>181.9841613769531</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2288932293168</v>
+        <v>184.2289086763207</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876480440623</v>
+        <v>180.4876631773748</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4606866221248</v>
+        <v>183.4607020047171</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289603321452563</v>
+        <v>-0.00528960288028224</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168212890625</v>
+        <v>185.1168365478516</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5610985176648</v>
+        <v>187.5611139779305</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741660895743</v>
+        <v>181.9741810893209</v>
       </c>
       <c r="E80" t="n">
-        <v>182.2136112701494</v>
+        <v>182.213626289633</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721400043751253</v>
+        <v>0.01721399899417375</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2388,7 +2388,7 @@
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125830460996126</v>
+        <v>-0.003125912631224192</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2421,22 +2421,22 @@
         <v>46002</v>
       </c>
       <c r="B83" t="n">
-        <v>180.5076141357422</v>
+        <v>180.5075988769531</v>
       </c>
       <c r="C83" t="n">
-        <v>180.896718300432</v>
+        <v>180.8967030087509</v>
       </c>
       <c r="D83" t="n">
-        <v>176.2076782062319</v>
+        <v>176.2076633109278</v>
       </c>
       <c r="E83" t="n">
-        <v>179.8591376409278</v>
+        <v>179.8591224369562</v>
       </c>
       <c r="F83" t="n">
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770804044477</v>
+        <v>-0.01550779126219859</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114196777344</v>
+        <v>174.6114044189453</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3932136047752</v>
+        <v>182.3931976659576</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123443447362</v>
+        <v>174.2123291208211</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871989054384</v>
+        <v>180.6871831157045</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266451936799664</v>
+        <v>-0.03266452212921567</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2484,7 +2484,7 @@
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256189498619836</v>
+        <v>0.007256277519845034</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3050994873047</v>
+        <v>177.3051147460938</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733061224419</v>
+        <v>178.0733214473424</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916756985292</v>
+        <v>174.4916907151964</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485012773324</v>
+        <v>175.8485164107673</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111661183153096</v>
+        <v>0.008111747940743541</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2532,7 +2532,7 @@
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814983424509077</v>
+        <v>-0.03814991702143256</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646057128906</v>
+        <v>186.0646209716797</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151249886817</v>
+        <v>190.1151405796458</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546345387688</v>
+        <v>186.0546497967401</v>
       </c>
       <c r="E96" t="n">
-        <v>189.1274459397885</v>
+        <v>189.127461449755</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545375898472038</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2772,7 +2772,7 @@
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0126006135839718</v>
+        <v>0.01260053054261179</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808166503906</v>
+        <v>187.6808319091797</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779629368336</v>
+        <v>193.1779786425506</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154145267434</v>
+        <v>185.7154296257417</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123182227279</v>
+        <v>191.3123337767646</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386561545941666</v>
+        <v>-0.00386553447189375</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2820,7 +2820,7 @@
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780623340899</v>
+        <v>-0.004677861544826856</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.3762054443359</v>
+        <v>185.376220703125</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708389078061</v>
+        <v>187.6708543554723</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718281779948</v>
+        <v>182.9718432388734</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5680989064521</v>
+        <v>184.5681140987238</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.00470412795042785</v>
+        <v>0.004704210650191332</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124481201172</v>
+        <v>182.7124328613281</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293738083791</v>
+        <v>184.0293584396101</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3779146434709</v>
+        <v>180.3778995796448</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8897012556695</v>
+        <v>183.8896858985649</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436946731018618</v>
+        <v>-0.01436963075249476</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2988,7 +2988,7 @@
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134982562154453</v>
+        <v>0.02134991091711691</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952423095703</v>
+        <v>185.7952270507812</v>
       </c>
       <c r="C107" t="n">
-        <v>189.9954207742267</v>
+        <v>189.99540517049</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455985734289</v>
+        <v>185.6455833269296</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385950815971</v>
+        <v>188.6385795892923</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849373637116</v>
+        <v>-0.004383931140514608</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.654296875</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542325986551</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953640623503</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753422141945</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381675942490471</v>
+        <v>-0.04381676302343995</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948280612693632</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766815185547</v>
+        <v>185.1766967773438</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557348322644</v>
+        <v>189.8557504766133</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4483900153819</v>
+        <v>184.4484052141589</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629659025267</v>
+        <v>186.7629812920276</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888093084756926</v>
+        <v>-0.02888085082614911</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3261,22 +3261,22 @@
         <v>46056</v>
       </c>
       <c r="B118" t="n">
-        <v>179.9189910888672</v>
+        <v>179.9189758300781</v>
       </c>
       <c r="C118" t="n">
-        <v>185.835155369684</v>
+        <v>185.8351396091497</v>
       </c>
       <c r="D118" t="n">
-        <v>175.8185853097543</v>
+        <v>175.8185703987175</v>
       </c>
       <c r="E118" t="n">
-        <v>185.8052266227915</v>
+        <v>185.8052108647954</v>
       </c>
       <c r="F118" t="n">
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839283211347909</v>
+        <v>-0.02839299457635047</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833557128906</v>
+        <v>173.7833404541016</v>
       </c>
       <c r="C119" t="n">
-        <v>179.1607721437711</v>
+        <v>179.160756412826</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086795929406</v>
+        <v>171.5086645338761</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410571553003</v>
+        <v>179.0410414348666</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221088304122</v>
+        <v>-0.03410221377522338</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787445068359</v>
+        <v>171.4787292480469</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4072143255947</v>
+        <v>176.4071986282528</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307227747363</v>
+        <v>170.6307075914073</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5216119878791</v>
+        <v>174.5215964583249</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.0132614035251003</v>
+        <v>-0.01326140468949821</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771575927734</v>
+        <v>184.9771423339844</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634420291942</v>
+        <v>186.5634266395524</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923963475411</v>
+        <v>174.1923819783884</v>
       </c>
       <c r="E121" t="n">
-        <v>176.2775135166603</v>
+        <v>176.277498975506</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.07871770419569057</v>
+        <v>0.0787177112002726</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963287353516</v>
+        <v>189.5963439941406</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2078878887748</v>
+        <v>193.2079034382237</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205500126207</v>
+        <v>183.5205647824287</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298238555102</v>
+        <v>183.8298386502086</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497157596478594</v>
+        <v>0.02497174300496052</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893035105149604</v>
+        <v>-0.007893114950312197</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832092285156</v>
+        <v>182.3832244873047</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622623874058</v>
+        <v>187.0622780376601</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660562233949</v>
+        <v>181.1660713803529</v>
       </c>
       <c r="E126" t="n">
-        <v>187.0423048169314</v>
+        <v>187.042320465516</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209274727292232</v>
+        <v>-0.02209266545793198</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3492,7 +3492,7 @@
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560666047221</v>
+        <v>0.0118155220086027</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768615722656</v>
+        <v>189.3768768310547</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856654675195</v>
+        <v>189.8856807673048</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059147845697</v>
+        <v>185.5059297314624</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344488846578</v>
+        <v>186.1344638821937</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021825301539225</v>
+        <v>0.01021833441238607</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028137207031</v>
+        <v>191.1028289794922</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972046328596</v>
+        <v>193.4972200828311</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374116308485</v>
+        <v>189.1374267327081</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531547742145</v>
+        <v>190.9531700210539</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113849147715847</v>
+        <v>0.009113848413379699</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786827395534711</v>
+        <v>0.006786747007672789</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583740234375</v>
+        <v>184.4583587646484</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364236513225</v>
+        <v>193.8364076167612</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8897126034445</v>
+        <v>183.8896973916963</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164813019665</v>
+        <v>193.8164652690549</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456121004512637</v>
+        <v>-0.05456128825383422</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164637217148226</v>
+        <v>-0.04164629289442512</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539855957031</v>
+        <v>182.0540008544922</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317086895539</v>
+        <v>183.0317240302905</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322921838959</v>
+        <v>174.2323067871125</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014235260267</v>
+        <v>174.601438160182</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486242594537</v>
+        <v>0.02985494874285899</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296691894531</v>
+        <v>179.6296539306641</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776756968921</v>
+        <v>180.4776603660684</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069714269912</v>
+        <v>176.5069564334623</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0733135069376</v>
+        <v>178.0732983803544</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331646982798718</v>
+        <v>-0.01331663634113589</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126708984375</v>
+        <v>182.6126861572266</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2687991412151</v>
+        <v>184.2688145383873</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396322236537</v>
+        <v>179.6396472340209</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187499528396</v>
+        <v>180.0187649948852</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660639760928495</v>
+        <v>0.01660656891157819</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119720458984</v>
+        <v>182.9119873046875</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6302923567135</v>
+        <v>183.6303076754259</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647274492447</v>
+        <v>177.4647422536165</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470399397241</v>
+        <v>180.7470550179114</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638994413631911</v>
+        <v>0.00163899427668035</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010798076634313</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3813,22 +3813,22 @@
         <v>46090</v>
       </c>
       <c r="B141" t="n">
-        <v>182.2236022949219</v>
+        <v>182.2235870361328</v>
       </c>
       <c r="C141" t="n">
-        <v>182.4830050745951</v>
+        <v>182.4829897940845</v>
       </c>
       <c r="D141" t="n">
-        <v>175.1501573668019</v>
+        <v>175.1501427003192</v>
       </c>
       <c r="E141" t="n">
-        <v>176.4171968477281</v>
+        <v>176.4171820751478</v>
       </c>
       <c r="F141" t="n">
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716221787178097</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3852,7 +3852,7 @@
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690076858506</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223358154297</v>
+        <v>182.7223510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182338343672</v>
+        <v>184.5182492431283</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355064165816</v>
+        <v>181.3355215595592</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302641505579</v>
+        <v>183.6302794851663</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553512051850658</v>
+        <v>-0.01553503830774738</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389434814453</v>
+        <v>179.8389282226562</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656218245341</v>
+        <v>185.6656060713691</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296528660815</v>
+        <v>179.5296376335348</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982918130038</v>
+        <v>184.4982761588831</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.01578018538957893</v>
+        <v>-0.0157803510879263</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021545410156</v>
+        <v>182.8021697998047</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492501487561</v>
+        <v>188.4492658789173</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962848148914</v>
+        <v>180.9962999229416</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527246843909</v>
+        <v>182.5527399223597</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647702662285733</v>
+        <v>0.01647719771483347</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5151062011719</v>
+        <v>181.5150909423828</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771941770484</v>
+        <v>184.9771786272242</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656763194747</v>
+        <v>181.2656610816535</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379731916982</v>
+        <v>184.6379576703901</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040662858024294</v>
+        <v>-0.007040829213523114</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409877322820725</v>
+        <v>-0.008409793966310586</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527709960938</v>
+        <v>178.1527862548828</v>
       </c>
       <c r="C149" t="n">
-        <v>179.5695306962835</v>
+        <v>179.569546076418</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890840362079</v>
+        <v>175.3890990582871</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040222894031</v>
+        <v>177.6040375011918</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019962135457131</v>
+        <v>-0.01019953657814543</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.30615234375</v>
+        <v>172.3061370849609</v>
       </c>
       <c r="C150" t="n">
-        <v>177.853470255105</v>
+        <v>177.8534545050662</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283915093003</v>
+        <v>171.3283763370981</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940686691464</v>
+        <v>177.5940529420793</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281800569058757</v>
+        <v>-0.03281817417975763</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702370190686442</v>
+        <v>0.01702379197069148</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379699707031</v>
+        <v>167.1379547119141</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800990993323</v>
+        <v>170.5800835262955</v>
       </c>
       <c r="D155" t="n">
-        <v>166.629123297364</v>
+        <v>166.6291080850299</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6123099949711</v>
+        <v>169.6122945102883</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172390091733423</v>
+        <v>-0.02172399022862981</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402823229793726</v>
+        <v>-0.01402814228406069</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022583007812</v>
+        <v>174.0022735595703</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217577880002</v>
+        <v>174.2217730660379</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792387089764</v>
+        <v>166.5792533168182</v>
       </c>
       <c r="E157" t="n">
-        <v>166.589210422399</v>
+        <v>166.5892250311153</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588174699846626</v>
+        <v>0.05588183959195892</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491821289062</v>
+        <v>175.3491973876953</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654826629128</v>
+        <v>176.9654980623514</v>
       </c>
       <c r="D158" t="n">
-        <v>174.351462742682</v>
+        <v>174.3514779146501</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986119754623</v>
+        <v>175.5986272559566</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740841074583615</v>
+        <v>0.007740840395765725</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854583740234</v>
+        <v>176.9854431152344</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852364118599</v>
+        <v>177.0852211444685</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791828272563</v>
+        <v>170.9791680862979</v>
       </c>
       <c r="E159" t="n">
-        <v>171.787333172162</v>
+        <v>171.7873183615289</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331530522419529</v>
+        <v>0.009331355671513775</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409269260350898</v>
+        <v>0.001409355596789341</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4906005859375</v>
+        <v>183.4905853271484</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6602110774668</v>
+        <v>183.6601958045732</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080948395415</v>
+        <v>180.2080798537204</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4253138719204</v>
+        <v>181.4252987848774</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005057963567002</v>
+        <v>0.01005049564145621</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566468527863064</v>
+        <v>0.02566477057129601</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148681640625</v>
+        <v>199.1148834228516</v>
       </c>
       <c r="C178" t="n">
-        <v>209.8203930740204</v>
+        <v>209.820409153207</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468419328838</v>
+        <v>198.2468571251534</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512265433391</v>
+        <v>209.4512425942353</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626047369511221</v>
+        <v>-0.04626040060709824</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974365234375</v>
+        <v>197.9974212646484</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370634031337</v>
+        <v>202.5370477944956</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704677294345</v>
+        <v>196.6704525729091</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209846036705</v>
+        <v>200.8209691272831</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005611994980225576</v>
+        <v>-0.005612147816343893</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001510485544036211</v>
+        <v>0.0001511256316393261</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.80615234375</v>
+        <v>224.8061676025391</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720511978</v>
+        <v>230.9720668751014</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286135177626</v>
+        <v>223.7286287034134</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360138852663</v>
+        <v>229.2360294447337</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420125203837699</v>
+        <v>-0.04420118716323318</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331435448943641</v>
+        <v>-0.01331442146103379</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613983154297</v>
+        <v>213.7613830566406</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0285063161196</v>
+        <v>215.0284909668814</v>
       </c>
       <c r="D197" t="n">
-        <v>210.738309512832</v>
+        <v>210.7382944698381</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981702457166</v>
+        <v>210.7981551984497</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007761068323773213</v>
+        <v>0.007760996387428776</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.01451574184062365</v>
+        <v>-0.0145156714944451</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103271484375</v>
+        <v>175.2103424072266</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535459787435</v>
+        <v>182.0535618334976</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607001855326</v>
+        <v>175.0607154312909</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837099150805</v>
+        <v>181.9837257637527</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709167480469</v>
+        <v>174.9709014892578</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694550698242</v>
+        <v>175.5694397588381</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870713158056</v>
+        <v>168.3870566311777</v>
       </c>
       <c r="E4" t="n">
-        <v>174.741483653999</v>
+        <v>174.7414684152183</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366417175785561</v>
+        <v>-0.001366591233594172</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -564,7 +564,7 @@
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394632757571458</v>
+        <v>-0.002394545758820588</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253173828125</v>
+        <v>181.3253326416016</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9437957277396</v>
+        <v>181.9438110385745</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725521067403</v>
+        <v>178.3725671170498</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6194940740671</v>
+        <v>179.6195091893087</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090028150092892</v>
+        <v>0.0109003665696572</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009350909542572561</v>
+        <v>-0.0009351750270146786</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3621978759766</v>
+        <v>170.3622131347656</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9582896803931</v>
+        <v>171.9583050821389</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109095936823</v>
+        <v>166.810924534394</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841073072249</v>
+        <v>169.5841224963229</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952009877813865</v>
+        <v>-0.01952001095973654</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.000936778679744843</v>
+        <v>-0.0009368681625865349</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114196777344</v>
+        <v>166.6114044189453</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164970921864</v>
+        <v>168.6164816497661</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686393698748</v>
+        <v>163.6686243805947</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189434134908</v>
+        <v>167.6189280624296</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703016265075109</v>
+        <v>-0.02703025175833773</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982543945312</v>
+        <v>167.8982696533203</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417807313731</v>
+        <v>170.5417962304089</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406114031506</v>
+        <v>166.9406265749079</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401190912332</v>
+        <v>167.140134281122</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723568524209856</v>
+        <v>0.00772375239776002</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643629502945</v>
+        <v>0.01455634409096618</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465515136719</v>
+        <v>176.7465362548828</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491190407138</v>
+        <v>179.8491035140756</v>
       </c>
       <c r="D19" t="n">
-        <v>176.058198218447</v>
+        <v>176.0581830190845</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505469868697</v>
+        <v>179.2505315119071</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008459364815304182</v>
+        <v>-0.0008460227399664788</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -924,7 +924,7 @@
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668828349043585</v>
+        <v>0.003668914997253303</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251800537109</v>
+        <v>177.3251495361328</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225571584428</v>
+        <v>178.4225264520066</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0929181271268</v>
+        <v>174.0928881658194</v>
       </c>
       <c r="E21" t="n">
-        <v>175.2501493971494</v>
+        <v>175.250119236683</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936087097625718</v>
+        <v>-0.0003937807415412831</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620361328125</v>
+        <v>174.4620208740234</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757693786965</v>
+        <v>177.0757538913052</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632311486472</v>
+        <v>173.9632159334845</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769643945311</v>
+        <v>176.5769489507663</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629078640273</v>
+        <v>-0.01614620751539797</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624671755319263</v>
+        <v>-0.02624663238682878</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477416992188</v>
+        <v>176.2477264404297</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543753314711</v>
+        <v>177.6543599509016</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612974471592</v>
+        <v>174.7612823170602</v>
       </c>
       <c r="E25" t="n">
-        <v>175.349898865447</v>
+        <v>175.3498836843894</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439756788046976</v>
+        <v>0.002439670001024075</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1068,7 +1068,7 @@
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0392823835910463</v>
+        <v>0.03928247356775705</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470275878906</v>
+        <v>176.5470123291016</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3503090089054</v>
+        <v>179.3502935078314</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807727171775</v>
+        <v>174.9807575937583</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403383898065</v>
+        <v>179.3403228895943</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.008182577209651543</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1140,7 +1140,7 @@
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068473920816773</v>
+        <v>0.004068560701492752</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7640991210938</v>
+        <v>177.7641143798828</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403244887289</v>
+        <v>179.3403398828169</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118813132914</v>
+        <v>174.5118962929188</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441426621237</v>
+        <v>177.7441579191998</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813830697929731</v>
+        <v>0.002813916776754244</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153747558594</v>
+        <v>181.4153594970703</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602300506758</v>
+        <v>183.5602146114836</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890327563757</v>
+        <v>179.8890176259668</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987552370008</v>
+        <v>179.9987400973632</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.020540005843803</v>
+        <v>0.02053983240613322</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340637207031</v>
+        <v>186.1340484619141</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022276338177</v>
+        <v>186.9022123120565</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462469572146</v>
+        <v>181.0462321155116</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448190078555</v>
+        <v>181.6448041170831</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041378766245</v>
+        <v>0.02601041597539022</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.79248046875</v>
+        <v>186.7924957275391</v>
       </c>
       <c r="C33" t="n">
-        <v>187.6903232769056</v>
+        <v>187.690338609038</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604518817237</v>
+        <v>183.4604668683245</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972606974542</v>
+        <v>184.7972757932568</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537325381961498</v>
+        <v>0.003537489626782131</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1260,7 +1260,7 @@
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812223729646407</v>
+        <v>0.008812141321341782</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715850830078</v>
+        <v>187.1715545654297</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050419886609</v>
+        <v>189.9050110254035</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369484043502</v>
+        <v>184.9369182511207</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378401044004</v>
+        <v>188.7378093314507</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723425742952704</v>
+        <v>-0.006723587692724298</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965576171875</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7825209975275</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918479831437</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566599139491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108631272043314</v>
+        <v>-0.01108606995897354</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694862951503896</v>
+        <v>-0.002694945166262119</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199532691778505</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829618052309101</v>
+        <v>0.01829626288358566</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222290039062</v>
+        <v>182.7222442626953</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524395658232</v>
+        <v>195.1524558626357</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148814298513</v>
+        <v>181.6148965961679</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474821132437</v>
+        <v>193.0474982342752</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886536282782095</v>
+        <v>-0.04886528340035956</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699035644531</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556185865847</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155435929421</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207340107304</v>
+        <v>187.52074924116</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817213093671711</v>
+        <v>0.02817212858411589</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402082090329285</v>
+        <v>-0.04402089854789248</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001770019531</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281238318171</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D43" t="n">
-        <v>176.8662395170747</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3582990595379</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001111021714327642</v>
+        <v>-0.001110936754343372</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754577636719</v>
+        <v>181.3754425048828</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419455690647</v>
+        <v>182.8419301869027</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403402174659</v>
+        <v>179.3403251298876</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944521048813</v>
+        <v>181.7944368108431</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101047275832534</v>
+        <v>0.01101030171288664</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820739746094</v>
+        <v>182.7820892333984</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599754947305</v>
+        <v>183.6599908268075</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203666523256</v>
+        <v>179.3203816221287</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493315718189</v>
+        <v>179.7493465774322</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755273112916461</v>
+        <v>0.007755442021748715</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165507480461738</v>
+        <v>-0.003165590696970089</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491363525391</v>
+        <v>179.8491058349609</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015877245683</v>
+        <v>183.0015566720687</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375447580973</v>
+        <v>176.3375148363812</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070815937288</v>
+        <v>180.7070509305708</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.004857513336146591</v>
+        <v>-0.00485768219622118</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1620,7 +1620,7 @@
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042811947438915</v>
+        <v>0.01042829092822517</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148040771484</v>
+        <v>185.8148193359375</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219186862977</v>
+        <v>187.0219340442129</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614063875393</v>
+        <v>183.0614214202242</v>
       </c>
       <c r="E50" t="n">
-        <v>183.400590081168</v>
+        <v>183.4006051417061</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250756853454439</v>
+        <v>0.02250765250109055</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323181152344</v>
+        <v>191.0323333740234</v>
       </c>
       <c r="C51" t="n">
-        <v>191.541093665248</v>
+        <v>191.5411089646758</v>
       </c>
       <c r="D51" t="n">
-        <v>187.979619148197</v>
+        <v>187.9796341631504</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359033209746</v>
+        <v>189.5359184602369</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910846500516</v>
+        <v>0.02807910615919784</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982498653692</v>
+        <v>0.04981974113173093</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451507568359</v>
+        <v>206.545166015625</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828509687219</v>
+        <v>211.6828666070652</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905578218423</v>
+        <v>204.2905729140704</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482906515472</v>
+        <v>207.482921843539</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989603835835264</v>
+        <v>0.02989611444324924</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050598144531</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672482532724</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286015136062</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596525726598</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448386811519</v>
+        <v>-0.02004448238730316</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1764,7 +1764,7 @@
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971380233034448</v>
+        <v>-0.001971455471800998</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151184082031</v>
+        <v>198.2151031494141</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824975937368</v>
+        <v>203.4824819294599</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569251230167</v>
+        <v>197.4569099225941</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5148147488263</v>
+        <v>202.5147991590425</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958816719273994</v>
+        <v>-0.03958824112615977</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1836,7 +1836,7 @@
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751470682650169</v>
+        <v>-0.01751463119384</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304779052734</v>
+        <v>187.6304931640625</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476699621838</v>
+        <v>197.1476859949454</v>
       </c>
       <c r="D59" t="n">
-        <v>185.9345440647224</v>
+        <v>185.934559185592</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505410878136</v>
+        <v>195.9505570232203</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652477773914087</v>
+        <v>-0.03652469938585123</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7003021240234</v>
+        <v>187.7002868652344</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8699092076593</v>
+        <v>187.8698939350823</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823961188316</v>
+        <v>178.4823816093971</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580698535366</v>
+        <v>184.4580548583195</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003721368699238781</v>
+        <v>0.0003719741924403941</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1893,22 +1893,22 @@
         <v>45971</v>
       </c>
       <c r="B61" t="n">
-        <v>198.5742492675781</v>
+        <v>198.5742645263672</v>
       </c>
       <c r="C61" t="n">
-        <v>199.4621214501376</v>
+        <v>199.4621367771523</v>
       </c>
       <c r="D61" t="n">
-        <v>193.3268115668235</v>
+        <v>193.3268264223904</v>
       </c>
       <c r="E61" t="n">
-        <v>194.6436639125443</v>
+        <v>194.6436788693004</v>
       </c>
       <c r="F61" t="n">
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793249675415924</v>
+        <v>0.05793266405042918</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1932,7 +1932,7 @@
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959052117289374</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3368072509766</v>
+        <v>193.3367919921875</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4218083488666</v>
+        <v>195.4217929255223</v>
       </c>
       <c r="D63" t="n">
-        <v>190.673190567689</v>
+        <v>190.6731755191215</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522164876445</v>
+        <v>195.2522010776849</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313331767584859</v>
+        <v>0.003313252582732629</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1980,7 +1980,7 @@
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581012967027952</v>
+        <v>-0.03581005357317613</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2037,22 +2037,22 @@
         <v>45979</v>
       </c>
       <c r="B67" t="n">
-        <v>180.9265441894531</v>
+        <v>180.9265289306641</v>
       </c>
       <c r="C67" t="n">
-        <v>184.3583249108488</v>
+        <v>184.3583093626339</v>
       </c>
       <c r="D67" t="n">
-        <v>179.2206244483882</v>
+        <v>179.2206093334711</v>
       </c>
       <c r="E67" t="n">
-        <v>182.9417205846578</v>
+        <v>182.941705155915</v>
       </c>
       <c r="F67" t="n">
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808146697607095</v>
+        <v>-0.02808154894469495</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2076,7 +2076,7 @@
         <v>247246400</v>
       </c>
       <c r="G68" t="n">
-        <v>0.02845165326524768</v>
+        <v>0.02845174000170858</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2085,22 +2085,22 @@
         <v>45981</v>
       </c>
       <c r="B69" t="n">
-        <v>180.2082366943359</v>
+        <v>180.208251953125</v>
       </c>
       <c r="C69" t="n">
-        <v>195.5315240889771</v>
+        <v>195.5315406452363</v>
       </c>
       <c r="D69" t="n">
-        <v>179.4201316368992</v>
+        <v>179.4201468289569</v>
       </c>
       <c r="E69" t="n">
-        <v>195.4816405536745</v>
+        <v>195.4816571057099</v>
       </c>
       <c r="F69" t="n">
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152487925147596</v>
+        <v>-0.03152479724769053</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2124,7 +2124,7 @@
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009742994296335628</v>
+        <v>-0.009743078144453632</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2133,22 +2133,22 @@
         <v>45985</v>
       </c>
       <c r="B71" t="n">
-        <v>182.1137084960938</v>
+        <v>182.1136932373047</v>
       </c>
       <c r="C71" t="n">
-        <v>183.0614349513779</v>
+        <v>183.0614196131816</v>
       </c>
       <c r="D71" t="n">
-        <v>176.0582084909882</v>
+        <v>176.0581937395723</v>
       </c>
       <c r="E71" t="n">
-        <v>179.0610243324759</v>
+        <v>179.0610093294625</v>
       </c>
       <c r="F71" t="n">
         <v>256618300</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02051660953286172</v>
+        <v>0.02051652402668092</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2172,7 +2172,7 @@
         <v>320600300</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02591075796874476</v>
+        <v>-0.02591067635257405</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291625976562</v>
+        <v>179.8291473388672</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728380763597</v>
+        <v>182.4728225932506</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8140014756398</v>
+        <v>177.8139863878403</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958985688627</v>
+        <v>181.1958831941039</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372168475193747</v>
+        <v>0.01372159873604817</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492693090802</v>
+        <v>-0.01808492846544285</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649711013028865</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607513427734</v>
+        <v>179.1607818603516</v>
       </c>
       <c r="C77" t="n">
-        <v>182.013916155068</v>
+        <v>182.0139471586436</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819028715845</v>
+        <v>178.6819333075974</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6471955161887</v>
+        <v>180.6472262869623</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030543487972591</v>
+        <v>-0.01030526629882311</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2301,22 +2301,22 @@
         <v>45995</v>
       </c>
       <c r="B78" t="n">
-        <v>182.951904296875</v>
+        <v>182.9518890380859</v>
       </c>
       <c r="C78" t="n">
-        <v>184.0892423581687</v>
+        <v>184.089227004522</v>
       </c>
       <c r="D78" t="n">
-        <v>179.5398901129937</v>
+        <v>179.5398751387779</v>
       </c>
       <c r="E78" t="n">
-        <v>181.1960032737075</v>
+        <v>181.1959881613664</v>
       </c>
       <c r="F78" t="n">
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116062209880032</v>
+        <v>0.02116036298998392</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2340,7 +2340,7 @@
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00528960288028224</v>
+        <v>-0.005289519918164731</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.8784332275391</v>
+        <v>175.87841796875</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034654802094</v>
+        <v>178.0034500370577</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213802569945</v>
+        <v>174.6213651072644</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245903328353</v>
+        <v>177.5245749312296</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256277519845034</v>
+        <v>0.007256190132717499</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2493,22 +2493,22 @@
         <v>46007</v>
       </c>
       <c r="B86" t="n">
-        <v>177.3051147460938</v>
+        <v>177.3050994873047</v>
       </c>
       <c r="C86" t="n">
-        <v>178.0733214473424</v>
+        <v>178.0733061224419</v>
       </c>
       <c r="D86" t="n">
-        <v>174.4916907151964</v>
+        <v>174.4916756985292</v>
       </c>
       <c r="E86" t="n">
-        <v>175.8485164107673</v>
+        <v>175.8485012773324</v>
       </c>
       <c r="F86" t="n">
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111747940743541</v>
+        <v>0.008111748644499261</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409393310547</v>
+        <v>170.5409240722656</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188256001934</v>
+        <v>175.7188098781239</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9124052081842</v>
+        <v>169.9123900056319</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888968536916</v>
+        <v>175.6888811343</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814991702143256</v>
+        <v>-0.03814992030459552</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01871996339485515</v>
+        <v>0.01872005454267267</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674743652344</v>
+        <v>180.5674896240234</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0263919449467</v>
+        <v>181.0264072425164</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283209122297</v>
+        <v>175.9283357789888</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575523358494</v>
+        <v>176.2575672304301</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933620451306163</v>
+        <v>0.03933629234179148</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491794177123418</v>
+        <v>0.01491785600596796</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682800292969</v>
+        <v>188.7682952880859</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8879950077845</v>
+        <v>188.8880102762506</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4729984678863</v>
+        <v>182.4730132178061</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428423541149</v>
+        <v>182.5428571096804</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005061362821149</v>
+        <v>0.03005069689074391</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.00317109577323571</v>
+        <v>-0.003171176350336591</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2733,22 +2733,22 @@
         <v>46022</v>
       </c>
       <c r="B96" t="n">
-        <v>186.0646209716797</v>
+        <v>186.0646057128906</v>
       </c>
       <c r="C96" t="n">
-        <v>190.1151405796458</v>
+        <v>190.1151249886817</v>
       </c>
       <c r="D96" t="n">
-        <v>186.0546497967401</v>
+        <v>186.0546345387688</v>
       </c>
       <c r="E96" t="n">
-        <v>189.127461449755</v>
+        <v>189.1274459397885</v>
       </c>
       <c r="F96" t="n">
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545375898472038</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2772,7 +2772,7 @@
         <v>148240500</v>
       </c>
       <c r="G97" t="n">
-        <v>0.01260053054261179</v>
+        <v>0.0126006135839718</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080169677734</v>
+        <v>184.6080017089844</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074981045344</v>
+        <v>189.1074824738404</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811352524241</v>
+        <v>183.2811201033086</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685228499072</v>
+        <v>188.6685072554968</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152187943302564</v>
+        <v>-0.02152196030920583</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009727675505442068</v>
+        <v>-0.0009726849758688871</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2949,22 +2949,22 @@
         <v>46036</v>
       </c>
       <c r="B105" t="n">
-        <v>182.7124328613281</v>
+        <v>182.7124481201172</v>
       </c>
       <c r="C105" t="n">
-        <v>184.0293584396101</v>
+        <v>184.0293738083791</v>
       </c>
       <c r="D105" t="n">
-        <v>180.3778995796448</v>
+        <v>180.3779146434709</v>
       </c>
       <c r="E105" t="n">
-        <v>183.8896858985649</v>
+        <v>183.8897012556695</v>
       </c>
       <c r="F105" t="n">
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436963075249476</v>
+        <v>-0.01436954843994676</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133270263672</v>
+        <v>186.6133117675781</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571344016907</v>
+        <v>189.2571189267257</v>
       </c>
       <c r="D106" t="n">
-        <v>185.895006678512</v>
+        <v>185.8949914784577</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0646079796491</v>
+        <v>186.0645927657271</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134991091711691</v>
+        <v>0.02134974210895835</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3012,7 +3012,7 @@
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383931140514608</v>
+        <v>-0.004383849732090828</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.654296875</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381676302343995</v>
+        <v>-0.04381668089652369</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948280612693632</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728912353516</v>
+        <v>191.0728759765625</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009553855833</v>
+        <v>191.9009400606663</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3968053634026</v>
+        <v>189.3967902384632</v>
       </c>
       <c r="E114" t="n">
-        <v>190.8234748728661</v>
+        <v>190.823459633995</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591342985123156</v>
+        <v>0.01591334872193784</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.00516915900963677</v>
+        <v>0.005169239280915949</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3237,22 +3237,22 @@
         <v>46055</v>
       </c>
       <c r="B117" t="n">
-        <v>185.1766967773438</v>
+        <v>185.1766815185547</v>
       </c>
       <c r="C117" t="n">
-        <v>189.8557504766133</v>
+        <v>189.8557348322644</v>
       </c>
       <c r="D117" t="n">
-        <v>184.4484052141589</v>
+        <v>184.4483900153819</v>
       </c>
       <c r="E117" t="n">
-        <v>186.7629812920276</v>
+        <v>186.7629659025267</v>
       </c>
       <c r="F117" t="n">
         <v>165794100</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.02888085082614911</v>
+        <v>-0.02888093084756926</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -3276,7 +3276,7 @@
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839299457635047</v>
+        <v>-0.02839291451472381</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3285,22 +3285,22 @@
         <v>46057</v>
       </c>
       <c r="B119" t="n">
-        <v>173.7833404541016</v>
+        <v>173.7833557128906</v>
       </c>
       <c r="C119" t="n">
-        <v>179.160756412826</v>
+        <v>179.1607721437711</v>
       </c>
       <c r="D119" t="n">
-        <v>171.5086645338761</v>
+        <v>171.5086795929406</v>
       </c>
       <c r="E119" t="n">
-        <v>179.0410414348666</v>
+        <v>179.0410571553003</v>
       </c>
       <c r="F119" t="n">
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.03410221377522338</v>
+        <v>-0.0341021289659974</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3309,22 +3309,22 @@
         <v>46058</v>
       </c>
       <c r="B120" t="n">
-        <v>171.4787292480469</v>
+        <v>171.4787445068359</v>
       </c>
       <c r="C120" t="n">
-        <v>176.4071986282528</v>
+        <v>176.4072143255947</v>
       </c>
       <c r="D120" t="n">
-        <v>170.6307075914073</v>
+        <v>170.6307227747363</v>
       </c>
       <c r="E120" t="n">
-        <v>174.5215964583249</v>
+        <v>174.5216119878791</v>
       </c>
       <c r="F120" t="n">
         <v>206312900</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.01326140468949821</v>
+        <v>-0.0132614035251003</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -3333,22 +3333,22 @@
         <v>46059</v>
       </c>
       <c r="B121" t="n">
-        <v>184.9771423339844</v>
+        <v>184.9771575927734</v>
       </c>
       <c r="C121" t="n">
-        <v>186.5634266395524</v>
+        <v>186.5634420291942</v>
       </c>
       <c r="D121" t="n">
-        <v>174.1923819783884</v>
+        <v>174.1923963475411</v>
       </c>
       <c r="E121" t="n">
-        <v>176.277498975506</v>
+        <v>176.2775135166603</v>
       </c>
       <c r="F121" t="n">
         <v>231346200</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0787177112002726</v>
+        <v>0.07871770419569057</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3372,7 +3372,7 @@
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.02497174300496052</v>
+        <v>0.024971658454912</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063232421875</v>
+        <v>189.6063385009766</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088208357837</v>
+        <v>192.8088363522974</v>
       </c>
       <c r="D124" t="n">
-        <v>188.329312674443</v>
+        <v>188.3293278304631</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007142509167</v>
+        <v>192.0007297023972</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.008008964809924857</v>
+        <v>0.00800904593061702</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410312537218</v>
+        <v>-0.01636418228460701</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3453,22 +3453,22 @@
         <v>46066</v>
       </c>
       <c r="B126" t="n">
-        <v>182.3832244873047</v>
+        <v>182.3832092285156</v>
       </c>
       <c r="C126" t="n">
-        <v>187.0622780376601</v>
+        <v>187.0622623874058</v>
       </c>
       <c r="D126" t="n">
-        <v>181.1660713803529</v>
+        <v>181.1660562233949</v>
       </c>
       <c r="E126" t="n">
-        <v>187.042320465516</v>
+        <v>187.0423048169314</v>
       </c>
       <c r="F126" t="n">
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209266545793198</v>
+        <v>-0.02209274727292232</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3492,7 +3492,7 @@
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0118155220086027</v>
+        <v>0.01181560666047221</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3573,22 +3573,22 @@
         <v>46076</v>
       </c>
       <c r="B131" t="n">
-        <v>191.1028289794922</v>
+        <v>191.1028137207031</v>
       </c>
       <c r="C131" t="n">
-        <v>193.4972200828311</v>
+        <v>193.4972046328596</v>
       </c>
       <c r="D131" t="n">
-        <v>189.1374267327081</v>
+        <v>189.1374116308485</v>
       </c>
       <c r="E131" t="n">
-        <v>190.9531700210539</v>
+        <v>190.9531547742145</v>
       </c>
       <c r="F131" t="n">
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113848413379699</v>
+        <v>0.009113767839714404</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3612,7 +3612,7 @@
         <v>175123600</v>
       </c>
       <c r="G132" t="n">
-        <v>0.006786747007672789</v>
+        <v>0.006786827395534711</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3765,22 +3765,22 @@
         <v>46086</v>
       </c>
       <c r="B139" t="n">
-        <v>182.9119873046875</v>
+        <v>182.9119720458984</v>
       </c>
       <c r="C139" t="n">
-        <v>183.6303076754259</v>
+        <v>183.6302923567135</v>
       </c>
       <c r="D139" t="n">
-        <v>177.4647422536165</v>
+        <v>177.4647274492447</v>
       </c>
       <c r="E139" t="n">
-        <v>180.7470550179114</v>
+        <v>180.7470399397241</v>
       </c>
       <c r="F139" t="n">
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.00163899427668035</v>
+        <v>0.001638910718471109</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010798076634313</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716213186068583</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386535644531</v>
+        <v>184.3386383056641</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047530762794</v>
+        <v>186.0047376795775</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850871183009</v>
+        <v>181.5850720874406</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741760435397</v>
+        <v>181.9741609804723</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690174050782</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.006873706730786022</v>
+        <v>0.0068737900756215</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103424072266</v>
+        <v>175.2103271484375</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535618334976</v>
+        <v>182.0535459787435</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607154312909</v>
+        <v>175.0607001855326</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837257637527</v>
+        <v>181.9837099150805</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709014892578</v>
+        <v>174.9709320068359</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694397588381</v>
+        <v>175.5694703808103</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870566311777</v>
+        <v>168.3870860004334</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414684152183</v>
+        <v>174.7414988927798</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366591233594172</v>
+        <v>-0.001366330087374079</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519256591797</v>
+        <v>174.5519409179688</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672267555024</v>
+        <v>176.4672421817212</v>
       </c>
       <c r="D5" t="n">
-        <v>173.384789767114</v>
+        <v>173.3848049238756</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222540410346</v>
+        <v>174.4222692884882</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394545758820588</v>
+        <v>-0.002394632548741393</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545806884766</v>
+        <v>177.5545654296875</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531037491236</v>
+        <v>178.1530884388983</v>
       </c>
       <c r="D6" t="n">
-        <v>170.781182841084</v>
+        <v>170.7811681643912</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877371490149</v>
+        <v>172.1877223514448</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720207335414736</v>
+        <v>0.01720189701660124</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531635496304</v>
+        <v>0.0102254031723028</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253326416016</v>
+        <v>181.3253173828125</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9438110385745</v>
+        <v>181.9437957277396</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725671170498</v>
+        <v>178.3725521067403</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6195091893087</v>
+        <v>179.6194940740671</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0109003665696572</v>
+        <v>0.01090028150092892</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -660,7 +660,7 @@
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009351750270146786</v>
+        <v>-0.0009350909542572561</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7292327880859</v>
+        <v>179.729248046875</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187163721073</v>
+        <v>184.0187319950683</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784366795831</v>
+        <v>175.9784516199342</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776517699909</v>
+        <v>180.3776670838299</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874598727247717</v>
+        <v>-0.007874514497031027</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -708,7 +708,7 @@
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324635455335401</v>
+        <v>-0.03324643662953308</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982696533203</v>
+        <v>167.8982543945312</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417962304089</v>
+        <v>170.5417807313731</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406265749079</v>
+        <v>166.9406114031506</v>
       </c>
       <c r="E16" t="n">
-        <v>167.140134281122</v>
+        <v>167.1401190912332</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00772375239776002</v>
+        <v>0.007723660814659139</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455634409096618</v>
+        <v>0.01455643629502945</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -861,22 +861,22 @@
         <v>45910</v>
       </c>
       <c r="B18" t="n">
-        <v>176.8961944580078</v>
+        <v>176.8962097167969</v>
       </c>
       <c r="C18" t="n">
-        <v>178.8513911308407</v>
+        <v>178.851406558282</v>
       </c>
       <c r="D18" t="n">
-        <v>175.0407440194845</v>
+        <v>175.0407591182253</v>
       </c>
       <c r="E18" t="n">
-        <v>176.2078799889887</v>
+        <v>176.2078951884048</v>
       </c>
       <c r="F18" t="n">
         <v>226852000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03847512663982333</v>
+        <v>0.03847521621706362</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -900,7 +900,7 @@
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460227399664788</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -933,22 +933,22 @@
         <v>45915</v>
       </c>
       <c r="B21" t="n">
-        <v>177.3251495361328</v>
+        <v>177.3251647949219</v>
       </c>
       <c r="C21" t="n">
-        <v>178.4225264520066</v>
+        <v>178.4225418052247</v>
       </c>
       <c r="D21" t="n">
-        <v>174.0928881658194</v>
+        <v>174.0929031464731</v>
       </c>
       <c r="E21" t="n">
-        <v>175.250119236683</v>
+        <v>175.2501343169162</v>
       </c>
       <c r="F21" t="n">
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003937807415412831</v>
+        <v>-0.0003936947256518719</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -972,7 +972,7 @@
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614620751539797</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1029,22 +1029,22 @@
         <v>45919</v>
       </c>
       <c r="B25" t="n">
-        <v>176.2477264404297</v>
+        <v>176.2477416992188</v>
       </c>
       <c r="C25" t="n">
-        <v>177.6543599509016</v>
+        <v>177.6543753314711</v>
       </c>
       <c r="D25" t="n">
-        <v>174.7612823170602</v>
+        <v>174.7612974471592</v>
       </c>
       <c r="E25" t="n">
-        <v>175.3498836843894</v>
+        <v>175.349898865447</v>
       </c>
       <c r="F25" t="n">
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439670001024075</v>
+        <v>0.002439756788046976</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711730957031</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089289332547</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924501658818</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810364137678</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928247356775705</v>
+        <v>0.03928229701524732</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821204324514892</v>
+        <v>-0.02821196229186118</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1101,22 +1101,22 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>176.5470123291016</v>
+        <v>176.5470275878906</v>
       </c>
       <c r="C28" t="n">
-        <v>179.3502935078314</v>
+        <v>179.3503090089054</v>
       </c>
       <c r="D28" t="n">
-        <v>174.9807575937583</v>
+        <v>174.9807727171775</v>
       </c>
       <c r="E28" t="n">
-        <v>179.3403228895943</v>
+        <v>179.3403383898065</v>
       </c>
       <c r="F28" t="n">
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182577209651543</v>
+        <v>-0.008182491487822352</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2653045654297</v>
+        <v>177.2652893066406</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291540783439</v>
+        <v>179.8291385988617</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7162058826927</v>
+        <v>172.7161910154847</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629701066951</v>
+        <v>174.0629551235593</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068560701492752</v>
+        <v>0.004068387491782843</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1164,7 +1164,7 @@
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002813916776754244</v>
+        <v>0.002814003097804996</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1197,22 +1197,22 @@
         <v>45930</v>
       </c>
       <c r="B32" t="n">
-        <v>186.1340484619141</v>
+        <v>186.1340637207031</v>
       </c>
       <c r="C32" t="n">
-        <v>186.9022123120565</v>
+        <v>186.9022276338177</v>
       </c>
       <c r="D32" t="n">
-        <v>181.0462321155116</v>
+        <v>181.0462469572146</v>
       </c>
       <c r="E32" t="n">
-        <v>181.6448041170831</v>
+        <v>181.6448190078555</v>
       </c>
       <c r="F32" t="n">
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601041597539022</v>
+        <v>0.02601050008507699</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1236,7 +1236,7 @@
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003537489626782131</v>
+        <v>0.0035374073593748</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1269,22 +1269,22 @@
         <v>45933</v>
       </c>
       <c r="B35" t="n">
-        <v>187.1715545654297</v>
+        <v>187.1715698242188</v>
       </c>
       <c r="C35" t="n">
-        <v>189.9050110254035</v>
+        <v>189.9050265070322</v>
       </c>
       <c r="D35" t="n">
-        <v>184.9369182511207</v>
+        <v>184.9369333277354</v>
       </c>
       <c r="E35" t="n">
-        <v>188.7378093314507</v>
+        <v>188.7378247179256</v>
       </c>
       <c r="F35" t="n">
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587692724298</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965576171875</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825209975275</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918479831437</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566599139491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108606995897354</v>
+        <v>-0.0110862321012164</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1317,22 +1317,22 @@
         <v>45937</v>
       </c>
       <c r="B37" t="n">
-        <v>184.5977325439453</v>
+        <v>184.5977172851562</v>
       </c>
       <c r="C37" t="n">
-        <v>188.6081286768816</v>
+        <v>188.6081130865945</v>
       </c>
       <c r="D37" t="n">
-        <v>183.5602249269612</v>
+        <v>183.5602097539322</v>
       </c>
       <c r="E37" t="n">
-        <v>185.7848907820332</v>
+        <v>185.784875425114</v>
       </c>
       <c r="F37" t="n">
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694945166262119</v>
+        <v>-0.002694945388425074</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199541139559646</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829626288358566</v>
+        <v>0.01829618052309101</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001922607422</v>
+        <v>179.4001770019531</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281395182556</v>
+        <v>184.4281238318171</v>
       </c>
       <c r="D43" t="n">
-        <v>176.866254560341</v>
+        <v>176.8662395170747</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3583147400375</v>
+        <v>184.3582990595379</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001110936754343372</v>
+        <v>-0.001111021714327642</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1500,7 +1500,7 @@
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101030171288664</v>
+        <v>0.01101038770384366</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.7246398925781</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925557149365</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602938591047</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988793025541</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829092822517</v>
+        <v>0.01042837577039868</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1629,22 +1629,22 @@
         <v>45954</v>
       </c>
       <c r="B50" t="n">
-        <v>185.8148193359375</v>
+        <v>185.8148040771484</v>
       </c>
       <c r="C50" t="n">
-        <v>187.0219340442129</v>
+        <v>187.0219186862977</v>
       </c>
       <c r="D50" t="n">
-        <v>183.0614214202242</v>
+        <v>183.0614063875393</v>
       </c>
       <c r="E50" t="n">
-        <v>183.4006051417061</v>
+        <v>183.400590081168</v>
       </c>
       <c r="F50" t="n">
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250765250109055</v>
+        <v>0.02250748267812286</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1668,7 +1668,7 @@
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807910615919784</v>
+        <v>0.02807919058326869</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1677,22 +1677,22 @@
         <v>45958</v>
       </c>
       <c r="B52" t="n">
-        <v>200.5495147705078</v>
+        <v>200.5495300292969</v>
       </c>
       <c r="C52" t="n">
-        <v>202.6644428640734</v>
+        <v>202.6644582837766</v>
       </c>
       <c r="D52" t="n">
-        <v>191.4513174538508</v>
+        <v>191.4513320204045</v>
       </c>
       <c r="E52" t="n">
-        <v>192.588592118433</v>
+        <v>192.5886067715161</v>
       </c>
       <c r="F52" t="n">
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981974113173093</v>
+        <v>0.04981982100715721</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.545166015625</v>
+        <v>206.5451354980469</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828666070652</v>
+        <v>211.6828353303786</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905729140704</v>
+        <v>204.2905427296142</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482921843539</v>
+        <v>207.482891187405</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02989611444324924</v>
+        <v>0.0298958839139345</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050750732422</v>
+        <v>202.4050598144531</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672637579894</v>
+        <v>205.6672482532724</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286166610889</v>
+        <v>200.9286015136062</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596680014167</v>
+        <v>204.6596525726598</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004448238730316</v>
+        <v>-0.02004441147263381</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060424804688</v>
+        <v>202.0060577392578</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729406961805</v>
+        <v>207.4729563679188</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870481318289</v>
+        <v>201.5870633589687</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565693232556</v>
+        <v>205.9565848804529</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971455471800998</v>
+        <v>-0.001971304845645117</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1788,7 +1788,7 @@
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02168005119548289</v>
+        <v>0.02167997402155764</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1797,22 +1797,22 @@
         <v>45965</v>
       </c>
       <c r="B57" t="n">
-        <v>198.2151031494141</v>
+        <v>198.2151184082031</v>
       </c>
       <c r="C57" t="n">
-        <v>203.4824819294599</v>
+        <v>203.4824975937368</v>
       </c>
       <c r="D57" t="n">
-        <v>197.4569099225941</v>
+        <v>197.4569251230167</v>
       </c>
       <c r="E57" t="n">
-        <v>202.5147991590425</v>
+        <v>202.5148147488263</v>
       </c>
       <c r="F57" t="n">
         <v>188919300</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.03958824112615977</v>
+        <v>-0.03958816719273994</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434387207031</v>
+        <v>194.7434234619141</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4350026612236</v>
+        <v>202.4349867997753</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847643800754</v>
+        <v>194.1847491650603</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949275919373</v>
+        <v>198.2949120548774</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751463119384</v>
+        <v>-0.01751478380745641</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1845,22 +1845,22 @@
         <v>45967</v>
       </c>
       <c r="B59" t="n">
-        <v>187.6304931640625</v>
+        <v>187.6304779052734</v>
       </c>
       <c r="C59" t="n">
-        <v>197.1476859949454</v>
+        <v>197.1476699621838</v>
       </c>
       <c r="D59" t="n">
-        <v>185.934559185592</v>
+        <v>185.9345440647224</v>
       </c>
       <c r="E59" t="n">
-        <v>195.9505570232203</v>
+        <v>195.9505410878136</v>
       </c>
       <c r="F59" t="n">
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652469938585123</v>
+        <v>-0.03652470224768178</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1884,7 +1884,7 @@
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003719741924403941</v>
+        <v>0.0003720555463071484</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983337402344</v>
+        <v>192.6983489990234</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529266552934</v>
+        <v>194.9529420926121</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427786999811</v>
+        <v>190.8427938118383</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935535589016</v>
+        <v>194.6935689756818</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959059574083223</v>
+        <v>-0.02959051889910702</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1941,22 +1941,22 @@
         <v>45973</v>
       </c>
       <c r="B63" t="n">
-        <v>193.3367919921875</v>
+        <v>193.3368072509766</v>
       </c>
       <c r="C63" t="n">
-        <v>195.4217929255223</v>
+        <v>195.4218083488666</v>
       </c>
       <c r="D63" t="n">
-        <v>190.6731755191215</v>
+        <v>190.673190567689</v>
       </c>
       <c r="E63" t="n">
-        <v>195.2522010776849</v>
+        <v>195.2522164876445</v>
       </c>
       <c r="F63" t="n">
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313252582732629</v>
+        <v>0.003313252320373383</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4133911132812</v>
+        <v>186.4134063720703</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824463944715</v>
+        <v>190.9824620272586</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4105907203728</v>
+        <v>183.4106057333689</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933791327836</v>
+        <v>190.5933947337238</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005357317613</v>
+        <v>-0.03581005074692667</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2004,7 +2004,7 @@
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0177137394870075</v>
+        <v>0.01771365618248799</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2181,22 +2181,22 @@
         <v>45987</v>
       </c>
       <c r="B73" t="n">
-        <v>179.8291473388672</v>
+        <v>179.8291625976562</v>
       </c>
       <c r="C73" t="n">
-        <v>182.4728225932506</v>
+        <v>182.4728380763597</v>
       </c>
       <c r="D73" t="n">
-        <v>177.8139863878403</v>
+        <v>177.8140014756398</v>
       </c>
       <c r="E73" t="n">
-        <v>181.1958831941039</v>
+        <v>181.1958985688627</v>
       </c>
       <c r="F73" t="n">
         <v>183852000</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01372159873604817</v>
+        <v>0.01372168475193747</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769500732422</v>
+        <v>176.5769653320312</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614700176124</v>
+        <v>178.8614854738169</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781451295325</v>
+        <v>176.0781603452176</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821404669205</v>
+        <v>178.5821558989869</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492846544285</v>
+        <v>-0.01808492693090802</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649719797026439</v>
+        <v>0.01649711013028865</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607818603516</v>
+        <v>179.1607666015625</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139471586436</v>
+        <v>182.0139316568558</v>
       </c>
       <c r="D77" t="n">
-        <v>178.6819333075974</v>
+        <v>178.681918089591</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472262869623</v>
+        <v>180.6472109015755</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030526629882311</v>
+        <v>-0.01030535058927451</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116036298998392</v>
+        <v>0.02116044996031174</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2349,22 +2349,22 @@
         <v>45999</v>
       </c>
       <c r="B80" t="n">
-        <v>185.1168365478516</v>
+        <v>185.1168212890625</v>
       </c>
       <c r="C80" t="n">
-        <v>187.5611139779305</v>
+        <v>187.5610985176648</v>
       </c>
       <c r="D80" t="n">
-        <v>181.9741810893209</v>
+        <v>181.9741660895743</v>
       </c>
       <c r="E80" t="n">
-        <v>182.213626289633</v>
+        <v>182.2136112701494</v>
       </c>
       <c r="F80" t="n">
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721399899417375</v>
+        <v>0.01721391514737669</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864265695677</v>
+        <v>185.2864418902268</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920356049676</v>
+        <v>182.8920507276432</v>
       </c>
       <c r="E81" t="n">
-        <v>185.12679644575</v>
+        <v>185.1268117532098</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125912631224192</v>
+        <v>-0.003125748033105724</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509674072266</v>
+        <v>183.3509521484375</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469957406681</v>
+        <v>185.0469803407326</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150239281505</v>
+        <v>181.6150088138297</v>
       </c>
       <c r="E82" t="n">
-        <v>184.5381918075859</v>
+        <v>184.538176449994</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433411769608655</v>
+        <v>-0.006433576610347602</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2436,7 +2436,7 @@
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550779126219859</v>
+        <v>-0.01550770933102352</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2445,22 +2445,22 @@
         <v>46003</v>
       </c>
       <c r="B84" t="n">
-        <v>174.6114044189453</v>
+        <v>174.6114196777344</v>
       </c>
       <c r="C84" t="n">
-        <v>182.3931976659576</v>
+        <v>182.3932136047752</v>
       </c>
       <c r="D84" t="n">
-        <v>174.2123291208211</v>
+        <v>174.2123443447362</v>
       </c>
       <c r="E84" t="n">
-        <v>180.6871831157045</v>
+        <v>180.6871989054384</v>
       </c>
       <c r="F84" t="n">
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266452212921567</v>
+        <v>-0.03266443759654691</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2469,22 +2469,22 @@
         <v>46006</v>
       </c>
       <c r="B85" t="n">
-        <v>175.87841796875</v>
+        <v>175.8784332275391</v>
       </c>
       <c r="C85" t="n">
-        <v>178.0034500370577</v>
+        <v>178.0034654802094</v>
       </c>
       <c r="D85" t="n">
-        <v>174.6213651072644</v>
+        <v>174.6213802569945</v>
       </c>
       <c r="E85" t="n">
-        <v>177.5245749312296</v>
+        <v>177.5245903328353</v>
       </c>
       <c r="F85" t="n">
         <v>164775600</v>
       </c>
       <c r="G85" t="n">
-        <v>0.007256190132717499</v>
+        <v>0.007256189498619836</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2508,7 +2508,7 @@
         <v>148588100</v>
       </c>
       <c r="G86" t="n">
-        <v>0.008111748644499261</v>
+        <v>0.008111661183153096</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -2517,22 +2517,22 @@
         <v>46008</v>
       </c>
       <c r="B87" t="n">
-        <v>170.5409240722656</v>
+        <v>170.5409393310547</v>
       </c>
       <c r="C87" t="n">
-        <v>175.7188098781239</v>
+        <v>175.7188256001934</v>
       </c>
       <c r="D87" t="n">
-        <v>169.9123900056319</v>
+        <v>169.9124052081842</v>
       </c>
       <c r="E87" t="n">
-        <v>175.6888811343</v>
+        <v>175.6888968536916</v>
       </c>
       <c r="F87" t="n">
         <v>222775500</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.03814992030459552</v>
+        <v>-0.03814983424509077</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -2556,7 +2556,7 @@
         <v>176096000</v>
       </c>
       <c r="G88" t="n">
-        <v>0.01872005454267267</v>
+        <v>0.01871996339485515</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -2565,22 +2565,22 @@
         <v>46010</v>
       </c>
       <c r="B89" t="n">
-        <v>180.5674896240234</v>
+        <v>180.5674743652344</v>
       </c>
       <c r="C89" t="n">
-        <v>181.0264072425164</v>
+        <v>181.0263919449467</v>
       </c>
       <c r="D89" t="n">
-        <v>175.9283357789888</v>
+        <v>175.9283209122297</v>
       </c>
       <c r="E89" t="n">
-        <v>176.2575672304301</v>
+        <v>176.2575523358494</v>
       </c>
       <c r="F89" t="n">
         <v>324925900</v>
       </c>
       <c r="G89" t="n">
-        <v>0.03933629234179148</v>
+        <v>0.03933620451306163</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2604,7 +2604,7 @@
         <v>129064400</v>
       </c>
       <c r="G90" t="n">
-        <v>0.01491785600596796</v>
+        <v>0.01491794177123418</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021728515625</v>
+        <v>187.1021881103516</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5487999407664</v>
+        <v>188.5488153175326</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4935963146986</v>
+        <v>186.4936115238563</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005508490403</v>
+        <v>187.8005661647843</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612838827051545</v>
+        <v>-0.003612757568446812</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545457451715641</v>
+        <v>-0.005545538552702456</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8028869628906</v>
+        <v>186.8029022216797</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213703933745</v>
+        <v>191.7213860539245</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838692947835</v>
+        <v>186.3838845193456</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752284670132</v>
+        <v>190.0752439930999</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677861544826856</v>
+        <v>-0.004677780243029006</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987164191344933</v>
+        <v>0.009987081691657185</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2973,22 +2973,22 @@
         <v>46037</v>
       </c>
       <c r="B106" t="n">
-        <v>186.6133117675781</v>
+        <v>186.6133270263672</v>
       </c>
       <c r="C106" t="n">
-        <v>189.2571189267257</v>
+        <v>189.2571344016907</v>
       </c>
       <c r="D106" t="n">
-        <v>185.8949914784577</v>
+        <v>185.895006678512</v>
       </c>
       <c r="E106" t="n">
-        <v>186.0645927657271</v>
+        <v>186.0646079796491</v>
       </c>
       <c r="F106" t="n">
         <v>206188600</v>
       </c>
       <c r="G106" t="n">
-        <v>0.02134974210895835</v>
+        <v>0.02134982562154453</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -2997,22 +2997,22 @@
         <v>46038</v>
       </c>
       <c r="B107" t="n">
-        <v>185.7952270507812</v>
+        <v>185.7952423095703</v>
       </c>
       <c r="C107" t="n">
-        <v>189.99540517049</v>
+        <v>189.9954207742267</v>
       </c>
       <c r="D107" t="n">
-        <v>185.6455833269296</v>
+        <v>185.6455985734289</v>
       </c>
       <c r="E107" t="n">
-        <v>188.6385795892923</v>
+        <v>188.6385950815971</v>
       </c>
       <c r="F107" t="n">
         <v>187967200</v>
       </c>
       <c r="G107" t="n">
-        <v>-0.004383849732090828</v>
+        <v>-0.004383849373637116</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.654296875</v>
+        <v>177.6542816162109</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542325986551</v>
+        <v>181.9542169705431</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953640623503</v>
+        <v>177.1953488429791</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753422141945</v>
+        <v>181.4753266272146</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.04381668089652369</v>
+        <v>-0.0438168415518142</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948280612693632</v>
+        <v>0.02948289454957864</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.0346832275391</v>
+        <v>186.03466796875</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784906596197</v>
+        <v>188.6784751839824</v>
       </c>
       <c r="D112" t="n">
-        <v>185.555808059744</v>
+        <v>185.5557928402329</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230748442759</v>
+        <v>186.7230595290241</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.00639415348837058</v>
+        <v>-0.006394234985120373</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099371233637481</v>
+        <v>0.01099379525930511</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5035858154297</v>
+        <v>186.5036010742188</v>
       </c>
       <c r="C125" t="n">
-        <v>193.1580126884611</v>
+        <v>193.158028491682</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745817463215</v>
+        <v>186.0745969700116</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793648877844</v>
+        <v>192.5793806436633</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636418228460701</v>
+        <v>-0.01636410180845216</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209274727292232</v>
+        <v>-0.02209282728038808</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381774902344</v>
+        <v>184.5381927490234</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130808403767</v>
+        <v>186.7130962790006</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7616860728079</v>
+        <v>178.7617008539599</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3256935584433</v>
+        <v>181.3257085516038</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181560666047221</v>
+        <v>0.01181569032381558</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627283983140582</v>
+        <v>0.01627275579951704</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613342285156</v>
+        <v>187.4613189697266</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900957055448</v>
+        <v>187.9900804037161</v>
       </c>
       <c r="D129" t="n">
-        <v>185.2265733363672</v>
+        <v>185.226558259481</v>
       </c>
       <c r="E129" t="n">
-        <v>186.62329889396</v>
+        <v>186.6232837033845</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004255251289267958</v>
+        <v>-0.0004256064912840918</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3549,22 +3549,22 @@
         <v>46073</v>
       </c>
       <c r="B130" t="n">
-        <v>189.3768768310547</v>
+        <v>189.3768615722656</v>
       </c>
       <c r="C130" t="n">
-        <v>189.8856807673048</v>
+        <v>189.8856654675195</v>
       </c>
       <c r="D130" t="n">
-        <v>185.5059297314624</v>
+        <v>185.5059147845697</v>
       </c>
       <c r="E130" t="n">
-        <v>186.1344638821937</v>
+        <v>186.1344488846578</v>
       </c>
       <c r="F130" t="n">
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833441238607</v>
+        <v>0.01021833524412785</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3588,7 +3588,7 @@
         <v>171584800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.009113767839714404</v>
+        <v>0.009113849147715847</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -3645,22 +3645,22 @@
         <v>46079</v>
       </c>
       <c r="B134" t="n">
-        <v>184.4583587646484</v>
+        <v>184.4583740234375</v>
       </c>
       <c r="C134" t="n">
-        <v>193.8364076167612</v>
+        <v>193.8364236513225</v>
       </c>
       <c r="D134" t="n">
-        <v>183.8896973916963</v>
+        <v>183.8897126034445</v>
       </c>
       <c r="E134" t="n">
-        <v>193.8164652690549</v>
+        <v>193.8164813019665</v>
       </c>
       <c r="F134" t="n">
         <v>360807900</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.05456128825383422</v>
+        <v>-0.05456121004512637</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763519287109</v>
+        <v>176.7763366699219</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637395256691</v>
+        <v>182.1637238018573</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682453114839</v>
+        <v>175.9682301224481</v>
       </c>
       <c r="E135" t="n">
-        <v>180.8268714126474</v>
+        <v>180.82685580423</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164629289442512</v>
+        <v>-0.04164645489360941</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0540008544922</v>
+        <v>182.0539703369141</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0317240302905</v>
+        <v>183.0316933488174</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2323067871125</v>
+        <v>174.2322775806792</v>
       </c>
       <c r="E136" t="n">
-        <v>174.601438160182</v>
+        <v>174.6014088918714</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985494874285899</v>
+        <v>0.02985486500292533</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3717,22 +3717,22 @@
         <v>46084</v>
       </c>
       <c r="B137" t="n">
-        <v>179.6296539306641</v>
+        <v>179.6296691894531</v>
       </c>
       <c r="C137" t="n">
-        <v>180.4776603660684</v>
+        <v>180.4776756968921</v>
       </c>
       <c r="D137" t="n">
-        <v>176.5069564334623</v>
+        <v>176.5069714269912</v>
       </c>
       <c r="E137" t="n">
-        <v>178.0732983803544</v>
+        <v>178.0733135069376</v>
       </c>
       <c r="F137" t="n">
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331663634113589</v>
+        <v>-0.01331638712945649</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3756,7 +3756,7 @@
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660656891157819</v>
+        <v>0.01660648255510222</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048919677734</v>
+        <v>177.4048767089844</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333469017365</v>
+        <v>182.3333312190456</v>
       </c>
       <c r="D140" t="n">
-        <v>176.4072264371208</v>
+        <v>176.407211264142</v>
       </c>
       <c r="E140" t="n">
-        <v>179.4201653790109</v>
+        <v>179.420149946886</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0301078164350177</v>
+        <v>-0.03010789985650675</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3828,7 +3828,7 @@
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716213186068583</v>
+        <v>0.02716222020803327</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3837,22 +3837,22 @@
         <v>46091</v>
       </c>
       <c r="B142" t="n">
-        <v>184.3386383056641</v>
+        <v>184.3386535644531</v>
       </c>
       <c r="C142" t="n">
-        <v>186.0047376795775</v>
+        <v>186.0047530762794</v>
       </c>
       <c r="D142" t="n">
-        <v>181.5850720874406</v>
+        <v>181.5850871183009</v>
       </c>
       <c r="E142" t="n">
-        <v>181.9741609804723</v>
+        <v>181.9741760435397</v>
       </c>
       <c r="F142" t="n">
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160690174050782</v>
+        <v>0.01160698547713768</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>145280400</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0068737900756215</v>
+        <v>0.006873706730786022</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -3885,22 +3885,22 @@
         <v>46093</v>
       </c>
       <c r="B144" t="n">
-        <v>182.7223510742188</v>
+        <v>182.7223358154297</v>
       </c>
       <c r="C144" t="n">
-        <v>184.5182492431283</v>
+        <v>184.5182338343672</v>
       </c>
       <c r="D144" t="n">
-        <v>181.3355215595592</v>
+        <v>181.3355064165816</v>
       </c>
       <c r="E144" t="n">
-        <v>183.6302794851663</v>
+        <v>183.6302641505579</v>
       </c>
       <c r="F144" t="n">
         <v>155762700</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.01553503830774738</v>
+        <v>-0.01553512051850658</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -3909,22 +3909,22 @@
         <v>46094</v>
       </c>
       <c r="B145" t="n">
-        <v>179.8389282226562</v>
+        <v>179.8389434814453</v>
       </c>
       <c r="C145" t="n">
-        <v>185.6656060713691</v>
+        <v>185.6656218245341</v>
       </c>
       <c r="D145" t="n">
-        <v>179.5296376335348</v>
+        <v>179.5296528660815</v>
       </c>
       <c r="E145" t="n">
-        <v>184.4982761588831</v>
+        <v>184.4982918130038</v>
       </c>
       <c r="F145" t="n">
         <v>160988400</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0157803510879263</v>
+        <v>-0.01578018538957893</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3933,22 +3933,22 @@
         <v>46097</v>
       </c>
       <c r="B146" t="n">
-        <v>182.8021697998047</v>
+        <v>182.8021545410156</v>
       </c>
       <c r="C146" t="n">
-        <v>188.4492658789173</v>
+        <v>188.4492501487561</v>
       </c>
       <c r="D146" t="n">
-        <v>180.9962999229416</v>
+        <v>180.9962848148914</v>
       </c>
       <c r="E146" t="n">
-        <v>182.5527399223597</v>
+        <v>182.5527246843909</v>
       </c>
       <c r="F146" t="n">
         <v>217307400</v>
       </c>
       <c r="G146" t="n">
-        <v>0.01647719771483347</v>
+        <v>0.01647702662285733</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3957,22 +3957,22 @@
         <v>46098</v>
       </c>
       <c r="B147" t="n">
-        <v>181.5150909423828</v>
+        <v>181.5151062011719</v>
       </c>
       <c r="C147" t="n">
-        <v>184.9771786272242</v>
+        <v>184.9771941770484</v>
       </c>
       <c r="D147" t="n">
-        <v>181.2656610816535</v>
+        <v>181.2656763194747</v>
       </c>
       <c r="E147" t="n">
-        <v>184.6379576703901</v>
+        <v>184.6379731916982</v>
       </c>
       <c r="F147" t="n">
         <v>182497800</v>
       </c>
       <c r="G147" t="n">
-        <v>-0.007040829213523114</v>
+        <v>-0.007040662858024294</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -3996,7 +3996,7 @@
         <v>156683100</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.008409793966310586</v>
+        <v>-0.008409877322820725</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -4005,22 +4005,22 @@
         <v>46100</v>
       </c>
       <c r="B149" t="n">
-        <v>178.1527862548828</v>
+        <v>178.1527709960938</v>
       </c>
       <c r="C149" t="n">
-        <v>179.569546076418</v>
+        <v>179.5695306962835</v>
       </c>
       <c r="D149" t="n">
-        <v>175.3890990582871</v>
+        <v>175.3890840362079</v>
       </c>
       <c r="E149" t="n">
-        <v>177.6040375011918</v>
+        <v>177.6040222894031</v>
       </c>
       <c r="F149" t="n">
         <v>170968500</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.01019953657814543</v>
+        <v>-0.01019962135457131</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -4029,22 +4029,22 @@
         <v>46101</v>
       </c>
       <c r="B150" t="n">
-        <v>172.3061370849609</v>
+        <v>172.30615234375</v>
       </c>
       <c r="C150" t="n">
-        <v>177.8534545050662</v>
+        <v>177.853470255105</v>
       </c>
       <c r="D150" t="n">
-        <v>171.3283763370981</v>
+        <v>171.3283915093003</v>
       </c>
       <c r="E150" t="n">
-        <v>177.5940529420793</v>
+        <v>177.5940686691464</v>
       </c>
       <c r="F150" t="n">
         <v>241323500</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.03281817417975763</v>
+        <v>-0.03281800569058757</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>182836300</v>
       </c>
       <c r="G151" t="n">
-        <v>0.01702379197069148</v>
+        <v>0.01702370190686442</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -4149,22 +4149,22 @@
         <v>46108</v>
       </c>
       <c r="B155" t="n">
-        <v>167.1379547119141</v>
+        <v>167.1379699707031</v>
       </c>
       <c r="C155" t="n">
-        <v>170.5800835262955</v>
+        <v>170.5800990993323</v>
       </c>
       <c r="D155" t="n">
-        <v>166.6291080850299</v>
+        <v>166.629123297364</v>
       </c>
       <c r="E155" t="n">
-        <v>169.6122945102883</v>
+        <v>169.6123099949711</v>
       </c>
       <c r="F155" t="n">
         <v>196212700</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.02172399022862981</v>
+        <v>-0.02172390091733423</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4188,7 +4188,7 @@
         <v>185627000</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.01402814228406069</v>
+        <v>-0.01402823229793726</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -4197,22 +4197,22 @@
         <v>46112</v>
       </c>
       <c r="B157" t="n">
-        <v>174.0022735595703</v>
+        <v>174.0022583007812</v>
       </c>
       <c r="C157" t="n">
-        <v>174.2217730660379</v>
+        <v>174.2217577880002</v>
       </c>
       <c r="D157" t="n">
-        <v>166.5792533168182</v>
+        <v>166.5792387089764</v>
       </c>
       <c r="E157" t="n">
-        <v>166.5892250311153</v>
+        <v>166.589210422399</v>
       </c>
       <c r="F157" t="n">
         <v>226181300</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05588183959195892</v>
+        <v>0.05588174699846626</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -4221,22 +4221,22 @@
         <v>46113</v>
       </c>
       <c r="B158" t="n">
-        <v>175.3491973876953</v>
+        <v>175.3491821289062</v>
       </c>
       <c r="C158" t="n">
-        <v>176.9654980623514</v>
+        <v>176.9654826629128</v>
       </c>
       <c r="D158" t="n">
-        <v>174.3514779146501</v>
+        <v>174.351462742682</v>
       </c>
       <c r="E158" t="n">
-        <v>175.5986272559566</v>
+        <v>175.5986119754623</v>
       </c>
       <c r="F158" t="n">
         <v>168132000</v>
       </c>
       <c r="G158" t="n">
-        <v>0.007740840395765725</v>
+        <v>0.007740841074583615</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -4245,22 +4245,22 @@
         <v>46114</v>
       </c>
       <c r="B159" t="n">
-        <v>176.9854431152344</v>
+        <v>176.9854583740234</v>
       </c>
       <c r="C159" t="n">
-        <v>177.0852211444685</v>
+        <v>177.0852364118599</v>
       </c>
       <c r="D159" t="n">
-        <v>170.9791680862979</v>
+        <v>170.9791828272563</v>
       </c>
       <c r="E159" t="n">
-        <v>171.7873183615289</v>
+        <v>171.787333172162</v>
       </c>
       <c r="F159" t="n">
         <v>143143200</v>
       </c>
       <c r="G159" t="n">
-        <v>0.009331355671513775</v>
+        <v>0.009331530522419529</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -4284,7 +4284,7 @@
         <v>107564300</v>
       </c>
       <c r="G160" t="n">
-        <v>0.001409355596789341</v>
+        <v>0.001409269260350898</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4341,22 +4341,22 @@
         <v>46121</v>
       </c>
       <c r="B163" t="n">
-        <v>183.4905853271484</v>
+        <v>183.4906005859375</v>
       </c>
       <c r="C163" t="n">
-        <v>183.6601958045732</v>
+        <v>183.6602110774668</v>
       </c>
       <c r="D163" t="n">
-        <v>180.2080798537204</v>
+        <v>180.2080948395415</v>
       </c>
       <c r="E163" t="n">
-        <v>181.4252987848774</v>
+        <v>181.4253138719204</v>
       </c>
       <c r="F163" t="n">
         <v>116428500</v>
       </c>
       <c r="G163" t="n">
-        <v>0.01005049564145621</v>
+        <v>0.01005057963567002</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4380,7 +4380,7 @@
         <v>160459500</v>
       </c>
       <c r="G164" t="n">
-        <v>0.02566477057129601</v>
+        <v>0.02566468527863064</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -4701,22 +4701,22 @@
         <v>46142</v>
       </c>
       <c r="B178" t="n">
-        <v>199.1148834228516</v>
+        <v>199.1148681640625</v>
       </c>
       <c r="C178" t="n">
-        <v>209.820409153207</v>
+        <v>209.8203930740204</v>
       </c>
       <c r="D178" t="n">
-        <v>198.2468571251534</v>
+        <v>198.2468419328838</v>
       </c>
       <c r="E178" t="n">
-        <v>209.4512425942353</v>
+        <v>209.4512265433391</v>
       </c>
       <c r="F178" t="n">
         <v>225239200</v>
       </c>
       <c r="G178" t="n">
-        <v>-0.04626040060709824</v>
+        <v>-0.04626047369511221</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
@@ -4725,22 +4725,22 @@
         <v>46143</v>
       </c>
       <c r="B179" t="n">
-        <v>197.9974212646484</v>
+        <v>197.9974365234375</v>
       </c>
       <c r="C179" t="n">
-        <v>202.5370477944956</v>
+        <v>202.5370634031337</v>
       </c>
       <c r="D179" t="n">
-        <v>196.6704525729091</v>
+        <v>196.6704677294345</v>
       </c>
       <c r="E179" t="n">
-        <v>200.8209691272831</v>
+        <v>200.8209846036705</v>
       </c>
       <c r="F179" t="n">
         <v>128647000</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.005612147816343893</v>
+        <v>-0.005611994980225576</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -4764,7 +4764,7 @@
         <v>125368100</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001511256316393261</v>
+        <v>0.0001510485544036211</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -4965,22 +4965,22 @@
         <v>46157</v>
       </c>
       <c r="B189" t="n">
-        <v>224.8061676025391</v>
+        <v>224.80615234375</v>
       </c>
       <c r="C189" t="n">
-        <v>230.9720668751014</v>
+        <v>230.9720511978</v>
       </c>
       <c r="D189" t="n">
-        <v>223.7286287034134</v>
+        <v>223.7286135177626</v>
       </c>
       <c r="E189" t="n">
-        <v>229.2360294447337</v>
+        <v>229.2360138852663</v>
       </c>
       <c r="F189" t="n">
         <v>180977600</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.04420118716323318</v>
+        <v>-0.04420125203837699</v>
       </c>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5004,7 +5004,7 @@
         <v>146280900</v>
       </c>
       <c r="G190" t="n">
-        <v>-0.01331442146103379</v>
+        <v>-0.01331435448943641</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5157,22 +5157,22 @@
         <v>46170</v>
       </c>
       <c r="B197" t="n">
-        <v>213.7613830566406</v>
+        <v>213.7613983154297</v>
       </c>
       <c r="C197" t="n">
-        <v>215.0284909668814</v>
+        <v>215.0285063161196</v>
       </c>
       <c r="D197" t="n">
-        <v>210.7382944698381</v>
+        <v>210.738309512832</v>
       </c>
       <c r="E197" t="n">
-        <v>210.7981551984497</v>
+        <v>210.7981702457166</v>
       </c>
       <c r="F197" t="n">
         <v>143996000</v>
       </c>
       <c r="G197" t="n">
-        <v>0.007760996387428776</v>
+        <v>0.007761068323773213</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5196,7 +5196,7 @@
         <v>289410600</v>
       </c>
       <c r="G198" t="n">
-        <v>-0.0145156714944451</v>
+        <v>-0.01451574184062365</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -7521,12 +7521,36 @@
         <v>216.5599975585938</v>
       </c>
       <c r="F295" t="n">
-        <v>120855100</v>
+        <v>121252500</v>
       </c>
       <c r="G295" t="n">
         <v>-0.01427054691201457</v>
       </c>
       <c r="H295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B296" t="n">
+        <v>217.0899963378906</v>
+      </c>
+      <c r="C296" t="n">
+        <v>219.6199951171875</v>
+      </c>
+      <c r="D296" t="n">
+        <v>214.6999969482422</v>
+      </c>
+      <c r="E296" t="n">
+        <v>218.1000061035156</v>
+      </c>
+      <c r="F296" t="n">
+        <v>98403300</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0.0138233381010664</v>
+      </c>
+      <c r="H296" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H296"/>
+  <dimension ref="A1:H297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709320068359</v>
+        <v>174.9709014892578</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694703808103</v>
+        <v>175.5694397588381</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870860004334</v>
+        <v>168.3870566311777</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414988927798</v>
+        <v>174.7414684152183</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366330087374079</v>
+        <v>-0.001366504264196933</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -564,7 +564,7 @@
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394632548741393</v>
+        <v>-0.002394458551239653</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545654296875</v>
+        <v>177.5545806884766</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1530884388983</v>
+        <v>178.1531037491236</v>
       </c>
       <c r="D6" t="n">
-        <v>170.7811681643912</v>
+        <v>170.781182841084</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877223514448</v>
+        <v>172.1877371490149</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01720189701660124</v>
+        <v>0.0172019844334983</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -612,7 +612,7 @@
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0102254031723028</v>
+        <v>0.01022531635496304</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -621,22 +621,22 @@
         <v>45895</v>
       </c>
       <c r="B8" t="n">
-        <v>181.3253173828125</v>
+        <v>181.3253326416016</v>
       </c>
       <c r="C8" t="n">
-        <v>181.9437957277396</v>
+        <v>181.9438110385745</v>
       </c>
       <c r="D8" t="n">
-        <v>178.3725521067403</v>
+        <v>178.3725671170498</v>
       </c>
       <c r="E8" t="n">
-        <v>179.6194940740671</v>
+        <v>179.6195091893087</v>
       </c>
       <c r="F8" t="n">
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01090028150092892</v>
+        <v>0.0109003665696572</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.15576171875</v>
+        <v>181.1557312011719</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435839210746</v>
+        <v>182.0435532539336</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618774176739</v>
+        <v>178.6618473202167</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5348217819195</v>
+        <v>181.5347912004848</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009350909542572561</v>
+        <v>-0.0009353433299080782</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>45897</v>
       </c>
       <c r="B10" t="n">
-        <v>179.729248046875</v>
+        <v>179.7292327880859</v>
       </c>
       <c r="C10" t="n">
-        <v>184.0187319950683</v>
+        <v>184.0187163721073</v>
       </c>
       <c r="D10" t="n">
-        <v>175.9784516199342</v>
+        <v>175.9784366795831</v>
       </c>
       <c r="E10" t="n">
-        <v>180.3776670838299</v>
+        <v>180.3776517699909</v>
       </c>
       <c r="F10" t="n">
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874514497031027</v>
+        <v>-0.007874431593344555</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.7538909912109</v>
+        <v>173.75390625</v>
       </c>
       <c r="C11" t="n">
-        <v>177.714180280125</v>
+        <v>177.7141958867003</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264119284913</v>
+        <v>172.7264270970488</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6742848307548</v>
+        <v>177.6743004338266</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324643662953308</v>
+        <v>-0.03324626965459365</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622131347656</v>
+        <v>170.3622283935547</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583050821389</v>
+        <v>171.9583204838847</v>
       </c>
       <c r="D12" t="n">
-        <v>166.810924534394</v>
+        <v>166.8109394751057</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841224963229</v>
+        <v>169.5841376854209</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952001095973654</v>
+        <v>-0.01952000924552055</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009368681625865349</v>
+        <v>-0.0009369576454122397</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400665283203</v>
+        <v>171.2400817871094</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395742178918</v>
+        <v>171.4395894944585</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955707723543</v>
+        <v>168.9955858311417</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527366819141</v>
+        <v>170.1527518438138</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095443250276666</v>
+        <v>0.006095532901013501</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -789,22 +789,22 @@
         <v>45905</v>
       </c>
       <c r="B15" t="n">
-        <v>166.6114044189453</v>
+        <v>166.6114196777344</v>
       </c>
       <c r="C15" t="n">
-        <v>168.6164816497661</v>
+        <v>168.6164970921864</v>
       </c>
       <c r="D15" t="n">
-        <v>163.6686243805947</v>
+        <v>163.6686393698748</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6189280624296</v>
+        <v>167.6189434134908</v>
       </c>
       <c r="F15" t="n">
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703025175833773</v>
+        <v>-0.02703024934973741</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -828,7 +828,7 @@
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723660814659139</v>
+        <v>0.007723568524209856</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465362548828</v>
+        <v>176.7465515136719</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491035140756</v>
+        <v>179.8491190407138</v>
       </c>
       <c r="D19" t="n">
-        <v>176.0581830190845</v>
+        <v>176.058198218447</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505315119071</v>
+        <v>179.2505469868697</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008461089254183651</v>
+        <v>-0.0008460226669898541</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -924,7 +924,7 @@
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668914997253303</v>
+        <v>0.003668828349043585</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620208740234</v>
+        <v>174.4620361328125</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757538913052</v>
+        <v>177.0757693786965</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632159334845</v>
+        <v>173.9632311486472</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769489507663</v>
+        <v>176.5769643945311</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614629217578734</v>
+        <v>-0.01614620612602058</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624663238682878</v>
+        <v>-0.02624671755319263</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187866210938</v>
+        <v>175.8187713623047</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767318043244</v>
+        <v>176.6767164710769</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466271367534</v>
+        <v>172.5466121619453</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641783462465</v>
+        <v>173.5641632831282</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494055886175818</v>
+        <v>0.03494046904234804</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002439756788046976</v>
+        <v>0.00243984378681672</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.1711578369141</v>
+        <v>183.171142578125</v>
       </c>
       <c r="C26" t="n">
-        <v>184.1089135963474</v>
+        <v>184.10889825944</v>
       </c>
       <c r="D26" t="n">
-        <v>174.2924356467209</v>
+        <v>174.29242112756</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810218455756</v>
+        <v>174.8810072773835</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928229701524732</v>
+        <v>0.03928221043944835</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.02821196229186118</v>
+        <v>-0.0282118813385599</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1125,22 +1125,22 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>177.2652893066406</v>
+        <v>177.2653045654297</v>
       </c>
       <c r="C29" t="n">
-        <v>179.8291385988617</v>
+        <v>179.8291540783439</v>
       </c>
       <c r="D29" t="n">
-        <v>172.7161910154847</v>
+        <v>172.7162058826927</v>
       </c>
       <c r="E29" t="n">
-        <v>174.0629551235593</v>
+        <v>174.0629701066951</v>
       </c>
       <c r="F29" t="n">
         <v>191586700</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004068387491782843</v>
+        <v>0.004068473920816773</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1149,22 +1149,22 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>177.7641143798828</v>
+        <v>177.7640991210938</v>
       </c>
       <c r="C30" t="n">
-        <v>179.3403398828169</v>
+        <v>179.3403244887289</v>
       </c>
       <c r="D30" t="n">
-        <v>174.5118962929188</v>
+        <v>174.5118813132914</v>
       </c>
       <c r="E30" t="n">
-        <v>177.7441579191998</v>
+        <v>177.7441426621237</v>
       </c>
       <c r="F30" t="n">
         <v>148573700</v>
       </c>
       <c r="G30" t="n">
-        <v>0.002814003097804996</v>
+        <v>0.002813830697929731</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1173,22 +1173,22 @@
         <v>45929</v>
       </c>
       <c r="B31" t="n">
-        <v>181.4153594970703</v>
+        <v>181.4153747558594</v>
       </c>
       <c r="C31" t="n">
-        <v>183.5602146114836</v>
+        <v>183.5602300506758</v>
       </c>
       <c r="D31" t="n">
-        <v>179.8890176259668</v>
+        <v>179.8890327563757</v>
       </c>
       <c r="E31" t="n">
-        <v>179.9987400973632</v>
+        <v>179.9987552370008</v>
       </c>
       <c r="F31" t="n">
         <v>193063500</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02053983240613322</v>
+        <v>0.020540005843803</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1212,7 +1212,7 @@
         <v>236981000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02601050008507699</v>
+        <v>0.02601041378766245</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1221,22 +1221,22 @@
         <v>45931</v>
       </c>
       <c r="B33" t="n">
-        <v>186.7924957275391</v>
+        <v>186.79248046875</v>
       </c>
       <c r="C33" t="n">
-        <v>187.690338609038</v>
+        <v>187.6903232769056</v>
       </c>
       <c r="D33" t="n">
-        <v>183.4604668683245</v>
+        <v>183.4604518817237</v>
       </c>
       <c r="E33" t="n">
-        <v>184.7972757932568</v>
+        <v>184.7972606974542</v>
       </c>
       <c r="F33" t="n">
         <v>173844900</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0035374073593748</v>
+        <v>0.003537325381961498</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385375976562</v>
+        <v>188.4385528564453</v>
       </c>
       <c r="C34" t="n">
-        <v>190.59337868299</v>
+        <v>190.593394116267</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105195355423</v>
+        <v>187.6105347272827</v>
       </c>
       <c r="E34" t="n">
-        <v>189.146847340247</v>
+        <v>189.1468626563914</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812141321341782</v>
+        <v>0.008812305418101074</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723506717838501</v>
+        <v>-0.006723587148282584</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965423583984</v>
+        <v>185.0965270996094</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7825055997528</v>
+        <v>186.7824902019781</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918329061041</v>
+        <v>182.8918178290645</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566446584491</v>
+        <v>185.0566294029491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0110862321012164</v>
+        <v>-0.01108631362422263</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1317,22 +1317,22 @@
         <v>45937</v>
       </c>
       <c r="B37" t="n">
-        <v>184.5977172851562</v>
+        <v>184.5977325439453</v>
       </c>
       <c r="C37" t="n">
-        <v>188.6081130865945</v>
+        <v>188.6081286768816</v>
       </c>
       <c r="D37" t="n">
-        <v>183.5602097539322</v>
+        <v>183.5602249269612</v>
       </c>
       <c r="E37" t="n">
-        <v>185.784875425114</v>
+        <v>185.7848907820332</v>
       </c>
       <c r="F37" t="n">
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694945388425074</v>
+        <v>-0.002694780736732239</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580200195312</v>
+        <v>188.6580047607422</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468543796426</v>
+        <v>189.1468390813163</v>
       </c>
       <c r="D38" t="n">
-        <v>186.0941551173159</v>
+        <v>186.094140065894</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240974206304</v>
+        <v>186.1240823667868</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02199541139559646</v>
+        <v>0.0219952442581075</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1365,22 +1365,22 @@
         <v>45939</v>
       </c>
       <c r="B39" t="n">
-        <v>192.1097412109375</v>
+        <v>192.1097564697266</v>
       </c>
       <c r="C39" t="n">
-        <v>194.8332119113436</v>
+        <v>194.833227386451</v>
       </c>
       <c r="D39" t="n">
-        <v>190.6033405552435</v>
+        <v>190.6033556943829</v>
       </c>
       <c r="E39" t="n">
-        <v>191.7705422839889</v>
+        <v>191.7705575158363</v>
       </c>
       <c r="F39" t="n">
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829618052309101</v>
+        <v>0.01829634376427292</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1404,7 +1404,7 @@
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886528340035956</v>
+        <v>-0.04886535894656951</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699188232422</v>
+        <v>187.8699035644531</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556339904095</v>
+        <v>189.6556185865847</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155586605101</v>
+        <v>185.5155435929421</v>
       </c>
       <c r="E41" t="n">
-        <v>187.52074924116</v>
+        <v>187.5207340107304</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817212858411589</v>
+        <v>0.02817204507600701</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402089854789248</v>
+        <v>-0.04402082090329285</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1461,22 +1461,22 @@
         <v>45945</v>
       </c>
       <c r="B43" t="n">
-        <v>179.4001770019531</v>
+        <v>179.4001922607422</v>
       </c>
       <c r="C43" t="n">
-        <v>184.4281238318171</v>
+        <v>184.4281395182556</v>
       </c>
       <c r="D43" t="n">
-        <v>176.8662395170747</v>
+        <v>176.866254560341</v>
       </c>
       <c r="E43" t="n">
-        <v>184.3582990595379</v>
+        <v>184.3583147400375</v>
       </c>
       <c r="F43" t="n">
         <v>214450500</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.001111021714327642</v>
+        <v>-0.001110936754343372</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1485,22 +1485,22 @@
         <v>45946</v>
       </c>
       <c r="B44" t="n">
-        <v>181.3754425048828</v>
+        <v>181.3754577636719</v>
       </c>
       <c r="C44" t="n">
-        <v>182.8419301869027</v>
+        <v>182.8419455690647</v>
       </c>
       <c r="D44" t="n">
-        <v>179.3403251298876</v>
+        <v>179.3403402174659</v>
       </c>
       <c r="E44" t="n">
-        <v>181.7944368108431</v>
+        <v>181.7944521048813</v>
       </c>
       <c r="F44" t="n">
         <v>179723300</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01101038770384366</v>
+        <v>0.01101038676736099</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1509,22 +1509,22 @@
         <v>45947</v>
       </c>
       <c r="B45" t="n">
-        <v>182.7820892333984</v>
+        <v>182.7821044921875</v>
       </c>
       <c r="C45" t="n">
-        <v>183.6599908268075</v>
+        <v>183.6600061588844</v>
       </c>
       <c r="D45" t="n">
-        <v>179.3203816221287</v>
+        <v>179.3203965919317</v>
       </c>
       <c r="E45" t="n">
-        <v>179.7493465774322</v>
+        <v>179.7493615830456</v>
       </c>
       <c r="F45" t="n">
         <v>173135200</v>
       </c>
       <c r="G45" t="n">
-        <v>0.007755442021748715</v>
+        <v>0.007755441369297289</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         <v>128544700</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.003165590696970089</v>
+        <v>-0.003165673913464562</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246398925781</v>
+        <v>181.7246246337891</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925557149365</v>
+        <v>182.5925403832715</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602938591047</v>
+        <v>179.3602787988416</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988793025541</v>
+        <v>179.988777912505</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042837577039868</v>
+        <v>0.01042829092822517</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1644,7 +1644,7 @@
         <v>131296700</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02250748267812286</v>
+        <v>0.02250756853454439</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1653,22 +1653,22 @@
         <v>45957</v>
       </c>
       <c r="B51" t="n">
-        <v>191.0323333740234</v>
+        <v>191.0323181152344</v>
       </c>
       <c r="C51" t="n">
-        <v>191.5411089646758</v>
+        <v>191.541093665248</v>
       </c>
       <c r="D51" t="n">
-        <v>187.9796341631504</v>
+        <v>187.979619148197</v>
       </c>
       <c r="E51" t="n">
-        <v>189.5359184602369</v>
+        <v>189.5359033209746</v>
       </c>
       <c r="F51" t="n">
         <v>153452700</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02807919058326869</v>
+        <v>0.02807910846500516</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1692,7 +1692,7 @@
         <v>297986200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04981982100715721</v>
+        <v>0.04981990486196963</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1701,22 +1701,22 @@
         <v>45959</v>
       </c>
       <c r="B53" t="n">
-        <v>206.5451354980469</v>
+        <v>206.5451507568359</v>
       </c>
       <c r="C53" t="n">
-        <v>211.6828353303786</v>
+        <v>211.6828509687219</v>
       </c>
       <c r="D53" t="n">
-        <v>204.2905427296142</v>
+        <v>204.2905578218423</v>
       </c>
       <c r="E53" t="n">
-        <v>207.482891187405</v>
+        <v>207.482906515472</v>
       </c>
       <c r="F53" t="n">
         <v>308829600</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0298958839139345</v>
+        <v>0.02989595999882533</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1725,22 +1725,22 @@
         <v>45960</v>
       </c>
       <c r="B54" t="n">
-        <v>202.4050598144531</v>
+        <v>202.4050750732422</v>
       </c>
       <c r="C54" t="n">
-        <v>205.6672482532724</v>
+        <v>205.6672637579894</v>
       </c>
       <c r="D54" t="n">
-        <v>200.9286015136062</v>
+        <v>200.9286166610889</v>
       </c>
       <c r="E54" t="n">
-        <v>204.6596525726598</v>
+        <v>204.6596680014167</v>
       </c>
       <c r="F54" t="n">
         <v>178864400</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.02004441147263381</v>
+        <v>-0.02004440999182711</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1749,22 +1749,22 @@
         <v>45961</v>
       </c>
       <c r="B55" t="n">
-        <v>202.0060577392578</v>
+        <v>202.0060272216797</v>
       </c>
       <c r="C55" t="n">
-        <v>207.4729563679188</v>
+        <v>207.4729250244422</v>
       </c>
       <c r="D55" t="n">
-        <v>201.5870633589687</v>
+        <v>201.5870329046891</v>
       </c>
       <c r="E55" t="n">
-        <v>205.9565848804529</v>
+        <v>205.9565537660584</v>
       </c>
       <c r="F55" t="n">
         <v>179802200</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.001971304845645117</v>
+        <v>-0.001971530859184778</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1788,7 +1788,7 @@
         <v>180267300</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02167997402155764</v>
+        <v>0.02168012836941968</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1821,22 +1821,22 @@
         <v>45966</v>
       </c>
       <c r="B58" t="n">
-        <v>194.7434234619141</v>
+        <v>194.7434387207031</v>
       </c>
       <c r="C58" t="n">
-        <v>202.4349867997753</v>
+        <v>202.4350026612236</v>
       </c>
       <c r="D58" t="n">
-        <v>194.1847491650603</v>
+        <v>194.1847643800754</v>
       </c>
       <c r="E58" t="n">
-        <v>198.2949120548774</v>
+        <v>198.2949275919373</v>
       </c>
       <c r="F58" t="n">
         <v>171350300</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.01751478380745641</v>
+        <v>-0.01751470682650169</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>223029800</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.03652470224768178</v>
+        <v>-0.03652477773914087</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1869,22 +1869,22 @@
         <v>45968</v>
       </c>
       <c r="B60" t="n">
-        <v>187.7002868652344</v>
+        <v>187.7003021240234</v>
       </c>
       <c r="C60" t="n">
-        <v>187.8698939350823</v>
+        <v>187.8699092076593</v>
       </c>
       <c r="D60" t="n">
-        <v>178.4823816093971</v>
+        <v>178.4823961188316</v>
       </c>
       <c r="E60" t="n">
-        <v>184.4580548583195</v>
+        <v>184.4580698535366</v>
       </c>
       <c r="F60" t="n">
         <v>264942300</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003720555463071484</v>
+        <v>0.0003721368699238781</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -1908,7 +1908,7 @@
         <v>198897100</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05793266405042918</v>
+        <v>0.05793257804752372</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1917,22 +1917,22 @@
         <v>45972</v>
       </c>
       <c r="B62" t="n">
-        <v>192.6983489990234</v>
+        <v>192.6983337402344</v>
       </c>
       <c r="C62" t="n">
-        <v>194.9529420926121</v>
+        <v>194.9529266552934</v>
       </c>
       <c r="D62" t="n">
-        <v>190.8427938118383</v>
+        <v>190.8427786999811</v>
       </c>
       <c r="E62" t="n">
-        <v>194.6935689756818</v>
+        <v>194.6935535589016</v>
       </c>
       <c r="F62" t="n">
         <v>176483300</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.02959051889910702</v>
+        <v>-0.02959059574083223</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -1956,7 +1956,7 @@
         <v>154935300</v>
       </c>
       <c r="G63" t="n">
-        <v>0.003313252320373383</v>
+        <v>0.003313331767584859</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1965,22 +1965,22 @@
         <v>45974</v>
       </c>
       <c r="B64" t="n">
-        <v>186.4134063720703</v>
+        <v>186.4133911132812</v>
       </c>
       <c r="C64" t="n">
-        <v>190.9824620272586</v>
+        <v>190.9824463944715</v>
       </c>
       <c r="D64" t="n">
-        <v>183.4106057333689</v>
+        <v>183.4105907203728</v>
       </c>
       <c r="E64" t="n">
-        <v>190.5933947337238</v>
+        <v>190.5933791327836</v>
       </c>
       <c r="F64" t="n">
         <v>207423100</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.03581005074692667</v>
+        <v>-0.03581012967027952</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2004,7 +2004,7 @@
         <v>186591900</v>
       </c>
       <c r="G65" t="n">
-        <v>0.01771365618248799</v>
+        <v>0.0177137394870075</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2013,22 +2013,22 @@
         <v>45978</v>
       </c>
       <c r="B66" t="n">
-        <v>186.1540222167969</v>
+        <v>186.1540069580078</v>
       </c>
       <c r="C66" t="n">
-        <v>188.5482800008962</v>
+        <v>188.5482645458532</v>
       </c>
       <c r="D66" t="n">
-        <v>183.8794727552066</v>
+        <v>183.8794576828592</v>
       </c>
       <c r="E66" t="n">
-        <v>185.5255230789849</v>
+        <v>185.525507871713</v>
       </c>
       <c r="F66" t="n">
         <v>173628900</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.01877257113277342</v>
+        <v>-0.01877265156263563</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2052,7 +2052,7 @@
         <v>213598900</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.02808154894469495</v>
+        <v>-0.02808146927787025</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2085,22 +2085,22 @@
         <v>45981</v>
       </c>
       <c r="B69" t="n">
-        <v>180.208251953125</v>
+        <v>180.2082672119141</v>
       </c>
       <c r="C69" t="n">
-        <v>195.5315406452363</v>
+        <v>195.5315572014955</v>
       </c>
       <c r="D69" t="n">
-        <v>179.4201468289569</v>
+        <v>179.4201620210147</v>
       </c>
       <c r="E69" t="n">
-        <v>195.4816571057099</v>
+        <v>195.4816736577453</v>
       </c>
       <c r="F69" t="n">
         <v>343504800</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.03152479724769053</v>
+        <v>-0.0315247152439051</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2124,7 +2124,7 @@
         <v>346926200</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.009743078144453632</v>
+        <v>-0.009743161992557425</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2205,22 +2205,22 @@
         <v>45989</v>
       </c>
       <c r="B74" t="n">
-        <v>176.5769653320312</v>
+        <v>176.5769500732422</v>
       </c>
       <c r="C74" t="n">
-        <v>178.8614854738169</v>
+        <v>178.8614700176124</v>
       </c>
       <c r="D74" t="n">
-        <v>176.0781603452176</v>
+        <v>176.0781451295325</v>
       </c>
       <c r="E74" t="n">
-        <v>178.5821558989869</v>
+        <v>178.5821404669205</v>
       </c>
       <c r="F74" t="n">
         <v>121332800</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.01808492693090802</v>
+        <v>-0.01808501178249078</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2244,7 +2244,7 @@
         <v>188131000</v>
       </c>
       <c r="G75" t="n">
-        <v>0.01649711013028865</v>
+        <v>0.01649719797026439</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2277,22 +2277,22 @@
         <v>45994</v>
       </c>
       <c r="B77" t="n">
-        <v>179.1607666015625</v>
+        <v>179.1607818603516</v>
       </c>
       <c r="C77" t="n">
-        <v>182.0139316568558</v>
+        <v>182.0139471586436</v>
       </c>
       <c r="D77" t="n">
-        <v>178.681918089591</v>
+        <v>178.6819333075974</v>
       </c>
       <c r="E77" t="n">
-        <v>180.6472109015755</v>
+        <v>180.6472262869623</v>
       </c>
       <c r="F77" t="n">
         <v>165138000</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.01030535058927451</v>
+        <v>-0.01030526629882311</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>167364900</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02116044996031174</v>
+        <v>0.02116036298998392</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2325,22 +2325,22 @@
         <v>45996</v>
       </c>
       <c r="B79" t="n">
-        <v>181.9841613769531</v>
+        <v>181.9841461181641</v>
       </c>
       <c r="C79" t="n">
-        <v>184.2289086763207</v>
+        <v>184.2288932293168</v>
       </c>
       <c r="D79" t="n">
-        <v>180.4876631773748</v>
+        <v>180.4876480440623</v>
       </c>
       <c r="E79" t="n">
-        <v>183.4607020047171</v>
+        <v>183.4606866221248</v>
       </c>
       <c r="F79" t="n">
         <v>143971100</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.005289519918164731</v>
+        <v>-0.005289603321452563</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2364,7 +2364,7 @@
         <v>204378100</v>
       </c>
       <c r="G80" t="n">
-        <v>0.01721391514737669</v>
+        <v>0.01721400043751253</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -2373,22 +2373,22 @@
         <v>46000</v>
       </c>
       <c r="B81" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C81" t="n">
-        <v>185.2864418902268</v>
+        <v>185.2864265695677</v>
       </c>
       <c r="D81" t="n">
-        <v>182.8920507276432</v>
+        <v>182.8920356049676</v>
       </c>
       <c r="E81" t="n">
-        <v>185.1268117532098</v>
+        <v>185.12679644575</v>
       </c>
       <c r="F81" t="n">
         <v>144719700</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.003125748033105724</v>
+        <v>-0.003125830460996126</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2397,22 +2397,22 @@
         <v>46001</v>
       </c>
       <c r="B82" t="n">
-        <v>183.3509521484375</v>
+        <v>183.3509674072266</v>
       </c>
       <c r="C82" t="n">
-        <v>185.0469803407326</v>
+        <v>185.0469957406681</v>
       </c>
       <c r="D82" t="n">
-        <v>181.6150088138297</v>
+        <v>181.6150239281505</v>
       </c>
       <c r="E82" t="n">
-        <v>184.538176449994</v>
+        <v>184.5381918075859</v>
       </c>
       <c r="F82" t="n">
         <v>162785400</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.006433576610347602</v>
+        <v>-0.006433411769608655</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2421,22 +2421,22 @@
         <v>46002</v>
       </c>
       <c r="B83" t="n">
-        <v>180.5075988769531</v>
+        <v>180.5076141357422</v>
       </c>
       <c r="C83" t="n">
-        <v>180.8967030087509</v>
+        <v>180.896718300432</v>
       </c>
       <c r="D83" t="n">
-        <v>176.2076633109278</v>
+        <v>176.2076782062319</v>
       </c>
       <c r="E83" t="n">
-        <v>179.8591224369562</v>
+        <v>179.8591376409278</v>
       </c>
       <c r="F83" t="n">
         <v>182136600</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.01550770933102352</v>
+        <v>-0.01550770804044477</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -2460,7 +2460,7 @@
         <v>204274900</v>
       </c>
       <c r="G84" t="n">
-        <v>-0.03266443759654691</v>
+        <v>-0.03266451936799664</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -2613,22 +2613,22 @@
         <v>46014</v>
       </c>
       <c r="B91" t="n">
-        <v>188.7682952880859</v>
+        <v>188.7682800292969</v>
       </c>
       <c r="C91" t="n">
-        <v>188.8880102762506</v>
+        <v>188.8879950077845</v>
       </c>
       <c r="D91" t="n">
-        <v>182.4730132178061</v>
+        <v>182.4729984678863</v>
       </c>
       <c r="E91" t="n">
-        <v>182.5428571096804</v>
+        <v>182.5428423541149</v>
       </c>
       <c r="F91" t="n">
         <v>174873600</v>
       </c>
       <c r="G91" t="n">
-        <v>0.03005069689074391</v>
+        <v>0.03005061362821149</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2652,7 +2652,7 @@
         <v>65528500</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.003171176350336591</v>
+        <v>-0.00317109577323571</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -2709,22 +2709,22 @@
         <v>46021</v>
       </c>
       <c r="B95" t="n">
-        <v>187.1021881103516</v>
+        <v>187.1021728515625</v>
       </c>
       <c r="C95" t="n">
-        <v>188.5488153175326</v>
+        <v>188.5487999407664</v>
       </c>
       <c r="D95" t="n">
-        <v>186.4936115238563</v>
+        <v>186.4935963146986</v>
       </c>
       <c r="E95" t="n">
-        <v>187.8005661647843</v>
+        <v>187.8005508490403</v>
       </c>
       <c r="F95" t="n">
         <v>97687300</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.003612757568446812</v>
+        <v>-0.003612838827051545</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -2748,7 +2748,7 @@
         <v>120100500</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.005545538552702456</v>
+        <v>-0.005545457451715641</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -2781,22 +2781,22 @@
         <v>46027</v>
       </c>
       <c r="B98" t="n">
-        <v>187.6808319091797</v>
+        <v>187.6808166503906</v>
       </c>
       <c r="C98" t="n">
-        <v>193.1779786425506</v>
+        <v>193.1779629368336</v>
       </c>
       <c r="D98" t="n">
-        <v>185.7154296257417</v>
+        <v>185.7154145267434</v>
       </c>
       <c r="E98" t="n">
-        <v>191.3123337767646</v>
+        <v>191.3123182227279</v>
       </c>
       <c r="F98" t="n">
         <v>183529700</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.00386553447189375</v>
+        <v>-0.00386561545941666</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -2805,22 +2805,22 @@
         <v>46028</v>
       </c>
       <c r="B99" t="n">
-        <v>186.8029022216797</v>
+        <v>186.8028869628906</v>
       </c>
       <c r="C99" t="n">
-        <v>191.7213860539245</v>
+        <v>191.7213703933745</v>
       </c>
       <c r="D99" t="n">
-        <v>186.3838845193456</v>
+        <v>186.3838692947835</v>
       </c>
       <c r="E99" t="n">
-        <v>190.0752439930999</v>
+        <v>190.0752284670132</v>
       </c>
       <c r="F99" t="n">
         <v>176862600</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.004677780243029006</v>
+        <v>-0.004677780623340899</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2844,7 +2844,7 @@
         <v>153543200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.009987081691657185</v>
+        <v>0.009987164191344933</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -2853,22 +2853,22 @@
         <v>46030</v>
       </c>
       <c r="B101" t="n">
-        <v>184.6080017089844</v>
+        <v>184.6080169677734</v>
       </c>
       <c r="C101" t="n">
-        <v>189.1074824738404</v>
+        <v>189.1074981045344</v>
       </c>
       <c r="D101" t="n">
-        <v>183.2811201033086</v>
+        <v>183.2811352524241</v>
       </c>
       <c r="E101" t="n">
-        <v>188.6685072554968</v>
+        <v>188.6685228499072</v>
       </c>
       <c r="F101" t="n">
         <v>172457000</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.02152196030920583</v>
+        <v>-0.02152187943302564</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -2892,7 +2892,7 @@
         <v>131327500</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0009726849758688871</v>
+        <v>-0.0009727675505442068</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -2925,22 +2925,22 @@
         <v>46035</v>
       </c>
       <c r="B104" t="n">
-        <v>185.376220703125</v>
+        <v>185.3762054443359</v>
       </c>
       <c r="C104" t="n">
-        <v>187.6708543554723</v>
+        <v>187.6708389078061</v>
       </c>
       <c r="D104" t="n">
-        <v>182.9718432388734</v>
+        <v>182.9718281779948</v>
       </c>
       <c r="E104" t="n">
-        <v>184.5681140987238</v>
+        <v>184.5680989064521</v>
       </c>
       <c r="F104" t="n">
         <v>160128900</v>
       </c>
       <c r="G104" t="n">
-        <v>0.004704210650191332</v>
+        <v>0.00470412795042785</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -2964,7 +2964,7 @@
         <v>159586100</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.01436954843994676</v>
+        <v>-0.01436946731018618</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3021,22 +3021,22 @@
         <v>46042</v>
       </c>
       <c r="B108" t="n">
-        <v>177.6542816162109</v>
+        <v>177.654296875</v>
       </c>
       <c r="C108" t="n">
-        <v>181.9542169705431</v>
+        <v>181.9542325986551</v>
       </c>
       <c r="D108" t="n">
-        <v>177.1953488429791</v>
+        <v>177.1953640623503</v>
       </c>
       <c r="E108" t="n">
-        <v>181.4753266272146</v>
+        <v>181.4753422141945</v>
       </c>
       <c r="F108" t="n">
         <v>223345300</v>
       </c>
       <c r="G108" t="n">
-        <v>-0.0438168415518142</v>
+        <v>-0.04381675942490471</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3060,7 +3060,7 @@
         <v>200381000</v>
       </c>
       <c r="G109" t="n">
-        <v>0.02948289454957864</v>
+        <v>0.02948280612693632</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3117,22 +3117,22 @@
         <v>46048</v>
       </c>
       <c r="B112" t="n">
-        <v>186.03466796875</v>
+        <v>186.0346832275391</v>
       </c>
       <c r="C112" t="n">
-        <v>188.6784751839824</v>
+        <v>188.6784906596197</v>
       </c>
       <c r="D112" t="n">
-        <v>185.5557928402329</v>
+        <v>185.555808059744</v>
       </c>
       <c r="E112" t="n">
-        <v>186.7230595290241</v>
+        <v>186.7230748442759</v>
       </c>
       <c r="F112" t="n">
         <v>124799600</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.006394234985120373</v>
+        <v>-0.00639415348837058</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -3156,7 +3156,7 @@
         <v>143711600</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01099379525930511</v>
+        <v>0.01099371233637481</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -3165,22 +3165,22 @@
         <v>46050</v>
       </c>
       <c r="B114" t="n">
-        <v>191.0728759765625</v>
+        <v>191.0728912353516</v>
       </c>
       <c r="C114" t="n">
-        <v>191.9009400606663</v>
+        <v>191.9009553855833</v>
       </c>
       <c r="D114" t="n">
-        <v>189.3967902384632</v>
+        <v>189.3968053634026</v>
       </c>
       <c r="E114" t="n">
-        <v>190.823459633995</v>
+        <v>190.8234748728661</v>
       </c>
       <c r="F114" t="n">
         <v>148552700</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01591334872193784</v>
+        <v>0.01591342985123156</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -3204,7 +3204,7 @@
         <v>171764400</v>
       </c>
       <c r="G115" t="n">
-        <v>0.005169239280915949</v>
+        <v>0.00516915900963677</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -3261,22 +3261,22 @@
         <v>46056</v>
       </c>
       <c r="B118" t="n">
-        <v>179.9189758300781</v>
+        <v>179.9189910888672</v>
       </c>
       <c r="C118" t="n">
-        <v>185.8351396091497</v>
+        <v>185.835155369684</v>
       </c>
       <c r="D118" t="n">
-        <v>175.8185703987175</v>
+        <v>175.8185853097543</v>
       </c>
       <c r="E118" t="n">
-        <v>185.8052108647954</v>
+        <v>185.8052266227915</v>
       </c>
       <c r="F118" t="n">
         <v>204019600</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.02839291451472381</v>
+        <v>-0.02839283211347909</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -3300,7 +3300,7 @@
         <v>207014100</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.0341021289659974</v>
+        <v>-0.03410221088304122</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -3357,22 +3357,22 @@
         <v>46062</v>
       </c>
       <c r="B122" t="n">
-        <v>189.5963439941406</v>
+        <v>189.5963287353516</v>
       </c>
       <c r="C122" t="n">
-        <v>193.2079034382237</v>
+        <v>193.2078878887748</v>
       </c>
       <c r="D122" t="n">
-        <v>183.5205647824287</v>
+        <v>183.5205500126207</v>
       </c>
       <c r="E122" t="n">
-        <v>183.8298386502086</v>
+        <v>183.8298238555102</v>
       </c>
       <c r="F122" t="n">
         <v>196387400</v>
       </c>
       <c r="G122" t="n">
-        <v>0.024971658454912</v>
+        <v>0.02497157596478594</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3396,7 +3396,7 @@
         <v>136764800</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.007893114950312197</v>
+        <v>-0.007893035105149604</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3405,22 +3405,22 @@
         <v>46064</v>
       </c>
       <c r="B124" t="n">
-        <v>189.6063385009766</v>
+        <v>189.6063232421875</v>
       </c>
       <c r="C124" t="n">
-        <v>192.8088363522974</v>
+        <v>192.8088208357837</v>
       </c>
       <c r="D124" t="n">
-        <v>188.3293278304631</v>
+        <v>188.329312674443</v>
       </c>
       <c r="E124" t="n">
-        <v>192.0007297023972</v>
+        <v>192.0007142509167</v>
       </c>
       <c r="F124" t="n">
         <v>144192700</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00800904593061702</v>
+        <v>0.008008964809924857</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3429,22 +3429,22 @@
         <v>46065</v>
       </c>
       <c r="B125" t="n">
-        <v>186.5036010742188</v>
+        <v>186.5035858154297</v>
       </c>
       <c r="C125" t="n">
-        <v>193.158028491682</v>
+        <v>193.1580126884611</v>
       </c>
       <c r="D125" t="n">
-        <v>186.0745969700116</v>
+        <v>186.0745817463215</v>
       </c>
       <c r="E125" t="n">
-        <v>192.5793806436633</v>
+        <v>192.5793648877844</v>
       </c>
       <c r="F125" t="n">
         <v>189932500</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.01636410180845216</v>
+        <v>-0.01636410312537218</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>161888000</v>
       </c>
       <c r="G126" t="n">
-        <v>-0.02209282728038808</v>
+        <v>-0.02209274727292232</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3477,22 +3477,22 @@
         <v>46070</v>
       </c>
       <c r="B127" t="n">
-        <v>184.5381927490234</v>
+        <v>184.5381774902344</v>
       </c>
       <c r="C127" t="n">
-        <v>186.7130962790006</v>
+        <v>186.7130808403767</v>
       </c>
       <c r="D127" t="n">
-        <v>178.7617008539599</v>
+        <v>178.7616860728079</v>
       </c>
       <c r="E127" t="n">
-        <v>181.3257085516038</v>
+        <v>181.3256935584433</v>
       </c>
       <c r="F127" t="n">
         <v>162276900</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01181569032381558</v>
+        <v>0.01181560666047221</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -3516,7 +3516,7 @@
         <v>164749100</v>
       </c>
       <c r="G128" t="n">
-        <v>0.01627275579951704</v>
+        <v>0.01627283983140582</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -3525,22 +3525,22 @@
         <v>46072</v>
       </c>
       <c r="B129" t="n">
-        <v>187.4613189697266</v>
+        <v>187.4613342285156</v>
       </c>
       <c r="C129" t="n">
-        <v>187.9900804037161</v>
+        <v>187.9900957055448</v>
       </c>
       <c r="D129" t="n">
-        <v>185.226558259481</v>
+        <v>185.2265733363672</v>
       </c>
       <c r="E129" t="n">
-        <v>186.6232837033845</v>
+        <v>186.62329889396</v>
       </c>
       <c r="F129" t="n">
         <v>126554500</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0004256064912840918</v>
+        <v>-0.0004255251289267958</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -3564,7 +3564,7 @@
         <v>178422300</v>
       </c>
       <c r="G130" t="n">
-        <v>0.01021833524412785</v>
+        <v>0.01021825301539225</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -3669,22 +3669,22 @@
         <v>46080</v>
       </c>
       <c r="B135" t="n">
-        <v>176.7763366699219</v>
+        <v>176.7763519287109</v>
       </c>
       <c r="C135" t="n">
-        <v>182.1637238018573</v>
+        <v>182.1637395256691</v>
       </c>
       <c r="D135" t="n">
-        <v>175.9682301224481</v>
+        <v>175.9682453114839</v>
       </c>
       <c r="E135" t="n">
-        <v>180.82685580423</v>
+        <v>180.8268714126474</v>
       </c>
       <c r="F135" t="n">
         <v>311636500</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.04164645489360941</v>
+        <v>-0.04164637217148226</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -3693,22 +3693,22 @@
         <v>46083</v>
       </c>
       <c r="B136" t="n">
-        <v>182.0539703369141</v>
+        <v>182.0539855957031</v>
       </c>
       <c r="C136" t="n">
-        <v>183.0316933488174</v>
+        <v>183.0317086895539</v>
       </c>
       <c r="D136" t="n">
-        <v>174.2322775806792</v>
+        <v>174.2322921838959</v>
       </c>
       <c r="E136" t="n">
-        <v>174.6014088918714</v>
+        <v>174.6014235260267</v>
       </c>
       <c r="F136" t="n">
         <v>209095300</v>
       </c>
       <c r="G136" t="n">
-        <v>0.02985486500292533</v>
+        <v>0.02985486242594537</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -3732,7 +3732,7 @@
         <v>178099400</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.01331638712945649</v>
+        <v>-0.01331646982798718</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -3741,22 +3741,22 @@
         <v>46085</v>
       </c>
       <c r="B138" t="n">
-        <v>182.6126861572266</v>
+        <v>182.6126708984375</v>
       </c>
       <c r="C138" t="n">
-        <v>184.2688145383873</v>
+        <v>184.2687991412151</v>
       </c>
       <c r="D138" t="n">
-        <v>179.6396472340209</v>
+        <v>179.6396322236537</v>
       </c>
       <c r="E138" t="n">
-        <v>180.0187649948852</v>
+        <v>180.0187499528396</v>
       </c>
       <c r="F138" t="n">
         <v>177731200</v>
       </c>
       <c r="G138" t="n">
-        <v>0.01660648255510222</v>
+        <v>0.01660639760928495</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         <v>198779700</v>
       </c>
       <c r="G139" t="n">
-        <v>0.001638910718471109</v>
+        <v>0.001638994413631911</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -3789,22 +3789,22 @@
         <v>46087</v>
       </c>
       <c r="B140" t="n">
-        <v>177.4048767089844</v>
+        <v>177.4048919677734</v>
       </c>
       <c r="C140" t="n">
-        <v>182.3333312190456</v>
+        <v>182.3333469017365</v>
       </c>
       <c r="D140" t="n">
-        <v>176.407211264142</v>
+        <v>176.4072264371208</v>
       </c>
       <c r="E140" t="n">
-        <v>179.420149946886</v>
+        <v>179.4201653790109</v>
       </c>
       <c r="F140" t="n">
         <v>189021900</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.03010789985650675</v>
+        <v>-0.0301078164350177</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -3813,22 +3813,22 @@
         <v>46090</v>
       </c>
       <c r="B141" t="n">
-        <v>182.2235870361328</v>
+        <v>182.2236022949219</v>
       </c>
       <c r="C141" t="n">
-        <v>182.4829897940845</v>
+        <v>182.4830050745951</v>
       </c>
       <c r="D141" t="n">
-        <v>175.1501427003192</v>
+        <v>175.1501573668019</v>
       </c>
       <c r="E141" t="n">
-        <v>176.4171820751478</v>
+        <v>176.4171968477281</v>
       </c>
       <c r="F141" t="n">
         <v>177213600</v>
       </c>
       <c r="G141" t="n">
-        <v>0.02716222020803327</v>
+        <v>0.02716221787178097</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3852,7 +3852,7 @@
         <v>179118500</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01160698547713768</v>
+        <v>0.01160690076858506</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -7545,12 +7545,36 @@
         <v>218.1000061035156</v>
       </c>
       <c r="F296" t="n">
-        <v>98403300</v>
+        <v>98684700</v>
       </c>
       <c r="G296" t="n">
         <v>0.0138233381010664</v>
       </c>
       <c r="H296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B297" t="n">
+        <v>216.4700012207031</v>
+      </c>
+      <c r="C297" t="n">
+        <v>218.4600067138672</v>
+      </c>
+      <c r="D297" t="n">
+        <v>212.7700042724609</v>
+      </c>
+      <c r="E297" t="n">
+        <v>215.9799957275391</v>
+      </c>
+      <c r="F297" t="n">
+        <v>78967900</v>
+      </c>
+      <c r="G297" t="n">
+        <v>-0.002855935914350072</v>
+      </c>
+      <c r="H297" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_prices.xlsx
+++ b/stock_prices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,16 +503,16 @@
         <v>45888</v>
       </c>
       <c r="B3" t="n">
-        <v>175.2103271484375</v>
+        <v>175.2103424072266</v>
       </c>
       <c r="C3" t="n">
-        <v>182.0535459787435</v>
+        <v>182.0535618334976</v>
       </c>
       <c r="D3" t="n">
-        <v>175.0607001855326</v>
+        <v>175.0607154312909</v>
       </c>
       <c r="E3" t="n">
-        <v>181.9837099150805</v>
+        <v>181.9837257637527</v>
       </c>
       <c r="F3" t="n">
         <v>185229200</v>
@@ -525,22 +525,22 @@
         <v>45889</v>
       </c>
       <c r="B4" t="n">
-        <v>174.9709014892578</v>
+        <v>174.9709167480469</v>
       </c>
       <c r="C4" t="n">
-        <v>175.5694397588381</v>
+        <v>175.5694550698242</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3870566311777</v>
+        <v>168.3870713158056</v>
       </c>
       <c r="E4" t="n">
-        <v>174.7414684152183</v>
+        <v>174.741483653999</v>
       </c>
       <c r="F4" t="n">
         <v>215142700</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001366504264196933</v>
+        <v>-0.00136650414519035</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -549,22 +549,22 @@
         <v>45890</v>
       </c>
       <c r="B5" t="n">
-        <v>174.5519409179688</v>
+        <v>174.5519256591797</v>
       </c>
       <c r="C5" t="n">
-        <v>176.4672421817212</v>
+        <v>176.4672267555024</v>
       </c>
       <c r="D5" t="n">
-        <v>173.3848049238756</v>
+        <v>173.384789767114</v>
       </c>
       <c r="E5" t="n">
-        <v>174.4222692884882</v>
+        <v>174.4222540410346</v>
       </c>
       <c r="F5" t="n">
         <v>140040900</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002394458551239653</v>
+        <v>-0.002394632757571458</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -573,22 +573,22 @@
         <v>45891</v>
       </c>
       <c r="B6" t="n">
-        <v>177.5545806884766</v>
+        <v>177.5545654296875</v>
       </c>
       <c r="C6" t="n">
-        <v>178.1531037491236</v>
+        <v>178.1530884388983</v>
       </c>
       <c r="D6" t="n">
-        <v>170.781182841084</v>
+        <v>170.7811681643912</v>
       </c>
       <c r="E6" t="n">
-        <v>172.1877371490149</v>
+        <v>172.1877223514448</v>
       </c>
       <c r="F6" t="n">
         <v>172789400</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0172019844334983</v>
+        <v>0.01720198593724254</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -597,22 +597,22 @@
         <v>45894</v>
       </c>
       <c r="B7" t="n">
-        <v>179.3701324462891</v>
+        <v>179.3701477050781</v>
       </c>
       <c r="C7" t="n">
-        <v>181.4650013525793</v>
+        <v>181.4650167895762</v>
       </c>
       <c r="D7" t="n">
-        <v>176.1380681264219</v>
+        <v>176.1380831102634</v>
       </c>
       <c r="E7" t="n">
-        <v>177.913712535141</v>
+        <v>177.9137276700343</v>
       </c>
       <c r="F7" t="n">
         <v>163012800</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01022531635496304</v>
+        <v>0.01022548911089305</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -636,7 +636,7 @@
         <v>168688200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0109003665696572</v>
+        <v>0.01090028057365577</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -645,22 +645,22 @@
         <v>45896</v>
       </c>
       <c r="B9" t="n">
-        <v>181.1557312011719</v>
+        <v>181.1557464599609</v>
       </c>
       <c r="C9" t="n">
-        <v>182.0435532539336</v>
+        <v>182.0435685875041</v>
       </c>
       <c r="D9" t="n">
-        <v>178.6618473202167</v>
+        <v>178.6618623689453</v>
       </c>
       <c r="E9" t="n">
-        <v>181.5347912004848</v>
+        <v>181.5348064912021</v>
       </c>
       <c r="F9" t="n">
         <v>235518900</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0009353433299080782</v>
+        <v>-0.0009352591784613784</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -684,7 +684,7 @@
         <v>281787800</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.007874431593344555</v>
+        <v>-0.00787451516030313</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -693,22 +693,22 @@
         <v>45898</v>
       </c>
       <c r="B11" t="n">
-        <v>173.75390625</v>
+        <v>173.7538909912109</v>
       </c>
       <c r="C11" t="n">
-        <v>177.7141958867003</v>
+        <v>177.714180280125</v>
       </c>
       <c r="D11" t="n">
-        <v>172.7264270970488</v>
+        <v>172.7264119284913</v>
       </c>
       <c r="E11" t="n">
-        <v>177.6743004338266</v>
+        <v>177.6742848307548</v>
       </c>
       <c r="F11" t="n">
         <v>243257900</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.03324626965459365</v>
+        <v>-0.03324635455335401</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -717,22 +717,22 @@
         <v>45902</v>
       </c>
       <c r="B12" t="n">
-        <v>170.3622283935547</v>
+        <v>170.3622131347656</v>
       </c>
       <c r="C12" t="n">
-        <v>171.9583204838847</v>
+        <v>171.9583050821389</v>
       </c>
       <c r="D12" t="n">
-        <v>166.8109394751057</v>
+        <v>166.810924534394</v>
       </c>
       <c r="E12" t="n">
-        <v>169.5841376854209</v>
+        <v>169.5841224963229</v>
       </c>
       <c r="F12" t="n">
         <v>231164900</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01952000924552055</v>
+        <v>-0.01952001095973654</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -756,7 +756,7 @@
         <v>164424900</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009369576454122397</v>
+        <v>-0.0009368681625865349</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -765,22 +765,22 @@
         <v>45904</v>
       </c>
       <c r="B14" t="n">
-        <v>171.2400817871094</v>
+        <v>171.2400665283203</v>
       </c>
       <c r="C14" t="n">
-        <v>171.4395894944585</v>
+        <v>171.4395742178918</v>
       </c>
       <c r="D14" t="n">
-        <v>168.9955858311417</v>
+        <v>168.9955707723543</v>
       </c>
       <c r="E14" t="n">
-        <v>170.1527518438138</v>
+        <v>170.1527366819141</v>
       </c>
       <c r="F14" t="n">
         <v>141670100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006095532901013501</v>
+        <v>0.006095443250276666</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -804,7 +804,7 @@
         <v>224441400</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.02703024934973741</v>
+        <v>-0.02703016265075109</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -813,22 +813,22 @@
         <v>45908</v>
       </c>
       <c r="B16" t="n">
-        <v>167.8982543945312</v>
+        <v>167.8982391357422</v>
       </c>
       <c r="C16" t="n">
-        <v>170.5417807313731</v>
+        <v>170.5417652323373</v>
       </c>
       <c r="D16" t="n">
-        <v>166.9406114031506</v>
+        <v>166.9405962313932</v>
       </c>
       <c r="E16" t="n">
-        <v>167.1401190912332</v>
+        <v>167.1401039013443</v>
       </c>
       <c r="F16" t="n">
         <v>163769100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007723568524209856</v>
+        <v>0.007723476941117413</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -852,7 +852,7 @@
         <v>157548400</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01455643629502945</v>
+        <v>0.01455652849910916</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -885,22 +885,22 @@
         <v>45911</v>
       </c>
       <c r="B19" t="n">
-        <v>176.7465515136719</v>
+        <v>176.7465362548828</v>
       </c>
       <c r="C19" t="n">
-        <v>179.8491190407138</v>
+        <v>179.8491035140756</v>
       </c>
       <c r="D19" t="n">
-        <v>176.058198218447</v>
+        <v>176.0581830190845</v>
       </c>
       <c r="E19" t="n">
-        <v>179.2505469868697</v>
+        <v>179.2505315119071</v>
       </c>
       <c r="F19" t="n">
         <v>151159300</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0008460226669898541</v>
+        <v>-0.0008461089254183651</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -909,22 +909,22 @@
         <v>45912</v>
       </c>
       <c r="B20" t="n">
-        <v>177.3950042724609</v>
+        <v>177.39501953125</v>
       </c>
       <c r="C20" t="n">
-        <v>178.1731387966239</v>
+        <v>178.1731541223449</v>
       </c>
       <c r="D20" t="n">
-        <v>176.028268323246</v>
+        <v>176.028283464474</v>
       </c>
       <c r="E20" t="n">
-        <v>177.3451207317183</v>
+        <v>177.3451359862166</v>
       </c>
       <c r="F20" t="n">
         <v>124911000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003668828349043585</v>
+        <v>0.003669001328727717</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -948,7 +948,7 @@
         <v>147061600</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0003936947256518719</v>
+        <v>-0.0003937807076698219</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -957,22 +957,22 @@
         <v>45916</v>
       </c>
       <c r="B22" t="n">
-        <v>174.4620361328125</v>
+        <v>174.4620208740234</v>
       </c>
       <c r="C22" t="n">
-        <v>177.0757693786965</v>
+        <v>177.0757538913052</v>
       </c>
       <c r="D22" t="n">
-        <v>173.9632311486472</v>
+        <v>173.9632159334845</v>
       </c>
       <c r="E22" t="n">
-        <v>176.5769643945311</v>
+        <v>176.5769489507663</v>
       </c>
       <c r="F22" t="n">
         <v>140737800</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.01614620612602058</v>
+        <v>-0.01614629217578734</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -996,7 +996,7 @@
         <v>211843800</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.02624671755319263</v>
+        <v>-0.02624663238682878</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1005,22 +1005,22 @@
         <v>45918</v>
       </c>
       <c r="B24" t="n">
-        <v>175.8187713623047</v>
+        <v>175.8187561035156</v>
       </c>
       <c r="C24" t="n">
-        <v>176.6767164710769</v>
+        <v>176.6767011378293</v>
       </c>
       <c r="D24" t="n">
-        <v>172.5466121619453</v>
+        <v>172.5465971871373</v>
       </c>
       <c r="E24" t="n">
-        <v>173.5641632831282</v>
+        <v>173.5641482200099</v>
       </c>
       <c r="F24" t="n">
         <v>191763300</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03494046904234804</v>
+        <v>0.03494037922293813</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>237182100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.00243984378681672</v>
+        <v>0.002439930785601563</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1053,22 +1053,22 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>183.171142578125</v>
+        <v>183.1711578369141</v>
       </c>
       <c r="C26" t="n">
-        <v>184.10889825944</v>
+        <v>184.1089135963474</v>
       </c>
       <c r="D26" t="n">
-        <v>174.29242112756</v>
+        <v>174.2924356467209</v>
       </c>
       <c r="E26" t="n">
-        <v>174.8810072773835</v>
+        <v>174.8810218455756</v>
       </c>
       <c r="F26" t="n">
         <v>269637000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03928221043944835</v>
+        <v>0.03928229701524732</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1077,22 +1077,22 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>178.0035400390625</v>
+        <v>178.0035247802734</v>
       </c>
       <c r="C27" t="n">
-        <v>181.9840093083128</v>
+        <v>181.9839937083107</v>
       </c>
       <c r="D27" t="n">
-        <v>175.7888599052367</v>
+        <v>175.7888448362941</v>
       </c>
       <c r="E27" t="n">
-        <v>181.5350878652714</v>
+        <v>181.5350723037516</v>
       </c>
       <c r="F27" t="n">
         <v>192559600</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0282118813385599</v>
+        <v>-0.02821204559530932</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1116,7 +1116,7 @@
         <v>143564100</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.008182491487822352</v>
+        <v>-0.00818240646740398</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1245,22 +1245,22 @@
         <v>45932</v>
       </c>
       <c r="B34" t="n">
-        <v>188.4385528564453</v>
+        <v>188.4385375976562</v>
       </c>
       <c r="C34" t="n">
-        <v>190.593394116267</v>
+        <v>190.59337868299</v>
       </c>
       <c r="D34" t="n">
-        <v>187.6105347272827</v>
+        <v>187.6105195355423</v>
       </c>
       <c r="E34" t="n">
-        <v>189.1468626563914</v>
+        <v>189.146847340247</v>
       </c>
       <c r="F34" t="n">
         <v>136805800</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008812305418101074</v>
+        <v>0.008812223729646407</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1284,7 +1284,7 @@
         <v>137596900</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.006723587148282584</v>
+        <v>-0.006723506717838501</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1293,22 +1293,22 @@
         <v>45936</v>
       </c>
       <c r="B36" t="n">
-        <v>185.0965270996094</v>
+        <v>185.0965423583984</v>
       </c>
       <c r="C36" t="n">
-        <v>186.7824902019781</v>
+        <v>186.7825055997528</v>
       </c>
       <c r="D36" t="n">
-        <v>182.8918178290645</v>
+        <v>182.8918329061041</v>
       </c>
       <c r="E36" t="n">
-        <v>185.0566294029491</v>
+        <v>185.0566446584491</v>
       </c>
       <c r="F36" t="n">
         <v>157678100</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.01108631362422263</v>
+        <v>-0.0110862321012164</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
         <v>140088000</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.002694780736732239</v>
+        <v>-0.002694862951503896</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1341,22 +1341,22 @@
         <v>45938</v>
       </c>
       <c r="B38" t="n">
-        <v>188.6580047607422</v>
+        <v>188.6580200195312</v>
       </c>
       <c r="C38" t="n">
-        <v>189.1468390813163</v>
+        <v>189.1468543796426</v>
       </c>
       <c r="D38" t="n">
-        <v>186.094140065894</v>
+        <v>186.0941551173159</v>
       </c>
       <c r="E38" t="n">
-        <v>186.1240823667868</v>
+        <v>186.1240974206304</v>
       </c>
       <c r="F38" t="n">
         <v>130168900</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0219952442581075</v>
+        <v>0.02199532691778505</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1380,7 +1380,7 @@
         <v>182997200</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01829634376427292</v>
+        <v>0.01829626140377161</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1389,22 +1389,22 @@
         <v>45940</v>
       </c>
       <c r="B40" t="n">
-        <v>182.7222442626953</v>
+        <v>182.7222290039062</v>
       </c>
       <c r="C40" t="n">
-        <v>195.1524558626357</v>
+        <v>195.1524395658232</v>
       </c>
       <c r="D40" t="n">
-        <v>181.6148965961679</v>
+        <v>181.6148814298513</v>
       </c>
       <c r="E40" t="n">
-        <v>193.0474982342752</v>
+        <v>193.0474821132437</v>
       </c>
       <c r="F40" t="n">
         <v>268774400</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.04886535894656951</v>
+        <v>-0.04886543837402468</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1413,22 +1413,22 @@
         <v>45943</v>
       </c>
       <c r="B41" t="n">
-        <v>187.8699035644531</v>
+        <v>187.8699188232422</v>
       </c>
       <c r="C41" t="n">
-        <v>189.6556185865847</v>
+        <v>189.6556339904095</v>
       </c>
       <c r="D41" t="n">
-        <v>185.5155435929421</v>
+        <v>185.5155586605101</v>
       </c>
       <c r="E41" t="n">
-        <v>187.5207340107304</v>
+        <v>187.52074924116</v>
       </c>
       <c r="F41" t="n">
         <v>153482800</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02817204507600701</v>
+        <v>0.02817221444483309</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1452,7 +1452,7 @@
         <v>205641400</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.04402082090329285</v>
+        <v>-0.04402089854789248</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
         <v>45952</v>
       </c>
       <c r="B48" t="n">
-        <v>179.8491058349609</v>
+        <v>179.84912109375</v>
       </c>
       <c r="C48" t="n">
-        <v>183.0015566720687</v>
+        <v>183.0015721983185</v>
       </c>
       <c r="D48" t="n">
-        <v>176.3375148363812</v>
+        <v>176.3375297972393</v>
       </c>
       <c r="E48" t="n">
-        <v>180.7070509305708</v>
+        <v>180.7070662621498</v>
       </c>
       <c r="F48" t="n">
         <v>162249600</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.00485768219622118</v>
+        <v>-0.004857597766183885</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1605,22 +1605,22 @@
         <v>45953</v>
       </c>
       <c r="B49" t="n">
-        <v>181.7246246337891</v>
+        <v>181.724609375</v>
       </c>
       <c r="C49" t="n">
-        <v>182.5925403832715</v>
+        <v>182.5925250516066</v>
       </c>
       <c r="D49" t="n">
-        <v>179.3602787988416</v>
+        <v>179.3602637385785</v>
       </c>
       <c r="E49" t="n">
-        <v>179.988777912505</v>
+        <v>179.988762799469</v>
       </c>
       <c r="F49" t="n">
         <v>111363700</v>
       </c>
       <c r="G49" t="n">
-        <v>0.01042829092822517</v>
+        <v>0.01042812